--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -67,69 +67,57 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>NSE:ADANIENSOL-EQ_BULL_1771303500_1771311600</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENSOL-EQ</t>
+    <t>NSE:BAJAJ-AUTO-EQ_BULL_1771310700_1771387200</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJ-AUTO-EQ</t>
   </si>
   <si>
     <t>BULLISH</t>
   </si>
   <si>
-    <t>2026-02-17 12:30</t>
+    <t>2026-02-18 09:30</t>
   </si>
   <si>
     <t>YES</t>
   </si>
   <si>
+    <t>SL HIT</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:30</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BULL_1771300800_1771397100</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 12:15</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>Checked 11 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1771305300_1771386300</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 09:15</t>
+  </si>
+  <si>
     <t>TARGET HIT</t>
   </si>
   <si>
-    <t>2026-02-17 13:45</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>NSE:BAJAJ-AUTO-EQ_BULL_1771310700_1771387200</t>
-  </si>
-  <si>
-    <t>NSE:BAJAJ-AUTO-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 09:30</t>
-  </si>
-  <si>
-    <t>SL HIT</t>
-  </si>
-  <si>
-    <t>2026-02-18 11:30</t>
-  </si>
-  <si>
-    <t>NSE:BLUESTARCO-EQ_BULL_1771300800_1771397100</t>
-  </si>
-  <si>
-    <t>NSE:BLUESTARCO-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 12:15</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>Checked 11 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:HFCL-EQ_BULL_1771305300_1771386300</t>
-  </si>
-  <si>
-    <t>NSE:HFCL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 09:15</t>
-  </si>
-  <si>
     <t>2026-02-18 09:45</t>
   </si>
   <si>
@@ -190,18 +178,6 @@
     <t>2026-02-18 15:00</t>
   </si>
   <si>
-    <t>NSE:TATAELXSI-EQ_BEAR_1771317000_1771321500</t>
-  </si>
-  <si>
-    <t>NSE:TATAELXSI-EQ</t>
-  </si>
-  <si>
-    <t>BEARISH</t>
-  </si>
-  <si>
-    <t>2026-02-17 15:15</t>
-  </si>
-  <si>
     <t>NSE:UPL-EQ_BULL_1771314300_1771407000</t>
   </si>
   <si>
@@ -226,10 +202,10 @@
     <t>NSE:YESBANK-EQ</t>
   </si>
   <si>
-    <t>SUMMARY — 5W / 4L / 4 OPEN  |  Win Rate: 55.6%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 9 of 13</t>
+    <t>SUMMARY — 4W / 3L / 4 OPEN  |  Win Rate: 57.1%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 7 of 11</t>
   </si>
 </sst>
 </file>
@@ -260,13 +236,13 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF006400"/>
+      <color rgb="FF8B0000"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF8B0000"/>
+      <color rgb="FF006400"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -291,17 +267,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -332,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -343,12 +319,10 @@
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -690,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -780,22 +754,22 @@
         <v>21</v>
       </c>
       <c r="E2" s="3">
-        <v>1034.35</v>
+        <v>9918</v>
       </c>
       <c r="F2" s="3">
-        <v>1024</v>
+        <v>9842</v>
       </c>
       <c r="G2" s="3">
-        <v>1029.35</v>
+        <v>9913.5</v>
       </c>
       <c r="H2" s="3">
-        <v>1028.7</v>
+        <v>9914</v>
       </c>
       <c r="I2" s="3">
-        <v>1024</v>
+        <v>9842</v>
       </c>
       <c r="J2" s="3">
-        <v>1033.4</v>
+        <v>9986</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>22</v>
@@ -807,16 +781,16 @@
         <v>24</v>
       </c>
       <c r="N2" s="3">
-        <v>1033.4</v>
+        <v>9842</v>
       </c>
       <c r="O2" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P2" s="4">
-        <v>4.7</v>
+        <v>-72</v>
       </c>
       <c r="Q2" s="5">
-        <v>0.457</v>
+        <v>-0.726</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>25</v>
@@ -836,22 +810,22 @@
         <v>28</v>
       </c>
       <c r="E3" s="7">
-        <v>9918</v>
+        <v>2016.7</v>
       </c>
       <c r="F3" s="7">
-        <v>9842</v>
+        <v>1991</v>
       </c>
       <c r="G3" s="7">
-        <v>9913.5</v>
+        <v>2015.6</v>
       </c>
       <c r="H3" s="7">
-        <v>9914</v>
+        <v>2015.7</v>
       </c>
       <c r="I3" s="7">
-        <v>9842</v>
+        <v>1991</v>
       </c>
       <c r="J3" s="7">
-        <v>9986</v>
+        <v>2040.4</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>22</v>
@@ -859,606 +833,494 @@
       <c r="L3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="N3" s="7">
-        <v>9842</v>
-      </c>
-      <c r="O3" s="6">
-        <v>7</v>
-      </c>
-      <c r="P3" s="8">
-        <v>-72</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>-0.726</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="11">
-        <v>2016.7</v>
-      </c>
-      <c r="F4" s="11">
-        <v>1991</v>
-      </c>
-      <c r="G4" s="11">
-        <v>2015.6</v>
-      </c>
-      <c r="H4" s="11">
-        <v>2015.7</v>
-      </c>
-      <c r="I4" s="11">
-        <v>1991</v>
-      </c>
-      <c r="J4" s="11">
-        <v>2040.4</v>
-      </c>
-      <c r="K4" s="10" t="s">
+      <c r="E4" s="9">
+        <v>73.18</v>
+      </c>
+      <c r="F4" s="9">
+        <v>71.4</v>
+      </c>
+      <c r="G4" s="9">
+        <v>72.79</v>
+      </c>
+      <c r="H4" s="9">
+        <v>72.74</v>
+      </c>
+      <c r="I4" s="9">
+        <v>71.4</v>
+      </c>
+      <c r="J4" s="9">
+        <v>74.08</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>35</v>
+      </c>
+      <c r="N4" s="9">
+        <v>74.08</v>
+      </c>
+      <c r="O4" s="8">
+        <v>1</v>
+      </c>
+      <c r="P4" s="10">
+        <v>1.34</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>1.842</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="3">
-        <v>73.18</v>
-      </c>
-      <c r="F5" s="3">
-        <v>71.4</v>
-      </c>
-      <c r="G5" s="3">
-        <v>72.79</v>
-      </c>
-      <c r="H5" s="3">
-        <v>72.74</v>
-      </c>
-      <c r="I5" s="3">
-        <v>71.4</v>
-      </c>
-      <c r="J5" s="3">
-        <v>74.08</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="E5" s="9">
+        <v>84.1</v>
+      </c>
+      <c r="F5" s="9">
+        <v>83.6</v>
+      </c>
+      <c r="G5" s="9">
+        <v>84.1</v>
+      </c>
+      <c r="H5" s="9">
+        <v>84.09</v>
+      </c>
+      <c r="I5" s="9">
+        <v>83.6</v>
+      </c>
+      <c r="J5" s="9">
+        <v>84.58</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5" s="2" t="s">
+      <c r="L5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="3">
-        <v>74.08</v>
-      </c>
-      <c r="O5" s="2">
+      <c r="N5" s="9">
+        <v>84.58</v>
+      </c>
+      <c r="O5" s="8">
         <v>1</v>
       </c>
-      <c r="P5" s="4">
-        <v>1.34</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>1.842</v>
-      </c>
-      <c r="R5" s="2" t="s">
+      <c r="P5" s="10">
+        <v>0.49</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>0.583</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="3">
-        <v>84.1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>83.6</v>
-      </c>
-      <c r="G6" s="3">
-        <v>84.1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>84.09</v>
-      </c>
-      <c r="I6" s="3">
-        <v>83.6</v>
-      </c>
-      <c r="J6" s="3">
-        <v>84.58</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="E6" s="9">
+        <v>879.9</v>
+      </c>
+      <c r="F6" s="9">
+        <v>877</v>
+      </c>
+      <c r="G6" s="9">
+        <v>878.35</v>
+      </c>
+      <c r="H6" s="9">
+        <v>878.35</v>
+      </c>
+      <c r="I6" s="9">
+        <v>877</v>
+      </c>
+      <c r="J6" s="9">
+        <v>879.7</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="L6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="3">
-        <v>84.58</v>
-      </c>
-      <c r="O6" s="2">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4">
-        <v>0.49</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>0.583</v>
-      </c>
-      <c r="R6" s="2" t="s">
+      <c r="N6" s="9">
+        <v>879.7</v>
+      </c>
+      <c r="O6" s="8">
+        <v>2</v>
+      </c>
+      <c r="P6" s="10">
+        <v>1.35</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0.154</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="7">
+        <v>13428</v>
+      </c>
+      <c r="F7" s="7">
+        <v>13205</v>
+      </c>
+      <c r="G7" s="7">
+        <v>13372</v>
+      </c>
+      <c r="H7" s="7">
+        <v>13380</v>
+      </c>
+      <c r="I7" s="7">
+        <v>13205</v>
+      </c>
+      <c r="J7" s="7">
+        <v>13555</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="E7" s="3">
-        <v>879.9</v>
-      </c>
-      <c r="F7" s="3">
-        <v>877</v>
-      </c>
-      <c r="G7" s="3">
-        <v>878.35</v>
-      </c>
-      <c r="H7" s="3">
-        <v>878.35</v>
-      </c>
-      <c r="I7" s="3">
-        <v>877</v>
-      </c>
-      <c r="J7" s="3">
-        <v>879.7</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="3">
-        <v>879.7</v>
-      </c>
-      <c r="O7" s="2">
-        <v>2</v>
-      </c>
-      <c r="P7" s="4">
-        <v>1.35</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>0.154</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="11">
-        <v>13428</v>
-      </c>
-      <c r="F8" s="11">
-        <v>13205</v>
-      </c>
-      <c r="G8" s="11">
-        <v>13372</v>
-      </c>
-      <c r="H8" s="11">
-        <v>13380</v>
-      </c>
-      <c r="I8" s="11">
-        <v>13205</v>
-      </c>
-      <c r="J8" s="11">
-        <v>13555</v>
-      </c>
-      <c r="K8" s="10" t="s">
+      <c r="E8" s="3">
+        <v>1729.3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1723</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1729</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1729</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1723</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1735</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10" t="s">
+      <c r="L8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>50</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1723</v>
+      </c>
+      <c r="O8" s="2">
+        <v>6</v>
+      </c>
+      <c r="P8" s="4">
+        <v>-6</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>-0.347</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="7">
-        <v>1729.3</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1723</v>
-      </c>
-      <c r="G9" s="7">
-        <v>1729</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1729</v>
-      </c>
-      <c r="I9" s="7">
-        <v>1723</v>
-      </c>
-      <c r="J9" s="7">
-        <v>1735</v>
-      </c>
-      <c r="K9" s="6" t="s">
+      <c r="E9" s="9">
+        <v>1168.6</v>
+      </c>
+      <c r="F9" s="9">
+        <v>1162.9</v>
+      </c>
+      <c r="G9" s="9">
+        <v>1167.9</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1167.6</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1162.9</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1172.3</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="6" t="s">
+      <c r="L9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="7">
-        <v>1723</v>
-      </c>
-      <c r="O9" s="6">
-        <v>6</v>
-      </c>
-      <c r="P9" s="8">
-        <v>-6</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>-0.347</v>
-      </c>
-      <c r="R9" s="6" t="s">
+      <c r="N9" s="9">
+        <v>1172.3</v>
+      </c>
+      <c r="O9" s="8">
+        <v>1</v>
+      </c>
+      <c r="P9" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0.403</v>
+      </c>
+      <c r="R9" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="7">
+        <v>749.8</v>
+      </c>
+      <c r="F10" s="7">
+        <v>745.1</v>
+      </c>
+      <c r="G10" s="7">
+        <v>749</v>
+      </c>
+      <c r="H10" s="7">
+        <v>748.95</v>
+      </c>
+      <c r="I10" s="7">
+        <v>745.1</v>
+      </c>
+      <c r="J10" s="7">
+        <v>752.8</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1168.6</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1162.9</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1167.9</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1167.6</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1162.9</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1172.3</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1172.3</v>
-      </c>
-      <c r="O10" s="2">
-        <v>1</v>
-      </c>
-      <c r="P10" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>0.403</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="C11" s="6" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="E11" s="7">
-        <v>4931</v>
+        <v>13070</v>
       </c>
       <c r="F11" s="7">
-        <v>4892</v>
+        <v>13037</v>
       </c>
       <c r="G11" s="7">
-        <v>4904</v>
-      </c>
-      <c r="H11" s="7">
-        <v>4940</v>
-      </c>
+        <v>13068</v>
+      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="7">
-        <v>4892</v>
-      </c>
-      <c r="J11" s="7">
-        <v>4892</v>
-      </c>
+        <v>13037</v>
+      </c>
+      <c r="J11" s="6"/>
       <c r="K11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N11" s="7">
-        <v>4892</v>
-      </c>
-      <c r="O11" s="6">
-        <v>1</v>
-      </c>
-      <c r="P11" s="12">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0.972</v>
-      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
       <c r="R11" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="11">
-        <v>749.8</v>
-      </c>
-      <c r="F12" s="11">
-        <v>745.1</v>
-      </c>
-      <c r="G12" s="11">
-        <v>749</v>
-      </c>
-      <c r="H12" s="11">
-        <v>748.95</v>
-      </c>
-      <c r="I12" s="11">
-        <v>745.1</v>
-      </c>
-      <c r="J12" s="11">
-        <v>752.8</v>
-      </c>
-      <c r="K12" s="10" t="s">
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3">
+        <v>21.2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>21.09</v>
+      </c>
+      <c r="G12" s="3">
+        <v>21.18</v>
+      </c>
+      <c r="H12" s="3">
+        <v>21.18</v>
+      </c>
+      <c r="I12" s="3">
+        <v>21.09</v>
+      </c>
+      <c r="J12" s="3">
+        <v>21.27</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="11">
-        <v>13070</v>
-      </c>
-      <c r="F13" s="11">
-        <v>13037</v>
-      </c>
-      <c r="G13" s="11">
-        <v>13068</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="11">
-        <v>13037</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10" t="s">
-        <v>68</v>
+      <c r="L12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="3">
+        <v>21.09</v>
+      </c>
+      <c r="O12" s="2">
+        <v>1</v>
+      </c>
+      <c r="P12" s="4">
+        <v>-0.09</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>-0.425</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="7">
-        <v>21.2</v>
-      </c>
-      <c r="F14" s="7">
-        <v>21.09</v>
-      </c>
-      <c r="G14" s="7">
-        <v>21.18</v>
-      </c>
-      <c r="H14" s="7">
-        <v>21.18</v>
-      </c>
-      <c r="I14" s="7">
-        <v>21.09</v>
-      </c>
-      <c r="J14" s="7">
-        <v>21.27</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N14" s="7">
-        <v>21.09</v>
-      </c>
-      <c r="O14" s="6">
-        <v>1</v>
-      </c>
-      <c r="P14" s="8">
-        <v>-0.09</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>-0.425</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="P16" s="15">
-        <v>-17.51</v>
-      </c>
-      <c r="R16" s="14" t="s">
-        <v>72</v>
+      <c r="A14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="P14" s="13">
+        <v>-70.21</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="146">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -100,112 +100,355 @@
     <t>2026-02-18 12:15</t>
   </si>
   <si>
+    <t>2026-02-19 10:15</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1771305300_1771386300</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 09:15</t>
+  </si>
+  <si>
+    <t>TARGET HIT</t>
+  </si>
+  <si>
+    <t>2026-02-19 09:15</t>
+  </si>
+  <si>
+    <t>NSE:IDFCFIRSTB-EQ_BULL_1771313400_1771406100</t>
+  </si>
+  <si>
+    <t>NSE:IDFCFIRSTB-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 14:45</t>
+  </si>
+  <si>
+    <t>2026-02-18 15:15</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BULL_1771305300_1771399800</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 13:00</t>
+  </si>
+  <si>
+    <t>2026-02-18 13:45</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1771306200_1771386300</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 11 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:HFCL-EQ_BULL_1771305300_1771386300</t>
-  </si>
-  <si>
-    <t>NSE:HFCL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 09:15</t>
-  </si>
-  <si>
-    <t>TARGET HIT</t>
+    <t>Checked 48 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1771304400_1771395300</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:45</t>
+  </si>
+  <si>
+    <t>2026-02-18 13:30</t>
+  </si>
+  <si>
+    <t>NSE:TATACONSUM-EQ_BULL_1771315200_1771405200</t>
+  </si>
+  <si>
+    <t>NSE:TATACONSUM-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-18 15:00</t>
+  </si>
+  <si>
+    <t>NSE:UPL-EQ_BULL_1771314300_1771407000</t>
+  </si>
+  <si>
+    <t>NSE:UPL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BULL_1771315200_1771407900</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 09:30</t>
+  </si>
+  <si>
+    <t>NSE:YESBANK-EQ_BULL_1771308900_1771386300</t>
+  </si>
+  <si>
+    <t>NSE:YESBANK-EQ</t>
   </si>
   <si>
     <t>2026-02-18 09:45</t>
   </si>
   <si>
-    <t>NSE:IDFCFIRSTB-EQ_BULL_1771313400_1771406100</t>
-  </si>
-  <si>
-    <t>NSE:IDFCFIRSTB-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 14:45</t>
-  </si>
-  <si>
-    <t>2026-02-18 15:15</t>
-  </si>
-  <si>
-    <t>NSE:LICI-EQ_BULL_1771305300_1771399800</t>
-  </si>
-  <si>
-    <t>NSE:LICI-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 13:00</t>
-  </si>
-  <si>
-    <t>2026-02-18 13:45</t>
-  </si>
-  <si>
-    <t>NSE:SOLARINDS-EQ_BULL_1771306200_1771386300</t>
-  </si>
-  <si>
-    <t>NSE:SOLARINDS-EQ</t>
+    <t>NSE:CHOLAFIN-EQ_BEAR_1771398900_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ</t>
+  </si>
+  <si>
+    <t>BEARISH</t>
+  </si>
+  <si>
+    <t>2026-02-19 09:45</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BULL_1771389900_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ</t>
   </si>
   <si>
     <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
-    <t>NSE:SUNPHARMA-EQ_BULL_1771304400_1771395300</t>
-  </si>
-  <si>
-    <t>NSE:SUNPHARMA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 11:45</t>
-  </si>
-  <si>
-    <t>2026-02-18 13:30</t>
-  </si>
-  <si>
-    <t>NSE:TATACONSUM-EQ_BULL_1771315200_1771405200</t>
-  </si>
-  <si>
-    <t>NSE:TATACONSUM-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 14:30</t>
-  </si>
-  <si>
-    <t>2026-02-18 15:00</t>
-  </si>
-  <si>
-    <t>NSE:UPL-EQ_BULL_1771314300_1771407000</t>
-  </si>
-  <si>
-    <t>NSE:UPL-EQ</t>
+    <t>NSE:IIFL-EQ_BEAR_1771392600_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IRCTC-EQ_BULL_1771396200_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:IRCTC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ_BEAR_1771405200_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ABB-EQ_BEAR_1771483500_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ABB-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:00</t>
   </si>
   <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>NSE:ULTRACEMCO-EQ_BULL_1771315200_1771407900</t>
-  </si>
-  <si>
-    <t>NSE:ULTRACEMCO-EQ</t>
+    <t>NSE:ADANIPORTS-EQ_BEAR_1771473600_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ_BEAR_1771402500_1771484400</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 12:30</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:00</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BEAR_1771484400_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BEAR_1771386300_1771475400</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 10:00</t>
+  </si>
+  <si>
+    <t>2026-02-19 10:30</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ_BEAR_1771472700_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:15</t>
   </si>
   <si>
     <t>Entry candle not yet available — trade not entered</t>
   </si>
   <si>
-    <t>NSE:YESBANK-EQ_BULL_1771308900_1771386300</t>
-  </si>
-  <si>
-    <t>NSE:YESBANK-EQ</t>
-  </si>
-  <si>
-    <t>SUMMARY — 4W / 3L / 4 OPEN  |  Win Rate: 57.1%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 7 of 11</t>
+    <t>NSE:DABUR-EQ_BEAR_1771386300_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1771479000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BEAR_1771478100_1771489800</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:30</t>
+  </si>
+  <si>
+    <t>NSE:HAL-EQ_BEAR_1771479900_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:HAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BEAR_1771392600_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1771481700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BEAR_1771474500_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BEAR_1771480800_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1771388100_1771491600</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:INDUSTOWER-EQ_BEAR_1771485300_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:INDUSTOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1771488000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1771479900_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BEAR_1771481700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BEAR_1771472700_1771489800</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1771479000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ_BEAR_1771488000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BEAR_1771478100_1771484400</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BEAR_1771480800_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771476300_1771488900</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:45</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:15</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BEAR_1771485300_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771488000</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:30</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1771484400_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ZYDUSLIFE-EQ_BEAR_1771490700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ZYDUSLIFE-EQ</t>
+  </si>
+  <si>
+    <t>SUMMARY — 9W / 13L / 23 OPEN  |  Win Rate: 40.9%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 22 of 45</t>
   </si>
 </sst>
 </file>
@@ -272,12 +515,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -308,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -319,10 +562,12 @@
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -664,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -797,262 +1042,272 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="3">
         <v>2016.7</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="3">
         <v>1991</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="3">
         <v>2015.6</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="3">
         <v>2015.7</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="3">
         <v>1991</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="3">
         <v>2040.4</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="6" t="s">
+      <c r="K3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6" t="s">
+      <c r="N3" s="3">
+        <v>1991</v>
+      </c>
+      <c r="O3" s="2">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>-24.7</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>-1.225</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="E4" s="7">
+        <v>73.18</v>
+      </c>
+      <c r="F4" s="7">
+        <v>71.4</v>
+      </c>
+      <c r="G4" s="7">
+        <v>72.79</v>
+      </c>
+      <c r="H4" s="7">
+        <v>72.79</v>
+      </c>
+      <c r="I4" s="7">
+        <v>71.4</v>
+      </c>
+      <c r="J4" s="7">
+        <v>74.18</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="7">
+        <v>74.18</v>
+      </c>
+      <c r="O4" s="6">
+        <v>24</v>
+      </c>
+      <c r="P4" s="8">
+        <v>1.39</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>1.91</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="7">
+        <v>84.1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>83.6</v>
+      </c>
+      <c r="G5" s="7">
+        <v>84.1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>84.09</v>
+      </c>
+      <c r="I5" s="7">
+        <v>83.6</v>
+      </c>
+      <c r="J5" s="7">
+        <v>84.58</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="9">
-        <v>73.18</v>
-      </c>
-      <c r="F4" s="9">
-        <v>71.4</v>
-      </c>
-      <c r="G4" s="9">
-        <v>72.79</v>
-      </c>
-      <c r="H4" s="9">
-        <v>72.74</v>
-      </c>
-      <c r="I4" s="9">
-        <v>71.4</v>
-      </c>
-      <c r="J4" s="9">
-        <v>74.08</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="9">
-        <v>74.08</v>
-      </c>
-      <c r="O4" s="8">
+      <c r="M5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="7">
+        <v>84.58</v>
+      </c>
+      <c r="O5" s="6">
         <v>1</v>
       </c>
-      <c r="P4" s="10">
-        <v>1.34</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>1.842</v>
-      </c>
-      <c r="R4" s="8" t="s">
+      <c r="P5" s="8">
+        <v>0.49</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0.583</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="8" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="9">
-        <v>84.1</v>
-      </c>
-      <c r="F5" s="9">
-        <v>83.6</v>
-      </c>
-      <c r="G5" s="9">
-        <v>84.1</v>
-      </c>
-      <c r="H5" s="9">
-        <v>84.09</v>
-      </c>
-      <c r="I5" s="9">
-        <v>83.6</v>
-      </c>
-      <c r="J5" s="9">
-        <v>84.58</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="9">
-        <v>84.58</v>
-      </c>
-      <c r="O5" s="8">
-        <v>1</v>
-      </c>
-      <c r="P5" s="10">
-        <v>0.49</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>0.583</v>
-      </c>
-      <c r="R5" s="8" t="s">
+      <c r="D6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="7">
+        <v>879.9</v>
+      </c>
+      <c r="F6" s="7">
+        <v>877</v>
+      </c>
+      <c r="G6" s="7">
+        <v>878.35</v>
+      </c>
+      <c r="H6" s="7">
+        <v>878.35</v>
+      </c>
+      <c r="I6" s="7">
+        <v>877</v>
+      </c>
+      <c r="J6" s="7">
+        <v>879.7</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="7">
+        <v>879.7</v>
+      </c>
+      <c r="O6" s="6">
+        <v>2</v>
+      </c>
+      <c r="P6" s="8">
+        <v>1.35</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0.154</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="8" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="9">
-        <v>879.9</v>
-      </c>
-      <c r="F6" s="9">
-        <v>877</v>
-      </c>
-      <c r="G6" s="9">
-        <v>878.35</v>
-      </c>
-      <c r="H6" s="9">
-        <v>878.35</v>
-      </c>
-      <c r="I6" s="9">
-        <v>877</v>
-      </c>
-      <c r="J6" s="9">
-        <v>879.7</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="9">
-        <v>879.7</v>
-      </c>
-      <c r="O6" s="8">
-        <v>2</v>
-      </c>
-      <c r="P6" s="10">
-        <v>1.35</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0.154</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="D7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="11">
+        <v>13428</v>
+      </c>
+      <c r="F7" s="11">
+        <v>13205</v>
+      </c>
+      <c r="G7" s="11">
+        <v>13372</v>
+      </c>
+      <c r="H7" s="11">
+        <v>13372</v>
+      </c>
+      <c r="I7" s="11">
+        <v>13205</v>
+      </c>
+      <c r="J7" s="11">
+        <v>13539</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="7">
-        <v>13428</v>
-      </c>
-      <c r="F7" s="7">
-        <v>13205</v>
-      </c>
-      <c r="G7" s="7">
-        <v>13372</v>
-      </c>
-      <c r="H7" s="7">
-        <v>13380</v>
-      </c>
-      <c r="I7" s="7">
-        <v>13205</v>
-      </c>
-      <c r="J7" s="7">
-        <v>13555</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6" t="s">
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1113,58 +1368,58 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>1168.6</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="7">
         <v>1162.9</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="7">
         <v>1167.9</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="7">
         <v>1167.6</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="7">
         <v>1162.9</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="7">
         <v>1172.3</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="8" t="s">
+      <c r="K9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="7">
         <v>1172.3</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="6">
         <v>1</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="8">
         <v>4.7</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="Q9" s="9">
         <v>0.403</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="R9" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1203,71 +1458,95 @@
         <v>22</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="7">
+        <v>752.8</v>
+      </c>
+      <c r="O10" s="6">
+        <v>1</v>
+      </c>
+      <c r="P10" s="8">
+        <v>3.85</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0.514</v>
+      </c>
       <c r="R10" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="3">
+        <v>13070</v>
+      </c>
+      <c r="F11" s="3">
+        <v>13037</v>
+      </c>
+      <c r="G11" s="3">
+        <v>13068</v>
+      </c>
+      <c r="H11" s="3">
+        <v>13039</v>
+      </c>
+      <c r="I11" s="3">
+        <v>13037</v>
+      </c>
+      <c r="J11" s="3">
+        <v>13041</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="7">
-        <v>13070</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="N11" s="3">
         <v>13037</v>
       </c>
-      <c r="G11" s="7">
-        <v>13068</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7">
-        <v>13037</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6" t="s">
-        <v>60</v>
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+      <c r="P11" s="4">
+        <v>-2</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>-0.015</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="3">
         <v>21.2</v>
@@ -1294,7 +1573,7 @@
         <v>23</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N12" s="3">
         <v>21.09</v>
@@ -1312,15 +1591,1687 @@
         <v>25</v>
       </c>
     </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1728.9</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1706.1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1709.2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1708.7</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1706.1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1706.1</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="3">
+        <v>1706.1</v>
+      </c>
+      <c r="O13" s="2">
+        <v>1</v>
+      </c>
+      <c r="P13" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>0.152</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="P14" s="13">
-        <v>-70.21</v>
-      </c>
-      <c r="R14" s="12" t="s">
-        <v>64</v>
+      <c r="A14" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="11">
+        <v>6327.5</v>
+      </c>
+      <c r="F14" s="11">
+        <v>6251</v>
+      </c>
+      <c r="G14" s="11">
+        <v>6325</v>
+      </c>
+      <c r="H14" s="11">
+        <v>6324.5</v>
+      </c>
+      <c r="I14" s="11">
+        <v>6251</v>
+      </c>
+      <c r="J14" s="11">
+        <v>6398</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="7">
+        <v>515.8</v>
+      </c>
+      <c r="F15" s="7">
+        <v>506.7</v>
+      </c>
+      <c r="G15" s="7">
+        <v>507</v>
+      </c>
+      <c r="H15" s="7">
+        <v>507</v>
+      </c>
+      <c r="I15" s="7">
+        <v>506.7</v>
+      </c>
+      <c r="J15" s="7">
+        <v>506.7</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" s="7">
+        <v>506.7</v>
+      </c>
+      <c r="O15" s="6">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0.059</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="7">
+        <v>627.85</v>
+      </c>
+      <c r="F16" s="7">
+        <v>619.3</v>
+      </c>
+      <c r="G16" s="7">
+        <v>626.6</v>
+      </c>
+      <c r="H16" s="7">
+        <v>626.55</v>
+      </c>
+      <c r="I16" s="7">
+        <v>619.3</v>
+      </c>
+      <c r="J16" s="7">
+        <v>633.8</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="7">
+        <v>633.8</v>
+      </c>
+      <c r="O16" s="6">
+        <v>3</v>
+      </c>
+      <c r="P16" s="8">
+        <v>7.25</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1.157</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1489.9</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1475.7</v>
+      </c>
+      <c r="G17" s="7">
+        <v>1476.6</v>
+      </c>
+      <c r="H17" s="7">
+        <v>1476.5</v>
+      </c>
+      <c r="I17" s="7">
+        <v>1475.7</v>
+      </c>
+      <c r="J17" s="7">
+        <v>1475.7</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17" s="7">
+        <v>1475.7</v>
+      </c>
+      <c r="O17" s="6">
+        <v>1</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0.054</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="11">
+        <v>5770.5</v>
+      </c>
+      <c r="F18" s="11">
+        <v>5710</v>
+      </c>
+      <c r="G18" s="11">
+        <v>5710</v>
+      </c>
+      <c r="H18" s="11">
+        <v>5712.5</v>
+      </c>
+      <c r="I18" s="11">
+        <v>5710</v>
+      </c>
+      <c r="J18" s="11">
+        <v>5710</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="11">
+        <v>1523.8</v>
+      </c>
+      <c r="F19" s="11">
+        <v>1512.1</v>
+      </c>
+      <c r="G19" s="11">
+        <v>1513</v>
+      </c>
+      <c r="H19" s="11">
+        <v>1513.1</v>
+      </c>
+      <c r="I19" s="11">
+        <v>1512.1</v>
+      </c>
+      <c r="J19" s="11">
+        <v>1512.1</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2008.1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2000.2</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2002.1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2002.2</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2000.2</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2000.2</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2000.2</v>
+      </c>
+      <c r="O20" s="2">
+        <v>1</v>
+      </c>
+      <c r="P20" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="11">
+        <v>1338.4</v>
+      </c>
+      <c r="F21" s="11">
+        <v>1330.8</v>
+      </c>
+      <c r="G21" s="11">
+        <v>1331</v>
+      </c>
+      <c r="H21" s="11">
+        <v>1331</v>
+      </c>
+      <c r="I21" s="11">
+        <v>1330.8</v>
+      </c>
+      <c r="J21" s="11">
+        <v>1330.8</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="7">
+        <v>417.4</v>
+      </c>
+      <c r="F22" s="7">
+        <v>415.95</v>
+      </c>
+      <c r="G22" s="7">
+        <v>415.95</v>
+      </c>
+      <c r="H22" s="7">
+        <v>416.1</v>
+      </c>
+      <c r="I22" s="7">
+        <v>415.95</v>
+      </c>
+      <c r="J22" s="7">
+        <v>415.95</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="N22" s="7">
+        <v>415.95</v>
+      </c>
+      <c r="O22" s="6">
+        <v>1</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>0.036</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="11">
+        <v>509.55</v>
+      </c>
+      <c r="F23" s="11">
+        <v>501.1</v>
+      </c>
+      <c r="G23" s="11">
+        <v>501.1</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="11">
+        <v>501.1</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="11">
+        <v>504.45</v>
+      </c>
+      <c r="F24" s="11">
+        <v>501.45</v>
+      </c>
+      <c r="G24" s="11">
+        <v>501.65</v>
+      </c>
+      <c r="H24" s="11">
+        <v>501.65</v>
+      </c>
+      <c r="I24" s="11">
+        <v>501.45</v>
+      </c>
+      <c r="J24" s="11">
+        <v>501.45</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="11">
+        <v>335.7</v>
+      </c>
+      <c r="F25" s="11">
+        <v>332.05</v>
+      </c>
+      <c r="G25" s="11">
+        <v>333</v>
+      </c>
+      <c r="H25" s="11">
+        <v>333.15</v>
+      </c>
+      <c r="I25" s="11">
+        <v>332.05</v>
+      </c>
+      <c r="J25" s="11">
+        <v>332.05</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1198.4</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1194.4</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1196.3</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1196.2</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1194.4</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1194.4</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1194.4</v>
+      </c>
+      <c r="O26" s="2">
+        <v>1</v>
+      </c>
+      <c r="P26" s="12">
+        <v>1.8</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="11">
+        <v>4164.3</v>
+      </c>
+      <c r="F27" s="11">
+        <v>4134.9</v>
+      </c>
+      <c r="G27" s="11">
+        <v>4135.7</v>
+      </c>
+      <c r="H27" s="11">
+        <v>4135.8</v>
+      </c>
+      <c r="I27" s="11">
+        <v>4134.9</v>
+      </c>
+      <c r="J27" s="11">
+        <v>4134.9</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="11">
+        <v>498.25</v>
+      </c>
+      <c r="F28" s="11">
+        <v>492.35</v>
+      </c>
+      <c r="G28" s="11">
+        <v>496</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="11">
+        <v>492.35</v>
+      </c>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="11">
+        <v>124.71</v>
+      </c>
+      <c r="F29" s="11">
+        <v>123.71</v>
+      </c>
+      <c r="G29" s="11">
+        <v>123.77</v>
+      </c>
+      <c r="H29" s="11">
+        <v>123.77</v>
+      </c>
+      <c r="I29" s="11">
+        <v>123.71</v>
+      </c>
+      <c r="J29" s="11">
+        <v>123.71</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="11">
+        <v>112.28</v>
+      </c>
+      <c r="F30" s="11">
+        <v>111.52</v>
+      </c>
+      <c r="G30" s="11">
+        <v>111.55</v>
+      </c>
+      <c r="H30" s="11">
+        <v>111.54</v>
+      </c>
+      <c r="I30" s="11">
+        <v>111.52</v>
+      </c>
+      <c r="J30" s="11">
+        <v>111.52</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="11">
+        <v>126.77</v>
+      </c>
+      <c r="F31" s="11">
+        <v>126</v>
+      </c>
+      <c r="G31" s="11">
+        <v>126.02</v>
+      </c>
+      <c r="H31" s="11">
+        <v>126</v>
+      </c>
+      <c r="I31" s="11">
+        <v>126</v>
+      </c>
+      <c r="J31" s="11">
+        <v>126</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="3">
+        <v>168.95</v>
+      </c>
+      <c r="F32" s="3">
+        <v>168.48</v>
+      </c>
+      <c r="G32" s="3">
+        <v>168.49</v>
+      </c>
+      <c r="H32" s="3">
+        <v>168.6</v>
+      </c>
+      <c r="I32" s="3">
+        <v>168.48</v>
+      </c>
+      <c r="J32" s="3">
+        <v>168.48</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N32" s="3">
+        <v>168.48</v>
+      </c>
+      <c r="O32" s="2">
+        <v>1</v>
+      </c>
+      <c r="P32" s="12">
+        <v>0.12</v>
+      </c>
+      <c r="Q32" s="13">
+        <v>0.071</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="11">
+        <v>474.85</v>
+      </c>
+      <c r="F33" s="11">
+        <v>469.2</v>
+      </c>
+      <c r="G33" s="11">
+        <v>470.6</v>
+      </c>
+      <c r="H33" s="10"/>
+      <c r="I33" s="11">
+        <v>469.2</v>
+      </c>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="11">
+        <v>485.2</v>
+      </c>
+      <c r="F34" s="11">
+        <v>478.5</v>
+      </c>
+      <c r="G34" s="11">
+        <v>479.65</v>
+      </c>
+      <c r="H34" s="11">
+        <v>479.65</v>
+      </c>
+      <c r="I34" s="11">
+        <v>478.5</v>
+      </c>
+      <c r="J34" s="11">
+        <v>478.5</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="11">
+        <v>3919</v>
+      </c>
+      <c r="F35" s="11">
+        <v>3873.3</v>
+      </c>
+      <c r="G35" s="11">
+        <v>3874</v>
+      </c>
+      <c r="H35" s="11">
+        <v>3875.6</v>
+      </c>
+      <c r="I35" s="11">
+        <v>3873.3</v>
+      </c>
+      <c r="J35" s="11">
+        <v>3873.3</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="11">
+        <v>870.15</v>
+      </c>
+      <c r="F36" s="11">
+        <v>862.55</v>
+      </c>
+      <c r="G36" s="11">
+        <v>863.5</v>
+      </c>
+      <c r="H36" s="11">
+        <v>863.55</v>
+      </c>
+      <c r="I36" s="11">
+        <v>862.55</v>
+      </c>
+      <c r="J36" s="11">
+        <v>862.55</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="3">
+        <v>365.2</v>
+      </c>
+      <c r="F37" s="3">
+        <v>363.15</v>
+      </c>
+      <c r="G37" s="3">
+        <v>363.2</v>
+      </c>
+      <c r="H37" s="3">
+        <v>363.2</v>
+      </c>
+      <c r="I37" s="3">
+        <v>363.15</v>
+      </c>
+      <c r="J37" s="3">
+        <v>363.15</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N37" s="3">
+        <v>363.15</v>
+      </c>
+      <c r="O37" s="2">
+        <v>1</v>
+      </c>
+      <c r="P37" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="Q37" s="13">
+        <v>0.014</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="11">
+        <v>613.6</v>
+      </c>
+      <c r="F38" s="11">
+        <v>606.25</v>
+      </c>
+      <c r="G38" s="11">
+        <v>606.7</v>
+      </c>
+      <c r="H38" s="11">
+        <v>606.3</v>
+      </c>
+      <c r="I38" s="11">
+        <v>606.25</v>
+      </c>
+      <c r="J38" s="11">
+        <v>606.25</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="11">
+        <v>164.26</v>
+      </c>
+      <c r="F39" s="11">
+        <v>162.65</v>
+      </c>
+      <c r="G39" s="11">
+        <v>162.81</v>
+      </c>
+      <c r="H39" s="11">
+        <v>162.8</v>
+      </c>
+      <c r="I39" s="11">
+        <v>162.65</v>
+      </c>
+      <c r="J39" s="11">
+        <v>162.65</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="3">
+        <v>1421.7</v>
+      </c>
+      <c r="F40" s="3">
+        <v>1416.7</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1418.3</v>
+      </c>
+      <c r="H40" s="3">
+        <v>1418.1</v>
+      </c>
+      <c r="I40" s="3">
+        <v>1416.7</v>
+      </c>
+      <c r="J40" s="3">
+        <v>1416.7</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N40" s="3">
+        <v>1416.7</v>
+      </c>
+      <c r="O40" s="2">
+        <v>1</v>
+      </c>
+      <c r="P40" s="12">
+        <v>1.4</v>
+      </c>
+      <c r="Q40" s="13">
+        <v>0.099</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" s="11">
+        <v>1062.2</v>
+      </c>
+      <c r="F41" s="11">
+        <v>1053.5</v>
+      </c>
+      <c r="G41" s="11">
+        <v>1053.9</v>
+      </c>
+      <c r="H41" s="11">
+        <v>1053.4</v>
+      </c>
+      <c r="I41" s="11">
+        <v>1053.5</v>
+      </c>
+      <c r="J41" s="11">
+        <v>1053.3</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="3">
+        <v>158.62</v>
+      </c>
+      <c r="F42" s="3">
+        <v>158.22</v>
+      </c>
+      <c r="G42" s="3">
+        <v>158.29</v>
+      </c>
+      <c r="H42" s="3">
+        <v>158.3</v>
+      </c>
+      <c r="I42" s="3">
+        <v>158.22</v>
+      </c>
+      <c r="J42" s="3">
+        <v>158.22</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="N42" s="3">
+        <v>158.22</v>
+      </c>
+      <c r="O42" s="2">
+        <v>1</v>
+      </c>
+      <c r="P42" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="Q42" s="13">
+        <v>0.051</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="11">
+        <v>378.55</v>
+      </c>
+      <c r="F43" s="11">
+        <v>375.75</v>
+      </c>
+      <c r="G43" s="11">
+        <v>375.85</v>
+      </c>
+      <c r="H43" s="11">
+        <v>375.75</v>
+      </c>
+      <c r="I43" s="11">
+        <v>375.75</v>
+      </c>
+      <c r="J43" s="11">
+        <v>375.75</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12794</v>
+      </c>
+      <c r="F44" s="3">
+        <v>12734</v>
+      </c>
+      <c r="G44" s="3">
+        <v>12752</v>
+      </c>
+      <c r="H44" s="3">
+        <v>12752</v>
+      </c>
+      <c r="I44" s="3">
+        <v>12734</v>
+      </c>
+      <c r="J44" s="3">
+        <v>12734</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N44" s="3">
+        <v>12734</v>
+      </c>
+      <c r="O44" s="2">
+        <v>1</v>
+      </c>
+      <c r="P44" s="12">
+        <v>18</v>
+      </c>
+      <c r="Q44" s="13">
+        <v>0.141</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="11">
+        <v>456.4</v>
+      </c>
+      <c r="F45" s="11">
+        <v>453.3</v>
+      </c>
+      <c r="G45" s="11">
+        <v>453.55</v>
+      </c>
+      <c r="H45" s="11">
+        <v>453.55</v>
+      </c>
+      <c r="I45" s="11">
+        <v>453.3</v>
+      </c>
+      <c r="J45" s="11">
+        <v>453.3</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E46" s="11">
+        <v>906.95</v>
+      </c>
+      <c r="F46" s="11">
+        <v>901.5</v>
+      </c>
+      <c r="G46" s="11">
+        <v>901.75</v>
+      </c>
+      <c r="H46" s="11">
+        <v>901.95</v>
+      </c>
+      <c r="I46" s="11">
+        <v>901.5</v>
+      </c>
+      <c r="J46" s="11">
+        <v>901.5</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="P48" s="15">
+        <v>-58.46</v>
+      </c>
+      <c r="R48" s="14" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="192">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -148,81 +148,81 @@
     <t>NSE:SOLARINDS-EQ</t>
   </si>
   <si>
+    <t>2026-02-20 09:30</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1771304400_1771395300</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 11:45</t>
+  </si>
+  <si>
+    <t>2026-02-18 13:30</t>
+  </si>
+  <si>
+    <t>NSE:TATACONSUM-EQ_BULL_1771315200_1771405200</t>
+  </si>
+  <si>
+    <t>NSE:TATACONSUM-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-18 15:00</t>
+  </si>
+  <si>
+    <t>NSE:UPL-EQ_BULL_1771314300_1771407000</t>
+  </si>
+  <si>
+    <t>NSE:UPL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BULL_1771315200_1771407900</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 09:30</t>
+  </si>
+  <si>
+    <t>NSE:YESBANK-EQ_BULL_1771308900_1771386300</t>
+  </si>
+  <si>
+    <t>NSE:YESBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-18 09:45</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ_BEAR_1771398900_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ</t>
+  </si>
+  <si>
+    <t>BEARISH</t>
+  </si>
+  <si>
+    <t>2026-02-19 09:45</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BULL_1771389900_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
     <t>Checked 48 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
-    <t>NSE:SUNPHARMA-EQ_BULL_1771304400_1771395300</t>
-  </si>
-  <si>
-    <t>NSE:SUNPHARMA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 11:45</t>
-  </si>
-  <si>
-    <t>2026-02-18 13:30</t>
-  </si>
-  <si>
-    <t>NSE:TATACONSUM-EQ_BULL_1771315200_1771405200</t>
-  </si>
-  <si>
-    <t>NSE:TATACONSUM-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 14:30</t>
-  </si>
-  <si>
-    <t>2026-02-18 15:00</t>
-  </si>
-  <si>
-    <t>NSE:UPL-EQ_BULL_1771314300_1771407000</t>
-  </si>
-  <si>
-    <t>NSE:UPL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ULTRACEMCO-EQ_BULL_1771315200_1771407900</t>
-  </si>
-  <si>
-    <t>NSE:ULTRACEMCO-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 09:30</t>
-  </si>
-  <si>
-    <t>NSE:YESBANK-EQ_BULL_1771308900_1771386300</t>
-  </si>
-  <si>
-    <t>NSE:YESBANK-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-18 09:45</t>
-  </si>
-  <si>
-    <t>NSE:CHOLAFIN-EQ_BEAR_1771398900_1771472700</t>
-  </si>
-  <si>
-    <t>NSE:CHOLAFIN-EQ</t>
-  </si>
-  <si>
-    <t>BEARISH</t>
-  </si>
-  <si>
-    <t>2026-02-19 09:45</t>
-  </si>
-  <si>
-    <t>NSE:DIVISLAB-EQ_BULL_1771389900_1771472700</t>
-  </si>
-  <si>
-    <t>NSE:DIVISLAB-EQ</t>
-  </si>
-  <si>
-    <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
     <t>NSE:IIFL-EQ_BEAR_1771392600_1771472700</t>
   </si>
   <si>
@@ -250,205 +250,343 @@
     <t>2026-02-19 15:00</t>
   </si>
   <si>
+    <t>2026-02-20 09:15</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BEAR_1771473600_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ_BEAR_1771402500_1771484400</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 12:30</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:00</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BEAR_1771484400_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BEAR_1771386300_1771475400</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 10:00</t>
+  </si>
+  <si>
+    <t>2026-02-19 10:30</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ_BEAR_1771472700_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:15</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BEAR_1771386300_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1771479000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BEAR_1771478100_1771489800</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:30</t>
+  </si>
+  <si>
+    <t>NSE:HAL-EQ_BEAR_1771479900_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:HAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BEAR_1771392600_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1771481700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BEAR_1771474500_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BEAR_1771480800_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1771388100_1771491600</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:INDUSTOWER-EQ_BEAR_1771485300_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:INDUSTOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1771488000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1771479900_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BEAR_1771481700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BEAR_1771472700_1771489800</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1771479000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ_BEAR_1771488000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BEAR_1771478100_1771484400</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BEAR_1771480800_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771476300_1771488900</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:45</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:15</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BEAR_1771485300_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771488000</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:30</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1771484400_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ZYDUSLIFE-EQ_BEAR_1771490700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ZYDUSLIFE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BEAR_1771479900_1771560000</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 10:00</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1771475400_1771572600</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:00</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:30</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1771489800_1771570800</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 12:30</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ_BEAR_1771559100_1771571700</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:15</t>
+  </si>
+  <si>
+    <t>NSE:PHOENIXLTD-EQ_BEAR_1771473600_1771559100</t>
+  </si>
+  <si>
+    <t>NSE:PHOENIXLTD-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 09:45</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BEAR_1771481700_1771561800</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 10:30</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BEAR_1771472700_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:45</t>
+  </si>
+  <si>
+    <t>NSE:JUBLFOOD-EQ_BULL_1771571700_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:JUBLFOOD-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:00</t>
+  </si>
+  <si>
+    <t>NSE:TIINDIA-EQ_BULL_1771475400_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:TIINDIA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BULL_1771565400_1771574400</t>
+  </si>
+  <si>
+    <t>Checked 6 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1771481700_1771579800</t>
+  </si>
+  <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>NSE:ADANIPORTS-EQ_BEAR_1771473600_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:ADANIPORTS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BHARTIARTL-EQ_BEAR_1771402500_1771484400</t>
-  </si>
-  <si>
-    <t>NSE:BHARTIARTL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 12:30</t>
-  </si>
-  <si>
-    <t>2026-02-19 13:00</t>
-  </si>
-  <si>
-    <t>NSE:CIPLA-EQ_BEAR_1771484400_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:CIPLA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ_BEAR_1771386300_1771475400</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 10:00</t>
-  </si>
-  <si>
-    <t>2026-02-19 10:30</t>
-  </si>
-  <si>
-    <t>NSE:CONCOR-EQ_BEAR_1771472700_1771494300</t>
-  </si>
-  <si>
-    <t>NSE:CONCOR-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 15:15</t>
+    <t>NSE:INFY-EQ_BEAR_1771482600_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1771482600_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BEAR_1771488000_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:15</t>
   </si>
   <si>
     <t>Entry candle not yet available — trade not entered</t>
   </si>
   <si>
-    <t>NSE:DABUR-EQ_BEAR_1771386300_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:DABUR-EQ</t>
-  </si>
-  <si>
-    <t>NSE:EXIDEIND-EQ_BEAR_1771479000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:EXIDEIND-EQ</t>
-  </si>
-  <si>
-    <t>NSE:GODREJCP-EQ_BEAR_1771478100_1771489800</t>
-  </si>
-  <si>
-    <t>NSE:GODREJCP-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 14:00</t>
-  </si>
-  <si>
-    <t>2026-02-19 14:30</t>
-  </si>
-  <si>
-    <t>NSE:HAL-EQ_BEAR_1771479900_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:HAL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IIFL-EQ_BEAR_1771392600_1771494300</t>
-  </si>
-  <si>
-    <t>NSE:IEX-EQ_BEAR_1771481700_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:IEX-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IRFC-EQ_BEAR_1771474500_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:IRFC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ_BEAR_1771480800_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ_BEAR_1771388100_1771491600</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:INDUSTOWER-EQ_BEAR_1771485300_1771494300</t>
-  </si>
-  <si>
-    <t>NSE:INDUSTOWER-EQ</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BEAR_1771488000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ</t>
-  </si>
-  <si>
-    <t>NSE:KAYNES-EQ_BEAR_1771479900_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:KAYNES-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LICI-EQ_BEAR_1771481700_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:NTPC-EQ_BEAR_1771472700_1771489800</t>
-  </si>
-  <si>
-    <t>NSE:NTPC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BEAR_1771479000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PPLPHARMA-EQ_BEAR_1771488000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:PPLPHARMA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:RELIANCE-EQ_BEAR_1771478100_1771484400</t>
-  </si>
-  <si>
-    <t>NSE:RELIANCE-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SHRIRAMFIN-EQ_BEAR_1771480800_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:SHRIRAMFIN-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ_BEAR_1771476300_1771488900</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 13:45</t>
-  </si>
-  <si>
-    <t>2026-02-19 14:15</t>
-  </si>
-  <si>
-    <t>NSE:TMPV-EQ_BEAR_1771485300_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:TMPV-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771488000</t>
-  </si>
-  <si>
-    <t>2026-02-19 13:30</t>
-  </si>
-  <si>
-    <t>NSE:VBL-EQ_BEAR_1771484400_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:VBL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ZYDUSLIFE-EQ_BEAR_1771490700_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:ZYDUSLIFE-EQ</t>
-  </si>
-  <si>
-    <t>SUMMARY — 9W / 13L / 23 OPEN  |  Win Rate: 40.9%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 22 of 45</t>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BULL_1771564500_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ</t>
+  </si>
+  <si>
+    <t>SUMMARY — 12W / 41L / 10 OPEN  |  Win Rate: 22.6%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 53 of 63</t>
   </si>
 </sst>
 </file>
@@ -491,7 +629,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFF6B6B"/>
+      <color rgb="FF90EE90"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
@@ -564,10 +702,10 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -909,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R48"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1266,63 +1404,73 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="7">
         <v>13428</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="7">
         <v>13205</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="7">
         <v>13372</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="7">
         <v>13372</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="7">
         <v>13205</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="7">
         <v>13539</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="K7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10" t="s">
-        <v>46</v>
+      <c r="N7" s="7">
+        <v>13539</v>
+      </c>
+      <c r="O7" s="6">
+        <v>50</v>
+      </c>
+      <c r="P7" s="8">
+        <v>167</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.249</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3">
         <v>1729.3</v>
@@ -1349,7 +1497,7 @@
         <v>23</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N8" s="3">
         <v>1723</v>
@@ -1369,16 +1517,16 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="7">
         <v>1168.6</v>
@@ -1405,7 +1553,7 @@
         <v>33</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N9" s="7">
         <v>1172.3</v>
@@ -1425,16 +1573,16 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="7">
         <v>749.8</v>
@@ -1481,10 +1629,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>20</v>
@@ -1517,7 +1665,7 @@
         <v>23</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N11" s="3">
         <v>13037</v>
@@ -1537,10 +1685,10 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>20</v>
@@ -1573,7 +1721,7 @@
         <v>23</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N12" s="3">
         <v>21.09</v>
@@ -1593,13 +1741,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>34</v>
@@ -1629,7 +1777,7 @@
         <v>23</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N13" s="3">
         <v>1706.1</v>
@@ -1637,10 +1785,10 @@
       <c r="O13" s="2">
         <v>1</v>
       </c>
-      <c r="P13" s="12">
+      <c r="P13" s="10">
         <v>2.6</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="Q13" s="11">
         <v>0.152</v>
       </c>
       <c r="R13" s="2" t="s">
@@ -1648,48 +1796,48 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="13">
+        <v>6327.5</v>
+      </c>
+      <c r="F14" s="13">
+        <v>6251</v>
+      </c>
+      <c r="G14" s="13">
+        <v>6325</v>
+      </c>
+      <c r="H14" s="13">
+        <v>6324.5</v>
+      </c>
+      <c r="I14" s="13">
+        <v>6251</v>
+      </c>
+      <c r="J14" s="13">
+        <v>6398</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="11">
-        <v>6327.5</v>
-      </c>
-      <c r="F14" s="11">
-        <v>6251</v>
-      </c>
-      <c r="G14" s="11">
-        <v>6325</v>
-      </c>
-      <c r="H14" s="11">
-        <v>6324.5</v>
-      </c>
-      <c r="I14" s="11">
-        <v>6251</v>
-      </c>
-      <c r="J14" s="11">
-        <v>6398</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10" t="s">
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1701,7 +1849,7 @@
         <v>71</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>34</v>
@@ -1731,7 +1879,7 @@
         <v>33</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N15" s="7">
         <v>506.7</v>
@@ -1813,7 +1961,7 @@
         <v>75</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>34</v>
@@ -1843,7 +1991,7 @@
         <v>33</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N17" s="7">
         <v>1475.7</v>
@@ -1862,95 +2010,115 @@
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="3">
         <v>5770.5</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="3">
         <v>5710</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="3">
         <v>5710</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="3">
         <v>5712.5</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="3">
         <v>5710</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="3">
         <v>5710</v>
       </c>
-      <c r="K18" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10" t="s">
+      <c r="K18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>79</v>
       </c>
+      <c r="N18" s="3">
+        <v>5710</v>
+      </c>
+      <c r="O18" s="2">
+        <v>1</v>
+      </c>
+      <c r="P18" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>0.044</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="3">
         <v>1523.8</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="3">
         <v>1512.1</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="3">
         <v>1513</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="3">
         <v>1513.1</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="3">
         <v>1512.1</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="3">
         <v>1512.1</v>
       </c>
-      <c r="K19" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10" t="s">
+      <c r="K19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1512.1</v>
+      </c>
+      <c r="O19" s="2">
+        <v>1</v>
+      </c>
+      <c r="P19" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>0.066</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1961,7 +2129,7 @@
         <v>83</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>84</v>
@@ -1999,10 +2167,10 @@
       <c r="O20" s="2">
         <v>1</v>
       </c>
-      <c r="P20" s="12">
+      <c r="P20" s="10">
         <v>2</v>
       </c>
-      <c r="Q20" s="13">
+      <c r="Q20" s="11">
         <v>0.1</v>
       </c>
       <c r="R20" s="2" t="s">
@@ -2010,49 +2178,59 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="3">
         <v>1338.4</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="3">
         <v>1330.8</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="3">
         <v>1331</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="3">
         <v>1331</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="3">
         <v>1330.8</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="3">
         <v>1330.8</v>
       </c>
-      <c r="K21" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10" t="s">
+      <c r="K21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1330.8</v>
+      </c>
+      <c r="O21" s="2">
+        <v>1</v>
+      </c>
+      <c r="P21" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>0.015</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2063,7 +2241,7 @@
         <v>89</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>90</v>
@@ -2112,151 +2290,185 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="3">
         <v>509.55</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="3">
         <v>501.1</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="3">
         <v>501.1</v>
       </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="11">
+      <c r="H23" s="3">
+        <v>503.5</v>
+      </c>
+      <c r="I23" s="3">
         <v>501.1</v>
       </c>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" s="10" t="s">
+      <c r="J23" s="3">
+        <v>501.1</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10" t="s">
+      <c r="N23" s="3">
+        <v>501.1</v>
+      </c>
+      <c r="O23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>0.477</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="B24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="C24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="3">
+        <v>504.45</v>
+      </c>
+      <c r="F24" s="3">
+        <v>501.45</v>
+      </c>
+      <c r="G24" s="3">
+        <v>501.65</v>
+      </c>
+      <c r="H24" s="3">
+        <v>501.65</v>
+      </c>
+      <c r="I24" s="3">
+        <v>501.45</v>
+      </c>
+      <c r="J24" s="3">
+        <v>501.45</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N24" s="3">
+        <v>501.45</v>
+      </c>
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+      <c r="P24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="Q24" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="B25" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="11">
-        <v>504.45</v>
-      </c>
-      <c r="F24" s="11">
-        <v>501.45</v>
-      </c>
-      <c r="G24" s="11">
-        <v>501.65</v>
-      </c>
-      <c r="H24" s="11">
-        <v>501.65</v>
-      </c>
-      <c r="I24" s="11">
-        <v>501.45</v>
-      </c>
-      <c r="J24" s="11">
-        <v>501.45</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10" t="s">
+      <c r="E25" s="3">
+        <v>335.7</v>
+      </c>
+      <c r="F25" s="3">
+        <v>332.05</v>
+      </c>
+      <c r="G25" s="3">
+        <v>333</v>
+      </c>
+      <c r="H25" s="3">
+        <v>333.15</v>
+      </c>
+      <c r="I25" s="3">
+        <v>332.05</v>
+      </c>
+      <c r="J25" s="3">
+        <v>332.05</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="11">
-        <v>335.7</v>
-      </c>
-      <c r="F25" s="11">
+      <c r="N25" s="3">
         <v>332.05</v>
       </c>
-      <c r="G25" s="11">
-        <v>333</v>
-      </c>
-      <c r="H25" s="11">
-        <v>333.15</v>
-      </c>
-      <c r="I25" s="11">
-        <v>332.05</v>
-      </c>
-      <c r="J25" s="11">
-        <v>332.05</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10" t="s">
-        <v>79</v>
+      <c r="O25" s="2">
+        <v>1</v>
+      </c>
+      <c r="P25" s="10">
+        <v>1.1</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>0.33</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="E26" s="3">
         <v>1198.4</v>
@@ -2283,7 +2495,7 @@
         <v>23</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N26" s="3">
         <v>1194.4</v>
@@ -2291,10 +2503,10 @@
       <c r="O26" s="2">
         <v>1</v>
       </c>
-      <c r="P26" s="12">
+      <c r="P26" s="10">
         <v>1.8</v>
       </c>
-      <c r="Q26" s="13">
+      <c r="Q26" s="11">
         <v>0.15</v>
       </c>
       <c r="R26" s="2" t="s">
@@ -2302,243 +2514,297 @@
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4164.3</v>
+      </c>
+      <c r="F27" s="3">
+        <v>4134.9</v>
+      </c>
+      <c r="G27" s="3">
+        <v>4135.7</v>
+      </c>
+      <c r="H27" s="3">
+        <v>4135.8</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4134.9</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4134.9</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N27" s="3">
+        <v>4134.9</v>
+      </c>
+      <c r="O27" s="2">
+        <v>1</v>
+      </c>
+      <c r="P27" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="Q27" s="11">
+        <v>0.022</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="B28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="3">
+        <v>498.25</v>
+      </c>
+      <c r="F28" s="3">
+        <v>492.35</v>
+      </c>
+      <c r="G28" s="3">
+        <v>496</v>
+      </c>
+      <c r="H28" s="3">
+        <v>499</v>
+      </c>
+      <c r="I28" s="3">
+        <v>492.35</v>
+      </c>
+      <c r="J28" s="3">
+        <v>492.35</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N28" s="3">
+        <v>492.35</v>
+      </c>
+      <c r="O28" s="2">
+        <v>1</v>
+      </c>
+      <c r="P28" s="10">
+        <v>6.65</v>
+      </c>
+      <c r="Q28" s="11">
+        <v>1.333</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="11">
-        <v>4164.3</v>
-      </c>
-      <c r="F27" s="11">
-        <v>4134.9</v>
-      </c>
-      <c r="G27" s="11">
-        <v>4135.7</v>
-      </c>
-      <c r="H27" s="11">
-        <v>4135.8</v>
-      </c>
-      <c r="I27" s="11">
-        <v>4134.9</v>
-      </c>
-      <c r="J27" s="11">
-        <v>4134.9</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10" t="s">
+      <c r="E29" s="3">
+        <v>124.71</v>
+      </c>
+      <c r="F29" s="3">
+        <v>123.71</v>
+      </c>
+      <c r="G29" s="3">
+        <v>123.77</v>
+      </c>
+      <c r="H29" s="3">
+        <v>123.77</v>
+      </c>
+      <c r="I29" s="3">
+        <v>123.71</v>
+      </c>
+      <c r="J29" s="3">
+        <v>123.71</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E28" s="11">
-        <v>498.25</v>
-      </c>
-      <c r="F28" s="11">
-        <v>492.35</v>
-      </c>
-      <c r="G28" s="11">
-        <v>496</v>
-      </c>
-      <c r="H28" s="10"/>
-      <c r="I28" s="11">
-        <v>492.35</v>
-      </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B29" s="10" t="s">
+      <c r="N29" s="3">
+        <v>123.71</v>
+      </c>
+      <c r="O29" s="2">
+        <v>1</v>
+      </c>
+      <c r="P29" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>0.048</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="B30" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="11">
-        <v>124.71</v>
-      </c>
-      <c r="F29" s="11">
-        <v>123.71</v>
-      </c>
-      <c r="G29" s="11">
-        <v>123.77</v>
-      </c>
-      <c r="H29" s="11">
-        <v>123.77</v>
-      </c>
-      <c r="I29" s="11">
-        <v>123.71</v>
-      </c>
-      <c r="J29" s="11">
-        <v>123.71</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10" t="s">
+      <c r="E30" s="3">
+        <v>112.28</v>
+      </c>
+      <c r="F30" s="3">
+        <v>111.52</v>
+      </c>
+      <c r="G30" s="3">
+        <v>111.55</v>
+      </c>
+      <c r="H30" s="3">
+        <v>111.54</v>
+      </c>
+      <c r="I30" s="3">
+        <v>111.52</v>
+      </c>
+      <c r="J30" s="3">
+        <v>111.52</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="10" t="s">
+      <c r="N30" s="3">
+        <v>111.52</v>
+      </c>
+      <c r="O30" s="2">
+        <v>1</v>
+      </c>
+      <c r="P30" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="Q30" s="11">
+        <v>0.018</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="B31" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="11">
-        <v>112.28</v>
-      </c>
-      <c r="F30" s="11">
-        <v>111.52</v>
-      </c>
-      <c r="G30" s="11">
-        <v>111.55</v>
-      </c>
-      <c r="H30" s="11">
-        <v>111.54</v>
-      </c>
-      <c r="I30" s="11">
-        <v>111.52</v>
-      </c>
-      <c r="J30" s="11">
-        <v>111.52</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L30" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10" t="s">
+      <c r="E31" s="3">
+        <v>126.77</v>
+      </c>
+      <c r="F31" s="3">
+        <v>126</v>
+      </c>
+      <c r="G31" s="3">
+        <v>126.02</v>
+      </c>
+      <c r="H31" s="3">
+        <v>126</v>
+      </c>
+      <c r="I31" s="3">
+        <v>126</v>
+      </c>
+      <c r="J31" s="3">
+        <v>126</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="11">
-        <v>126.77</v>
-      </c>
-      <c r="F31" s="11">
+      <c r="N31" s="3">
         <v>126</v>
       </c>
-      <c r="G31" s="11">
-        <v>126.02</v>
-      </c>
-      <c r="H31" s="11">
-        <v>126</v>
-      </c>
-      <c r="I31" s="11">
-        <v>126</v>
-      </c>
-      <c r="J31" s="11">
-        <v>126</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10" t="s">
-        <v>79</v>
+      <c r="O31" s="2">
+        <v>1</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E32" s="3">
         <v>168.95</v>
@@ -2573,10 +2839,10 @@
       <c r="O32" s="2">
         <v>1</v>
       </c>
-      <c r="P32" s="12">
+      <c r="P32" s="10">
         <v>0.12</v>
       </c>
-      <c r="Q32" s="13">
+      <c r="Q32" s="11">
         <v>0.071</v>
       </c>
       <c r="R32" s="2" t="s">
@@ -2584,197 +2850,241 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="C33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="3">
+        <v>474.85</v>
+      </c>
+      <c r="F33" s="3">
+        <v>469.2</v>
+      </c>
+      <c r="G33" s="3">
+        <v>470.6</v>
+      </c>
+      <c r="H33" s="3">
+        <v>470.1</v>
+      </c>
+      <c r="I33" s="3">
+        <v>469.2</v>
+      </c>
+      <c r="J33" s="3">
+        <v>469.2</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N33" s="3">
+        <v>469.2</v>
+      </c>
+      <c r="O33" s="2">
+        <v>1</v>
+      </c>
+      <c r="P33" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>0.191</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" s="11">
-        <v>474.85</v>
-      </c>
-      <c r="F33" s="11">
-        <v>469.2</v>
-      </c>
-      <c r="G33" s="11">
-        <v>470.6</v>
-      </c>
-      <c r="H33" s="10"/>
-      <c r="I33" s="11">
-        <v>469.2</v>
-      </c>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="B34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="C34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="3">
+        <v>485.2</v>
+      </c>
+      <c r="F34" s="3">
+        <v>478.5</v>
+      </c>
+      <c r="G34" s="3">
+        <v>479.65</v>
+      </c>
+      <c r="H34" s="3">
+        <v>479.65</v>
+      </c>
+      <c r="I34" s="3">
+        <v>478.5</v>
+      </c>
+      <c r="J34" s="3">
+        <v>478.5</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N34" s="3">
+        <v>478.5</v>
+      </c>
+      <c r="O34" s="2">
+        <v>1</v>
+      </c>
+      <c r="P34" s="10">
+        <v>1.15</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="B35" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="11">
-        <v>485.2</v>
-      </c>
-      <c r="F34" s="11">
-        <v>478.5</v>
-      </c>
-      <c r="G34" s="11">
-        <v>479.65</v>
-      </c>
-      <c r="H34" s="11">
-        <v>479.65</v>
-      </c>
-      <c r="I34" s="11">
-        <v>478.5</v>
-      </c>
-      <c r="J34" s="11">
-        <v>478.5</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10" t="s">
+      <c r="E35" s="3">
+        <v>3919</v>
+      </c>
+      <c r="F35" s="3">
+        <v>3873.3</v>
+      </c>
+      <c r="G35" s="3">
+        <v>3874</v>
+      </c>
+      <c r="H35" s="3">
+        <v>3875.6</v>
+      </c>
+      <c r="I35" s="3">
+        <v>3873.3</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3873.3</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B35" s="10" t="s">
+      <c r="N35" s="3">
+        <v>3873.3</v>
+      </c>
+      <c r="O35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35" s="10">
+        <v>2.3</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>0.059</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="B36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="11">
-        <v>3919</v>
-      </c>
-      <c r="F35" s="11">
-        <v>3873.3</v>
-      </c>
-      <c r="G35" s="11">
-        <v>3874</v>
-      </c>
-      <c r="H35" s="11">
-        <v>3875.6</v>
-      </c>
-      <c r="I35" s="11">
-        <v>3873.3</v>
-      </c>
-      <c r="J35" s="11">
-        <v>3873.3</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10" t="s">
+      <c r="E36" s="3">
+        <v>870.15</v>
+      </c>
+      <c r="F36" s="3">
+        <v>862.55</v>
+      </c>
+      <c r="G36" s="3">
+        <v>863.5</v>
+      </c>
+      <c r="H36" s="3">
+        <v>863.55</v>
+      </c>
+      <c r="I36" s="3">
+        <v>862.55</v>
+      </c>
+      <c r="J36" s="3">
+        <v>862.55</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" s="11">
-        <v>870.15</v>
-      </c>
-      <c r="F36" s="11">
+      <c r="N36" s="3">
         <v>862.55</v>
       </c>
-      <c r="G36" s="11">
-        <v>863.5</v>
-      </c>
-      <c r="H36" s="11">
-        <v>863.55</v>
-      </c>
-      <c r="I36" s="11">
-        <v>862.55</v>
-      </c>
-      <c r="J36" s="11">
-        <v>862.55</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10" t="s">
-        <v>79</v>
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>0.116</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E37" s="3">
         <v>365.2</v>
@@ -2801,7 +3111,7 @@
         <v>23</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N37" s="3">
         <v>363.15</v>
@@ -2809,10 +3119,10 @@
       <c r="O37" s="2">
         <v>1</v>
       </c>
-      <c r="P37" s="12">
+      <c r="P37" s="10">
         <v>0.05</v>
       </c>
-      <c r="Q37" s="13">
+      <c r="Q37" s="11">
         <v>0.014</v>
       </c>
       <c r="R37" s="2" t="s">
@@ -2820,106 +3130,126 @@
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="C38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="3">
+        <v>613.6</v>
+      </c>
+      <c r="F38" s="3">
+        <v>606.25</v>
+      </c>
+      <c r="G38" s="3">
+        <v>606.7</v>
+      </c>
+      <c r="H38" s="3">
+        <v>606.3</v>
+      </c>
+      <c r="I38" s="3">
+        <v>606.25</v>
+      </c>
+      <c r="J38" s="3">
+        <v>606.25</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N38" s="3">
+        <v>606.25</v>
+      </c>
+      <c r="O38" s="2">
+        <v>1</v>
+      </c>
+      <c r="P38" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q38" s="11">
+        <v>0.008</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="10" t="s">
+      <c r="B39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="11">
-        <v>613.6</v>
-      </c>
-      <c r="F38" s="11">
-        <v>606.25</v>
-      </c>
-      <c r="G38" s="11">
-        <v>606.7</v>
-      </c>
-      <c r="H38" s="11">
-        <v>606.3</v>
-      </c>
-      <c r="I38" s="11">
-        <v>606.25</v>
-      </c>
-      <c r="J38" s="11">
-        <v>606.25</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L38" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10" t="s">
+      <c r="E39" s="3">
+        <v>164.26</v>
+      </c>
+      <c r="F39" s="3">
+        <v>162.65</v>
+      </c>
+      <c r="G39" s="3">
+        <v>162.81</v>
+      </c>
+      <c r="H39" s="3">
+        <v>162.8</v>
+      </c>
+      <c r="I39" s="3">
+        <v>162.65</v>
+      </c>
+      <c r="J39" s="3">
+        <v>162.65</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" s="11">
-        <v>164.26</v>
-      </c>
-      <c r="F39" s="11">
+      <c r="N39" s="3">
         <v>162.65</v>
       </c>
-      <c r="G39" s="11">
-        <v>162.81</v>
-      </c>
-      <c r="H39" s="11">
-        <v>162.8</v>
-      </c>
-      <c r="I39" s="11">
-        <v>162.65</v>
-      </c>
-      <c r="J39" s="11">
-        <v>162.65</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10" t="s">
-        <v>79</v>
+      <c r="O39" s="2">
+        <v>1</v>
+      </c>
+      <c r="P39" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="Q39" s="11">
+        <v>0.092</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>84</v>
@@ -2957,10 +3287,10 @@
       <c r="O40" s="2">
         <v>1</v>
       </c>
-      <c r="P40" s="12">
+      <c r="P40" s="10">
         <v>1.4</v>
       </c>
-      <c r="Q40" s="13">
+      <c r="Q40" s="11">
         <v>0.099</v>
       </c>
       <c r="R40" s="2" t="s">
@@ -2968,63 +3298,73 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="3">
         <v>1062.2</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="3">
         <v>1053.5</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="3">
         <v>1053.9</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="3">
         <v>1053.4</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="3">
         <v>1053.5</v>
       </c>
-      <c r="J41" s="11">
+      <c r="J41" s="3">
         <v>1053.3</v>
       </c>
-      <c r="K41" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10" t="s">
+      <c r="K41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="N41" s="3">
+        <v>1053.5</v>
+      </c>
+      <c r="O41" s="2">
+        <v>1</v>
+      </c>
+      <c r="P41" s="4">
+        <v>-0.1</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>-0.009</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="E42" s="3">
         <v>158.62</v>
@@ -3051,7 +3391,7 @@
         <v>23</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N42" s="3">
         <v>158.22</v>
@@ -3059,10 +3399,10 @@
       <c r="O42" s="2">
         <v>1</v>
       </c>
-      <c r="P42" s="12">
+      <c r="P42" s="10">
         <v>0.08</v>
       </c>
-      <c r="Q42" s="13">
+      <c r="Q42" s="11">
         <v>0.051</v>
       </c>
       <c r="R42" s="2" t="s">
@@ -3070,63 +3410,73 @@
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" s="10" t="s">
+      <c r="C43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="3">
         <v>378.55</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="3">
         <v>375.75</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="3">
         <v>375.85</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H43" s="3">
         <v>375.75</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="3">
         <v>375.75</v>
       </c>
-      <c r="J43" s="11">
+      <c r="J43" s="3">
         <v>375.75</v>
       </c>
-      <c r="K43" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10" t="s">
+      <c r="K43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="N43" s="3">
+        <v>375.75</v>
+      </c>
+      <c r="O43" s="2">
+        <v>1</v>
+      </c>
+      <c r="P43" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="11">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="E44" s="3">
         <v>12794</v>
@@ -3153,7 +3503,7 @@
         <v>23</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N44" s="3">
         <v>12734</v>
@@ -3161,10 +3511,10 @@
       <c r="O44" s="2">
         <v>1</v>
       </c>
-      <c r="P44" s="12">
+      <c r="P44" s="10">
         <v>18</v>
       </c>
-      <c r="Q44" s="13">
+      <c r="Q44" s="11">
         <v>0.141</v>
       </c>
       <c r="R44" s="2" t="s">
@@ -3172,106 +3522,1028 @@
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="C45" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="3">
+        <v>456.4</v>
+      </c>
+      <c r="F45" s="3">
+        <v>453.3</v>
+      </c>
+      <c r="G45" s="3">
+        <v>453.55</v>
+      </c>
+      <c r="H45" s="3">
+        <v>453.55</v>
+      </c>
+      <c r="I45" s="3">
+        <v>453.3</v>
+      </c>
+      <c r="J45" s="3">
+        <v>453.3</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N45" s="3">
+        <v>453.3</v>
+      </c>
+      <c r="O45" s="2">
+        <v>1</v>
+      </c>
+      <c r="P45" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="Q45" s="11">
+        <v>0.055</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" s="10" t="s">
+      <c r="B46" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E45" s="11">
-        <v>456.4</v>
-      </c>
-      <c r="F45" s="11">
-        <v>453.3</v>
-      </c>
-      <c r="G45" s="11">
-        <v>453.55</v>
-      </c>
-      <c r="H45" s="11">
-        <v>453.55</v>
-      </c>
-      <c r="I45" s="11">
-        <v>453.3</v>
-      </c>
-      <c r="J45" s="11">
-        <v>453.3</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L45" s="10" t="s">
+      <c r="E46" s="3">
+        <v>906.95</v>
+      </c>
+      <c r="F46" s="3">
+        <v>901.5</v>
+      </c>
+      <c r="G46" s="3">
+        <v>901.75</v>
+      </c>
+      <c r="H46" s="3">
+        <v>901.95</v>
+      </c>
+      <c r="I46" s="3">
+        <v>901.5</v>
+      </c>
+      <c r="J46" s="3">
+        <v>901.5</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N46" s="3">
+        <v>901.5</v>
+      </c>
+      <c r="O46" s="2">
+        <v>1</v>
+      </c>
+      <c r="P46" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="Q46" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10" t="s">
+      <c r="E47" s="3">
+        <v>1000.65</v>
+      </c>
+      <c r="F47" s="3">
+        <v>989.15</v>
+      </c>
+      <c r="G47" s="3">
+        <v>990.8</v>
+      </c>
+      <c r="H47" s="3">
+        <v>990.95</v>
+      </c>
+      <c r="I47" s="3">
+        <v>989.15</v>
+      </c>
+      <c r="J47" s="3">
+        <v>989.15</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="N47" s="3">
+        <v>989.15</v>
+      </c>
+      <c r="O47" s="2">
+        <v>1</v>
+      </c>
+      <c r="P47" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="Q47" s="11">
+        <v>0.182</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2165.4</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2156.5</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2159.4</v>
+      </c>
+      <c r="H48" s="3">
+        <v>2158.6</v>
+      </c>
+      <c r="I48" s="3">
+        <v>2156.5</v>
+      </c>
+      <c r="J48" s="3">
+        <v>2156.5</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="N48" s="3">
+        <v>2156.5</v>
+      </c>
+      <c r="O48" s="2">
+        <v>1</v>
+      </c>
+      <c r="P48" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="Q48" s="11">
+        <v>0.097</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7675.5</v>
+      </c>
+      <c r="F49" s="3">
+        <v>7647</v>
+      </c>
+      <c r="G49" s="3">
+        <v>7652</v>
+      </c>
+      <c r="H49" s="3">
+        <v>7653</v>
+      </c>
+      <c r="I49" s="3">
+        <v>7647</v>
+      </c>
+      <c r="J49" s="3">
+        <v>7647</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N49" s="3">
+        <v>7647</v>
+      </c>
+      <c r="O49" s="2">
+        <v>1</v>
+      </c>
+      <c r="P49" s="10">
+        <v>6</v>
+      </c>
+      <c r="Q49" s="11">
+        <v>0.078</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1018</v>
+      </c>
+      <c r="F50" s="7">
+        <v>1013.3</v>
+      </c>
+      <c r="G50" s="7">
+        <v>1013.9</v>
+      </c>
+      <c r="H50" s="7">
+        <v>1014.5</v>
+      </c>
+      <c r="I50" s="7">
+        <v>1013.3</v>
+      </c>
+      <c r="J50" s="7">
+        <v>1013.3</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="N50" s="7">
+        <v>1013.3</v>
+      </c>
+      <c r="O50" s="6">
+        <v>1</v>
+      </c>
+      <c r="P50" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="Q50" s="9">
+        <v>0.118</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E46" s="11">
-        <v>906.95</v>
-      </c>
-      <c r="F46" s="11">
-        <v>901.5</v>
-      </c>
-      <c r="G46" s="11">
-        <v>901.75</v>
-      </c>
-      <c r="H46" s="11">
-        <v>901.95</v>
-      </c>
-      <c r="I46" s="11">
-        <v>901.5</v>
-      </c>
-      <c r="J46" s="11">
-        <v>901.5</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="P48" s="15">
-        <v>-58.46</v>
-      </c>
-      <c r="R48" s="14" t="s">
+      <c r="E51" s="3">
+        <v>1746.1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1721.7</v>
+      </c>
+      <c r="G51" s="3">
+        <v>1725.9</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1725.7</v>
+      </c>
+      <c r="I51" s="3">
+        <v>1721.7</v>
+      </c>
+      <c r="J51" s="3">
+        <v>1721.7</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N51" s="3">
+        <v>1721.7</v>
+      </c>
+      <c r="O51" s="2">
+        <v>1</v>
+      </c>
+      <c r="P51" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q51" s="11">
+        <v>0.232</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>145</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1393.3</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1383.9</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1384.1</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1383.9</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1383.9</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1383.9</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="N52" s="3">
+        <v>1383.9</v>
+      </c>
+      <c r="O52" s="2">
+        <v>1</v>
+      </c>
+      <c r="P52" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="11">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E53" s="3">
+        <v>2203.5</v>
+      </c>
+      <c r="F53" s="3">
+        <v>2183.6</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2189</v>
+      </c>
+      <c r="H53" s="3">
+        <v>2188.5</v>
+      </c>
+      <c r="I53" s="3">
+        <v>2183.6</v>
+      </c>
+      <c r="J53" s="3">
+        <v>2183.6</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N53" s="3">
+        <v>2183.6</v>
+      </c>
+      <c r="O53" s="2">
+        <v>1</v>
+      </c>
+      <c r="P53" s="10">
+        <v>4.9</v>
+      </c>
+      <c r="Q53" s="11">
+        <v>0.224</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E54" s="3">
+        <v>539.45</v>
+      </c>
+      <c r="F54" s="3">
+        <v>532.15</v>
+      </c>
+      <c r="G54" s="3">
+        <v>538.85</v>
+      </c>
+      <c r="H54" s="3">
+        <v>539.05</v>
+      </c>
+      <c r="I54" s="3">
+        <v>532.15</v>
+      </c>
+      <c r="J54" s="3">
+        <v>545.95</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="N54" s="3">
+        <v>532.15</v>
+      </c>
+      <c r="O54" s="2">
+        <v>6</v>
+      </c>
+      <c r="P54" s="4">
+        <v>-6.9</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>-1.28</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2558</v>
+      </c>
+      <c r="F55" s="7">
+        <v>2537.7</v>
+      </c>
+      <c r="G55" s="7">
+        <v>2554.8</v>
+      </c>
+      <c r="H55" s="7">
+        <v>2554.8</v>
+      </c>
+      <c r="I55" s="7">
+        <v>2537.7</v>
+      </c>
+      <c r="J55" s="7">
+        <v>2571.9</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="N55" s="7">
+        <v>2571.9</v>
+      </c>
+      <c r="O55" s="6">
+        <v>1</v>
+      </c>
+      <c r="P55" s="8">
+        <v>17.1</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>0.669</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="13">
+        <v>372.35</v>
+      </c>
+      <c r="F56" s="13">
+        <v>370.75</v>
+      </c>
+      <c r="G56" s="13">
+        <v>372.3</v>
+      </c>
+      <c r="H56" s="13">
+        <v>372.3</v>
+      </c>
+      <c r="I56" s="13">
+        <v>370.75</v>
+      </c>
+      <c r="J56" s="13">
+        <v>373.85</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="12"/>
+      <c r="P56" s="12"/>
+      <c r="Q56" s="12"/>
+      <c r="R56" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E57" s="13">
+        <v>1976</v>
+      </c>
+      <c r="F57" s="13">
+        <v>1965.6</v>
+      </c>
+      <c r="G57" s="13">
+        <v>1966.6</v>
+      </c>
+      <c r="H57" s="13">
+        <v>1966.5</v>
+      </c>
+      <c r="I57" s="13">
+        <v>1965.6</v>
+      </c>
+      <c r="J57" s="13">
+        <v>1965.6</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="12"/>
+      <c r="P57" s="12"/>
+      <c r="Q57" s="12"/>
+      <c r="R57" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E58" s="13">
+        <v>1358.2</v>
+      </c>
+      <c r="F58" s="13">
+        <v>1351.2</v>
+      </c>
+      <c r="G58" s="13">
+        <v>1352.8</v>
+      </c>
+      <c r="H58" s="13">
+        <v>1352.7</v>
+      </c>
+      <c r="I58" s="13">
+        <v>1351.2</v>
+      </c>
+      <c r="J58" s="13">
+        <v>1351.2</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M58" s="12"/>
+      <c r="N58" s="12"/>
+      <c r="O58" s="12"/>
+      <c r="P58" s="12"/>
+      <c r="Q58" s="12"/>
+      <c r="R58" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="13">
+        <v>2041.8</v>
+      </c>
+      <c r="F59" s="13">
+        <v>2026.6</v>
+      </c>
+      <c r="G59" s="13">
+        <v>2028</v>
+      </c>
+      <c r="H59" s="13">
+        <v>2028</v>
+      </c>
+      <c r="I59" s="13">
+        <v>2026.6</v>
+      </c>
+      <c r="J59" s="13">
+        <v>2026.6</v>
+      </c>
+      <c r="K59" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L59" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M59" s="12"/>
+      <c r="N59" s="12"/>
+      <c r="O59" s="12"/>
+      <c r="P59" s="12"/>
+      <c r="Q59" s="12"/>
+      <c r="R59" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="13">
+        <v>12812</v>
+      </c>
+      <c r="F60" s="13">
+        <v>12739</v>
+      </c>
+      <c r="G60" s="13">
+        <v>12766</v>
+      </c>
+      <c r="H60" s="13">
+        <v>12766</v>
+      </c>
+      <c r="I60" s="13">
+        <v>12739</v>
+      </c>
+      <c r="J60" s="13">
+        <v>12739</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L60" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
+      <c r="O60" s="12"/>
+      <c r="P60" s="12"/>
+      <c r="Q60" s="12"/>
+      <c r="R60" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E61" s="13">
+        <v>6119</v>
+      </c>
+      <c r="F61" s="13">
+        <v>6086</v>
+      </c>
+      <c r="G61" s="13">
+        <v>6088</v>
+      </c>
+      <c r="H61" s="12"/>
+      <c r="I61" s="13">
+        <v>6086</v>
+      </c>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L61" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="12"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E62" s="13">
+        <v>4785</v>
+      </c>
+      <c r="F62" s="13">
+        <v>4741.9</v>
+      </c>
+      <c r="G62" s="13">
+        <v>4782.6</v>
+      </c>
+      <c r="H62" s="12"/>
+      <c r="I62" s="13">
+        <v>4741.9</v>
+      </c>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E63" s="13">
+        <v>1851.9</v>
+      </c>
+      <c r="F63" s="13">
+        <v>1842.2</v>
+      </c>
+      <c r="G63" s="13">
+        <v>1850</v>
+      </c>
+      <c r="H63" s="12"/>
+      <c r="I63" s="13">
+        <v>1842.2</v>
+      </c>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="12"/>
+      <c r="P63" s="12"/>
+      <c r="Q63" s="12"/>
+      <c r="R63" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E64" s="13">
+        <v>4245</v>
+      </c>
+      <c r="F64" s="13">
+        <v>4212</v>
+      </c>
+      <c r="G64" s="13">
+        <v>4245</v>
+      </c>
+      <c r="H64" s="12"/>
+      <c r="I64" s="13">
+        <v>4212</v>
+      </c>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
+      <c r="P64" s="12"/>
+      <c r="Q64" s="12"/>
+      <c r="R64" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="P66" s="15">
+        <v>159.92</v>
+      </c>
+      <c r="R66" s="14" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="288">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -217,376 +217,664 @@
     <t>NSE:DIVISLAB-EQ</t>
   </si>
   <si>
+    <t>2026-02-23 14:15</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BEAR_1771392600_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IRCTC-EQ_BULL_1771396200_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:IRCTC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ_BEAR_1771405200_1771472700</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ABB-EQ_BEAR_1771483500_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ABB-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:00</t>
+  </si>
+  <si>
+    <t>2026-02-20 09:15</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BEAR_1771473600_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ_BEAR_1771402500_1771484400</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 12:30</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:00</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BEAR_1771484400_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BEAR_1771386300_1771475400</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 10:00</t>
+  </si>
+  <si>
+    <t>2026-02-19 10:30</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ_BEAR_1771472700_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 15:15</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BEAR_1771386300_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1771479000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BEAR_1771478100_1771489800</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:30</t>
+  </si>
+  <si>
+    <t>NSE:HAL-EQ_BEAR_1771479900_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:HAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BEAR_1771392600_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1771481700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BEAR_1771474500_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BEAR_1771480800_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1771388100_1771491600</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:INDUSTOWER-EQ_BEAR_1771485300_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:INDUSTOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1771488000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1771479900_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BEAR_1771481700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BEAR_1771472700_1771489800</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1771479000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ_BEAR_1771488000_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BEAR_1771478100_1771484400</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BEAR_1771480800_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771476300_1771488900</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:45</t>
+  </si>
+  <si>
+    <t>2026-02-19 14:15</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BEAR_1771485300_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771488000</t>
+  </si>
+  <si>
+    <t>2026-02-19 13:30</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1771484400_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ZYDUSLIFE-EQ_BEAR_1771490700_1771493400</t>
+  </si>
+  <si>
+    <t>NSE:ZYDUSLIFE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BEAR_1771479900_1771560000</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 10:00</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1771475400_1771572600</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:00</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:30</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1771489800_1771570800</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 12:30</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ_BEAR_1771559100_1771571700</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:15</t>
+  </si>
+  <si>
+    <t>NSE:PHOENIXLTD-EQ_BEAR_1771473600_1771559100</t>
+  </si>
+  <si>
+    <t>NSE:PHOENIXLTD-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 09:45</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BEAR_1771481700_1771561800</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 10:30</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BEAR_1771472700_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:45</t>
+  </si>
+  <si>
+    <t>NSE:JUBLFOOD-EQ_BULL_1771571700_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:JUBLFOOD-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:00</t>
+  </si>
+  <si>
+    <t>NSE:TIINDIA-EQ_BULL_1771475400_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:TIINDIA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BULL_1771565400_1771574400</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:15</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1771481700_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ_BEAR_1771482600_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1771482600_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BEAR_1771488000_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:30</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:00</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BULL_1771564500_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 48 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:IIFL-EQ_BEAR_1771392600_1771472700</t>
-  </si>
-  <si>
-    <t>NSE:IIFL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IRCTC-EQ_BULL_1771396200_1771472700</t>
-  </si>
-  <si>
-    <t>NSE:IRCTC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PIDILITIND-EQ_BEAR_1771405200_1771472700</t>
-  </si>
-  <si>
-    <t>NSE:PIDILITIND-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ABB-EQ_BEAR_1771483500_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:ABB-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 15:00</t>
-  </si>
-  <si>
-    <t>2026-02-20 09:15</t>
-  </si>
-  <si>
-    <t>NSE:ADANIPORTS-EQ_BEAR_1771473600_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:ADANIPORTS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BHARTIARTL-EQ_BEAR_1771402500_1771484400</t>
-  </si>
-  <si>
-    <t>NSE:BHARTIARTL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 12:30</t>
-  </si>
-  <si>
-    <t>2026-02-19 13:00</t>
-  </si>
-  <si>
-    <t>NSE:CIPLA-EQ_BEAR_1771484400_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:CIPLA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ_BEAR_1771386300_1771475400</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 10:00</t>
-  </si>
-  <si>
-    <t>2026-02-19 10:30</t>
-  </si>
-  <si>
-    <t>NSE:CONCOR-EQ_BEAR_1771472700_1771494300</t>
-  </si>
-  <si>
-    <t>NSE:CONCOR-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 15:15</t>
-  </si>
-  <si>
-    <t>NSE:DABUR-EQ_BEAR_1771386300_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:DABUR-EQ</t>
-  </si>
-  <si>
-    <t>NSE:EXIDEIND-EQ_BEAR_1771479000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:EXIDEIND-EQ</t>
-  </si>
-  <si>
-    <t>NSE:GODREJCP-EQ_BEAR_1771478100_1771489800</t>
-  </si>
-  <si>
-    <t>NSE:GODREJCP-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 14:00</t>
-  </si>
-  <si>
-    <t>2026-02-19 14:30</t>
-  </si>
-  <si>
-    <t>NSE:HAL-EQ_BEAR_1771479900_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:HAL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IIFL-EQ_BEAR_1771392600_1771494300</t>
-  </si>
-  <si>
-    <t>NSE:IEX-EQ_BEAR_1771481700_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:IEX-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IRFC-EQ_BEAR_1771474500_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:IRFC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ_BEAR_1771480800_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ_BEAR_1771388100_1771491600</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:INDUSTOWER-EQ_BEAR_1771485300_1771494300</t>
-  </si>
-  <si>
-    <t>NSE:INDUSTOWER-EQ</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BEAR_1771488000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ</t>
-  </si>
-  <si>
-    <t>NSE:KAYNES-EQ_BEAR_1771479900_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:KAYNES-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LICI-EQ_BEAR_1771481700_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:NTPC-EQ_BEAR_1771472700_1771489800</t>
-  </si>
-  <si>
-    <t>NSE:NTPC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BEAR_1771479000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PPLPHARMA-EQ_BEAR_1771488000_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:PPLPHARMA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:RELIANCE-EQ_BEAR_1771478100_1771484400</t>
-  </si>
-  <si>
-    <t>NSE:RELIANCE-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SHRIRAMFIN-EQ_BEAR_1771480800_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:SHRIRAMFIN-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ_BEAR_1771476300_1771488900</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-19 13:45</t>
-  </si>
-  <si>
-    <t>2026-02-19 14:15</t>
-  </si>
-  <si>
-    <t>NSE:TMPV-EQ_BEAR_1771485300_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:TMPV-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771488000</t>
-  </si>
-  <si>
-    <t>2026-02-19 13:30</t>
-  </si>
-  <si>
-    <t>NSE:VBL-EQ_BEAR_1771484400_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:VBL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ZYDUSLIFE-EQ_BEAR_1771490700_1771493400</t>
-  </si>
-  <si>
-    <t>NSE:ZYDUSLIFE-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENSOL-EQ_BEAR_1771479900_1771560000</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENSOL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 10:00</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENT-EQ_BEAR_1771475400_1771572600</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENT-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 13:00</t>
-  </si>
-  <si>
-    <t>2026-02-20 13:30</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ_BEAR_1771489800_1771570800</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 12:30</t>
-  </si>
-  <si>
-    <t>NSE:KFINTECH-EQ_BEAR_1771559100_1771571700</t>
-  </si>
-  <si>
-    <t>NSE:KFINTECH-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 12:45</t>
-  </si>
-  <si>
-    <t>2026-02-20 13:15</t>
-  </si>
-  <si>
-    <t>NSE:PHOENIXLTD-EQ_BEAR_1771473600_1771559100</t>
-  </si>
-  <si>
-    <t>NSE:PHOENIXLTD-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 09:45</t>
-  </si>
-  <si>
-    <t>NSE:UNITDSPR-EQ_BEAR_1771481700_1771561800</t>
-  </si>
-  <si>
-    <t>NSE:UNITDSPR-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 10:30</t>
-  </si>
-  <si>
-    <t>NSE:APLAPOLLO-EQ_BEAR_1771472700_1771573500</t>
-  </si>
-  <si>
-    <t>NSE:APLAPOLLO-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 13:45</t>
-  </si>
-  <si>
-    <t>NSE:JUBLFOOD-EQ_BULL_1771571700_1771573500</t>
-  </si>
-  <si>
-    <t>NSE:JUBLFOOD-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 15:00</t>
-  </si>
-  <si>
-    <t>NSE:TIINDIA-EQ_BULL_1771475400_1771573500</t>
-  </si>
-  <si>
-    <t>NSE:TIINDIA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:NTPC-EQ_BULL_1771565400_1771574400</t>
-  </si>
-  <si>
-    <t>Checked 6 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:BLUESTARCO-EQ_BEAR_1771481700_1771579800</t>
+    <t>Checked 24 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ_BEAR_1771320600_1771565400</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:00</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:30</t>
+  </si>
+  <si>
+    <t>NSE:HCLTECH-EQ_BEAR_1771317900_1771559100</t>
+  </si>
+  <si>
+    <t>NSE:HCLTECH-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HDFCBANK-EQ_BEAR_1771320600_1771572600</t>
+  </si>
+  <si>
+    <t>NSE:HDFCBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HDFCLIFE-EQ_BULL_1771229700_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:HDFCLIFE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1771307100_1771475400</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ASHOKLEY-EQ_BULL_1771570800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:ASHOKLEY-EQ</t>
+  </si>
+  <si>
+    <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ_BULL_1771564500_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:30</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:45</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:45</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:30</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:45</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:30</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1771560000_1771826400</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:00</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1771571700_1771828200</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:45</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:45</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:00</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ_BULL_1771569000_1771830000</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1771566300_1771832700</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:15</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771821000_1771835400</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:00</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1771819200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:45</t>
+  </si>
+  <si>
+    <t>Checked 1 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:00</t>
   </si>
   <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>NSE:INFY-EQ_BEAR_1771482600_1771579800</t>
-  </si>
-  <si>
-    <t>NSE:INFY-EQ</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ_BEAR_1771482600_1771579800</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771579800</t>
-  </si>
-  <si>
-    <t>NSE:BRITANNIA-EQ_BEAR_1771488000_1771580700</t>
-  </si>
-  <si>
-    <t>NSE:BRITANNIA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 15:15</t>
+    <t>NSE:APOLLOHOSP-EQ_BULL_1771576200_1771839000</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ</t>
   </si>
   <si>
     <t>Entry candle not yet available — trade not entered</t>
   </si>
   <si>
-    <t>NSE:KEI-EQ_BULL_1771563600_1771580700</t>
-  </si>
-  <si>
-    <t>NSE:KEI-EQ</t>
-  </si>
-  <si>
-    <t>NSE:MFSL-EQ_BULL_1771564500_1771580700</t>
-  </si>
-  <si>
-    <t>NSE:MFSL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771580700</t>
-  </si>
-  <si>
-    <t>NSE:TORNTPHARM-EQ</t>
-  </si>
-  <si>
-    <t>SUMMARY — 12W / 41L / 10 OPEN  |  Win Rate: 22.6%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 53 of 63</t>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771839900</t>
+  </si>
+  <si>
+    <t>SUMMARY — 21W / 64L / 18 OPEN  |  Win Rate: 24.7%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 85 of 103</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1796,57 +2084,67 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="3">
         <v>6327.5</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="3">
         <v>6251</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="3">
         <v>6325</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="3">
         <v>6324.5</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="3">
         <v>6251</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="3">
         <v>6398</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="12" t="s">
+      <c r="K14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12" t="s">
+      <c r="N14" s="3">
+        <v>6251</v>
+      </c>
+      <c r="O14" s="2">
         <v>69</v>
+      </c>
+      <c r="P14" s="4">
+        <v>-73.5</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>-1.162</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>64</v>
@@ -1899,10 +2197,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>20</v>
@@ -1955,10 +2253,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>64</v>
@@ -2011,16 +2309,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" s="3">
         <v>5770.5</v>
@@ -2047,7 +2345,7 @@
         <v>23</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N18" s="3">
         <v>5710</v>
@@ -2067,16 +2365,16 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" s="3">
         <v>1523.8</v>
@@ -2103,7 +2401,7 @@
         <v>23</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N19" s="3">
         <v>1512.1</v>
@@ -2123,16 +2421,16 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" s="3">
         <v>2008.1</v>
@@ -2159,7 +2457,7 @@
         <v>23</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N20" s="3">
         <v>2000.2</v>
@@ -2179,16 +2477,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" s="3">
         <v>1338.4</v>
@@ -2215,7 +2513,7 @@
         <v>23</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N21" s="3">
         <v>1330.8</v>
@@ -2235,16 +2533,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="7">
         <v>417.4</v>
@@ -2271,7 +2569,7 @@
         <v>33</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N22" s="7">
         <v>415.95</v>
@@ -2291,16 +2589,16 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" s="3">
         <v>509.55</v>
@@ -2347,16 +2645,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" s="3">
         <v>504.45</v>
@@ -2383,7 +2681,7 @@
         <v>23</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N24" s="3">
         <v>501.45</v>
@@ -2403,16 +2701,16 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25" s="3">
         <v>335.7</v>
@@ -2439,7 +2737,7 @@
         <v>23</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N25" s="3">
         <v>332.05</v>
@@ -2459,16 +2757,16 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
         <v>1198.4</v>
@@ -2495,7 +2793,7 @@
         <v>23</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N26" s="3">
         <v>1194.4</v>
@@ -2515,16 +2813,16 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" s="3">
         <v>4164.3</v>
@@ -2551,7 +2849,7 @@
         <v>23</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N27" s="3">
         <v>4134.9</v>
@@ -2571,16 +2869,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E28" s="3">
         <v>498.25</v>
@@ -2627,16 +2925,16 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" s="3">
         <v>124.71</v>
@@ -2663,7 +2961,7 @@
         <v>23</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N29" s="3">
         <v>123.71</v>
@@ -2683,16 +2981,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" s="3">
         <v>112.28</v>
@@ -2719,7 +3017,7 @@
         <v>23</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N30" s="3">
         <v>111.52</v>
@@ -2739,16 +3037,16 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" s="3">
         <v>126.77</v>
@@ -2775,7 +3073,7 @@
         <v>23</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N31" s="3">
         <v>126</v>
@@ -2795,16 +3093,16 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E32" s="3">
         <v>168.95</v>
@@ -2831,7 +3129,7 @@
         <v>23</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N32" s="3">
         <v>168.48</v>
@@ -2851,16 +3149,16 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E33" s="3">
         <v>474.85</v>
@@ -2907,16 +3205,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E34" s="3">
         <v>485.2</v>
@@ -2943,7 +3241,7 @@
         <v>23</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N34" s="3">
         <v>478.5</v>
@@ -2963,16 +3261,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E35" s="3">
         <v>3919</v>
@@ -2999,7 +3297,7 @@
         <v>23</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N35" s="3">
         <v>3873.3</v>
@@ -3019,7 +3317,7 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>40</v>
@@ -3028,7 +3326,7 @@
         <v>64</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E36" s="3">
         <v>870.15</v>
@@ -3055,7 +3353,7 @@
         <v>23</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N36" s="3">
         <v>862.55</v>
@@ -3075,16 +3373,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E37" s="3">
         <v>365.2</v>
@@ -3111,7 +3409,7 @@
         <v>23</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N37" s="3">
         <v>363.15</v>
@@ -3131,16 +3429,16 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E38" s="3">
         <v>613.6</v>
@@ -3167,7 +3465,7 @@
         <v>23</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N38" s="3">
         <v>606.25</v>
@@ -3187,16 +3485,16 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E39" s="3">
         <v>164.26</v>
@@ -3223,7 +3521,7 @@
         <v>23</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N39" s="3">
         <v>162.65</v>
@@ -3243,16 +3541,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E40" s="3">
         <v>1421.7</v>
@@ -3279,7 +3577,7 @@
         <v>23</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N40" s="3">
         <v>1416.7</v>
@@ -3299,16 +3597,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E41" s="3">
         <v>1062.2</v>
@@ -3335,7 +3633,7 @@
         <v>23</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N41" s="3">
         <v>1053.5</v>
@@ -3355,16 +3653,16 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E42" s="3">
         <v>158.62</v>
@@ -3391,7 +3689,7 @@
         <v>23</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N42" s="3">
         <v>158.22</v>
@@ -3411,16 +3709,16 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E43" s="3">
         <v>378.55</v>
@@ -3447,7 +3745,7 @@
         <v>23</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N43" s="3">
         <v>375.75</v>
@@ -3467,7 +3765,7 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>57</v>
@@ -3476,7 +3774,7 @@
         <v>64</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E44" s="3">
         <v>12794</v>
@@ -3503,7 +3801,7 @@
         <v>23</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N44" s="3">
         <v>12734</v>
@@ -3523,16 +3821,16 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E45" s="3">
         <v>456.4</v>
@@ -3559,7 +3857,7 @@
         <v>23</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N45" s="3">
         <v>453.3</v>
@@ -3579,16 +3877,16 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E46" s="3">
         <v>906.95</v>
@@ -3615,7 +3913,7 @@
         <v>23</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N46" s="3">
         <v>901.5</v>
@@ -3635,10 +3933,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>64</v>
@@ -3671,7 +3969,7 @@
         <v>23</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N47" s="3">
         <v>989.15</v>
@@ -3691,16 +3989,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E48" s="3">
         <v>2165.4</v>
@@ -3727,7 +4025,7 @@
         <v>23</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N48" s="3">
         <v>2156.5</v>
@@ -3747,16 +4045,16 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E49" s="3">
         <v>7675.5</v>
@@ -3768,7 +4066,7 @@
         <v>7652</v>
       </c>
       <c r="H49" s="3">
-        <v>7653</v>
+        <v>7652</v>
       </c>
       <c r="I49" s="3">
         <v>7647</v>
@@ -3783,7 +4081,7 @@
         <v>23</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N49" s="3">
         <v>7647</v>
@@ -3792,10 +4090,10 @@
         <v>1</v>
       </c>
       <c r="P49" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q49" s="11">
-        <v>0.078</v>
+        <v>0.065</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>25</v>
@@ -3803,16 +4101,16 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E50" s="7">
         <v>1018</v>
@@ -3839,7 +4137,7 @@
         <v>33</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N50" s="7">
         <v>1013.3</v>
@@ -3859,16 +4157,16 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E51" s="3">
         <v>1746.1</v>
@@ -3895,7 +4193,7 @@
         <v>23</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N51" s="3">
         <v>1721.7</v>
@@ -3915,16 +4213,16 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E52" s="3">
         <v>1393.3</v>
@@ -3951,7 +4249,7 @@
         <v>23</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N52" s="3">
         <v>1383.9</v>
@@ -3971,16 +4269,16 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E53" s="3">
         <v>2203.5</v>
@@ -4007,7 +4305,7 @@
         <v>23</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N53" s="3">
         <v>2183.6</v>
@@ -4027,16 +4325,16 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E54" s="3">
         <v>539.45</v>
@@ -4063,7 +4361,7 @@
         <v>23</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N54" s="3">
         <v>532.15</v>
@@ -4083,16 +4381,16 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E55" s="7">
         <v>2558</v>
@@ -4119,7 +4417,7 @@
         <v>33</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N55" s="7">
         <v>2571.9</v>
@@ -4138,331 +4436,409 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" s="7">
+        <v>372.35</v>
+      </c>
+      <c r="F56" s="7">
+        <v>370.75</v>
+      </c>
+      <c r="G56" s="7">
+        <v>372.3</v>
+      </c>
+      <c r="H56" s="7">
+        <v>372.3</v>
+      </c>
+      <c r="I56" s="7">
+        <v>370.75</v>
+      </c>
+      <c r="J56" s="7">
+        <v>373.85</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M56" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="12" t="s">
+      <c r="N56" s="7">
+        <v>373.85</v>
+      </c>
+      <c r="O56" s="6">
+        <v>7</v>
+      </c>
+      <c r="P56" s="8">
+        <v>1.55</v>
+      </c>
+      <c r="Q56" s="9">
+        <v>0.416</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1976</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1965.6</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1966.6</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1966.6</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1965.6</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1965.6</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N57" s="3">
+        <v>1965.6</v>
+      </c>
+      <c r="O57" s="2">
+        <v>1</v>
+      </c>
+      <c r="P57" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="11">
+        <v>0.051</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1358.2</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1351.2</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1352.8</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1352.7</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1351.2</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1351.2</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N58" s="3">
+        <v>1351.2</v>
+      </c>
+      <c r="O58" s="2">
+        <v>1</v>
+      </c>
+      <c r="P58" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="Q58" s="11">
+        <v>0.111</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2041.8</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2026.6</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2028</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2028</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2026.6</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2026.6</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N59" s="3">
+        <v>2026.6</v>
+      </c>
+      <c r="O59" s="2">
+        <v>1</v>
+      </c>
+      <c r="P59" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="Q59" s="11">
+        <v>0.069</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E60" s="3">
+        <v>12812</v>
+      </c>
+      <c r="F60" s="3">
+        <v>12739</v>
+      </c>
+      <c r="G60" s="3">
+        <v>12766</v>
+      </c>
+      <c r="H60" s="3">
+        <v>12766</v>
+      </c>
+      <c r="I60" s="3">
+        <v>12739</v>
+      </c>
+      <c r="J60" s="3">
+        <v>12739</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="N60" s="3">
+        <v>12739</v>
+      </c>
+      <c r="O60" s="2">
+        <v>1</v>
+      </c>
+      <c r="P60" s="10">
+        <v>27</v>
+      </c>
+      <c r="Q60" s="11">
+        <v>0.211</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6119</v>
+      </c>
+      <c r="F61" s="3">
+        <v>6086</v>
+      </c>
+      <c r="G61" s="3">
+        <v>6088</v>
+      </c>
+      <c r="H61" s="3">
+        <v>6136</v>
+      </c>
+      <c r="I61" s="3">
+        <v>6086</v>
+      </c>
+      <c r="J61" s="3">
+        <v>6086</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="N61" s="3">
+        <v>6086</v>
+      </c>
+      <c r="O61" s="2">
+        <v>1</v>
+      </c>
+      <c r="P61" s="10">
+        <v>50</v>
+      </c>
+      <c r="Q61" s="11">
+        <v>0.815</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" s="13">
-        <v>372.35</v>
-      </c>
-      <c r="F56" s="13">
-        <v>370.75</v>
-      </c>
-      <c r="G56" s="13">
-        <v>372.3</v>
-      </c>
-      <c r="H56" s="13">
-        <v>372.3</v>
-      </c>
-      <c r="I56" s="13">
-        <v>370.75</v>
-      </c>
-      <c r="J56" s="13">
-        <v>373.85</v>
-      </c>
-      <c r="K56" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L56" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M56" s="12"/>
-      <c r="N56" s="12"/>
-      <c r="O56" s="12"/>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
-      <c r="R56" s="12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E57" s="13">
-        <v>1976</v>
-      </c>
-      <c r="F57" s="13">
-        <v>1965.6</v>
-      </c>
-      <c r="G57" s="13">
-        <v>1966.6</v>
-      </c>
-      <c r="H57" s="13">
-        <v>1966.5</v>
-      </c>
-      <c r="I57" s="13">
-        <v>1965.6</v>
-      </c>
-      <c r="J57" s="13">
-        <v>1965.6</v>
-      </c>
-      <c r="K57" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L57" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12"/>
-      <c r="Q57" s="12"/>
-      <c r="R57" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E58" s="13">
-        <v>1358.2</v>
-      </c>
-      <c r="F58" s="13">
-        <v>1351.2</v>
-      </c>
-      <c r="G58" s="13">
-        <v>1352.8</v>
-      </c>
-      <c r="H58" s="13">
-        <v>1352.7</v>
-      </c>
-      <c r="I58" s="13">
-        <v>1351.2</v>
-      </c>
-      <c r="J58" s="13">
-        <v>1351.2</v>
-      </c>
-      <c r="K58" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L58" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M58" s="12"/>
-      <c r="N58" s="12"/>
-      <c r="O58" s="12"/>
-      <c r="P58" s="12"/>
-      <c r="Q58" s="12"/>
-      <c r="R58" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E59" s="13">
-        <v>2041.8</v>
-      </c>
-      <c r="F59" s="13">
-        <v>2026.6</v>
-      </c>
-      <c r="G59" s="13">
-        <v>2028</v>
-      </c>
-      <c r="H59" s="13">
-        <v>2028</v>
-      </c>
-      <c r="I59" s="13">
-        <v>2026.6</v>
-      </c>
-      <c r="J59" s="13">
-        <v>2026.6</v>
-      </c>
-      <c r="K59" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L59" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M59" s="12"/>
-      <c r="N59" s="12"/>
-      <c r="O59" s="12"/>
-      <c r="P59" s="12"/>
-      <c r="Q59" s="12"/>
-      <c r="R59" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E60" s="13">
-        <v>12812</v>
-      </c>
-      <c r="F60" s="13">
-        <v>12739</v>
-      </c>
-      <c r="G60" s="13">
-        <v>12766</v>
-      </c>
-      <c r="H60" s="13">
-        <v>12766</v>
-      </c>
-      <c r="I60" s="13">
-        <v>12739</v>
-      </c>
-      <c r="J60" s="13">
-        <v>12739</v>
-      </c>
-      <c r="K60" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L60" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M60" s="12"/>
-      <c r="N60" s="12"/>
-      <c r="O60" s="12"/>
-      <c r="P60" s="12"/>
-      <c r="Q60" s="12"/>
-      <c r="R60" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
+      <c r="D62" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="E61" s="13">
-        <v>6119</v>
-      </c>
-      <c r="F61" s="13">
-        <v>6086</v>
-      </c>
-      <c r="G61" s="13">
-        <v>6088</v>
-      </c>
-      <c r="H61" s="12"/>
-      <c r="I61" s="13">
-        <v>6086</v>
-      </c>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L61" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M61" s="12"/>
-      <c r="N61" s="12"/>
-      <c r="O61" s="12"/>
-      <c r="P61" s="12"/>
-      <c r="Q61" s="12"/>
-      <c r="R61" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
+      <c r="E62" s="3">
+        <v>4785</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4741.9</v>
+      </c>
+      <c r="G62" s="3">
+        <v>4782.6</v>
+      </c>
+      <c r="H62" s="3">
+        <v>4806</v>
+      </c>
+      <c r="I62" s="3">
+        <v>4741.9</v>
+      </c>
+      <c r="J62" s="3">
+        <v>4870.1</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M62" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="E62" s="13">
-        <v>4785</v>
-      </c>
-      <c r="F62" s="13">
+      <c r="N62" s="3">
         <v>4741.9</v>
       </c>
-      <c r="G62" s="13">
-        <v>4782.6</v>
-      </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="13">
-        <v>4741.9</v>
-      </c>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L62" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="M62" s="12"/>
-      <c r="N62" s="12"/>
-      <c r="O62" s="12"/>
-      <c r="P62" s="12"/>
-      <c r="Q62" s="12"/>
-      <c r="R62" s="12" t="s">
-        <v>183</v>
+      <c r="O62" s="2">
+        <v>7</v>
+      </c>
+      <c r="P62" s="4">
+        <v>-64.1</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>-1.334</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>186</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>187</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E63" s="13">
         <v>1851.9</v>
@@ -4473,16 +4849,20 @@
       <c r="G63" s="13">
         <v>1850</v>
       </c>
-      <c r="H63" s="12"/>
+      <c r="H63" s="13">
+        <v>1868.3</v>
+      </c>
       <c r="I63" s="13">
         <v>1842.2</v>
       </c>
-      <c r="J63" s="12"/>
+      <c r="J63" s="13">
+        <v>1894.4</v>
+      </c>
       <c r="K63" s="12" t="s">
         <v>22</v>
       </c>
       <c r="L63" s="12" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="M63" s="12"/>
       <c r="N63" s="12"/>
@@ -4490,21 +4870,21 @@
       <c r="P63" s="12"/>
       <c r="Q63" s="12"/>
       <c r="R63" s="12" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E64" s="13">
         <v>4245</v>
@@ -4515,16 +4895,20 @@
       <c r="G64" s="13">
         <v>4245</v>
       </c>
-      <c r="H64" s="12"/>
+      <c r="H64" s="13">
+        <v>4276.1</v>
+      </c>
       <c r="I64" s="13">
         <v>4212</v>
       </c>
-      <c r="J64" s="12"/>
+      <c r="J64" s="13">
+        <v>4340.2</v>
+      </c>
       <c r="K64" s="12" t="s">
         <v>22</v>
       </c>
       <c r="L64" s="12" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="M64" s="12"/>
       <c r="N64" s="12"/>
@@ -4532,18 +4916,2086 @@
       <c r="P64" s="12"/>
       <c r="Q64" s="12"/>
       <c r="R64" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E65" s="3">
+        <v>11152</v>
+      </c>
+      <c r="F65" s="3">
+        <v>11074</v>
+      </c>
+      <c r="G65" s="3">
+        <v>11081</v>
+      </c>
+      <c r="H65" s="3">
+        <v>11080</v>
+      </c>
+      <c r="I65" s="3">
+        <v>11074</v>
+      </c>
+      <c r="J65" s="3">
+        <v>11074</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="N65" s="3">
+        <v>11074</v>
+      </c>
+      <c r="O65" s="2">
+        <v>1</v>
+      </c>
+      <c r="P65" s="10">
+        <v>6</v>
+      </c>
+      <c r="Q65" s="11">
+        <v>0.054</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1447.5</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1431</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1433.8</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1433.7</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1431</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1431</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="N66" s="3">
+        <v>1431</v>
+      </c>
+      <c r="O66" s="2">
+        <v>1</v>
+      </c>
+      <c r="P66" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="Q66" s="11">
+        <v>0.188</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E67" s="3">
+        <v>911.9</v>
+      </c>
+      <c r="F67" s="3">
+        <v>908.4</v>
+      </c>
+      <c r="G67" s="3">
+        <v>909.4</v>
+      </c>
+      <c r="H67" s="3">
+        <v>909.4</v>
+      </c>
+      <c r="I67" s="3">
+        <v>908.4</v>
+      </c>
+      <c r="J67" s="3">
+        <v>908.4</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N67" s="3">
+        <v>908.4</v>
+      </c>
+      <c r="O67" s="2">
+        <v>1</v>
+      </c>
+      <c r="P67" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="11">
+        <v>0.11</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68" s="3">
+        <v>734.85</v>
+      </c>
+      <c r="F68" s="3">
+        <v>731.2</v>
+      </c>
+      <c r="G68" s="3">
+        <v>734.45</v>
+      </c>
+      <c r="H68" s="3">
+        <v>733.15</v>
+      </c>
+      <c r="I68" s="3">
+        <v>731.2</v>
+      </c>
+      <c r="J68" s="3">
+        <v>735.1</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N68" s="3">
+        <v>731.2</v>
+      </c>
+      <c r="O68" s="2">
+        <v>1</v>
+      </c>
+      <c r="P68" s="4">
+        <v>-1.95</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>-0.266</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E69" s="3">
+        <v>414</v>
+      </c>
+      <c r="F69" s="3">
+        <v>412.05</v>
+      </c>
+      <c r="G69" s="3">
+        <v>412.15</v>
+      </c>
+      <c r="H69" s="3">
+        <v>412.15</v>
+      </c>
+      <c r="I69" s="3">
+        <v>412.05</v>
+      </c>
+      <c r="J69" s="3">
+        <v>412.05</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N69" s="3">
+        <v>412.05</v>
+      </c>
+      <c r="O69" s="2">
+        <v>1</v>
+      </c>
+      <c r="P69" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="Q69" s="11">
+        <v>0.024</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E70" s="13">
+        <v>211.13</v>
+      </c>
+      <c r="F70" s="13">
+        <v>208.96</v>
+      </c>
+      <c r="G70" s="13">
+        <v>210.79</v>
+      </c>
+      <c r="H70" s="13">
+        <v>210.76</v>
+      </c>
+      <c r="I70" s="13">
+        <v>208.96</v>
+      </c>
+      <c r="J70" s="13">
+        <v>212.56</v>
+      </c>
+      <c r="K70" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L70" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
+      <c r="P70" s="12"/>
+      <c r="Q70" s="12"/>
+      <c r="R70" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E71" s="13">
+        <v>1397.6</v>
+      </c>
+      <c r="F71" s="13">
+        <v>1380.2</v>
+      </c>
+      <c r="G71" s="13">
+        <v>1396.5</v>
+      </c>
+      <c r="H71" s="13">
+        <v>1396.4</v>
+      </c>
+      <c r="I71" s="13">
+        <v>1380.2</v>
+      </c>
+      <c r="J71" s="13">
+        <v>1412.6</v>
+      </c>
+      <c r="K71" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L71" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="12"/>
+      <c r="P71" s="12"/>
+      <c r="Q71" s="12"/>
+      <c r="R71" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E72" s="7">
+        <v>1040</v>
+      </c>
+      <c r="F72" s="7">
+        <v>1031.95</v>
+      </c>
+      <c r="G72" s="7">
+        <v>1037.2</v>
+      </c>
+      <c r="H72" s="7">
+        <v>1037</v>
+      </c>
+      <c r="I72" s="7">
+        <v>1031.95</v>
+      </c>
+      <c r="J72" s="7">
+        <v>1042.05</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="N72" s="7">
+        <v>1042.05</v>
+      </c>
+      <c r="O72" s="6">
+        <v>12</v>
+      </c>
+      <c r="P72" s="8">
+        <v>5.05</v>
+      </c>
+      <c r="Q72" s="9">
+        <v>0.487</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E73" s="13">
+        <v>174.38</v>
+      </c>
+      <c r="F73" s="13">
+        <v>171.83</v>
+      </c>
+      <c r="G73" s="13">
+        <v>174.23</v>
+      </c>
+      <c r="H73" s="13">
+        <v>174.3</v>
+      </c>
+      <c r="I73" s="13">
+        <v>171.83</v>
+      </c>
+      <c r="J73" s="13">
+        <v>176.77</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M73" s="12"/>
+      <c r="N73" s="12"/>
+      <c r="O73" s="12"/>
+      <c r="P73" s="12"/>
+      <c r="Q73" s="12"/>
+      <c r="R73" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" s="13">
+        <v>24170</v>
+      </c>
+      <c r="F74" s="13">
+        <v>23827</v>
+      </c>
+      <c r="G74" s="13">
+        <v>24170</v>
+      </c>
+      <c r="H74" s="13">
+        <v>24151</v>
+      </c>
+      <c r="I74" s="13">
+        <v>23827</v>
+      </c>
+      <c r="J74" s="13">
+        <v>24475</v>
+      </c>
+      <c r="K74" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M74" s="12"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="12"/>
+      <c r="Q74" s="12"/>
+      <c r="R74" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="3">
+        <v>1230</v>
+      </c>
+      <c r="F75" s="3">
+        <v>1219.1</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1223.7</v>
+      </c>
+      <c r="H75" s="3">
+        <v>1224</v>
+      </c>
+      <c r="I75" s="3">
+        <v>1219.1</v>
+      </c>
+      <c r="J75" s="3">
+        <v>1228.9</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="N75" s="3">
+        <v>1219.1</v>
+      </c>
+      <c r="O75" s="2">
+        <v>1</v>
+      </c>
+      <c r="P75" s="4">
+        <v>-4.9</v>
+      </c>
+      <c r="Q75" s="5">
+        <v>-0.4</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" s="3">
+        <v>498.95</v>
+      </c>
+      <c r="F76" s="3">
+        <v>492.05</v>
+      </c>
+      <c r="G76" s="3">
+        <v>495.95</v>
+      </c>
+      <c r="H76" s="3">
+        <v>495.8</v>
+      </c>
+      <c r="I76" s="3">
+        <v>492.05</v>
+      </c>
+      <c r="J76" s="3">
+        <v>499.55</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="N76" s="3">
+        <v>492.05</v>
+      </c>
+      <c r="O76" s="2">
+        <v>1</v>
+      </c>
+      <c r="P76" s="4">
+        <v>-3.75</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>-0.756</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E77" s="3">
+        <v>303</v>
+      </c>
+      <c r="F77" s="3">
+        <v>298.4</v>
+      </c>
+      <c r="G77" s="3">
+        <v>301.95</v>
+      </c>
+      <c r="H77" s="3">
+        <v>302.2</v>
+      </c>
+      <c r="I77" s="3">
+        <v>298.4</v>
+      </c>
+      <c r="J77" s="3">
+        <v>306</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="N77" s="3">
+        <v>298.4</v>
+      </c>
+      <c r="O77" s="2">
+        <v>9</v>
+      </c>
+      <c r="P77" s="4">
+        <v>-3.8</v>
+      </c>
+      <c r="Q77" s="5">
+        <v>-1.257</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E78" s="13">
+        <v>1311.2</v>
+      </c>
+      <c r="F78" s="13">
+        <v>1295.5</v>
+      </c>
+      <c r="G78" s="13">
+        <v>1309.7</v>
+      </c>
+      <c r="H78" s="13">
+        <v>1309.8</v>
+      </c>
+      <c r="I78" s="13">
+        <v>1295.5</v>
+      </c>
+      <c r="J78" s="13">
+        <v>1324.1</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L78" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
+      <c r="O78" s="12"/>
+      <c r="P78" s="12"/>
+      <c r="Q78" s="12"/>
+      <c r="R78" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79" s="7">
+        <v>313.9</v>
+      </c>
+      <c r="F79" s="7">
+        <v>310</v>
+      </c>
+      <c r="G79" s="7">
+        <v>313.15</v>
+      </c>
+      <c r="H79" s="7">
+        <v>313.05</v>
+      </c>
+      <c r="I79" s="7">
+        <v>310</v>
+      </c>
+      <c r="J79" s="7">
+        <v>316.1</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N79" s="7">
+        <v>316.1</v>
+      </c>
+      <c r="O79" s="6">
+        <v>8</v>
+      </c>
+      <c r="P79" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>0.974</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E80" s="13">
+        <v>2104.9</v>
+      </c>
+      <c r="F80" s="13">
+        <v>2072.2</v>
+      </c>
+      <c r="G80" s="13">
+        <v>2104.3</v>
+      </c>
+      <c r="H80" s="13">
+        <v>2104.9</v>
+      </c>
+      <c r="I80" s="13">
+        <v>2072.2</v>
+      </c>
+      <c r="J80" s="13">
+        <v>2137.6</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L80" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
+      <c r="O80" s="12"/>
+      <c r="P80" s="12"/>
+      <c r="Q80" s="12"/>
+      <c r="R80" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E81" s="13">
+        <v>380.45</v>
+      </c>
+      <c r="F81" s="13">
+        <v>376.8</v>
+      </c>
+      <c r="G81" s="13">
+        <v>380.2</v>
+      </c>
+      <c r="H81" s="13">
+        <v>380.5</v>
+      </c>
+      <c r="I81" s="13">
+        <v>376.8</v>
+      </c>
+      <c r="J81" s="13">
+        <v>384.2</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L81" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="12"/>
+      <c r="P81" s="12"/>
+      <c r="Q81" s="12"/>
+      <c r="R81" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E82" s="13">
+        <v>295.1</v>
+      </c>
+      <c r="F82" s="13">
+        <v>288</v>
+      </c>
+      <c r="G82" s="13">
+        <v>294.5</v>
+      </c>
+      <c r="H82" s="13">
+        <v>294.6</v>
+      </c>
+      <c r="I82" s="13">
+        <v>288</v>
+      </c>
+      <c r="J82" s="13">
+        <v>301.2</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="12"/>
+      <c r="P82" s="12"/>
+      <c r="Q82" s="12"/>
+      <c r="R82" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E83" s="3">
+        <v>932.15</v>
+      </c>
+      <c r="F83" s="3">
+        <v>921.75</v>
+      </c>
+      <c r="G83" s="3">
+        <v>930</v>
+      </c>
+      <c r="H83" s="3">
+        <v>929.85</v>
+      </c>
+      <c r="I83" s="3">
+        <v>921.75</v>
+      </c>
+      <c r="J83" s="3">
+        <v>937.95</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="N83" s="3">
+        <v>921.75</v>
+      </c>
+      <c r="O83" s="2">
+        <v>8</v>
+      </c>
+      <c r="P83" s="4">
+        <v>-8.1</v>
+      </c>
+      <c r="Q83" s="5">
+        <v>-0.871</v>
+      </c>
+      <c r="R83" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+      <c r="C84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E84" s="3">
+        <v>4836.5</v>
+      </c>
+      <c r="F84" s="3">
+        <v>4786.5</v>
+      </c>
+      <c r="G84" s="3">
+        <v>4834</v>
+      </c>
+      <c r="H84" s="3">
+        <v>4833.1</v>
+      </c>
+      <c r="I84" s="3">
+        <v>4786.5</v>
+      </c>
+      <c r="J84" s="3">
+        <v>4879.7</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="N84" s="3">
+        <v>4786.5</v>
+      </c>
+      <c r="O84" s="2">
+        <v>1</v>
+      </c>
+      <c r="P84" s="4">
+        <v>-46.6</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>-0.964</v>
+      </c>
+      <c r="R84" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E85" s="7">
+        <v>441.25</v>
+      </c>
+      <c r="F85" s="7">
+        <v>439.05</v>
+      </c>
+      <c r="G85" s="7">
+        <v>439.55</v>
+      </c>
+      <c r="H85" s="7">
+        <v>439.6</v>
+      </c>
+      <c r="I85" s="7">
+        <v>439.05</v>
+      </c>
+      <c r="J85" s="7">
+        <v>439.05</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="N85" s="7">
+        <v>439.05</v>
+      </c>
+      <c r="O85" s="6">
+        <v>1</v>
+      </c>
+      <c r="P85" s="8">
+        <v>0.55</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E86" s="7">
+        <v>196.2</v>
+      </c>
+      <c r="F86" s="7">
+        <v>195.5</v>
+      </c>
+      <c r="G86" s="7">
+        <v>195.5</v>
+      </c>
+      <c r="H86" s="7">
+        <v>195.56</v>
+      </c>
+      <c r="I86" s="7">
+        <v>195.5</v>
+      </c>
+      <c r="J86" s="7">
+        <v>195.5</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="N86" s="7">
+        <v>195.5</v>
+      </c>
+      <c r="O86" s="6">
+        <v>1</v>
+      </c>
+      <c r="P86" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="Q86" s="9">
+        <v>0.031</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E87" s="7">
+        <v>1025.5</v>
+      </c>
+      <c r="F87" s="7">
+        <v>1022.3</v>
+      </c>
+      <c r="G87" s="7">
+        <v>1022.8</v>
+      </c>
+      <c r="H87" s="7">
+        <v>1022.7</v>
+      </c>
+      <c r="I87" s="7">
+        <v>1022.3</v>
+      </c>
+      <c r="J87" s="7">
+        <v>1022.3</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="N87" s="7">
+        <v>1022.3</v>
+      </c>
+      <c r="O87" s="6">
+        <v>1</v>
+      </c>
+      <c r="P87" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>0.039</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E88" s="3">
+        <v>884.95</v>
+      </c>
+      <c r="F88" s="3">
+        <v>879.15</v>
+      </c>
+      <c r="G88" s="3">
+        <v>884.7</v>
+      </c>
+      <c r="H88" s="3">
+        <v>884.55</v>
+      </c>
+      <c r="I88" s="3">
+        <v>879.15</v>
+      </c>
+      <c r="J88" s="3">
+        <v>889.95</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="N88" s="3">
+        <v>879.15</v>
+      </c>
+      <c r="O88" s="2">
+        <v>13</v>
+      </c>
+      <c r="P88" s="4">
+        <v>-5.4</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>-0.61</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1160.4</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1154.6</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1154.6</v>
+      </c>
+      <c r="H89" s="3">
+        <v>1154.2</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1154.6</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1153.8</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="N89" s="3">
+        <v>1154.6</v>
+      </c>
+      <c r="O89" s="2">
+        <v>1</v>
+      </c>
+      <c r="P89" s="4">
+        <v>-0.4</v>
+      </c>
+      <c r="Q89" s="5">
+        <v>-0.035</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E90" s="7">
+        <v>7984</v>
+      </c>
+      <c r="F90" s="7">
+        <v>7912</v>
+      </c>
+      <c r="G90" s="7">
+        <v>7955.5</v>
+      </c>
+      <c r="H90" s="7">
+        <v>7955</v>
+      </c>
+      <c r="I90" s="7">
+        <v>7912</v>
+      </c>
+      <c r="J90" s="7">
+        <v>7998</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="N90" s="7">
+        <v>7998</v>
+      </c>
+      <c r="O90" s="6">
+        <v>6</v>
+      </c>
+      <c r="P90" s="8">
+        <v>43</v>
+      </c>
+      <c r="Q90" s="9">
+        <v>0.541</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E91" s="3">
+        <v>1402.8</v>
+      </c>
+      <c r="F91" s="3">
+        <v>1399.1</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1399.5</v>
+      </c>
+      <c r="H91" s="3">
+        <v>1399.5</v>
+      </c>
+      <c r="I91" s="3">
+        <v>1399.1</v>
+      </c>
+      <c r="J91" s="3">
+        <v>1399.1</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="N91" s="3">
+        <v>1399.1</v>
+      </c>
+      <c r="O91" s="2">
+        <v>1</v>
+      </c>
+      <c r="P91" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="Q91" s="11">
+        <v>0.029</v>
+      </c>
+      <c r="R91" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E92" s="3">
+        <v>1046</v>
+      </c>
+      <c r="F92" s="3">
+        <v>1037</v>
+      </c>
+      <c r="G92" s="3">
+        <v>1041.05</v>
+      </c>
+      <c r="H92" s="3">
+        <v>1041.05</v>
+      </c>
+      <c r="I92" s="3">
+        <v>1037</v>
+      </c>
+      <c r="J92" s="3">
+        <v>1045.1</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="N92" s="3">
+        <v>1037</v>
+      </c>
+      <c r="O92" s="2">
+        <v>1</v>
+      </c>
+      <c r="P92" s="4">
+        <v>-4.05</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>-0.389</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E93" s="3">
+        <v>303.9</v>
+      </c>
+      <c r="F93" s="3">
+        <v>302.45</v>
+      </c>
+      <c r="G93" s="3">
+        <v>303.85</v>
+      </c>
+      <c r="H93" s="3">
+        <v>303.9</v>
+      </c>
+      <c r="I93" s="3">
+        <v>302.45</v>
+      </c>
+      <c r="J93" s="3">
+        <v>305.35</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="N93" s="3">
+        <v>302.45</v>
+      </c>
+      <c r="O93" s="2">
+        <v>4</v>
+      </c>
+      <c r="P93" s="4">
+        <v>-1.45</v>
+      </c>
+      <c r="Q93" s="5">
+        <v>-0.477</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E94" s="7">
+        <v>1730.3</v>
+      </c>
+      <c r="F94" s="7">
+        <v>1725</v>
+      </c>
+      <c r="G94" s="7">
+        <v>1730</v>
+      </c>
+      <c r="H94" s="7">
+        <v>1730</v>
+      </c>
+      <c r="I94" s="7">
+        <v>1725</v>
+      </c>
+      <c r="J94" s="7">
+        <v>1735</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="N94" s="7">
+        <v>1735</v>
+      </c>
+      <c r="O94" s="6">
+        <v>7</v>
+      </c>
+      <c r="P94" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="9">
+        <v>0.289</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E95" s="3">
+        <v>156.75</v>
+      </c>
+      <c r="F95" s="3">
+        <v>156.05</v>
+      </c>
+      <c r="G95" s="3">
+        <v>156.11</v>
+      </c>
+      <c r="H95" s="3">
+        <v>156.2</v>
+      </c>
+      <c r="I95" s="3">
+        <v>156.05</v>
+      </c>
+      <c r="J95" s="3">
+        <v>156.05</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="N95" s="3">
+        <v>156.05</v>
+      </c>
+      <c r="O95" s="2">
+        <v>1</v>
+      </c>
+      <c r="P95" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="Q95" s="11">
+        <v>0.096</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E96" s="13">
+        <v>434.2</v>
+      </c>
+      <c r="F96" s="13">
+        <v>431.7</v>
+      </c>
+      <c r="G96" s="13">
+        <v>433.65</v>
+      </c>
+      <c r="H96" s="13">
+        <v>433.4</v>
+      </c>
+      <c r="I96" s="13">
+        <v>431.7</v>
+      </c>
+      <c r="J96" s="13">
+        <v>435.1</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L96" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
+      <c r="R96" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E97" s="13">
+        <v>3135.5</v>
+      </c>
+      <c r="F97" s="13">
+        <v>3093.2</v>
+      </c>
+      <c r="G97" s="13">
+        <v>3123</v>
+      </c>
+      <c r="H97" s="13">
+        <v>3127</v>
+      </c>
+      <c r="I97" s="13">
+        <v>3093.2</v>
+      </c>
+      <c r="J97" s="13">
+        <v>3160.8</v>
+      </c>
+      <c r="K97" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L97" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M97" s="12"/>
+      <c r="N97" s="12"/>
+      <c r="O97" s="12"/>
+      <c r="P97" s="12"/>
+      <c r="Q97" s="12"/>
+      <c r="R97" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E98" s="7">
+        <v>799.9</v>
+      </c>
+      <c r="F98" s="7">
+        <v>795.95</v>
+      </c>
+      <c r="G98" s="7">
+        <v>799.9</v>
+      </c>
+      <c r="H98" s="7">
+        <v>799.85</v>
+      </c>
+      <c r="I98" s="7">
+        <v>795.95</v>
+      </c>
+      <c r="J98" s="7">
+        <v>803.75</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="N98" s="7">
+        <v>803.75</v>
+      </c>
+      <c r="O98" s="6">
+        <v>1</v>
+      </c>
+      <c r="P98" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="Q98" s="9">
+        <v>0.488</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E99" s="13">
+        <v>447.7</v>
+      </c>
+      <c r="F99" s="13">
+        <v>442.55</v>
+      </c>
+      <c r="G99" s="13">
+        <v>447.05</v>
+      </c>
+      <c r="H99" s="13">
+        <v>447.35</v>
+      </c>
+      <c r="I99" s="13">
+        <v>442.55</v>
+      </c>
+      <c r="J99" s="13">
+        <v>452.15</v>
+      </c>
+      <c r="K99" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L99" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M99" s="12"/>
+      <c r="N99" s="12"/>
+      <c r="O99" s="12"/>
+      <c r="P99" s="12"/>
+      <c r="Q99" s="12"/>
+      <c r="R99" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="E100" s="13">
+        <v>514.5</v>
+      </c>
+      <c r="F100" s="13">
+        <v>512.05</v>
+      </c>
+      <c r="G100" s="13">
+        <v>513.1</v>
+      </c>
+      <c r="H100" s="13">
+        <v>513.4</v>
+      </c>
+      <c r="I100" s="13">
+        <v>512.05</v>
+      </c>
+      <c r="J100" s="13">
+        <v>514.75</v>
+      </c>
+      <c r="K100" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L100" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M100" s="12"/>
+      <c r="N100" s="12"/>
+      <c r="O100" s="12"/>
+      <c r="P100" s="12"/>
+      <c r="Q100" s="12"/>
+      <c r="R100" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="E101" s="13">
+        <v>7697.5</v>
+      </c>
+      <c r="F101" s="13">
+        <v>7669</v>
+      </c>
+      <c r="G101" s="13">
+        <v>7691.5</v>
+      </c>
+      <c r="H101" s="13">
+        <v>7691.5</v>
+      </c>
+      <c r="I101" s="13">
+        <v>7669</v>
+      </c>
+      <c r="J101" s="13">
+        <v>7714</v>
+      </c>
+      <c r="K101" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L101" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M101" s="12"/>
+      <c r="N101" s="12"/>
+      <c r="O101" s="12"/>
+      <c r="P101" s="12"/>
+      <c r="Q101" s="12"/>
+      <c r="R101" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E102" s="13">
+        <v>373.9</v>
+      </c>
+      <c r="F102" s="13">
+        <v>371.7</v>
+      </c>
+      <c r="G102" s="13">
+        <v>373.5</v>
+      </c>
+      <c r="H102" s="12"/>
+      <c r="I102" s="13">
+        <v>371.7</v>
+      </c>
+      <c r="J102" s="12"/>
+      <c r="K102" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L102" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M102" s="12"/>
+      <c r="N102" s="12"/>
+      <c r="O102" s="12"/>
+      <c r="P102" s="12"/>
+      <c r="Q102" s="12"/>
+      <c r="R102" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E103" s="13">
+        <v>320.9</v>
+      </c>
+      <c r="F103" s="13">
+        <v>318.1</v>
+      </c>
+      <c r="G103" s="13">
+        <v>320.15</v>
+      </c>
+      <c r="H103" s="12"/>
+      <c r="I103" s="13">
+        <v>318.1</v>
+      </c>
+      <c r="J103" s="12"/>
+      <c r="K103" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L103" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M103" s="12"/>
+      <c r="N103" s="12"/>
+      <c r="O103" s="12"/>
+      <c r="P103" s="12"/>
+      <c r="Q103" s="12"/>
+      <c r="R103" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B104" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="P66" s="15">
-        <v>159.92</v>
-      </c>
-      <c r="R66" s="14" t="s">
-        <v>191</v>
+      <c r="C104" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E104" s="13">
+        <v>4325</v>
+      </c>
+      <c r="F104" s="13">
+        <v>4300</v>
+      </c>
+      <c r="G104" s="13">
+        <v>4318.5</v>
+      </c>
+      <c r="H104" s="12"/>
+      <c r="I104" s="13">
+        <v>4300</v>
+      </c>
+      <c r="J104" s="12"/>
+      <c r="K104" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L104" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="M104" s="12"/>
+      <c r="N104" s="12"/>
+      <c r="O104" s="12"/>
+      <c r="P104" s="12"/>
+      <c r="Q104" s="12"/>
+      <c r="R104" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="P106" s="15">
+        <v>94.73</v>
+      </c>
+      <c r="R106" s="14" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="477">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -637,7 +637,7 @@
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 73 candle(s) — neither SL nor Target hit yet</t>
+    <t>Checked 98 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
     <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
@@ -727,6 +727,9 @@
     <t>NSE:FEDERALBNK-EQ</t>
   </si>
   <si>
+    <t>2026-02-26 09:30</t>
+  </si>
+  <si>
     <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
   </si>
   <si>
@@ -1210,28 +1213,235 @@
     <t>NSE:ASTRAL-EQ_BULL_1771910100_1772011800</t>
   </si>
   <si>
+    <t>2026-02-26 09:15</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1771910100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BULL_1771921800_1772012700</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:00</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BULL_1771999200_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BEAR_1772003700_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771993800_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BULL_1771992000_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1771996500_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:30</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ</t>
+  </si>
+  <si>
+    <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1771997400_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BULL_1771994700_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:15</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1772010000_1772078400</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:15</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772078400</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BULL_1771996500_1772079300</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771993800_1772079300</t>
+  </si>
+  <si>
+    <t>Checked 21 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1771994700_1772081100</t>
+  </si>
+  <si>
+    <t>Checked 19 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772081100</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:15</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771992000_1772082000</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 11:30</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ_BEAR_1772007300_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 11:45</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ_BULL_1772009100_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BEAR_1772002800_1772090100</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:15</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ_BULL_1772077500_1772091900</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:15</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ_BEAR_1771993800_1772092800</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772012700_1772096400</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:00</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>NSE:GLENMARK-EQ_BULL_1771910100_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:IIFL-EQ_BULL_1771995600_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BULL_1771997400_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:SONACOMS-EQ</t>
-  </si>
-  <si>
-    <t>SUMMARY — 51W / 99L / 7 OPEN  |  Win Rate: 34.0%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 150 of 157</t>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1772078400_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ</t>
+  </si>
+  <si>
+    <t>Entry candle not yet available — trade not entered</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ_BEAR_1772092800_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ_BULL_1771994700_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ</t>
+  </si>
+  <si>
+    <t>SUMMARY — 64W / 114L / 13 OPEN  |  Win Rate: 36.0%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 178 of 191</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R160"/>
+  <dimension ref="A1:R194"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6239,57 +6449,67 @@
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E82" s="13">
+      <c r="E82" s="7">
         <v>295.1</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="7">
         <v>288</v>
       </c>
-      <c r="G82" s="13">
+      <c r="G82" s="7">
         <v>294.5</v>
       </c>
-      <c r="H82" s="13">
+      <c r="H82" s="7">
         <v>294.6</v>
       </c>
-      <c r="I82" s="13">
+      <c r="I82" s="7">
         <v>288</v>
       </c>
-      <c r="J82" s="13">
+      <c r="J82" s="7">
         <v>301.2</v>
       </c>
-      <c r="K82" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L82" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M82" s="12"/>
-      <c r="N82" s="12"/>
-      <c r="O82" s="12"/>
-      <c r="P82" s="12"/>
-      <c r="Q82" s="12"/>
-      <c r="R82" s="12" t="s">
-        <v>208</v>
+      <c r="K82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="N82" s="7">
+        <v>301.2</v>
+      </c>
+      <c r="O82" s="6">
+        <v>75</v>
+      </c>
+      <c r="P82" s="8">
+        <v>6.6</v>
+      </c>
+      <c r="Q82" s="9">
+        <v>2.24</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>20</v>
@@ -6342,7 +6562,7 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>183</v>
@@ -6378,7 +6598,7 @@
         <v>23</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N84" s="3">
         <v>4786.5</v>
@@ -6398,16 +6618,16 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E85" s="7">
         <v>441.25</v>
@@ -6434,7 +6654,7 @@
         <v>33</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N85" s="7">
         <v>439.05</v>
@@ -6454,16 +6674,16 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E86" s="7">
         <v>196.2</v>
@@ -6490,7 +6710,7 @@
         <v>33</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N86" s="7">
         <v>195.5</v>
@@ -6510,16 +6730,16 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E87" s="7">
         <v>1025.5</v>
@@ -6546,7 +6766,7 @@
         <v>33</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N87" s="7">
         <v>1022.3</v>
@@ -6566,7 +6786,7 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>40</v>
@@ -6602,7 +6822,7 @@
         <v>23</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N88" s="3">
         <v>879.15</v>
@@ -6622,10 +6842,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>64</v>
@@ -6658,7 +6878,7 @@
         <v>23</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N89" s="3">
         <v>1154.6</v>
@@ -6678,16 +6898,16 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E90" s="7">
         <v>7984</v>
@@ -6714,7 +6934,7 @@
         <v>33</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N90" s="7">
         <v>7998</v>
@@ -6734,16 +6954,16 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E91" s="3">
         <v>1402.8</v>
@@ -6770,7 +6990,7 @@
         <v>23</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N91" s="3">
         <v>1399.1</v>
@@ -6790,7 +7010,7 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>210</v>
@@ -6826,7 +7046,7 @@
         <v>23</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N92" s="3">
         <v>1037</v>
@@ -6846,10 +7066,10 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>20</v>
@@ -6882,7 +7102,7 @@
         <v>23</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N93" s="3">
         <v>302.45</v>
@@ -6902,7 +7122,7 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>47</v>
@@ -6911,7 +7131,7 @@
         <v>20</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E94" s="7">
         <v>1730.3</v>
@@ -6938,7 +7158,7 @@
         <v>33</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N94" s="7">
         <v>1735</v>
@@ -6958,7 +7178,7 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>131</v>
@@ -6967,7 +7187,7 @@
         <v>64</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E95" s="3">
         <v>156.75</v>
@@ -6994,7 +7214,7 @@
         <v>23</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N95" s="3">
         <v>156.05</v>
@@ -7014,16 +7234,16 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E96" s="3">
         <v>434.2</v>
@@ -7070,16 +7290,16 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E97" s="3">
         <v>3135.5</v>
@@ -7106,7 +7326,7 @@
         <v>23</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N97" s="3">
         <v>3093.2</v>
@@ -7126,16 +7346,16 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E98" s="7">
         <v>799.9</v>
@@ -7162,7 +7382,7 @@
         <v>33</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N98" s="7">
         <v>803.75</v>
@@ -7182,16 +7402,16 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E99" s="3">
         <v>447.7</v>
@@ -7218,7 +7438,7 @@
         <v>23</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N99" s="3">
         <v>442.55</v>
@@ -7238,7 +7458,7 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>95</v>
@@ -7247,7 +7467,7 @@
         <v>20</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E100" s="7">
         <v>514.5</v>
@@ -7294,16 +7514,16 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E101" s="3">
         <v>7697.5</v>
@@ -7350,16 +7570,16 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E102" s="7">
         <v>373.9</v>
@@ -7386,7 +7606,7 @@
         <v>33</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N102" s="7">
         <v>371.7</v>
@@ -7406,7 +7626,7 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>229</v>
@@ -7415,7 +7635,7 @@
         <v>20</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E103" s="3">
         <v>320.9</v>
@@ -7442,7 +7662,7 @@
         <v>23</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N103" s="3">
         <v>318.1</v>
@@ -7462,7 +7682,7 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>189</v>
@@ -7471,7 +7691,7 @@
         <v>20</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E104" s="7">
         <v>4325</v>
@@ -7498,7 +7718,7 @@
         <v>33</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N104" s="7">
         <v>4314</v>
@@ -7518,10 +7738,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>64</v>
@@ -7574,10 +7794,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>64</v>
@@ -7630,7 +7850,7 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>67</v>
@@ -7686,10 +7906,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>64</v>
@@ -7742,10 +7962,10 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>20</v>
@@ -7778,7 +7998,7 @@
         <v>33</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N109" s="7">
         <v>179.87</v>
@@ -7798,10 +8018,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>20</v>
@@ -7834,7 +8054,7 @@
         <v>23</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N110" s="3">
         <v>473.5</v>
@@ -7854,10 +8074,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>64</v>
@@ -7910,7 +8130,7 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>99</v>
@@ -7919,7 +8139,7 @@
         <v>20</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E112" s="3">
         <v>1229.2</v>
@@ -7946,7 +8166,7 @@
         <v>23</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N112" s="3">
         <v>1222.3</v>
@@ -7966,16 +8186,16 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E113" s="7">
         <v>529.7</v>
@@ -8002,7 +8222,7 @@
         <v>33</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N113" s="7">
         <v>526</v>
@@ -8022,16 +8242,16 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E114" s="3">
         <v>1491</v>
@@ -8058,7 +8278,7 @@
         <v>23</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N114" s="3">
         <v>1485.9</v>
@@ -8078,7 +8298,7 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>110</v>
@@ -8087,7 +8307,7 @@
         <v>64</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E115" s="7">
         <v>126.41</v>
@@ -8114,7 +8334,7 @@
         <v>33</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N115" s="7">
         <v>125.9</v>
@@ -8134,16 +8354,16 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E116" s="3">
         <v>26505</v>
@@ -8190,7 +8410,7 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>131</v>
@@ -8199,7 +8419,7 @@
         <v>64</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E117" s="3">
         <v>156.1</v>
@@ -8246,7 +8466,7 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>112</v>
@@ -8255,7 +8475,7 @@
         <v>20</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E118" s="3">
         <v>171.45</v>
@@ -8282,7 +8502,7 @@
         <v>23</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N118" s="3">
         <v>170.13</v>
@@ -8302,7 +8522,7 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>19</v>
@@ -8311,7 +8531,7 @@
         <v>64</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E119" s="3">
         <v>9810</v>
@@ -8338,7 +8558,7 @@
         <v>23</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N119" s="3">
         <v>9769.5</v>
@@ -8358,16 +8578,16 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E120" s="3">
         <v>2049.3</v>
@@ -8394,7 +8614,7 @@
         <v>23</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N120" s="3">
         <v>2039</v>
@@ -8414,7 +8634,7 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>51</v>
@@ -8423,7 +8643,7 @@
         <v>20</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E121" s="3">
         <v>1177.1</v>
@@ -8450,7 +8670,7 @@
         <v>23</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N121" s="3">
         <v>1171</v>
@@ -8470,7 +8690,7 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>116</v>
@@ -8479,7 +8699,7 @@
         <v>64</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E122" s="3">
         <v>482.35</v>
@@ -8506,7 +8726,7 @@
         <v>23</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N122" s="3">
         <v>480.55</v>
@@ -8526,7 +8746,7 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>198</v>
@@ -8535,7 +8755,7 @@
         <v>64</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E123" s="3">
         <v>914.25</v>
@@ -8562,7 +8782,7 @@
         <v>23</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N123" s="3">
         <v>912.15</v>
@@ -8582,16 +8802,16 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E124" s="3">
         <v>1388.1</v>
@@ -8618,7 +8838,7 @@
         <v>23</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N124" s="3">
         <v>1384.4</v>
@@ -8638,16 +8858,16 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E125" s="7">
         <v>1659.8</v>
@@ -8674,7 +8894,7 @@
         <v>33</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N125" s="7">
         <v>1667.7</v>
@@ -8694,7 +8914,7 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>219</v>
@@ -8703,7 +8923,7 @@
         <v>20</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E126" s="7">
         <v>1238.4</v>
@@ -8750,16 +8970,16 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E127" s="7">
         <v>1256</v>
@@ -8806,16 +9026,16 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E128" s="7">
         <v>531.45</v>
@@ -8862,16 +9082,16 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E129" s="7">
         <v>693.5</v>
@@ -8898,7 +9118,7 @@
         <v>33</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N129" s="7">
         <v>696.6</v>
@@ -8918,7 +9138,7 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>179</v>
@@ -8927,7 +9147,7 @@
         <v>20</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E130" s="7">
         <v>6173</v>
@@ -8974,16 +9194,16 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E131" s="7">
         <v>437.35</v>
@@ -9030,7 +9250,7 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>80</v>
@@ -9039,7 +9259,7 @@
         <v>20</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E132" s="7">
         <v>1564</v>
@@ -9066,7 +9286,7 @@
         <v>33</v>
       </c>
       <c r="M132" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N132" s="7">
         <v>1580.4</v>
@@ -9086,7 +9306,7 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>150</v>
@@ -9095,7 +9315,7 @@
         <v>20</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E133" s="7">
         <v>8011</v>
@@ -9122,7 +9342,7 @@
         <v>33</v>
       </c>
       <c r="M133" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N133" s="7">
         <v>8028.5</v>
@@ -9142,7 +9362,7 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>219</v>
@@ -9178,7 +9398,7 @@
         <v>33</v>
       </c>
       <c r="M134" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N134" s="7">
         <v>1253.9</v>
@@ -9198,10 +9418,10 @@
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>20</v>
@@ -9234,7 +9454,7 @@
         <v>33</v>
       </c>
       <c r="M135" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N135" s="7">
         <v>1282.7</v>
@@ -9254,10 +9474,10 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>20</v>
@@ -9275,13 +9495,13 @@
         <v>311.6</v>
       </c>
       <c r="H136" s="7">
-        <v>311.75</v>
+        <v>311.6</v>
       </c>
       <c r="I136" s="7">
         <v>307.65</v>
       </c>
       <c r="J136" s="7">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>22</v>
@@ -9290,19 +9510,19 @@
         <v>33</v>
       </c>
       <c r="M136" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N136" s="7">
-        <v>315.85</v>
+        <v>315.55</v>
       </c>
       <c r="O136" s="6">
         <v>7</v>
       </c>
       <c r="P136" s="8">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q136" s="9">
-        <v>1.315</v>
+        <v>1.268</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>25</v>
@@ -9310,10 +9530,10 @@
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>20</v>
@@ -9346,7 +9566,7 @@
         <v>23</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N137" s="3">
         <v>419.65</v>
@@ -9366,10 +9586,10 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>20</v>
@@ -9402,7 +9622,7 @@
         <v>33</v>
       </c>
       <c r="M138" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N138" s="7">
         <v>214.8</v>
@@ -9422,16 +9642,16 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E139" s="7">
         <v>722.9</v>
@@ -9458,7 +9678,7 @@
         <v>33</v>
       </c>
       <c r="M139" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N139" s="7">
         <v>731.6</v>
@@ -9478,16 +9698,16 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E140" s="3">
         <v>5827.5</v>
@@ -9514,7 +9734,7 @@
         <v>23</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N140" s="3">
         <v>5758.5</v>
@@ -9534,16 +9754,16 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E141" s="3">
         <v>621.3</v>
@@ -9570,7 +9790,7 @@
         <v>23</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N141" s="3">
         <v>616.4</v>
@@ -9590,16 +9810,16 @@
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E142" s="7">
         <v>1061</v>
@@ -9626,7 +9846,7 @@
         <v>33</v>
       </c>
       <c r="M142" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N142" s="7">
         <v>1069.9</v>
@@ -9646,7 +9866,7 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>72</v>
@@ -9655,7 +9875,7 @@
         <v>64</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E143" s="3">
         <v>612.45</v>
@@ -9667,7 +9887,7 @@
         <v>609.4</v>
       </c>
       <c r="H143" s="3">
-        <v>609.2</v>
+        <v>609.4</v>
       </c>
       <c r="I143" s="3">
         <v>607.75</v>
@@ -9682,7 +9902,7 @@
         <v>23</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N143" s="3">
         <v>607.75</v>
@@ -9691,10 +9911,10 @@
         <v>1</v>
       </c>
       <c r="P143" s="10">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="Q143" s="11">
-        <v>0.238</v>
+        <v>0.271</v>
       </c>
       <c r="R143" s="2" t="s">
         <v>25</v>
@@ -9702,7 +9922,7 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>74</v>
@@ -9711,7 +9931,7 @@
         <v>20</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E144" s="3">
         <v>1501.2</v>
@@ -9738,7 +9958,7 @@
         <v>23</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N144" s="3">
         <v>1495.4</v>
@@ -9758,16 +9978,16 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E145" s="3">
         <v>1135.6</v>
@@ -9794,7 +10014,7 @@
         <v>23</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N145" s="3">
         <v>1126.2</v>
@@ -9814,7 +10034,7 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>92</v>
@@ -9823,7 +10043,7 @@
         <v>64</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E146" s="3">
         <v>501.05</v>
@@ -9850,7 +10070,7 @@
         <v>23</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N146" s="3">
         <v>499.25</v>
@@ -9870,16 +10090,16 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E147" s="7">
         <v>1130.9</v>
@@ -9906,7 +10126,7 @@
         <v>33</v>
       </c>
       <c r="M147" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N147" s="7">
         <v>1136.9</v>
@@ -9926,16 +10146,16 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E148" s="3">
         <v>2408.4</v>
@@ -9962,7 +10182,7 @@
         <v>23</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N148" s="3">
         <v>2400</v>
@@ -9982,16 +10202,16 @@
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E149" s="3">
         <v>161.4</v>
@@ -10018,7 +10238,7 @@
         <v>23</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N149" s="3">
         <v>158.78</v>
@@ -10038,7 +10258,7 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>176</v>
@@ -10047,7 +10267,7 @@
         <v>20</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E150" s="7">
         <v>2128</v>
@@ -10094,16 +10314,16 @@
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E151" s="7">
         <v>379.15</v>
@@ -10130,7 +10350,7 @@
         <v>33</v>
       </c>
       <c r="M151" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N151" s="7">
         <v>380.2</v>
@@ -10150,16 +10370,16 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E152" s="7">
         <v>1215</v>
@@ -10186,7 +10406,7 @@
         <v>33</v>
       </c>
       <c r="M152" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N152" s="7">
         <v>1219.9</v>
@@ -10206,10 +10426,10 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>20</v>
@@ -10242,7 +10462,7 @@
         <v>33</v>
       </c>
       <c r="M153" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N153" s="7">
         <v>1212.5</v>
@@ -10261,244 +10481,2066 @@
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A154" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="B154" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="C154" s="12" t="s">
+      <c r="A154" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D154" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E154" s="13">
+      <c r="D154" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E154" s="3">
         <v>1687.5</v>
       </c>
-      <c r="F154" s="13">
+      <c r="F154" s="3">
         <v>1677.5</v>
       </c>
-      <c r="G154" s="13">
+      <c r="G154" s="3">
         <v>1685.9</v>
       </c>
-      <c r="H154" s="13">
+      <c r="H154" s="3">
         <v>1686.5</v>
       </c>
-      <c r="I154" s="13">
+      <c r="I154" s="3">
         <v>1677.5</v>
       </c>
-      <c r="J154" s="13">
+      <c r="J154" s="3">
         <v>1695.5</v>
       </c>
-      <c r="K154" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L154" s="12" t="s">
+      <c r="K154" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="N154" s="3">
+        <v>1677.5</v>
+      </c>
+      <c r="O154" s="2">
+        <v>1</v>
+      </c>
+      <c r="P154" s="4">
+        <v>-9</v>
+      </c>
+      <c r="Q154" s="5">
+        <v>-0.534</v>
+      </c>
+      <c r="R154" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E155" s="7">
+        <v>2088.9</v>
+      </c>
+      <c r="F155" s="7">
+        <v>2079.2</v>
+      </c>
+      <c r="G155" s="7">
+        <v>2086.7</v>
+      </c>
+      <c r="H155" s="7">
+        <v>2086.7</v>
+      </c>
+      <c r="I155" s="7">
+        <v>2079.2</v>
+      </c>
+      <c r="J155" s="7">
+        <v>2094.2</v>
+      </c>
+      <c r="K155" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L155" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M155" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="N155" s="7">
+        <v>2094.2</v>
+      </c>
+      <c r="O155" s="6">
+        <v>1</v>
+      </c>
+      <c r="P155" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="Q155" s="9">
+        <v>0.359</v>
+      </c>
+      <c r="R155" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E156" s="3">
+        <v>510.4</v>
+      </c>
+      <c r="F156" s="3">
+        <v>506.3</v>
+      </c>
+      <c r="G156" s="3">
+        <v>509.4</v>
+      </c>
+      <c r="H156" s="3">
+        <v>509.4</v>
+      </c>
+      <c r="I156" s="3">
+        <v>506.3</v>
+      </c>
+      <c r="J156" s="3">
+        <v>512.5</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="N156" s="3">
+        <v>506.3</v>
+      </c>
+      <c r="O156" s="2">
+        <v>1</v>
+      </c>
+      <c r="P156" s="4">
+        <v>-3.1</v>
+      </c>
+      <c r="Q156" s="5">
+        <v>-0.609</v>
+      </c>
+      <c r="R156" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A157" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E157" s="7">
+        <v>624.1</v>
+      </c>
+      <c r="F157" s="7">
+        <v>618.45</v>
+      </c>
+      <c r="G157" s="7">
+        <v>624</v>
+      </c>
+      <c r="H157" s="7">
+        <v>624.1</v>
+      </c>
+      <c r="I157" s="7">
+        <v>618.45</v>
+      </c>
+      <c r="J157" s="7">
+        <v>629.75</v>
+      </c>
+      <c r="K157" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L157" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M157" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="N157" s="7">
+        <v>629.75</v>
+      </c>
+      <c r="O157" s="6">
+        <v>2</v>
+      </c>
+      <c r="P157" s="8">
+        <v>5.65</v>
+      </c>
+      <c r="Q157" s="9">
+        <v>0.905</v>
+      </c>
+      <c r="R157" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E158" s="3">
+        <v>542.7</v>
+      </c>
+      <c r="F158" s="3">
+        <v>540.05</v>
+      </c>
+      <c r="G158" s="3">
+        <v>541.25</v>
+      </c>
+      <c r="H158" s="3">
+        <v>541.55</v>
+      </c>
+      <c r="I158" s="3">
+        <v>540.05</v>
+      </c>
+      <c r="J158" s="3">
+        <v>543.05</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="N158" s="3">
+        <v>540.05</v>
+      </c>
+      <c r="O158" s="2">
+        <v>1</v>
+      </c>
+      <c r="P158" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="Q158" s="5">
+        <v>-0.277</v>
+      </c>
+      <c r="R158" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E159" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="F159" s="3">
+        <v>616.25</v>
+      </c>
+      <c r="G159" s="3">
+        <v>620</v>
+      </c>
+      <c r="H159" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="I159" s="3">
+        <v>616.25</v>
+      </c>
+      <c r="J159" s="3">
+        <v>624.75</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N159" s="3">
+        <v>616.25</v>
+      </c>
+      <c r="O159" s="2">
+        <v>3</v>
+      </c>
+      <c r="P159" s="4">
+        <v>-4.25</v>
+      </c>
+      <c r="Q159" s="5">
+        <v>-0.685</v>
+      </c>
+      <c r="R159" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A160" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E160" s="7">
+        <v>2164.5</v>
+      </c>
+      <c r="F160" s="7">
+        <v>2139</v>
+      </c>
+      <c r="G160" s="7">
+        <v>2159.3</v>
+      </c>
+      <c r="H160" s="7">
+        <v>2158.6</v>
+      </c>
+      <c r="I160" s="7">
+        <v>2139</v>
+      </c>
+      <c r="J160" s="7">
+        <v>2178.2</v>
+      </c>
+      <c r="K160" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L160" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M160" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="N160" s="7">
+        <v>2178.2</v>
+      </c>
+      <c r="O160" s="6">
+        <v>2</v>
+      </c>
+      <c r="P160" s="8">
+        <v>19.6</v>
+      </c>
+      <c r="Q160" s="9">
+        <v>0.908</v>
+      </c>
+      <c r="R160" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E161" s="3">
+        <v>2247.7</v>
+      </c>
+      <c r="F161" s="3">
+        <v>2234.3</v>
+      </c>
+      <c r="G161" s="3">
+        <v>2242.4</v>
+      </c>
+      <c r="H161" s="3">
+        <v>2242.4</v>
+      </c>
+      <c r="I161" s="3">
+        <v>2234.3</v>
+      </c>
+      <c r="J161" s="3">
+        <v>2250.5</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="N161" s="3">
+        <v>2234.3</v>
+      </c>
+      <c r="O161" s="2">
+        <v>1</v>
+      </c>
+      <c r="P161" s="4">
+        <v>-8.1</v>
+      </c>
+      <c r="Q161" s="5">
+        <v>-0.361</v>
+      </c>
+      <c r="R161" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E162" s="3">
+        <v>982.9</v>
+      </c>
+      <c r="F162" s="3">
+        <v>973</v>
+      </c>
+      <c r="G162" s="3">
+        <v>976.45</v>
+      </c>
+      <c r="H162" s="3">
+        <v>976.5</v>
+      </c>
+      <c r="I162" s="3">
+        <v>973</v>
+      </c>
+      <c r="J162" s="3">
+        <v>973</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="N162" s="3">
+        <v>973</v>
+      </c>
+      <c r="O162" s="2">
+        <v>1</v>
+      </c>
+      <c r="P162" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="Q162" s="11">
+        <v>0.358</v>
+      </c>
+      <c r="R162" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A163" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E163" s="7">
+        <v>6468</v>
+      </c>
+      <c r="F163" s="7">
+        <v>6420</v>
+      </c>
+      <c r="G163" s="7">
+        <v>6466</v>
+      </c>
+      <c r="H163" s="7">
+        <v>6465</v>
+      </c>
+      <c r="I163" s="7">
+        <v>6420</v>
+      </c>
+      <c r="J163" s="7">
+        <v>6510</v>
+      </c>
+      <c r="K163" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L163" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M163" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="N163" s="7">
+        <v>6510</v>
+      </c>
+      <c r="O163" s="6">
+        <v>1</v>
+      </c>
+      <c r="P163" s="8">
+        <v>45</v>
+      </c>
+      <c r="Q163" s="9">
+        <v>0.696</v>
+      </c>
+      <c r="R163" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A164" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E164" s="7">
+        <v>948</v>
+      </c>
+      <c r="F164" s="7">
+        <v>935.15</v>
+      </c>
+      <c r="G164" s="7">
+        <v>947.55</v>
+      </c>
+      <c r="H164" s="7">
+        <v>947.25</v>
+      </c>
+      <c r="I164" s="7">
+        <v>935.15</v>
+      </c>
+      <c r="J164" s="7">
+        <v>959.35</v>
+      </c>
+      <c r="K164" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L164" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M164" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="N164" s="7">
+        <v>959.35</v>
+      </c>
+      <c r="O164" s="6">
+        <v>1</v>
+      </c>
+      <c r="P164" s="8">
+        <v>12.1</v>
+      </c>
+      <c r="Q164" s="9">
+        <v>1.277</v>
+      </c>
+      <c r="R164" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E165" s="3">
+        <v>171.2</v>
+      </c>
+      <c r="F165" s="3">
+        <v>170.3</v>
+      </c>
+      <c r="G165" s="3">
+        <v>170.66</v>
+      </c>
+      <c r="H165" s="3">
+        <v>170.6</v>
+      </c>
+      <c r="I165" s="3">
+        <v>170.3</v>
+      </c>
+      <c r="J165" s="3">
+        <v>170.9</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="N165" s="3">
+        <v>170.3</v>
+      </c>
+      <c r="O165" s="2">
+        <v>1</v>
+      </c>
+      <c r="P165" s="4">
+        <v>-0.3</v>
+      </c>
+      <c r="Q165" s="5">
+        <v>-0.176</v>
+      </c>
+      <c r="R165" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E166" s="3">
+        <v>130.7</v>
+      </c>
+      <c r="F166" s="3">
+        <v>128.61</v>
+      </c>
+      <c r="G166" s="3">
+        <v>129.65</v>
+      </c>
+      <c r="H166" s="3">
+        <v>129.66</v>
+      </c>
+      <c r="I166" s="3">
+        <v>128.61</v>
+      </c>
+      <c r="J166" s="3">
+        <v>130.71</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M166" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="N166" s="3">
+        <v>128.61</v>
+      </c>
+      <c r="O166" s="2">
+        <v>2</v>
+      </c>
+      <c r="P166" s="4">
+        <v>-1.05</v>
+      </c>
+      <c r="Q166" s="5">
+        <v>-0.81</v>
+      </c>
+      <c r="R166" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E167" s="7">
+        <v>946.8</v>
+      </c>
+      <c r="F167" s="7">
+        <v>936.3</v>
+      </c>
+      <c r="G167" s="7">
+        <v>945.95</v>
+      </c>
+      <c r="H167" s="7">
+        <v>945.95</v>
+      </c>
+      <c r="I167" s="7">
+        <v>936.3</v>
+      </c>
+      <c r="J167" s="7">
+        <v>955.6</v>
+      </c>
+      <c r="K167" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L167" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M167" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="N167" s="7">
+        <v>955.6</v>
+      </c>
+      <c r="O167" s="6">
+        <v>1</v>
+      </c>
+      <c r="P167" s="8">
+        <v>9.65</v>
+      </c>
+      <c r="Q167" s="9">
+        <v>1.02</v>
+      </c>
+      <c r="R167" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E168" s="3">
+        <v>3987.9</v>
+      </c>
+      <c r="F168" s="3">
+        <v>3916</v>
+      </c>
+      <c r="G168" s="3">
+        <v>3966.1</v>
+      </c>
+      <c r="H168" s="3">
+        <v>3964.8</v>
+      </c>
+      <c r="I168" s="3">
+        <v>3916</v>
+      </c>
+      <c r="J168" s="3">
+        <v>4013.6</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="N168" s="3">
+        <v>3916</v>
+      </c>
+      <c r="O168" s="2">
+        <v>12</v>
+      </c>
+      <c r="P168" s="4">
+        <v>-48.8</v>
+      </c>
+      <c r="Q168" s="5">
+        <v>-1.231</v>
+      </c>
+      <c r="R168" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A169" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E169" s="13">
+        <v>154.34</v>
+      </c>
+      <c r="F169" s="13">
+        <v>151.22</v>
+      </c>
+      <c r="G169" s="13">
+        <v>153.52</v>
+      </c>
+      <c r="H169" s="13">
+        <v>153.6</v>
+      </c>
+      <c r="I169" s="13">
+        <v>151.22</v>
+      </c>
+      <c r="J169" s="13">
+        <v>155.98</v>
+      </c>
+      <c r="K169" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="M154" s="12"/>
-      <c r="N154" s="12"/>
-      <c r="O154" s="12"/>
-      <c r="P154" s="12"/>
-      <c r="Q154" s="12"/>
-      <c r="R154" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A155" s="12" t="s">
+      <c r="M169" s="12"/>
+      <c r="N169" s="12"/>
+      <c r="O169" s="12"/>
+      <c r="P169" s="12"/>
+      <c r="Q169" s="12"/>
+      <c r="R169" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A170" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D170" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="B155" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="C155" s="12" t="s">
+      <c r="E170" s="13">
+        <v>869.15</v>
+      </c>
+      <c r="F170" s="13">
+        <v>836.05</v>
+      </c>
+      <c r="G170" s="13">
+        <v>855</v>
+      </c>
+      <c r="H170" s="13">
+        <v>855</v>
+      </c>
+      <c r="I170" s="13">
+        <v>836.05</v>
+      </c>
+      <c r="J170" s="13">
+        <v>873.95</v>
+      </c>
+      <c r="K170" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M170" s="12"/>
+      <c r="N170" s="12"/>
+      <c r="O170" s="12"/>
+      <c r="P170" s="12"/>
+      <c r="Q170" s="12"/>
+      <c r="R170" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D155" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E155" s="13">
-        <v>2088.9</v>
-      </c>
-      <c r="F155" s="13">
-        <v>2079.2</v>
-      </c>
-      <c r="G155" s="13">
-        <v>2086.7</v>
-      </c>
-      <c r="H155" s="13">
-        <v>2086.7</v>
-      </c>
-      <c r="I155" s="13">
-        <v>2079.2</v>
-      </c>
-      <c r="J155" s="13">
-        <v>2094.2</v>
-      </c>
-      <c r="K155" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L155" s="12" t="s">
+      <c r="D171" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E171" s="3">
+        <v>1105</v>
+      </c>
+      <c r="F171" s="3">
+        <v>1087</v>
+      </c>
+      <c r="G171" s="3">
+        <v>1099.3</v>
+      </c>
+      <c r="H171" s="3">
+        <v>1099.4</v>
+      </c>
+      <c r="I171" s="3">
+        <v>1087</v>
+      </c>
+      <c r="J171" s="3">
+        <v>1111.8</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M171" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="N171" s="3">
+        <v>1087</v>
+      </c>
+      <c r="O171" s="2">
+        <v>11</v>
+      </c>
+      <c r="P171" s="4">
+        <v>-12.4</v>
+      </c>
+      <c r="Q171" s="5">
+        <v>-1.128</v>
+      </c>
+      <c r="R171" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A172" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E172" s="7">
+        <v>2793.6</v>
+      </c>
+      <c r="F172" s="7">
+        <v>2770</v>
+      </c>
+      <c r="G172" s="7">
+        <v>2791.2</v>
+      </c>
+      <c r="H172" s="7">
+        <v>2791.4</v>
+      </c>
+      <c r="I172" s="7">
+        <v>2770</v>
+      </c>
+      <c r="J172" s="7">
+        <v>2812.8</v>
+      </c>
+      <c r="K172" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L172" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M172" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="N172" s="7">
+        <v>2812.8</v>
+      </c>
+      <c r="O172" s="6">
+        <v>2</v>
+      </c>
+      <c r="P172" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="Q172" s="9">
+        <v>0.767</v>
+      </c>
+      <c r="R172" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E173" s="3">
+        <v>630.75</v>
+      </c>
+      <c r="F173" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="G173" s="3">
+        <v>628.55</v>
+      </c>
+      <c r="H173" s="3">
+        <v>628.5</v>
+      </c>
+      <c r="I173" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="J173" s="3">
+        <v>636.5</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="N173" s="3">
+        <v>620.5</v>
+      </c>
+      <c r="O173" s="2">
+        <v>11</v>
+      </c>
+      <c r="P173" s="4">
+        <v>-8</v>
+      </c>
+      <c r="Q173" s="5">
+        <v>-1.273</v>
+      </c>
+      <c r="R173" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E174" s="3">
+        <v>1364.6</v>
+      </c>
+      <c r="F174" s="3">
+        <v>1353.1</v>
+      </c>
+      <c r="G174" s="3">
+        <v>1363.9</v>
+      </c>
+      <c r="H174" s="3">
+        <v>1363.5</v>
+      </c>
+      <c r="I174" s="3">
+        <v>1353.1</v>
+      </c>
+      <c r="J174" s="3">
+        <v>1373.9</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M174" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="N174" s="3">
+        <v>1353.1</v>
+      </c>
+      <c r="O174" s="2">
+        <v>1</v>
+      </c>
+      <c r="P174" s="4">
+        <v>-10.4</v>
+      </c>
+      <c r="Q174" s="5">
+        <v>-0.763</v>
+      </c>
+      <c r="R174" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A175" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="E175" s="13">
+        <v>500.35</v>
+      </c>
+      <c r="F175" s="13">
+        <v>493.9</v>
+      </c>
+      <c r="G175" s="13">
+        <v>500.3</v>
+      </c>
+      <c r="H175" s="13">
+        <v>500.2</v>
+      </c>
+      <c r="I175" s="13">
+        <v>493.9</v>
+      </c>
+      <c r="J175" s="13">
+        <v>506.5</v>
+      </c>
+      <c r="K175" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L175" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="M155" s="12"/>
-      <c r="N155" s="12"/>
-      <c r="O155" s="12"/>
-      <c r="P155" s="12"/>
-      <c r="Q155" s="12"/>
-      <c r="R155" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A156" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="B156" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C156" s="12" t="s">
+      <c r="M175" s="12"/>
+      <c r="N175" s="12"/>
+      <c r="O175" s="12"/>
+      <c r="P175" s="12"/>
+      <c r="Q175" s="12"/>
+      <c r="R175" s="12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A176" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C176" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D156" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E156" s="13">
-        <v>510.4</v>
-      </c>
-      <c r="F156" s="13">
-        <v>506.3</v>
-      </c>
-      <c r="G156" s="13">
-        <v>509.4</v>
-      </c>
-      <c r="H156" s="13">
-        <v>509.4</v>
-      </c>
-      <c r="I156" s="13">
-        <v>506.3</v>
-      </c>
-      <c r="J156" s="13">
-        <v>512.5</v>
-      </c>
-      <c r="K156" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L156" s="12" t="s">
+      <c r="D176" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="E176" s="13">
+        <v>13770</v>
+      </c>
+      <c r="F176" s="13">
+        <v>13554</v>
+      </c>
+      <c r="G176" s="13">
+        <v>13741</v>
+      </c>
+      <c r="H176" s="13">
+        <v>13740</v>
+      </c>
+      <c r="I176" s="13">
+        <v>13554</v>
+      </c>
+      <c r="J176" s="13">
+        <v>13926</v>
+      </c>
+      <c r="K176" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L176" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="M156" s="12"/>
-      <c r="N156" s="12"/>
-      <c r="O156" s="12"/>
-      <c r="P156" s="12"/>
-      <c r="Q156" s="12"/>
-      <c r="R156" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A157" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C157" s="12" t="s">
+      <c r="M176" s="12"/>
+      <c r="N176" s="12"/>
+      <c r="O176" s="12"/>
+      <c r="P176" s="12"/>
+      <c r="Q176" s="12"/>
+      <c r="R176" s="12" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C177" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D157" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E157" s="13">
-        <v>624.1</v>
-      </c>
-      <c r="F157" s="13">
-        <v>618.45</v>
-      </c>
-      <c r="G157" s="13">
-        <v>624</v>
-      </c>
-      <c r="H157" s="13">
-        <v>624.1</v>
-      </c>
-      <c r="I157" s="13">
-        <v>618.45</v>
-      </c>
-      <c r="J157" s="13">
-        <v>629.75</v>
-      </c>
-      <c r="K157" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L157" s="12" t="s">
+      <c r="D177" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E177" s="7">
+        <v>390.45</v>
+      </c>
+      <c r="F177" s="7">
+        <v>386.6</v>
+      </c>
+      <c r="G177" s="7">
+        <v>389.65</v>
+      </c>
+      <c r="H177" s="7">
+        <v>389.75</v>
+      </c>
+      <c r="I177" s="7">
+        <v>386.6</v>
+      </c>
+      <c r="J177" s="7">
+        <v>392.9</v>
+      </c>
+      <c r="K177" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L177" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M177" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="N177" s="7">
+        <v>392.9</v>
+      </c>
+      <c r="O177" s="6">
+        <v>19</v>
+      </c>
+      <c r="P177" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="Q177" s="9">
+        <v>0.808</v>
+      </c>
+      <c r="R177" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E178" s="3">
+        <v>385.4</v>
+      </c>
+      <c r="F178" s="3">
+        <v>381.45</v>
+      </c>
+      <c r="G178" s="3">
+        <v>383.3</v>
+      </c>
+      <c r="H178" s="3">
+        <v>383.5</v>
+      </c>
+      <c r="I178" s="3">
+        <v>381.45</v>
+      </c>
+      <c r="J178" s="3">
+        <v>385.55</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M178" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="N178" s="3">
+        <v>381.45</v>
+      </c>
+      <c r="O178" s="2">
+        <v>3</v>
+      </c>
+      <c r="P178" s="4">
+        <v>-2.05</v>
+      </c>
+      <c r="Q178" s="5">
+        <v>-0.535</v>
+      </c>
+      <c r="R178" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E179" s="3">
+        <v>2054.9</v>
+      </c>
+      <c r="F179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="G179" s="3">
+        <v>2050.4</v>
+      </c>
+      <c r="H179" s="3">
+        <v>2050.5</v>
+      </c>
+      <c r="I179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="J179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M179" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="N179" s="3">
+        <v>2047.1</v>
+      </c>
+      <c r="O179" s="2">
+        <v>1</v>
+      </c>
+      <c r="P179" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="Q179" s="11">
+        <v>0.166</v>
+      </c>
+      <c r="R179" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A180" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="E180" s="7">
+        <v>1100.05</v>
+      </c>
+      <c r="F180" s="7">
+        <v>1089</v>
+      </c>
+      <c r="G180" s="7">
+        <v>1100.05</v>
+      </c>
+      <c r="H180" s="7">
+        <v>1100.35</v>
+      </c>
+      <c r="I180" s="7">
+        <v>1089</v>
+      </c>
+      <c r="J180" s="7">
+        <v>1111.7</v>
+      </c>
+      <c r="K180" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L180" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M180" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="N180" s="7">
+        <v>1111.7</v>
+      </c>
+      <c r="O180" s="6">
+        <v>13</v>
+      </c>
+      <c r="P180" s="8">
+        <v>11.35</v>
+      </c>
+      <c r="Q180" s="9">
+        <v>1.031</v>
+      </c>
+      <c r="R180" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A181" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="E181" s="7">
+        <v>1020.15</v>
+      </c>
+      <c r="F181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="G181" s="7">
+        <v>1015.1</v>
+      </c>
+      <c r="H181" s="7">
+        <v>1015.05</v>
+      </c>
+      <c r="I181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="J181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="K181" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L181" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M181" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="N181" s="7">
+        <v>1012.15</v>
+      </c>
+      <c r="O181" s="6">
+        <v>1</v>
+      </c>
+      <c r="P181" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="Q181" s="9">
+        <v>0.286</v>
+      </c>
+      <c r="R181" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E182" s="3">
+        <v>15208</v>
+      </c>
+      <c r="F182" s="3">
+        <v>15150</v>
+      </c>
+      <c r="G182" s="3">
+        <v>15195</v>
+      </c>
+      <c r="H182" s="3">
+        <v>15191</v>
+      </c>
+      <c r="I182" s="3">
+        <v>15150</v>
+      </c>
+      <c r="J182" s="3">
+        <v>15232</v>
+      </c>
+      <c r="K182" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L182" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M182" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="N182" s="3">
+        <v>15150</v>
+      </c>
+      <c r="O182" s="2">
+        <v>3</v>
+      </c>
+      <c r="P182" s="4">
+        <v>-41</v>
+      </c>
+      <c r="Q182" s="5">
+        <v>-0.27</v>
+      </c>
+      <c r="R182" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A183" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="E183" s="7">
+        <v>424.6</v>
+      </c>
+      <c r="F183" s="7">
+        <v>423</v>
+      </c>
+      <c r="G183" s="7">
+        <v>423.15</v>
+      </c>
+      <c r="H183" s="7">
+        <v>423.15</v>
+      </c>
+      <c r="I183" s="7">
+        <v>423</v>
+      </c>
+      <c r="J183" s="7">
+        <v>423</v>
+      </c>
+      <c r="K183" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L183" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M183" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="N183" s="7">
+        <v>423</v>
+      </c>
+      <c r="O183" s="6">
+        <v>1</v>
+      </c>
+      <c r="P183" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="Q183" s="9">
+        <v>0.035</v>
+      </c>
+      <c r="R183" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A184" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E184" s="7">
+        <v>447.35</v>
+      </c>
+      <c r="F184" s="7">
+        <v>445.4</v>
+      </c>
+      <c r="G184" s="7">
+        <v>447.3</v>
+      </c>
+      <c r="H184" s="7">
+        <v>447.3</v>
+      </c>
+      <c r="I184" s="7">
+        <v>445.4</v>
+      </c>
+      <c r="J184" s="7">
+        <v>449.2</v>
+      </c>
+      <c r="K184" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L184" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M184" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="N184" s="7">
+        <v>449.2</v>
+      </c>
+      <c r="O184" s="6">
+        <v>1</v>
+      </c>
+      <c r="P184" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="Q184" s="9">
+        <v>0.425</v>
+      </c>
+      <c r="R184" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A185" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E185" s="13">
+        <v>964.9</v>
+      </c>
+      <c r="F185" s="13">
+        <v>957.25</v>
+      </c>
+      <c r="G185" s="13">
+        <v>963.65</v>
+      </c>
+      <c r="H185" s="13">
+        <v>963.95</v>
+      </c>
+      <c r="I185" s="13">
+        <v>957.25</v>
+      </c>
+      <c r="J185" s="13">
+        <v>970.65</v>
+      </c>
+      <c r="K185" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L185" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="M157" s="12"/>
-      <c r="N157" s="12"/>
-      <c r="O157" s="12"/>
-      <c r="P157" s="12"/>
-      <c r="Q157" s="12"/>
-      <c r="R157" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A158" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="B158" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="C158" s="12" t="s">
+      <c r="M185" s="12"/>
+      <c r="N185" s="12"/>
+      <c r="O185" s="12"/>
+      <c r="P185" s="12"/>
+      <c r="Q185" s="12"/>
+      <c r="R185" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A186" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C186" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D158" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E158" s="13">
-        <v>542.7</v>
-      </c>
-      <c r="F158" s="13">
-        <v>540.05</v>
-      </c>
-      <c r="G158" s="13">
-        <v>541.25</v>
-      </c>
-      <c r="H158" s="13">
-        <v>541.55</v>
-      </c>
-      <c r="I158" s="13">
-        <v>540.05</v>
-      </c>
-      <c r="J158" s="13">
-        <v>543.05</v>
-      </c>
-      <c r="K158" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L158" s="12" t="s">
+      <c r="D186" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E186" s="13">
+        <v>2284</v>
+      </c>
+      <c r="F186" s="13">
+        <v>2271</v>
+      </c>
+      <c r="G186" s="13">
+        <v>2282.5</v>
+      </c>
+      <c r="H186" s="13">
+        <v>2282.6</v>
+      </c>
+      <c r="I186" s="13">
+        <v>2271</v>
+      </c>
+      <c r="J186" s="13">
+        <v>2294.2</v>
+      </c>
+      <c r="K186" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L186" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="M158" s="12"/>
-      <c r="N158" s="12"/>
-      <c r="O158" s="12"/>
-      <c r="P158" s="12"/>
-      <c r="Q158" s="12"/>
-      <c r="R158" s="12" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A160" s="14" t="s">
+      <c r="M186" s="12"/>
+      <c r="N186" s="12"/>
+      <c r="O186" s="12"/>
+      <c r="P186" s="12"/>
+      <c r="Q186" s="12"/>
+      <c r="R186" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A187" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E187" s="13">
+        <v>135.65</v>
+      </c>
+      <c r="F187" s="13">
+        <v>134.95</v>
+      </c>
+      <c r="G187" s="13">
+        <v>135.35</v>
+      </c>
+      <c r="H187" s="13">
+        <v>135.33</v>
+      </c>
+      <c r="I187" s="13">
+        <v>134.95</v>
+      </c>
+      <c r="J187" s="13">
+        <v>135.71</v>
+      </c>
+      <c r="K187" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L187" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M187" s="12"/>
+      <c r="N187" s="12"/>
+      <c r="O187" s="12"/>
+      <c r="P187" s="12"/>
+      <c r="Q187" s="12"/>
+      <c r="R187" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A188" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="B188" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="P160" s="15">
-        <v>530.67</v>
-      </c>
-      <c r="R160" s="14" t="s">
-        <v>406</v>
+      <c r="C188" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E188" s="13">
+        <v>546</v>
+      </c>
+      <c r="F188" s="13">
+        <v>543.15</v>
+      </c>
+      <c r="G188" s="13">
+        <v>545.3</v>
+      </c>
+      <c r="H188" s="13">
+        <v>545.05</v>
+      </c>
+      <c r="I188" s="13">
+        <v>543.15</v>
+      </c>
+      <c r="J188" s="13">
+        <v>546.95</v>
+      </c>
+      <c r="K188" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L188" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M188" s="12"/>
+      <c r="N188" s="12"/>
+      <c r="O188" s="12"/>
+      <c r="P188" s="12"/>
+      <c r="Q188" s="12"/>
+      <c r="R188" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A189" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E189" s="13">
+        <v>391.8</v>
+      </c>
+      <c r="F189" s="13">
+        <v>388.9</v>
+      </c>
+      <c r="G189" s="13">
+        <v>391.65</v>
+      </c>
+      <c r="H189" s="13">
+        <v>391.7</v>
+      </c>
+      <c r="I189" s="13">
+        <v>388.9</v>
+      </c>
+      <c r="J189" s="13">
+        <v>394.5</v>
+      </c>
+      <c r="K189" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L189" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M189" s="12"/>
+      <c r="N189" s="12"/>
+      <c r="O189" s="12"/>
+      <c r="P189" s="12"/>
+      <c r="Q189" s="12"/>
+      <c r="R189" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A190" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D190" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E190" s="13">
+        <v>6880</v>
+      </c>
+      <c r="F190" s="13">
+        <v>6840.5</v>
+      </c>
+      <c r="G190" s="13">
+        <v>6870</v>
+      </c>
+      <c r="H190" s="12"/>
+      <c r="I190" s="13">
+        <v>6840.5</v>
+      </c>
+      <c r="J190" s="12"/>
+      <c r="K190" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L190" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M190" s="12"/>
+      <c r="N190" s="12"/>
+      <c r="O190" s="12"/>
+      <c r="P190" s="12"/>
+      <c r="Q190" s="12"/>
+      <c r="R190" s="12" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A191" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E191" s="13">
+        <v>130.72</v>
+      </c>
+      <c r="F191" s="13">
+        <v>130.13</v>
+      </c>
+      <c r="G191" s="13">
+        <v>130.14</v>
+      </c>
+      <c r="H191" s="12"/>
+      <c r="I191" s="13">
+        <v>130.13</v>
+      </c>
+      <c r="J191" s="12"/>
+      <c r="K191" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L191" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M191" s="12"/>
+      <c r="N191" s="12"/>
+      <c r="O191" s="12"/>
+      <c r="P191" s="12"/>
+      <c r="Q191" s="12"/>
+      <c r="R191" s="12" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A192" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E192" s="13">
+        <v>3970</v>
+      </c>
+      <c r="F192" s="13">
+        <v>3951.8</v>
+      </c>
+      <c r="G192" s="13">
+        <v>3959.9</v>
+      </c>
+      <c r="H192" s="12"/>
+      <c r="I192" s="13">
+        <v>3951.8</v>
+      </c>
+      <c r="J192" s="12"/>
+      <c r="K192" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L192" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M192" s="12"/>
+      <c r="N192" s="12"/>
+      <c r="O192" s="12"/>
+      <c r="P192" s="12"/>
+      <c r="Q192" s="12"/>
+      <c r="R192" s="12" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A194" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="P194" s="15">
+        <v>534.62</v>
+      </c>
+      <c r="R194" s="14" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="584">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -634,814 +634,1135 @@
     <t>NSE:AXISBANK-EQ</t>
   </si>
   <si>
+    <t>2026-03-02 09:15</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:30</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:45</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:30</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:45</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:45</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:15</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:30</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:30</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:30</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:45</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:30</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1771560000_1771826400</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:00</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1771571700_1771828200</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:45</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:45</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:00</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ_BULL_1771569000_1771830000</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1771566300_1771832700</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:15</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:15</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771821000_1771835400</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:00</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1771819200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:45</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:15</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:30</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:00</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ_BULL_1771576200_1771839000</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ_BEAR_1771828200_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BEAR_1771822800_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BEAR_1771834500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ITC-EQ_BEAR_1771821000_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ITC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IOC-EQ_BULL_1771825500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:IOC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:00</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ_BULL_1771834500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:00</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ_BEAR_1771832700_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BULL_1771819200_1771911000</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:00</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ_BEAR_1771836300_1771913700</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:45</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:15</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ_BEAR_1771836300_1771914600</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:30</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BEAR_1771818300_1771915500</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:45</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ_BEAR_1771830900_1771917300</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771821000_1771917300</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BULL_1771907400_1771918200</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:45</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1771904700_1771920000</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:30</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:00</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1771910100_1771920900</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:45</t>
+  </si>
+  <si>
+    <t>NSE:TATACONSUM-EQ_BULL_1771819200_1771920900</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:30</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1771838100_1771922700</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:15</t>
+  </si>
+  <si>
+    <t>NSE:HDFCBANK-EQ_BEAR_1771911000_1771923600</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771923600</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1771910100_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:15</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ_BULL_1771907400_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1771907400_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BULL_1771909200_1771925400</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1771918200_1771925400</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BULL_1771821900_1771926300</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:00</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BULL_1771908300_1771926300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771991100</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:15</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771991100</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:00</t>
+  </si>
+  <si>
+    <t>NSE:PETRONET-EQ_BULL_1771925400_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:PETRONET-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:15</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1771912800_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:45</t>
+  </si>
+  <si>
+    <t>NSE:TATASTEEL-EQ_BULL_1771905600_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:TATASTEEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1771907400_1771992900</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:45</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:30</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ_BULL_1771992000_1771999200</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:30</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:30</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BULL_1771921800_1771999200</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BULL_1771923600_1771999200</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:15</t>
+  </si>
+  <si>
+    <t>NSE:IRCTC-EQ_BEAR_1771906500_1772001900</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:45</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ_BULL_1771907400_1772001900</t>
+  </si>
+  <si>
+    <t>NSE:PAYTM-EQ_BEAR_1771905600_1772002800</t>
+  </si>
+  <si>
+    <t>NSE:PAYTM-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:00</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ_BEAR_1771904700_1772003700</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:15</t>
+  </si>
+  <si>
+    <t>NSE:360ONE-EQ_BULL_1771994700_1772004600</t>
+  </si>
+  <si>
+    <t>NSE:360ONE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:15</t>
+  </si>
+  <si>
+    <t>NSE:ASIANPAINT-EQ_BEAR_1771911000_1772005500</t>
+  </si>
+  <si>
+    <t>NSE:ASIANPAINT-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:45</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BULL_1771991100_1772007300</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:45</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772008200</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:00</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771925400_1772009100</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:15</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BULL_1771997400_1772009100</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:00</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1771992900_1772010000</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1771910100_1772011800</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:15</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1771910100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BULL_1771921800_1772012700</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:00</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BULL_1771999200_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BEAR_1772003700_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771993800_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BULL_1771992000_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1771996500_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:30</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:45</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1771997400_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:45</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BULL_1771994700_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:15</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1772010000_1772078400</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:15</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772078400</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BULL_1771996500_1772079300</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771993800_1772079300</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:15</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1771994700_1772081100</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772081100</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:15</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771992000_1772082000</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 11:30</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ_BEAR_1772007300_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 11:45</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ_BULL_1772009100_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BEAR_1772002800_1772090100</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:15</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ_BULL_1772077500_1772091900</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:15</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ_BEAR_1771993800_1772092800</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772012700_1772096400</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:00</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772098200</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:30</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1772078400_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:00</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ_BEAR_1772092800_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ_BULL_1771994700_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ_BEAR_1772165700_1772184600</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:00</t>
+  </si>
+  <si>
+    <t>NSE:BIOCON-EQ_BEAR_1772167500_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:BIOCON-EQ</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1772163900_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BEAR_1772165700_1772176500</t>
+  </si>
+  <si>
+    <t>2026-02-27 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-27 13:15</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ_BEAR_1772164800_1772169300</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 11:15</t>
+  </si>
+  <si>
+    <t>NSE:HINDUNILVR-EQ_BEAR_1772166600_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:HINDUNILVR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ICICIGI-EQ_BEAR_1772164800_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:ICICIGI-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1772172000_1772185500</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-04 09:15</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1772167500_1772185500</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:30</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1772165700_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BEAR_1772168400_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BEAR_1772169300_1772185500</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 98 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:30</t>
-  </si>
-  <si>
-    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:BANKINDIA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 09:45</t>
-  </si>
-  <si>
-    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:POWERINDIA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 10:30</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 09:45</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:LTF-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 11:45</t>
-  </si>
-  <si>
-    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:NESTLEIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 09:15</t>
-  </si>
-  <si>
-    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:RVNL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 11:30</t>
-  </si>
-  <si>
-    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:SBILIFE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:30</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ</t>
-  </si>
-  <si>
-    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:FEDERALBNK-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-26 09:30</t>
-  </si>
-  <si>
-    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
-  </si>
-  <si>
-    <t>NSE:FORTIS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
-  </si>
-  <si>
-    <t>2026-02-23 10:00</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 10:15</t>
-  </si>
-  <si>
-    <t>2026-02-23 10:45</t>
-  </si>
-  <si>
-    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:HUDCO-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
-  </si>
-  <si>
-    <t>2026-02-23 14:30</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ_BEAR_1771560000_1771826400</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:00</t>
-  </si>
-  <si>
-    <t>NSE:POLYCAB-EQ_BULL_1771571700_1771828200</t>
-  </si>
-  <si>
-    <t>NSE:POLYCAB-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 13:45</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:15</t>
-  </si>
-  <si>
-    <t>2026-02-23 12:45</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
-  </si>
-  <si>
-    <t>2026-02-23 13:00</t>
-  </si>
-  <si>
-    <t>NSE:POWERGRID-EQ_BULL_1771569000_1771830000</t>
-  </si>
-  <si>
-    <t>NSE:POWERGRID-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SUNPHARMA-EQ_BULL_1771566300_1771832700</t>
-  </si>
-  <si>
-    <t>2026-02-23 13:15</t>
-  </si>
-  <si>
-    <t>2026-02-23 15:15</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ_BEAR_1771821000_1771835400</t>
-  </si>
-  <si>
-    <t>2026-02-23 14:00</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ_BULL_1771819200_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 14:45</t>
-  </si>
-  <si>
-    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:PIIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 10:15</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:SYNGENE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 09:30</t>
-  </si>
-  <si>
-    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
-  </si>
-  <si>
-    <t>2026-02-23 15:00</t>
-  </si>
-  <si>
-    <t>NSE:APOLLOHOSP-EQ_BULL_1771576200_1771839000</t>
-  </si>
-  <si>
-    <t>NSE:APOLLOHOSP-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:RVNL-EQ_BULL_1771570800_1771839900</t>
-  </si>
-  <si>
-    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771839900</t>
-  </si>
-  <si>
-    <t>NSE:ABCAPITAL-EQ_BEAR_1771828200_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:ABCAPITAL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BDL-EQ_BEAR_1771822800_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:BDL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:DIVISLAB-EQ_BEAR_1771834500_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:ITC-EQ_BEAR_1771821000_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:ITC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IOC-EQ_BULL_1771825500_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:IOC-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 15:00</t>
-  </si>
-  <si>
-    <t>NSE:OIL-EQ_BULL_1771834500_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:OIL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 10:00</t>
-  </si>
-  <si>
-    <t>NSE:SBICARD-EQ_BEAR_1771832700_1771904700</t>
-  </si>
-  <si>
-    <t>NSE:SBICARD-EQ</t>
-  </si>
-  <si>
-    <t>NSE:GODREJCP-EQ_BULL_1771819200_1771911000</t>
-  </si>
-  <si>
-    <t>2026-02-24 11:00</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:00</t>
-  </si>
-  <si>
-    <t>NSE:PATANJALI-EQ_BEAR_1771836300_1771913700</t>
-  </si>
-  <si>
-    <t>NSE:PATANJALI-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 11:45</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:15</t>
-  </si>
-  <si>
-    <t>NSE:POLICYBZR-EQ_BEAR_1771836300_1771914600</t>
-  </si>
-  <si>
-    <t>NSE:POLICYBZR-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:30</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ_BEAR_1771818300_1771915500</t>
-  </si>
-  <si>
-    <t>2026-02-24 12:45</t>
-  </si>
-  <si>
-    <t>NSE:SHREECEM-EQ_BEAR_1771830900_1771917300</t>
-  </si>
-  <si>
-    <t>NSE:SHREECEM-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SAIL-EQ_BEAR_1771821000_1771917300</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ_BULL_1771907400_1771918200</t>
-  </si>
-  <si>
-    <t>2026-02-24 13:00</t>
-  </si>
-  <si>
-    <t>2026-02-24 13:45</t>
-  </si>
-  <si>
-    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1771904700_1771920000</t>
-  </si>
-  <si>
-    <t>2026-02-24 13:30</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:00</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ_BULL_1771910100_1771920900</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:45</t>
-  </si>
-  <si>
-    <t>NSE:TATACONSUM-EQ_BULL_1771819200_1771920900</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:30</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BEAR_1771838100_1771922700</t>
-  </si>
-  <si>
-    <t>2026-02-24 14:15</t>
-  </si>
-  <si>
-    <t>NSE:HDFCBANK-EQ_BEAR_1771911000_1771923600</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771923600</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BULL_1771910100_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-24 15:15</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:JSWSTEEL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LICHSGFIN-EQ_BULL_1771907400_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:LICHSGFIN-EQ</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ_BULL_1771907400_1771924500</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BRITANNIA-EQ_BULL_1771909200_1771925400</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ_BULL_1771918200_1771925400</t>
-  </si>
-  <si>
-    <t>NSE:ADANIPORTS-EQ_BULL_1771821900_1771926300</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:00</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ_BULL_1771908300_1771926300</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771991100</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:15</t>
-  </si>
-  <si>
-    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771991100</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:00</t>
-  </si>
-  <si>
-    <t>NSE:PETRONET-EQ_BULL_1771925400_1771991100</t>
-  </si>
-  <si>
-    <t>NSE:PETRONET-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 11:15</t>
-  </si>
-  <si>
-    <t>NSE:PFC-EQ_BULL_1771912800_1771991100</t>
-  </si>
-  <si>
-    <t>NSE:PFC-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:45</t>
-  </si>
-  <si>
-    <t>NSE:TATASTEEL-EQ_BULL_1771905600_1771991100</t>
-  </si>
-  <si>
-    <t>NSE:TATASTEEL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ_BULL_1771907400_1771992900</t>
-  </si>
-  <si>
-    <t>2026-02-25 09:45</t>
-  </si>
-  <si>
-    <t>2026-02-25 10:30</t>
-  </si>
-  <si>
-    <t>NSE:HEROMOTOCO-EQ_BULL_1771992000_1771999200</t>
-  </si>
-  <si>
-    <t>NSE:HEROMOTOCO-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 11:30</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:30</t>
-  </si>
-  <si>
-    <t>NSE:HINDZINC-EQ_BULL_1771921800_1771999200</t>
-  </si>
-  <si>
-    <t>NSE:HINDZINC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ_BULL_1771923600_1771999200</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:15</t>
-  </si>
-  <si>
-    <t>NSE:IRCTC-EQ_BEAR_1771906500_1772001900</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:45</t>
-  </si>
-  <si>
-    <t>NSE:PIDILITIND-EQ_BULL_1771907400_1772001900</t>
-  </si>
-  <si>
-    <t>NSE:PAYTM-EQ_BEAR_1771905600_1772002800</t>
-  </si>
-  <si>
-    <t>NSE:PAYTM-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 13:00</t>
-  </si>
-  <si>
-    <t>NSE:CONCOR-EQ_BEAR_1771904700_1772003700</t>
-  </si>
-  <si>
-    <t>2026-02-25 13:15</t>
-  </si>
-  <si>
-    <t>NSE:360ONE-EQ_BULL_1771994700_1772004600</t>
-  </si>
-  <si>
-    <t>NSE:360ONE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:15</t>
-  </si>
-  <si>
-    <t>NSE:ASIANPAINT-EQ_BEAR_1771911000_1772005500</t>
-  </si>
-  <si>
-    <t>NSE:ASIANPAINT-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 13:45</t>
-  </si>
-  <si>
-    <t>NSE:SAMMAANCAP-EQ_BULL_1771991100_1772007300</t>
-  </si>
-  <si>
-    <t>NSE:SAMMAANCAP-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:45</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ_BULL_1771991100_1772008200</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:00</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ_BULL_1771925400_1772009100</t>
-  </si>
-  <si>
-    <t>2026-02-25 14:15</t>
-  </si>
-  <si>
-    <t>NSE:UNOMINDA-EQ_BULL_1771997400_1772009100</t>
-  </si>
-  <si>
-    <t>NSE:UNOMINDA-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:00</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ_BULL_1771992900_1772010000</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BULL_1771910100_1772011800</t>
-  </si>
-  <si>
-    <t>2026-02-26 09:15</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ_BULL_1771910100_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:IIFL-EQ_BULL_1771995600_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BULL_1771997400_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:SONACOMS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:HINDZINC-EQ_BULL_1771921800_1772012700</t>
-  </si>
-  <si>
-    <t>2026-02-26 10:00</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ_BULL_1771991100_1772011800</t>
-  </si>
-  <si>
-    <t>NSE:APLAPOLLO-EQ_BULL_1771999200_1772077500</t>
-  </si>
-  <si>
-    <t>2026-02-26 09:45</t>
-  </si>
-  <si>
-    <t>NSE:AUBANK-EQ_BEAR_1772003700_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:AUBANK-EQ</t>
-  </si>
-  <si>
-    <t>NSE:DIVISLAB-EQ_BULL_1771995600_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:FORTIS-EQ_BULL_1771993800_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:GAIL-EQ_BULL_1771991100_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:GAIL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IEX-EQ_BULL_1771992000_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:INDUSINDBK-EQ</t>
-  </si>
-  <si>
-    <t>NSE:KAYNES-EQ_BULL_1771996500_1772077500</t>
-  </si>
-  <si>
-    <t>2026-02-26 12:30</t>
-  </si>
-  <si>
-    <t>NSE:NCC-EQ_BULL_1771995600_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:NCC-EQ</t>
+    <t>Checked 74 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BEAR_1772170200_1772181000</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:30</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1772170200_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ_BEAR_1772164800_1772424000</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:00</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ_BEAR_1772167500_1772425800</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:30</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:45</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BEAR_1772163900_1772425800</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1772172000_1772432100</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:15</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ_BEAR_1772164800_1772432100</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1772430300_1772595900</t>
+  </si>
+  <si>
+    <t>2026-03-04 09:45</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1772431200_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IDFCFIRSTB-EQ_BEAR_1772423100_1772601300</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 11:15</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ_BEAR_1772426700_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ_BEAR_1772423100_1772604900</t>
+  </si>
+  <si>
+    <t>2026-03-04 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 12:15</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ_BEAR_1772423100_1772605800</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-04 12:30</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772609400</t>
+  </si>
+  <si>
+    <t>2026-03-04 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-04 14:15</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ_BULL_1772424900_1772615700</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-05 09:15</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BEAR_1772424000_1772617500</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-05 09:30</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ_BEAR_1772423100_1772616600</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:00</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BEAR_1772423100_1772616600</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ_BEAR_1772427600_1772616600</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772616600</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1772423100_1772617500</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772617500</t>
+  </si>
+  <si>
+    <t>Checked 24 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1772598600_1772682300</t>
   </si>
   <si>
     <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
-    <t>NSE:PNBHOUSING-EQ_BULL_1771997400_1772077500</t>
-  </si>
-  <si>
-    <t>NSE:PNBHOUSING-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SHRIRAMFIN-EQ_BULL_1771994700_1772077500</t>
-  </si>
-  <si>
-    <t>2026-02-26 12:15</t>
-  </si>
-  <si>
-    <t>NSE:BSE-EQ_BULL_1772010000_1772078400</t>
-  </si>
-  <si>
-    <t>NSE:BSE-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-26 10:15</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BULL_1771997400_1772078400</t>
-  </si>
-  <si>
-    <t>NSE:CIPLA-EQ_BULL_1771996500_1772079300</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BULL_1771993800_1772079300</t>
-  </si>
-  <si>
-    <t>Checked 21 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:SOLARINDS-EQ_BULL_1771994700_1772081100</t>
-  </si>
-  <si>
-    <t>Checked 19 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:TMPV-EQ_BULL_1771997400_1772081100</t>
-  </si>
-  <si>
-    <t>2026-02-26 15:15</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ_BULL_1771992000_1772082000</t>
-  </si>
-  <si>
-    <t>2026-02-26 10:30</t>
-  </si>
-  <si>
-    <t>2026-02-26 11:30</t>
-  </si>
-  <si>
-    <t>NSE:BAJAJFINSV-EQ_BEAR_1772007300_1772086500</t>
-  </si>
-  <si>
-    <t>NSE:BAJAJFINSV-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-26 11:45</t>
-  </si>
-  <si>
-    <t>NSE:MAXHEALTH-EQ_BULL_1772009100_1772086500</t>
-  </si>
-  <si>
-    <t>NSE:MAXHEALTH-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ_BEAR_1772002800_1772090100</t>
-  </si>
-  <si>
-    <t>2026-02-26 12:45</t>
-  </si>
-  <si>
-    <t>2026-02-26 13:15</t>
-  </si>
-  <si>
-    <t>NSE:MARUTI-EQ_BULL_1772077500_1772091900</t>
-  </si>
-  <si>
-    <t>NSE:MARUTI-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-26 14:15</t>
-  </si>
-  <si>
-    <t>NSE:KOTAKBANK-EQ_BEAR_1771993800_1772092800</t>
-  </si>
-  <si>
-    <t>NSE:KOTAKBANK-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-26 13:30</t>
-  </si>
-  <si>
-    <t>2026-02-26 14:00</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ_BULL_1772012700_1772096400</t>
-  </si>
-  <si>
-    <t>2026-02-26 14:30</t>
-  </si>
-  <si>
-    <t>2026-02-26 15:00</t>
-  </si>
-  <si>
-    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772098200</t>
+    <t>NSE:LUPIN-EQ_BULL_1772615700_1772682300</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772693100</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-05 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-05 12:45</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BULL_1772685900_1772701200</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:30</t>
+  </si>
+  <si>
+    <t>Checked 2 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772701200</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BEAR_1772595900_1772702100</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-05 15:15</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BULL_1772691300_1772702100</t>
+  </si>
+  <si>
+    <t>Checked 1 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BEAR_1772686800_1772703000</t>
+  </si>
+  <si>
+    <t>2026-03-05 15:00</t>
   </si>
   <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>NSE:MANKIND-EQ_BULL_1771991100_1772098200</t>
-  </si>
-  <si>
-    <t>NSE:MOTHERSON-EQ_BULL_1771991100_1772098200</t>
-  </si>
-  <si>
-    <t>NSE:MOTHERSON-EQ</t>
-  </si>
-  <si>
-    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772098200</t>
-  </si>
-  <si>
-    <t>NSE:TMPV-EQ_BULL_1771997400_1772098200</t>
-  </si>
-  <si>
-    <t>NSE:OFSS-EQ_BULL_1772078400_1772099100</t>
-  </si>
-  <si>
-    <t>NSE:OFSS-EQ</t>
-  </si>
-  <si>
-    <t>Entry candle not yet available — trade not entered</t>
-  </si>
-  <si>
-    <t>NSE:PNB-EQ_BEAR_1772092800_1772099100</t>
-  </si>
-  <si>
-    <t>NSE:PNB-EQ</t>
-  </si>
-  <si>
-    <t>NSE:TVSMOTOR-EQ_BULL_1771994700_1772099100</t>
-  </si>
-  <si>
-    <t>NSE:TVSMOTOR-EQ</t>
-  </si>
-  <si>
-    <t>SUMMARY — 64W / 114L / 13 OPEN  |  Win Rate: 36.0%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 178 of 191</t>
+    <t>SUMMARY — 75W / 159L / 8 OPEN  |  Win Rate: 32.1%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 234 of 242</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +2223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R194"/>
+  <dimension ref="A1:R245"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5843,57 +6164,67 @@
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="3">
         <v>1397.6</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="3">
         <v>1380.2</v>
       </c>
-      <c r="G71" s="13">
+      <c r="G71" s="3">
         <v>1396.5</v>
       </c>
-      <c r="H71" s="13">
+      <c r="H71" s="3">
         <v>1396.4</v>
       </c>
-      <c r="I71" s="13">
+      <c r="I71" s="3">
         <v>1380.2</v>
       </c>
-      <c r="J71" s="13">
+      <c r="J71" s="3">
         <v>1412.6</v>
       </c>
-      <c r="K71" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L71" s="12" t="s">
+      <c r="K71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M71" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="M71" s="12"/>
-      <c r="N71" s="12"/>
-      <c r="O71" s="12"/>
-      <c r="P71" s="12"/>
-      <c r="Q71" s="12"/>
-      <c r="R71" s="12" t="s">
-        <v>208</v>
+      <c r="N71" s="3">
+        <v>1380.2</v>
+      </c>
+      <c r="O71" s="2">
+        <v>124</v>
+      </c>
+      <c r="P71" s="4">
+        <v>-16.2</v>
+      </c>
+      <c r="Q71" s="5">
+        <v>-1.16</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>20</v>
@@ -5926,7 +6257,7 @@
         <v>33</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N72" s="7">
         <v>1042.05</v>
@@ -5946,10 +6277,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>20</v>
@@ -5982,7 +6313,7 @@
         <v>33</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N73" s="7">
         <v>176.77</v>
@@ -6002,10 +6333,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>20</v>
@@ -6038,7 +6369,7 @@
         <v>33</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N74" s="7">
         <v>24475</v>
@@ -6058,10 +6389,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>20</v>
@@ -6094,7 +6425,7 @@
         <v>23</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N75" s="3">
         <v>1219.1</v>
@@ -6114,7 +6445,7 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>116</v>
@@ -6150,7 +6481,7 @@
         <v>23</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N76" s="3">
         <v>492.05</v>
@@ -6170,10 +6501,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>20</v>
@@ -6206,7 +6537,7 @@
         <v>23</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N77" s="3">
         <v>298.4</v>
@@ -6226,10 +6557,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>20</v>
@@ -6262,7 +6593,7 @@
         <v>33</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N78" s="7">
         <v>1324.1</v>
@@ -6282,10 +6613,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>20</v>
@@ -6318,7 +6649,7 @@
         <v>33</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N79" s="7">
         <v>316.1</v>
@@ -6338,10 +6669,10 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>20</v>
@@ -6374,7 +6705,7 @@
         <v>23</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N80" s="3">
         <v>2072.2</v>
@@ -6394,10 +6725,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>20</v>
@@ -6450,10 +6781,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>20</v>
@@ -6486,7 +6817,7 @@
         <v>33</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N82" s="7">
         <v>301.2</v>
@@ -6506,10 +6837,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>20</v>
@@ -6542,7 +6873,7 @@
         <v>23</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N83" s="3">
         <v>921.75</v>
@@ -6562,7 +6893,7 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>183</v>
@@ -6598,7 +6929,7 @@
         <v>23</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N84" s="3">
         <v>4786.5</v>
@@ -6618,16 +6949,16 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E85" s="7">
         <v>441.25</v>
@@ -6654,7 +6985,7 @@
         <v>33</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N85" s="7">
         <v>439.05</v>
@@ -6674,16 +7005,16 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E86" s="7">
         <v>196.2</v>
@@ -6710,7 +7041,7 @@
         <v>33</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N86" s="7">
         <v>195.5</v>
@@ -6730,16 +7061,16 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E87" s="7">
         <v>1025.5</v>
@@ -6766,7 +7097,7 @@
         <v>33</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N87" s="7">
         <v>1022.3</v>
@@ -6786,7 +7117,7 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>40</v>
@@ -6822,7 +7153,7 @@
         <v>23</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N88" s="3">
         <v>879.15</v>
@@ -6842,16 +7173,16 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E89" s="3">
         <v>1160.4</v>
@@ -6878,7 +7209,7 @@
         <v>23</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N89" s="3">
         <v>1154.6</v>
@@ -6898,16 +7229,16 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E90" s="7">
         <v>7984</v>
@@ -6934,7 +7265,7 @@
         <v>33</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N90" s="7">
         <v>7998</v>
@@ -6954,16 +7285,16 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E91" s="3">
         <v>1402.8</v>
@@ -6990,7 +7321,7 @@
         <v>23</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N91" s="3">
         <v>1399.1</v>
@@ -7010,16 +7341,16 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E92" s="3">
         <v>1046</v>
@@ -7046,7 +7377,7 @@
         <v>23</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N92" s="3">
         <v>1037</v>
@@ -7066,16 +7397,16 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E93" s="3">
         <v>303.9</v>
@@ -7102,7 +7433,7 @@
         <v>23</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N93" s="3">
         <v>302.45</v>
@@ -7122,7 +7453,7 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>47</v>
@@ -7131,7 +7462,7 @@
         <v>20</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E94" s="7">
         <v>1730.3</v>
@@ -7158,7 +7489,7 @@
         <v>33</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N94" s="7">
         <v>1735</v>
@@ -7178,7 +7509,7 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>131</v>
@@ -7187,7 +7518,7 @@
         <v>64</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E95" s="3">
         <v>156.75</v>
@@ -7214,7 +7545,7 @@
         <v>23</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N95" s="3">
         <v>156.05</v>
@@ -7234,16 +7565,16 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E96" s="3">
         <v>434.2</v>
@@ -7290,16 +7621,16 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E97" s="3">
         <v>3135.5</v>
@@ -7326,7 +7657,7 @@
         <v>23</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N97" s="3">
         <v>3093.2</v>
@@ -7346,16 +7677,16 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E98" s="7">
         <v>799.9</v>
@@ -7382,7 +7713,7 @@
         <v>33</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N98" s="7">
         <v>803.75</v>
@@ -7402,16 +7733,16 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E99" s="3">
         <v>447.7</v>
@@ -7438,7 +7769,7 @@
         <v>23</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N99" s="3">
         <v>442.55</v>
@@ -7458,7 +7789,7 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>95</v>
@@ -7467,7 +7798,7 @@
         <v>20</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E100" s="7">
         <v>514.5</v>
@@ -7514,16 +7845,16 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E101" s="3">
         <v>7697.5</v>
@@ -7570,16 +7901,16 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E102" s="7">
         <v>373.9</v>
@@ -7606,7 +7937,7 @@
         <v>33</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N102" s="7">
         <v>371.7</v>
@@ -7626,16 +7957,16 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E103" s="3">
         <v>320.9</v>
@@ -7662,7 +7993,7 @@
         <v>23</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N103" s="3">
         <v>318.1</v>
@@ -7682,7 +8013,7 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>189</v>
@@ -7691,7 +8022,7 @@
         <v>20</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E104" s="7">
         <v>4325</v>
@@ -7718,7 +8049,7 @@
         <v>33</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N104" s="7">
         <v>4314</v>
@@ -7738,10 +8069,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>64</v>
@@ -7774,7 +8105,7 @@
         <v>23</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N105" s="3">
         <v>341.65</v>
@@ -7794,10 +8125,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>64</v>
@@ -7830,7 +8161,7 @@
         <v>23</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N106" s="3">
         <v>1248.3</v>
@@ -7850,7 +8181,7 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>67</v>
@@ -7886,7 +8217,7 @@
         <v>23</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N107" s="3">
         <v>6230</v>
@@ -7906,10 +8237,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>64</v>
@@ -7942,7 +8273,7 @@
         <v>23</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N108" s="3">
         <v>322.65</v>
@@ -7962,10 +8293,10 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>20</v>
@@ -7998,7 +8329,7 @@
         <v>33</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N109" s="7">
         <v>179.87</v>
@@ -8018,10 +8349,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>20</v>
@@ -8054,7 +8385,7 @@
         <v>23</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N110" s="3">
         <v>473.5</v>
@@ -8074,10 +8405,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>64</v>
@@ -8110,7 +8441,7 @@
         <v>23</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N111" s="3">
         <v>769.55</v>
@@ -8130,7 +8461,7 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>99</v>
@@ -8139,7 +8470,7 @@
         <v>20</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E112" s="3">
         <v>1229.2</v>
@@ -8166,7 +8497,7 @@
         <v>23</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N112" s="3">
         <v>1222.3</v>
@@ -8186,16 +8517,16 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B113" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E113" s="7">
         <v>529.7</v>
@@ -8222,7 +8553,7 @@
         <v>33</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N113" s="7">
         <v>526</v>
@@ -8242,16 +8573,16 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E114" s="3">
         <v>1491</v>
@@ -8278,7 +8609,7 @@
         <v>23</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N114" s="3">
         <v>1485.9</v>
@@ -8298,7 +8629,7 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>110</v>
@@ -8307,7 +8638,7 @@
         <v>64</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E115" s="7">
         <v>126.41</v>
@@ -8334,7 +8665,7 @@
         <v>33</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N115" s="7">
         <v>125.9</v>
@@ -8354,16 +8685,16 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E116" s="3">
         <v>26505</v>
@@ -8410,7 +8741,7 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>131</v>
@@ -8419,7 +8750,7 @@
         <v>64</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E117" s="3">
         <v>156.1</v>
@@ -8466,7 +8797,7 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>112</v>
@@ -8475,7 +8806,7 @@
         <v>20</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E118" s="3">
         <v>171.45</v>
@@ -8502,7 +8833,7 @@
         <v>23</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N118" s="3">
         <v>170.13</v>
@@ -8522,7 +8853,7 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>19</v>
@@ -8531,7 +8862,7 @@
         <v>64</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E119" s="3">
         <v>9810</v>
@@ -8558,7 +8889,7 @@
         <v>23</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N119" s="3">
         <v>9769.5</v>
@@ -8578,16 +8909,16 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E120" s="3">
         <v>2049.3</v>
@@ -8614,7 +8945,7 @@
         <v>23</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N120" s="3">
         <v>2039</v>
@@ -8634,7 +8965,7 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>51</v>
@@ -8643,7 +8974,7 @@
         <v>20</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E121" s="3">
         <v>1177.1</v>
@@ -8670,7 +9001,7 @@
         <v>23</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N121" s="3">
         <v>1171</v>
@@ -8690,7 +9021,7 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>116</v>
@@ -8699,7 +9030,7 @@
         <v>64</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E122" s="3">
         <v>482.35</v>
@@ -8726,7 +9057,7 @@
         <v>23</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N122" s="3">
         <v>480.55</v>
@@ -8746,7 +9077,7 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>198</v>
@@ -8755,7 +9086,7 @@
         <v>64</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E123" s="3">
         <v>914.25</v>
@@ -8782,7 +9113,7 @@
         <v>23</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N123" s="3">
         <v>912.15</v>
@@ -8802,16 +9133,16 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E124" s="3">
         <v>1388.1</v>
@@ -8838,7 +9169,7 @@
         <v>23</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N124" s="3">
         <v>1384.4</v>
@@ -8858,16 +9189,16 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B125" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E125" s="7">
         <v>1659.8</v>
@@ -8894,7 +9225,7 @@
         <v>33</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N125" s="7">
         <v>1667.7</v>
@@ -8914,16 +9245,16 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E126" s="7">
         <v>1238.4</v>
@@ -8950,7 +9281,7 @@
         <v>33</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N126" s="7">
         <v>1245.2</v>
@@ -8970,16 +9301,16 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B127" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E127" s="7">
         <v>1256</v>
@@ -9006,7 +9337,7 @@
         <v>33</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N127" s="7">
         <v>1261.9</v>
@@ -9026,16 +9357,16 @@
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B128" s="6" t="s">
         <v>342</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E128" s="7">
         <v>531.45</v>
@@ -9062,7 +9393,7 @@
         <v>33</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N128" s="7">
         <v>535.1</v>
@@ -9082,16 +9413,16 @@
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B129" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E129" s="7">
         <v>693.5</v>
@@ -9118,7 +9449,7 @@
         <v>33</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N129" s="7">
         <v>696.6</v>
@@ -9138,7 +9469,7 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>179</v>
@@ -9147,7 +9478,7 @@
         <v>20</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E130" s="7">
         <v>6173</v>
@@ -9174,7 +9505,7 @@
         <v>33</v>
       </c>
       <c r="M130" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N130" s="7">
         <v>6191</v>
@@ -9194,16 +9525,16 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E131" s="7">
         <v>437.35</v>
@@ -9230,7 +9561,7 @@
         <v>33</v>
       </c>
       <c r="M131" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N131" s="7">
         <v>438.7</v>
@@ -9250,7 +9581,7 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>80</v>
@@ -9259,7 +9590,7 @@
         <v>20</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E132" s="7">
         <v>1564</v>
@@ -9286,7 +9617,7 @@
         <v>33</v>
       </c>
       <c r="M132" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N132" s="7">
         <v>1580.4</v>
@@ -9306,7 +9637,7 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>150</v>
@@ -9315,7 +9646,7 @@
         <v>20</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E133" s="7">
         <v>8011</v>
@@ -9342,7 +9673,7 @@
         <v>33</v>
       </c>
       <c r="M133" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N133" s="7">
         <v>8028.5</v>
@@ -9362,16 +9693,16 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E134" s="7">
         <v>1249.9</v>
@@ -9398,7 +9729,7 @@
         <v>33</v>
       </c>
       <c r="M134" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="N134" s="7">
         <v>1253.9</v>
@@ -9418,16 +9749,16 @@
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E135" s="7">
         <v>1270.1</v>
@@ -9454,7 +9785,7 @@
         <v>33</v>
       </c>
       <c r="M135" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N135" s="7">
         <v>1282.7</v>
@@ -9474,16 +9805,16 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B136" s="6" t="s">
         <v>355</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>356</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E136" s="7">
         <v>312.75</v>
@@ -9510,7 +9841,7 @@
         <v>33</v>
       </c>
       <c r="M136" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N136" s="7">
         <v>315.55</v>
@@ -9530,16 +9861,16 @@
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E137" s="3">
         <v>425.25</v>
@@ -9566,7 +9897,7 @@
         <v>23</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N137" s="3">
         <v>419.65</v>
@@ -9586,16 +9917,16 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B138" s="6" t="s">
         <v>361</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>362</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E138" s="7">
         <v>212.1</v>
@@ -9622,7 +9953,7 @@
         <v>33</v>
       </c>
       <c r="M138" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N138" s="7">
         <v>214.8</v>
@@ -9642,16 +9973,16 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E139" s="7">
         <v>722.9</v>
@@ -9678,7 +10009,7 @@
         <v>33</v>
       </c>
       <c r="M139" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N139" s="7">
         <v>731.6</v>
@@ -9698,16 +10029,16 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E140" s="3">
         <v>5827.5</v>
@@ -9734,7 +10065,7 @@
         <v>23</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N140" s="3">
         <v>5758.5</v>
@@ -9754,16 +10085,16 @@
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E141" s="3">
         <v>621.3</v>
@@ -9790,7 +10121,7 @@
         <v>23</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N141" s="3">
         <v>616.4</v>
@@ -9810,16 +10141,16 @@
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E142" s="7">
         <v>1061</v>
@@ -9846,7 +10177,7 @@
         <v>33</v>
       </c>
       <c r="M142" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="N142" s="7">
         <v>1069.9</v>
@@ -9866,7 +10197,7 @@
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>72</v>
@@ -9875,7 +10206,7 @@
         <v>64</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E143" s="3">
         <v>612.45</v>
@@ -9902,7 +10233,7 @@
         <v>23</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N143" s="3">
         <v>607.75</v>
@@ -9922,7 +10253,7 @@
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>74</v>
@@ -9931,7 +10262,7 @@
         <v>20</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E144" s="3">
         <v>1501.2</v>
@@ -9958,7 +10289,7 @@
         <v>23</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N144" s="3">
         <v>1495.4</v>
@@ -9978,16 +10309,16 @@
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E145" s="3">
         <v>1135.6</v>
@@ -10014,7 +10345,7 @@
         <v>23</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N145" s="3">
         <v>1126.2</v>
@@ -10034,7 +10365,7 @@
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>92</v>
@@ -10043,7 +10374,7 @@
         <v>64</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E146" s="3">
         <v>501.05</v>
@@ -10070,7 +10401,7 @@
         <v>23</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N146" s="3">
         <v>499.25</v>
@@ -10090,16 +10421,16 @@
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B147" s="6" t="s">
         <v>382</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>383</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E147" s="7">
         <v>1130.9</v>
@@ -10126,7 +10457,7 @@
         <v>33</v>
       </c>
       <c r="M147" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N147" s="7">
         <v>1136.9</v>
@@ -10146,16 +10477,16 @@
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E148" s="3">
         <v>2408.4</v>
@@ -10182,7 +10513,7 @@
         <v>23</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N148" s="3">
         <v>2400</v>
@@ -10202,16 +10533,16 @@
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E149" s="3">
         <v>161.4</v>
@@ -10238,7 +10569,7 @@
         <v>23</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N149" s="3">
         <v>158.78</v>
@@ -10258,7 +10589,7 @@
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>176</v>
@@ -10267,7 +10598,7 @@
         <v>20</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E150" s="7">
         <v>2128</v>
@@ -10294,7 +10625,7 @@
         <v>33</v>
       </c>
       <c r="M150" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N150" s="7">
         <v>2136.3</v>
@@ -10314,16 +10645,16 @@
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E151" s="7">
         <v>379.15</v>
@@ -10350,7 +10681,7 @@
         <v>33</v>
       </c>
       <c r="M151" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N151" s="7">
         <v>380.2</v>
@@ -10370,16 +10701,16 @@
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B152" s="6" t="s">
         <v>395</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>396</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E152" s="7">
         <v>1215</v>
@@ -10406,7 +10737,7 @@
         <v>33</v>
       </c>
       <c r="M152" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N152" s="7">
         <v>1219.9</v>
@@ -10426,16 +10757,16 @@
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E153" s="7">
         <v>1213.8</v>
@@ -10462,7 +10793,7 @@
         <v>33</v>
       </c>
       <c r="M153" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N153" s="7">
         <v>1212.5</v>
@@ -10482,16 +10813,16 @@
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E154" s="3">
         <v>1687.5</v>
@@ -10518,7 +10849,7 @@
         <v>23</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N154" s="3">
         <v>1677.5</v>
@@ -10538,16 +10869,16 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E155" s="7">
         <v>2088.9</v>
@@ -10574,7 +10905,7 @@
         <v>33</v>
       </c>
       <c r="M155" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N155" s="7">
         <v>2094.2</v>
@@ -10594,7 +10925,7 @@
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>70</v>
@@ -10603,7 +10934,7 @@
         <v>20</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E156" s="3">
         <v>510.4</v>
@@ -10630,7 +10961,7 @@
         <v>23</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N156" s="3">
         <v>506.3</v>
@@ -10650,7 +10981,7 @@
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>123</v>
@@ -10659,7 +10990,7 @@
         <v>20</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E157" s="7">
         <v>624.1</v>
@@ -10686,7 +11017,7 @@
         <v>33</v>
       </c>
       <c r="M157" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N157" s="7">
         <v>629.75</v>
@@ -10706,16 +11037,16 @@
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E158" s="3">
         <v>542.7</v>
@@ -10742,7 +11073,7 @@
         <v>23</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N158" s="3">
         <v>540.05</v>
@@ -10762,16 +11093,16 @@
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E159" s="3">
         <v>620.5</v>
@@ -10798,7 +11129,7 @@
         <v>23</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N159" s="3">
         <v>616.25</v>
@@ -10818,7 +11149,7 @@
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>176</v>
@@ -10827,7 +11158,7 @@
         <v>20</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E160" s="7">
         <v>2164.5</v>
@@ -10854,7 +11185,7 @@
         <v>33</v>
       </c>
       <c r="M160" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N160" s="7">
         <v>2178.2</v>
@@ -10874,7 +11205,7 @@
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>163</v>
@@ -10883,7 +11214,7 @@
         <v>20</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E161" s="3">
         <v>2247.7</v>
@@ -10910,7 +11241,7 @@
         <v>23</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N161" s="3">
         <v>2234.3</v>
@@ -10930,16 +11261,16 @@
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E162" s="3">
         <v>982.9</v>
@@ -10966,7 +11297,7 @@
         <v>23</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N162" s="3">
         <v>973</v>
@@ -10986,7 +11317,7 @@
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>67</v>
@@ -10995,7 +11326,7 @@
         <v>20</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E163" s="7">
         <v>6468</v>
@@ -11022,7 +11353,7 @@
         <v>33</v>
       </c>
       <c r="M163" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N163" s="7">
         <v>6510</v>
@@ -11042,16 +11373,16 @@
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E164" s="7">
         <v>948</v>
@@ -11078,7 +11409,7 @@
         <v>33</v>
       </c>
       <c r="M164" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N164" s="7">
         <v>959.35</v>
@@ -11098,16 +11429,16 @@
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E165" s="3">
         <v>171.2</v>
@@ -11134,7 +11465,7 @@
         <v>23</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N165" s="3">
         <v>170.3</v>
@@ -11154,7 +11485,7 @@
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>106</v>
@@ -11163,7 +11494,7 @@
         <v>20</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E166" s="3">
         <v>130.7</v>
@@ -11190,7 +11521,7 @@
         <v>23</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N166" s="3">
         <v>128.61</v>
@@ -11210,16 +11541,16 @@
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B167" s="6" t="s">
         <v>418</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>419</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E167" s="7">
         <v>946.8</v>
@@ -11246,7 +11577,7 @@
         <v>33</v>
       </c>
       <c r="M167" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N167" s="7">
         <v>955.6</v>
@@ -11266,7 +11597,7 @@
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>118</v>
@@ -11275,7 +11606,7 @@
         <v>20</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E168" s="3">
         <v>3987.9</v>
@@ -11302,7 +11633,7 @@
         <v>23</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N168" s="3">
         <v>3916</v>
@@ -11321,95 +11652,115 @@
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A169" s="12" t="s">
+      <c r="A169" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B169" s="12" t="s">
+      <c r="C169" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E169" s="3">
+        <v>154.34</v>
+      </c>
+      <c r="F169" s="3">
+        <v>151.22</v>
+      </c>
+      <c r="G169" s="3">
+        <v>153.52</v>
+      </c>
+      <c r="H169" s="3">
+        <v>153.6</v>
+      </c>
+      <c r="I169" s="3">
+        <v>151.22</v>
+      </c>
+      <c r="J169" s="3">
+        <v>155.98</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L169" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M169" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C169" s="12" t="s">
+      <c r="N169" s="3">
+        <v>151.22</v>
+      </c>
+      <c r="O169" s="2">
+        <v>30</v>
+      </c>
+      <c r="P169" s="4">
+        <v>-2.38</v>
+      </c>
+      <c r="Q169" s="5">
+        <v>-1.549</v>
+      </c>
+      <c r="R169" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D169" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="E169" s="13">
-        <v>154.34</v>
-      </c>
-      <c r="F169" s="13">
-        <v>151.22</v>
-      </c>
-      <c r="G169" s="13">
-        <v>153.52</v>
-      </c>
-      <c r="H169" s="13">
-        <v>153.6</v>
-      </c>
-      <c r="I169" s="13">
-        <v>151.22</v>
-      </c>
-      <c r="J169" s="13">
-        <v>155.98</v>
-      </c>
-      <c r="K169" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L169" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M169" s="12"/>
-      <c r="N169" s="12"/>
-      <c r="O169" s="12"/>
-      <c r="P169" s="12"/>
-      <c r="Q169" s="12"/>
-      <c r="R169" s="12" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A170" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="B170" s="12" t="s">
+      <c r="D170" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E170" s="3">
+        <v>869.15</v>
+      </c>
+      <c r="F170" s="3">
+        <v>836.05</v>
+      </c>
+      <c r="G170" s="3">
+        <v>855</v>
+      </c>
+      <c r="H170" s="3">
+        <v>855</v>
+      </c>
+      <c r="I170" s="3">
+        <v>836.05</v>
+      </c>
+      <c r="J170" s="3">
+        <v>873.95</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M170" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C170" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D170" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="E170" s="13">
-        <v>869.15</v>
-      </c>
-      <c r="F170" s="13">
+      <c r="N170" s="3">
         <v>836.05</v>
       </c>
-      <c r="G170" s="13">
-        <v>855</v>
-      </c>
-      <c r="H170" s="13">
-        <v>855</v>
-      </c>
-      <c r="I170" s="13">
-        <v>836.05</v>
-      </c>
-      <c r="J170" s="13">
-        <v>873.95</v>
-      </c>
-      <c r="K170" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L170" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M170" s="12"/>
-      <c r="N170" s="12"/>
-      <c r="O170" s="12"/>
-      <c r="P170" s="12"/>
-      <c r="Q170" s="12"/>
-      <c r="R170" s="12" t="s">
-        <v>424</v>
+      <c r="O170" s="2">
+        <v>26</v>
+      </c>
+      <c r="P170" s="4">
+        <v>-18.95</v>
+      </c>
+      <c r="Q170" s="5">
+        <v>-2.216</v>
+      </c>
+      <c r="R170" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.25">
@@ -11423,7 +11774,7 @@
         <v>20</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E171" s="3">
         <v>1105</v>
@@ -11479,7 +11830,7 @@
         <v>20</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E172" s="7">
         <v>2793.6</v>
@@ -11535,7 +11886,7 @@
         <v>20</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E173" s="3">
         <v>630.75</v>
@@ -11562,7 +11913,7 @@
         <v>23</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N173" s="3">
         <v>620.5</v>
@@ -11591,7 +11942,7 @@
         <v>20</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E174" s="3">
         <v>1364.6</v>
@@ -11637,100 +11988,120 @@
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B175" s="12" t="s">
+      <c r="B175" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C175" s="12" t="s">
+      <c r="C175" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D175" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E175" s="13">
+      <c r="D175" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E175" s="3">
         <v>500.35</v>
       </c>
-      <c r="F175" s="13">
+      <c r="F175" s="3">
         <v>493.9</v>
       </c>
-      <c r="G175" s="13">
+      <c r="G175" s="3">
         <v>500.3</v>
       </c>
-      <c r="H175" s="13">
+      <c r="H175" s="3">
         <v>500.2</v>
       </c>
-      <c r="I175" s="13">
+      <c r="I175" s="3">
         <v>493.9</v>
       </c>
-      <c r="J175" s="13">
+      <c r="J175" s="3">
         <v>506.5</v>
       </c>
-      <c r="K175" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L175" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M175" s="12"/>
-      <c r="N175" s="12"/>
-      <c r="O175" s="12"/>
-      <c r="P175" s="12"/>
-      <c r="Q175" s="12"/>
-      <c r="R175" s="12" t="s">
+      <c r="K175" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L175" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M175" s="2" t="s">
         <v>435</v>
       </c>
+      <c r="N175" s="3">
+        <v>493.9</v>
+      </c>
+      <c r="O175" s="2">
+        <v>22</v>
+      </c>
+      <c r="P175" s="4">
+        <v>-6.3</v>
+      </c>
+      <c r="Q175" s="5">
+        <v>-1.259</v>
+      </c>
+      <c r="R175" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A176" s="12" t="s">
+      <c r="A176" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="B176" s="12" t="s">
+      <c r="B176" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C176" s="12" t="s">
+      <c r="C176" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D176" s="12" t="s">
+      <c r="D176" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E176" s="13">
+      <c r="E176" s="3">
         <v>13770</v>
       </c>
-      <c r="F176" s="13">
+      <c r="F176" s="3">
         <v>13554</v>
       </c>
-      <c r="G176" s="13">
+      <c r="G176" s="3">
         <v>13741</v>
       </c>
-      <c r="H176" s="13">
+      <c r="H176" s="3">
         <v>13740</v>
       </c>
-      <c r="I176" s="13">
+      <c r="I176" s="3">
         <v>13554</v>
       </c>
-      <c r="J176" s="13">
+      <c r="J176" s="3">
         <v>13926</v>
       </c>
-      <c r="K176" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L176" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M176" s="12"/>
-      <c r="N176" s="12"/>
-      <c r="O176" s="12"/>
-      <c r="P176" s="12"/>
-      <c r="Q176" s="12"/>
-      <c r="R176" s="12" t="s">
-        <v>437</v>
+      <c r="K176" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M176" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N176" s="3">
+        <v>13554</v>
+      </c>
+      <c r="O176" s="2">
+        <v>22</v>
+      </c>
+      <c r="P176" s="4">
+        <v>-186</v>
+      </c>
+      <c r="Q176" s="5">
+        <v>-1.354</v>
+      </c>
+      <c r="R176" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>135</v>
@@ -11766,7 +12137,7 @@
         <v>33</v>
       </c>
       <c r="M177" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N177" s="7">
         <v>392.9</v>
@@ -11786,16 +12157,16 @@
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E178" s="3">
         <v>385.4</v>
@@ -11822,7 +12193,7 @@
         <v>23</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N178" s="3">
         <v>381.45</v>
@@ -11842,16 +12213,16 @@
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E179" s="3">
         <v>2054.9</v>
@@ -11898,16 +12269,16 @@
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B180" s="6" t="s">
         <v>446</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>447</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E180" s="7">
         <v>1100.05</v>
@@ -11934,7 +12305,7 @@
         <v>33</v>
       </c>
       <c r="M180" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N180" s="7">
         <v>1111.7</v>
@@ -11954,16 +12325,16 @@
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E181" s="7">
         <v>1020.15</v>
@@ -11990,7 +12361,7 @@
         <v>33</v>
       </c>
       <c r="M181" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N181" s="7">
         <v>1012.15</v>
@@ -12010,16 +12381,16 @@
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E182" s="3">
         <v>15208</v>
@@ -12046,7 +12417,7 @@
         <v>23</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N182" s="3">
         <v>15150</v>
@@ -12066,16 +12437,16 @@
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B183" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>455</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E183" s="7">
         <v>424.6</v>
@@ -12102,7 +12473,7 @@
         <v>33</v>
       </c>
       <c r="M183" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N183" s="7">
         <v>423</v>
@@ -12122,16 +12493,16 @@
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E184" s="7">
         <v>447.35</v>
@@ -12158,7 +12529,7 @@
         <v>33</v>
       </c>
       <c r="M184" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N184" s="7">
         <v>449.2</v>
@@ -12177,370 +12548,3238 @@
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A185" s="12" t="s">
+      <c r="A185" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E185" s="3">
+        <v>964.9</v>
+      </c>
+      <c r="F185" s="3">
+        <v>957.25</v>
+      </c>
+      <c r="G185" s="3">
+        <v>963.65</v>
+      </c>
+      <c r="H185" s="3">
+        <v>963.95</v>
+      </c>
+      <c r="I185" s="3">
+        <v>957.25</v>
+      </c>
+      <c r="J185" s="3">
+        <v>970.65</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N185" s="3">
+        <v>957.25</v>
+      </c>
+      <c r="O185" s="2">
+        <v>1</v>
+      </c>
+      <c r="P185" s="4">
+        <v>-6.7</v>
+      </c>
+      <c r="Q185" s="5">
+        <v>-0.695</v>
+      </c>
+      <c r="R185" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B185" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="C185" s="12" t="s">
+      <c r="B186" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D185" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="E185" s="13">
-        <v>964.9</v>
-      </c>
-      <c r="F185" s="13">
-        <v>957.25</v>
-      </c>
-      <c r="G185" s="13">
-        <v>963.65</v>
-      </c>
-      <c r="H185" s="13">
-        <v>963.95</v>
-      </c>
-      <c r="I185" s="13">
-        <v>957.25</v>
-      </c>
-      <c r="J185" s="13">
-        <v>970.65</v>
-      </c>
-      <c r="K185" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L185" s="12" t="s">
+      <c r="D186" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E186" s="3">
+        <v>2284</v>
+      </c>
+      <c r="F186" s="3">
+        <v>2271</v>
+      </c>
+      <c r="G186" s="3">
+        <v>2282.5</v>
+      </c>
+      <c r="H186" s="3">
+        <v>2282.6</v>
+      </c>
+      <c r="I186" s="3">
+        <v>2271</v>
+      </c>
+      <c r="J186" s="3">
+        <v>2294.2</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L186" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N186" s="3">
+        <v>2271</v>
+      </c>
+      <c r="O186" s="2">
+        <v>1</v>
+      </c>
+      <c r="P186" s="4">
+        <v>-11.6</v>
+      </c>
+      <c r="Q186" s="5">
+        <v>-0.508</v>
+      </c>
+      <c r="R186" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E187" s="3">
+        <v>135.65</v>
+      </c>
+      <c r="F187" s="3">
+        <v>134.95</v>
+      </c>
+      <c r="G187" s="3">
+        <v>135.35</v>
+      </c>
+      <c r="H187" s="3">
+        <v>135.33</v>
+      </c>
+      <c r="I187" s="3">
+        <v>134.95</v>
+      </c>
+      <c r="J187" s="3">
+        <v>135.71</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N187" s="3">
+        <v>134.95</v>
+      </c>
+      <c r="O187" s="2">
+        <v>1</v>
+      </c>
+      <c r="P187" s="4">
+        <v>-0.38</v>
+      </c>
+      <c r="Q187" s="5">
+        <v>-0.281</v>
+      </c>
+      <c r="R187" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E188" s="3">
+        <v>546</v>
+      </c>
+      <c r="F188" s="3">
+        <v>543.15</v>
+      </c>
+      <c r="G188" s="3">
+        <v>545.3</v>
+      </c>
+      <c r="H188" s="3">
+        <v>545.3</v>
+      </c>
+      <c r="I188" s="3">
+        <v>543.15</v>
+      </c>
+      <c r="J188" s="3">
+        <v>547.45</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N188" s="3">
+        <v>543.15</v>
+      </c>
+      <c r="O188" s="2">
+        <v>1</v>
+      </c>
+      <c r="P188" s="4">
+        <v>-2.15</v>
+      </c>
+      <c r="Q188" s="5">
+        <v>-0.394</v>
+      </c>
+      <c r="R188" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E189" s="3">
+        <v>391.8</v>
+      </c>
+      <c r="F189" s="3">
+        <v>388.9</v>
+      </c>
+      <c r="G189" s="3">
+        <v>391.65</v>
+      </c>
+      <c r="H189" s="3">
+        <v>391.7</v>
+      </c>
+      <c r="I189" s="3">
+        <v>388.9</v>
+      </c>
+      <c r="J189" s="3">
+        <v>394.5</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L189" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M189" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="N189" s="3">
+        <v>388.9</v>
+      </c>
+      <c r="O189" s="2">
+        <v>2</v>
+      </c>
+      <c r="P189" s="4">
+        <v>-2.8</v>
+      </c>
+      <c r="Q189" s="5">
+        <v>-0.715</v>
+      </c>
+      <c r="R189" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E190" s="3">
+        <v>6880</v>
+      </c>
+      <c r="F190" s="3">
+        <v>6840.5</v>
+      </c>
+      <c r="G190" s="3">
+        <v>6870</v>
+      </c>
+      <c r="H190" s="3">
+        <v>6904</v>
+      </c>
+      <c r="I190" s="3">
+        <v>6840.5</v>
+      </c>
+      <c r="J190" s="3">
+        <v>6967.5</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L190" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M190" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="N190" s="3">
+        <v>6840.5</v>
+      </c>
+      <c r="O190" s="2">
+        <v>3</v>
+      </c>
+      <c r="P190" s="4">
+        <v>-63.5</v>
+      </c>
+      <c r="Q190" s="5">
+        <v>-0.92</v>
+      </c>
+      <c r="R190" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E191" s="3">
+        <v>130.72</v>
+      </c>
+      <c r="F191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="G191" s="3">
+        <v>130.14</v>
+      </c>
+      <c r="H191" s="3">
+        <v>130.25</v>
+      </c>
+      <c r="I191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="J191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M191" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="N191" s="3">
+        <v>130.13</v>
+      </c>
+      <c r="O191" s="2">
+        <v>1</v>
+      </c>
+      <c r="P191" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="Q191" s="11">
+        <v>0.092</v>
+      </c>
+      <c r="R191" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E192" s="3">
+        <v>3970</v>
+      </c>
+      <c r="F192" s="3">
+        <v>3951.8</v>
+      </c>
+      <c r="G192" s="3">
+        <v>3959.9</v>
+      </c>
+      <c r="H192" s="3">
+        <v>3954.2</v>
+      </c>
+      <c r="I192" s="3">
+        <v>3951.8</v>
+      </c>
+      <c r="J192" s="3">
+        <v>3956.6</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="N192" s="3">
+        <v>3951.8</v>
+      </c>
+      <c r="O192" s="2">
+        <v>1</v>
+      </c>
+      <c r="P192" s="4">
+        <v>-2.4</v>
+      </c>
+      <c r="Q192" s="5">
+        <v>-0.061</v>
+      </c>
+      <c r="R192" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E193" s="3">
+        <v>347.25</v>
+      </c>
+      <c r="F193" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="G193" s="3">
+        <v>344.9</v>
+      </c>
+      <c r="H193" s="3">
+        <v>344.9</v>
+      </c>
+      <c r="I193" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="J193" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L193" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M193" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="M185" s="12"/>
-      <c r="N185" s="12"/>
-      <c r="O185" s="12"/>
-      <c r="P185" s="12"/>
-      <c r="Q185" s="12"/>
-      <c r="R185" s="12" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A186" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="B186" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="C186" s="12" t="s">
+      <c r="N193" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="O193" s="2">
+        <v>1</v>
+      </c>
+      <c r="P193" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="Q193" s="11">
+        <v>1.943</v>
+      </c>
+      <c r="R193" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E194" s="3">
+        <v>391.7</v>
+      </c>
+      <c r="F194" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="G194" s="3">
+        <v>389.8</v>
+      </c>
+      <c r="H194" s="3">
+        <v>389.8</v>
+      </c>
+      <c r="I194" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="J194" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="K194" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M194" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N194" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="O194" s="2">
+        <v>1</v>
+      </c>
+      <c r="P194" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q194" s="11">
+        <v>0.257</v>
+      </c>
+      <c r="R194" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A195" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E195" s="7">
+        <v>337.2</v>
+      </c>
+      <c r="F195" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="G195" s="7">
+        <v>334</v>
+      </c>
+      <c r="H195" s="7">
+        <v>334</v>
+      </c>
+      <c r="I195" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="J195" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="K195" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L195" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M195" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N195" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="O195" s="6">
+        <v>1</v>
+      </c>
+      <c r="P195" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q195" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="R195" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E196" s="3">
+        <v>1228.4</v>
+      </c>
+      <c r="F196" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="G196" s="3">
+        <v>1220.9</v>
+      </c>
+      <c r="H196" s="3">
+        <v>1220.9</v>
+      </c>
+      <c r="I196" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="J196" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L196" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M196" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="N196" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="O196" s="2">
+        <v>1</v>
+      </c>
+      <c r="P196" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="Q196" s="11">
+        <v>0.049</v>
+      </c>
+      <c r="R196" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E197" s="3">
+        <v>2731</v>
+      </c>
+      <c r="F197" s="3">
+        <v>2717</v>
+      </c>
+      <c r="G197" s="3">
+        <v>2718.6</v>
+      </c>
+      <c r="H197" s="3">
+        <v>2718.6</v>
+      </c>
+      <c r="I197" s="3">
+        <v>2717</v>
+      </c>
+      <c r="J197" s="3">
+        <v>2717</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L197" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M197" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="N197" s="3">
+        <v>2717</v>
+      </c>
+      <c r="O197" s="2">
+        <v>1</v>
+      </c>
+      <c r="P197" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="Q197" s="11">
+        <v>0.059</v>
+      </c>
+      <c r="R197" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E198" s="3">
+        <v>2349.3</v>
+      </c>
+      <c r="F198" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="G198" s="3">
+        <v>2339.5</v>
+      </c>
+      <c r="H198" s="3">
+        <v>2339.4</v>
+      </c>
+      <c r="I198" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="J198" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="K198" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L198" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M198" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N198" s="3">
+        <v>2330.6</v>
+      </c>
+      <c r="O198" s="2">
+        <v>1</v>
+      </c>
+      <c r="P198" s="10">
+        <v>8.8</v>
+      </c>
+      <c r="Q198" s="11">
+        <v>0.376</v>
+      </c>
+      <c r="R198" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E199" s="3">
+        <v>1914</v>
+      </c>
+      <c r="F199" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="G199" s="3">
+        <v>1898</v>
+      </c>
+      <c r="H199" s="3">
+        <v>1898</v>
+      </c>
+      <c r="I199" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="J199" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="K199" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L199" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M199" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N199" s="3">
+        <v>1894.6</v>
+      </c>
+      <c r="O199" s="2">
+        <v>1</v>
+      </c>
+      <c r="P199" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="Q199" s="11">
+        <v>0.179</v>
+      </c>
+      <c r="R199" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A200" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E200" s="7">
+        <v>125.75</v>
+      </c>
+      <c r="F200" s="7">
+        <v>125.07</v>
+      </c>
+      <c r="G200" s="7">
+        <v>125.16</v>
+      </c>
+      <c r="H200" s="7">
+        <v>122.14</v>
+      </c>
+      <c r="I200" s="7">
+        <v>125.07</v>
+      </c>
+      <c r="J200" s="7">
+        <v>119.21</v>
+      </c>
+      <c r="K200" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L200" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M200" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="N200" s="7">
+        <v>119.21</v>
+      </c>
+      <c r="O200" s="6">
+        <v>25</v>
+      </c>
+      <c r="P200" s="8">
+        <v>2.93</v>
+      </c>
+      <c r="Q200" s="9">
+        <v>2.399</v>
+      </c>
+      <c r="R200" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E201" s="3">
+        <v>488.55</v>
+      </c>
+      <c r="F201" s="3">
+        <v>484.35</v>
+      </c>
+      <c r="G201" s="3">
+        <v>485.55</v>
+      </c>
+      <c r="H201" s="3">
+        <v>468</v>
+      </c>
+      <c r="I201" s="3">
+        <v>484.35</v>
+      </c>
+      <c r="J201" s="3">
+        <v>451.65</v>
+      </c>
+      <c r="K201" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L201" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M201" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="N201" s="3">
+        <v>484.35</v>
+      </c>
+      <c r="O201" s="2">
+        <v>1</v>
+      </c>
+      <c r="P201" s="4">
+        <v>-16.35</v>
+      </c>
+      <c r="Q201" s="5">
+        <v>-3.494</v>
+      </c>
+      <c r="R201" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A202" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E202" s="7">
+        <v>3904</v>
+      </c>
+      <c r="F202" s="7">
+        <v>3841</v>
+      </c>
+      <c r="G202" s="7">
+        <v>3848.6</v>
+      </c>
+      <c r="H202" s="7">
+        <v>3852</v>
+      </c>
+      <c r="I202" s="7">
+        <v>3841</v>
+      </c>
+      <c r="J202" s="7">
+        <v>3841</v>
+      </c>
+      <c r="K202" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L202" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M202" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N202" s="7">
+        <v>3841</v>
+      </c>
+      <c r="O202" s="6">
+        <v>1</v>
+      </c>
+      <c r="P202" s="8">
+        <v>11</v>
+      </c>
+      <c r="Q202" s="9">
+        <v>0.286</v>
+      </c>
+      <c r="R202" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A203" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E203" s="7">
+        <v>418.75</v>
+      </c>
+      <c r="F203" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="G203" s="7">
+        <v>414.05</v>
+      </c>
+      <c r="H203" s="7">
+        <v>414.05</v>
+      </c>
+      <c r="I203" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="J203" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="K203" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L203" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M203" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N203" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="O203" s="6">
+        <v>1</v>
+      </c>
+      <c r="P203" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="Q203" s="9">
+        <v>0.181</v>
+      </c>
+      <c r="R203" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A204" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="E204" s="13">
+        <v>536.2</v>
+      </c>
+      <c r="F204" s="13">
+        <v>532.05</v>
+      </c>
+      <c r="G204" s="13">
+        <v>533.25</v>
+      </c>
+      <c r="H204" s="13">
+        <v>502</v>
+      </c>
+      <c r="I204" s="13">
+        <v>532.05</v>
+      </c>
+      <c r="J204" s="13">
+        <v>471.95</v>
+      </c>
+      <c r="K204" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M204" s="12"/>
+      <c r="N204" s="12"/>
+      <c r="O204" s="12"/>
+      <c r="P204" s="12"/>
+      <c r="Q204" s="12"/>
+      <c r="R204" s="12" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A205" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="E205" s="7">
+        <v>1205.8</v>
+      </c>
+      <c r="F205" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="G205" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="H205" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="I205" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="J205" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="K205" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L205" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M205" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="N205" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="O205" s="6">
+        <v>1</v>
+      </c>
+      <c r="P205" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q205" s="9">
+        <v>0</v>
+      </c>
+      <c r="R205" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A206" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E206" s="7">
+        <v>455.55</v>
+      </c>
+      <c r="F206" s="7">
+        <v>450</v>
+      </c>
+      <c r="G206" s="7">
+        <v>451</v>
+      </c>
+      <c r="H206" s="7">
+        <v>451</v>
+      </c>
+      <c r="I206" s="7">
+        <v>450</v>
+      </c>
+      <c r="J206" s="7">
+        <v>450</v>
+      </c>
+      <c r="K206" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L206" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M206" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N206" s="7">
+        <v>450</v>
+      </c>
+      <c r="O206" s="6">
+        <v>1</v>
+      </c>
+      <c r="P206" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q206" s="9">
+        <v>0.222</v>
+      </c>
+      <c r="R206" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E207" s="3">
+        <v>1373.1</v>
+      </c>
+      <c r="F207" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="G207" s="3">
+        <v>1366.2</v>
+      </c>
+      <c r="H207" s="3">
+        <v>1366.1</v>
+      </c>
+      <c r="I207" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="J207" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="K207" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L207" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M207" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="N207" s="3">
+        <v>1365.5</v>
+      </c>
+      <c r="O207" s="2">
+        <v>1</v>
+      </c>
+      <c r="P207" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="Q207" s="11">
+        <v>0.044</v>
+      </c>
+      <c r="R207" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E208" s="3">
+        <v>1278.8</v>
+      </c>
+      <c r="F208" s="3">
+        <v>1274</v>
+      </c>
+      <c r="G208" s="3">
+        <v>1276.6</v>
+      </c>
+      <c r="H208" s="3">
+        <v>1277.3</v>
+      </c>
+      <c r="I208" s="3">
+        <v>1274</v>
+      </c>
+      <c r="J208" s="3">
+        <v>1274</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L208" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M208" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="N208" s="3">
+        <v>1274</v>
+      </c>
+      <c r="O208" s="2">
+        <v>1</v>
+      </c>
+      <c r="P208" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="Q208" s="11">
+        <v>0.258</v>
+      </c>
+      <c r="R208" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E209" s="3">
+        <v>654</v>
+      </c>
+      <c r="F209" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="G209" s="3">
+        <v>647.35</v>
+      </c>
+      <c r="H209" s="3">
+        <v>646.9</v>
+      </c>
+      <c r="I209" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="J209" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L209" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M209" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="N209" s="3">
+        <v>646.35</v>
+      </c>
+      <c r="O209" s="2">
+        <v>1</v>
+      </c>
+      <c r="P209" s="10">
+        <v>0.55</v>
+      </c>
+      <c r="Q209" s="11">
+        <v>0.085</v>
+      </c>
+      <c r="R209" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E210" s="3">
+        <v>1280</v>
+      </c>
+      <c r="F210" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="G210" s="3">
+        <v>1276</v>
+      </c>
+      <c r="H210" s="3">
+        <v>1276.2</v>
+      </c>
+      <c r="I210" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="J210" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L210" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M210" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="N210" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="O210" s="2">
+        <v>1</v>
+      </c>
+      <c r="P210" s="10">
+        <v>1.1</v>
+      </c>
+      <c r="Q210" s="11">
+        <v>0.086</v>
+      </c>
+      <c r="R210" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E211" s="3">
+        <v>122.43</v>
+      </c>
+      <c r="F211" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="G211" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="H211" s="3">
+        <v>121.56</v>
+      </c>
+      <c r="I211" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="J211" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L211" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M211" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="N211" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="O211" s="2">
+        <v>1</v>
+      </c>
+      <c r="P211" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q211" s="11">
+        <v>0.041</v>
+      </c>
+      <c r="R211" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E212" s="3">
+        <v>3306.1</v>
+      </c>
+      <c r="F212" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="G212" s="3">
+        <v>3285.9</v>
+      </c>
+      <c r="H212" s="3">
+        <v>3285.2</v>
+      </c>
+      <c r="I212" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="J212" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M212" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="N212" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="O212" s="2">
+        <v>1</v>
+      </c>
+      <c r="P212" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="Q212" s="11">
+        <v>0.055</v>
+      </c>
+      <c r="R212" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E213" s="3">
+        <v>1202.9</v>
+      </c>
+      <c r="F213" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="G213" s="3">
+        <v>1188.3</v>
+      </c>
+      <c r="H213" s="3">
+        <v>1188.4</v>
+      </c>
+      <c r="I213" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="J213" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L213" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M213" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N213" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="O213" s="2">
+        <v>1</v>
+      </c>
+      <c r="P213" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q213" s="11">
+        <v>0.421</v>
+      </c>
+      <c r="R213" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E214" s="3">
+        <v>1870</v>
+      </c>
+      <c r="F214" s="3">
+        <v>1833</v>
+      </c>
+      <c r="G214" s="3">
+        <v>1841.4</v>
+      </c>
+      <c r="H214" s="3">
+        <v>1840.4</v>
+      </c>
+      <c r="I214" s="3">
+        <v>1833</v>
+      </c>
+      <c r="J214" s="3">
+        <v>1833</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L214" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M214" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N214" s="3">
+        <v>1833</v>
+      </c>
+      <c r="O214" s="2">
+        <v>1</v>
+      </c>
+      <c r="P214" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="Q214" s="11">
+        <v>0.402</v>
+      </c>
+      <c r="R214" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E215" s="3">
+        <v>2203.6</v>
+      </c>
+      <c r="F215" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="G215" s="3">
+        <v>2192.8</v>
+      </c>
+      <c r="H215" s="3">
+        <v>2192.6</v>
+      </c>
+      <c r="I215" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="J215" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="K215" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L215" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M215" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N215" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="O215" s="2">
+        <v>1</v>
+      </c>
+      <c r="P215" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="Q215" s="11">
+        <v>0.328</v>
+      </c>
+      <c r="R215" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E216" s="3">
+        <v>70.31</v>
+      </c>
+      <c r="F216" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="G216" s="3">
+        <v>70.1</v>
+      </c>
+      <c r="H216" s="3">
+        <v>70.08</v>
+      </c>
+      <c r="I216" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="J216" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L216" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M216" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="N216" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="O216" s="2">
+        <v>1</v>
+      </c>
+      <c r="P216" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="Q216" s="11">
+        <v>0.086</v>
+      </c>
+      <c r="R216" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A217" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="E217" s="7">
+        <v>961.35</v>
+      </c>
+      <c r="F217" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="G217" s="7">
+        <v>949.25</v>
+      </c>
+      <c r="H217" s="7">
+        <v>949.05</v>
+      </c>
+      <c r="I217" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="J217" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="K217" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L217" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M217" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="N217" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="O217" s="6">
+        <v>1</v>
+      </c>
+      <c r="P217" s="8">
+        <v>1.95</v>
+      </c>
+      <c r="Q217" s="9">
+        <v>0.205</v>
+      </c>
+      <c r="R217" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E218" s="3">
+        <v>165.26</v>
+      </c>
+      <c r="F218" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="G218" s="3">
+        <v>162.38</v>
+      </c>
+      <c r="H218" s="3">
+        <v>162.4</v>
+      </c>
+      <c r="I218" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="J218" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="K218" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L218" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M218" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N218" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="O218" s="2">
+        <v>1</v>
+      </c>
+      <c r="P218" s="10">
+        <v>0.37</v>
+      </c>
+      <c r="Q218" s="11">
+        <v>0.228</v>
+      </c>
+      <c r="R218" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E219" s="3">
+        <v>1253.9</v>
+      </c>
+      <c r="F219" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="G219" s="3">
+        <v>1217</v>
+      </c>
+      <c r="H219" s="3">
+        <v>1218</v>
+      </c>
+      <c r="I219" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="J219" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L219" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M219" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N219" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="O219" s="2">
+        <v>1</v>
+      </c>
+      <c r="P219" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="Q219" s="11">
+        <v>0.222</v>
+      </c>
+      <c r="R219" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E220" s="3">
+        <v>396.3</v>
+      </c>
+      <c r="F220" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="G220" s="3">
+        <v>392.55</v>
+      </c>
+      <c r="H220" s="3">
+        <v>392.45</v>
+      </c>
+      <c r="I220" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="J220" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L220" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M220" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N220" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="O220" s="2">
+        <v>1</v>
+      </c>
+      <c r="P220" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="Q220" s="11">
+        <v>0.612</v>
+      </c>
+      <c r="R220" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E221" s="3">
+        <v>1067.8</v>
+      </c>
+      <c r="F221" s="3">
+        <v>1047</v>
+      </c>
+      <c r="G221" s="3">
+        <v>1050.6</v>
+      </c>
+      <c r="H221" s="3">
+        <v>1051.4</v>
+      </c>
+      <c r="I221" s="3">
+        <v>1047</v>
+      </c>
+      <c r="J221" s="3">
+        <v>1047</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L221" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M221" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N221" s="3">
+        <v>1047</v>
+      </c>
+      <c r="O221" s="2">
+        <v>1</v>
+      </c>
+      <c r="P221" s="10">
+        <v>4.4</v>
+      </c>
+      <c r="Q221" s="11">
+        <v>0.418</v>
+      </c>
+      <c r="R221" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E222" s="3">
+        <v>147.09</v>
+      </c>
+      <c r="F222" s="3">
+        <v>145</v>
+      </c>
+      <c r="G222" s="3">
+        <v>145.4</v>
+      </c>
+      <c r="H222" s="3">
+        <v>145.31</v>
+      </c>
+      <c r="I222" s="3">
+        <v>145</v>
+      </c>
+      <c r="J222" s="3">
+        <v>145</v>
+      </c>
+      <c r="K222" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L222" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M222" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N222" s="3">
+        <v>145</v>
+      </c>
+      <c r="O222" s="2">
+        <v>1</v>
+      </c>
+      <c r="P222" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="Q222" s="11">
+        <v>0.213</v>
+      </c>
+      <c r="R222" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E223" s="3">
+        <v>373.85</v>
+      </c>
+      <c r="F223" s="3">
+        <v>366.6</v>
+      </c>
+      <c r="G223" s="3">
+        <v>366.9</v>
+      </c>
+      <c r="H223" s="3">
+        <v>366.75</v>
+      </c>
+      <c r="I223" s="3">
+        <v>366.6</v>
+      </c>
+      <c r="J223" s="3">
+        <v>366.6</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L223" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M223" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N223" s="3">
+        <v>366.6</v>
+      </c>
+      <c r="O223" s="2">
+        <v>1</v>
+      </c>
+      <c r="P223" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="Q223" s="11">
+        <v>0.041</v>
+      </c>
+      <c r="R223" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E224" s="3">
+        <v>606.95</v>
+      </c>
+      <c r="F224" s="3">
+        <v>590.5</v>
+      </c>
+      <c r="G224" s="3">
+        <v>591.7</v>
+      </c>
+      <c r="H224" s="3">
+        <v>591.55</v>
+      </c>
+      <c r="I224" s="3">
+        <v>590.5</v>
+      </c>
+      <c r="J224" s="3">
+        <v>590.5</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L224" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M224" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="N224" s="3">
+        <v>590.5</v>
+      </c>
+      <c r="O224" s="2">
+        <v>1</v>
+      </c>
+      <c r="P224" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="Q224" s="11">
+        <v>0.177</v>
+      </c>
+      <c r="R224" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E225" s="3">
+        <v>9827</v>
+      </c>
+      <c r="F225" s="3">
+        <v>9792</v>
+      </c>
+      <c r="G225" s="3">
+        <v>9797</v>
+      </c>
+      <c r="H225" s="3">
+        <v>9795</v>
+      </c>
+      <c r="I225" s="3">
+        <v>9792</v>
+      </c>
+      <c r="J225" s="3">
+        <v>9792</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L225" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M225" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="N225" s="3">
+        <v>9792</v>
+      </c>
+      <c r="O225" s="2">
+        <v>1</v>
+      </c>
+      <c r="P225" s="10">
+        <v>3</v>
+      </c>
+      <c r="Q225" s="11">
+        <v>0.031</v>
+      </c>
+      <c r="R225" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A226" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="E226" s="7">
+        <v>4662.9</v>
+      </c>
+      <c r="F226" s="7">
+        <v>4646.6</v>
+      </c>
+      <c r="G226" s="7">
+        <v>4650.6</v>
+      </c>
+      <c r="H226" s="7">
+        <v>4651.3</v>
+      </c>
+      <c r="I226" s="7">
+        <v>4646.6</v>
+      </c>
+      <c r="J226" s="7">
+        <v>4646.6</v>
+      </c>
+      <c r="K226" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L226" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M226" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N226" s="7">
+        <v>4646.6</v>
+      </c>
+      <c r="O226" s="6">
+        <v>1</v>
+      </c>
+      <c r="P226" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="Q226" s="9">
+        <v>0.101</v>
+      </c>
+      <c r="R226" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A227" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C227" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D186" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="E186" s="13">
-        <v>2284</v>
-      </c>
-      <c r="F186" s="13">
-        <v>2271</v>
-      </c>
-      <c r="G186" s="13">
-        <v>2282.5</v>
-      </c>
-      <c r="H186" s="13">
-        <v>2282.6</v>
-      </c>
-      <c r="I186" s="13">
-        <v>2271</v>
-      </c>
-      <c r="J186" s="13">
-        <v>2294.2</v>
-      </c>
-      <c r="K186" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L186" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M186" s="12"/>
-      <c r="N186" s="12"/>
-      <c r="O186" s="12"/>
-      <c r="P186" s="12"/>
-      <c r="Q186" s="12"/>
-      <c r="R186" s="12" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A187" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="B187" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="C187" s="12" t="s">
+      <c r="D227" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E227" s="7">
+        <v>14499</v>
+      </c>
+      <c r="F227" s="7">
+        <v>14393</v>
+      </c>
+      <c r="G227" s="7">
+        <v>14455</v>
+      </c>
+      <c r="H227" s="7">
+        <v>14465</v>
+      </c>
+      <c r="I227" s="7">
+        <v>14393</v>
+      </c>
+      <c r="J227" s="7">
+        <v>14537</v>
+      </c>
+      <c r="K227" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L227" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M227" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="N227" s="7">
+        <v>14537</v>
+      </c>
+      <c r="O227" s="6">
+        <v>4</v>
+      </c>
+      <c r="P227" s="8">
+        <v>72</v>
+      </c>
+      <c r="Q227" s="9">
+        <v>0.498</v>
+      </c>
+      <c r="R227" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A228" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="C228" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D187" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="E187" s="13">
-        <v>135.65</v>
-      </c>
-      <c r="F187" s="13">
-        <v>134.95</v>
-      </c>
-      <c r="G187" s="13">
-        <v>135.35</v>
-      </c>
-      <c r="H187" s="13">
-        <v>135.33</v>
-      </c>
-      <c r="I187" s="13">
-        <v>134.95</v>
-      </c>
-      <c r="J187" s="13">
-        <v>135.71</v>
-      </c>
-      <c r="K187" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L187" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M187" s="12"/>
-      <c r="N187" s="12"/>
-      <c r="O187" s="12"/>
-      <c r="P187" s="12"/>
-      <c r="Q187" s="12"/>
-      <c r="R187" s="12" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A188" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="B188" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="C188" s="12" t="s">
+      <c r="D228" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E228" s="7">
+        <v>377.3</v>
+      </c>
+      <c r="F228" s="7">
+        <v>371.4</v>
+      </c>
+      <c r="G228" s="7">
+        <v>375.95</v>
+      </c>
+      <c r="H228" s="7">
+        <v>375.8</v>
+      </c>
+      <c r="I228" s="7">
+        <v>371.4</v>
+      </c>
+      <c r="J228" s="7">
+        <v>380.2</v>
+      </c>
+      <c r="K228" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L228" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M228" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="N228" s="7">
+        <v>380.2</v>
+      </c>
+      <c r="O228" s="6">
+        <v>2</v>
+      </c>
+      <c r="P228" s="8">
+        <v>4.4</v>
+      </c>
+      <c r="Q228" s="9">
+        <v>1.171</v>
+      </c>
+      <c r="R228" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E229" s="3">
+        <v>6317.5</v>
+      </c>
+      <c r="F229" s="3">
+        <v>6281.5</v>
+      </c>
+      <c r="G229" s="3">
+        <v>6281.5</v>
+      </c>
+      <c r="H229" s="3">
+        <v>6316.5</v>
+      </c>
+      <c r="I229" s="3">
+        <v>6281.5</v>
+      </c>
+      <c r="J229" s="3">
+        <v>6281.5</v>
+      </c>
+      <c r="K229" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L229" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M229" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="N229" s="3">
+        <v>6281.5</v>
+      </c>
+      <c r="O229" s="2">
+        <v>1</v>
+      </c>
+      <c r="P229" s="10">
+        <v>35</v>
+      </c>
+      <c r="Q229" s="11">
+        <v>0.554</v>
+      </c>
+      <c r="R229" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E230" s="3">
+        <v>1444</v>
+      </c>
+      <c r="F230" s="3">
+        <v>1436.5</v>
+      </c>
+      <c r="G230" s="3">
+        <v>1436.9</v>
+      </c>
+      <c r="H230" s="3">
+        <v>1437.2</v>
+      </c>
+      <c r="I230" s="3">
+        <v>1436.5</v>
+      </c>
+      <c r="J230" s="3">
+        <v>1436.5</v>
+      </c>
+      <c r="K230" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L230" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M230" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="N230" s="3">
+        <v>1436.5</v>
+      </c>
+      <c r="O230" s="2">
+        <v>1</v>
+      </c>
+      <c r="P230" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="Q230" s="11">
+        <v>0.049</v>
+      </c>
+      <c r="R230" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E231" s="3">
+        <v>490.8</v>
+      </c>
+      <c r="F231" s="3">
+        <v>486.65</v>
+      </c>
+      <c r="G231" s="3">
+        <v>487.15</v>
+      </c>
+      <c r="H231" s="3">
+        <v>487.15</v>
+      </c>
+      <c r="I231" s="3">
+        <v>486.65</v>
+      </c>
+      <c r="J231" s="3">
+        <v>486.65</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L231" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M231" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="N231" s="3">
+        <v>486.65</v>
+      </c>
+      <c r="O231" s="2">
+        <v>1</v>
+      </c>
+      <c r="P231" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="Q231" s="11">
+        <v>0.103</v>
+      </c>
+      <c r="R231" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E232" s="3">
+        <v>249.5</v>
+      </c>
+      <c r="F232" s="3">
+        <v>247.25</v>
+      </c>
+      <c r="G232" s="3">
+        <v>247.45</v>
+      </c>
+      <c r="H232" s="3">
+        <v>247.4</v>
+      </c>
+      <c r="I232" s="3">
+        <v>247.25</v>
+      </c>
+      <c r="J232" s="3">
+        <v>247.25</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M232" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="N232" s="3">
+        <v>247.25</v>
+      </c>
+      <c r="O232" s="2">
+        <v>1</v>
+      </c>
+      <c r="P232" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="Q232" s="11">
+        <v>0.061</v>
+      </c>
+      <c r="R232" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E233" s="3">
+        <v>1656.3</v>
+      </c>
+      <c r="F233" s="3">
+        <v>1645</v>
+      </c>
+      <c r="G233" s="3">
+        <v>1647.7</v>
+      </c>
+      <c r="H233" s="3">
+        <v>1647.7</v>
+      </c>
+      <c r="I233" s="3">
+        <v>1645</v>
+      </c>
+      <c r="J233" s="3">
+        <v>1645</v>
+      </c>
+      <c r="K233" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L233" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M233" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="N233" s="3">
+        <v>1645</v>
+      </c>
+      <c r="O233" s="2">
+        <v>1</v>
+      </c>
+      <c r="P233" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="Q233" s="11">
+        <v>0.164</v>
+      </c>
+      <c r="R233" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E234" s="3">
+        <v>157.7</v>
+      </c>
+      <c r="F234" s="3">
+        <v>156.8</v>
+      </c>
+      <c r="G234" s="3">
+        <v>157.18</v>
+      </c>
+      <c r="H234" s="3">
+        <v>157.99</v>
+      </c>
+      <c r="I234" s="3">
+        <v>156.8</v>
+      </c>
+      <c r="J234" s="3">
+        <v>156.8</v>
+      </c>
+      <c r="K234" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L234" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M234" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="N234" s="3">
+        <v>156.8</v>
+      </c>
+      <c r="O234" s="2">
+        <v>1</v>
+      </c>
+      <c r="P234" s="10">
+        <v>1.19</v>
+      </c>
+      <c r="Q234" s="11">
+        <v>0.753</v>
+      </c>
+      <c r="R234" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A235" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C235" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D188" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="E188" s="13">
-        <v>546</v>
-      </c>
-      <c r="F188" s="13">
-        <v>543.15</v>
-      </c>
-      <c r="G188" s="13">
-        <v>545.3</v>
-      </c>
-      <c r="H188" s="13">
-        <v>545.05</v>
-      </c>
-      <c r="I188" s="13">
-        <v>543.15</v>
-      </c>
-      <c r="J188" s="13">
-        <v>546.95</v>
-      </c>
-      <c r="K188" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L188" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M188" s="12"/>
-      <c r="N188" s="12"/>
-      <c r="O188" s="12"/>
-      <c r="P188" s="12"/>
-      <c r="Q188" s="12"/>
-      <c r="R188" s="12" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A189" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="B189" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C189" s="12" t="s">
+      <c r="D235" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="E235" s="13">
+        <v>14599</v>
+      </c>
+      <c r="F235" s="13">
+        <v>14500</v>
+      </c>
+      <c r="G235" s="13">
+        <v>14598</v>
+      </c>
+      <c r="H235" s="13">
+        <v>14796</v>
+      </c>
+      <c r="I235" s="13">
+        <v>14500</v>
+      </c>
+      <c r="J235" s="13">
+        <v>15092</v>
+      </c>
+      <c r="K235" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L235" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M235" s="12"/>
+      <c r="N235" s="12"/>
+      <c r="O235" s="12"/>
+      <c r="P235" s="12"/>
+      <c r="Q235" s="12"/>
+      <c r="R235" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A236" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C236" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D189" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="E189" s="13">
-        <v>391.8</v>
-      </c>
-      <c r="F189" s="13">
-        <v>388.9</v>
-      </c>
-      <c r="G189" s="13">
-        <v>391.65</v>
-      </c>
-      <c r="H189" s="13">
-        <v>391.7</v>
-      </c>
-      <c r="I189" s="13">
-        <v>388.9</v>
-      </c>
-      <c r="J189" s="13">
-        <v>394.5</v>
-      </c>
-      <c r="K189" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L189" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M189" s="12"/>
-      <c r="N189" s="12"/>
-      <c r="O189" s="12"/>
-      <c r="P189" s="12"/>
-      <c r="Q189" s="12"/>
-      <c r="R189" s="12" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A190" s="12" t="s">
+      <c r="D236" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E236" s="13">
+        <v>452.4</v>
+      </c>
+      <c r="F236" s="13">
+        <v>440</v>
+      </c>
+      <c r="G236" s="13">
+        <v>451.05</v>
+      </c>
+      <c r="H236" s="13">
+        <v>451.05</v>
+      </c>
+      <c r="I236" s="13">
+        <v>440</v>
+      </c>
+      <c r="J236" s="13">
+        <v>462.1</v>
+      </c>
+      <c r="K236" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L236" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M236" s="12"/>
+      <c r="N236" s="12"/>
+      <c r="O236" s="12"/>
+      <c r="P236" s="12"/>
+      <c r="Q236" s="12"/>
+      <c r="R236" s="12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A237" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D237" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E237" s="13">
+        <v>2352.3</v>
+      </c>
+      <c r="F237" s="13">
+        <v>2310</v>
+      </c>
+      <c r="G237" s="13">
+        <v>2348</v>
+      </c>
+      <c r="H237" s="13">
+        <v>2349.9</v>
+      </c>
+      <c r="I237" s="13">
+        <v>2310</v>
+      </c>
+      <c r="J237" s="13">
+        <v>2389.8</v>
+      </c>
+      <c r="K237" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L237" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M237" s="12"/>
+      <c r="N237" s="12"/>
+      <c r="O237" s="12"/>
+      <c r="P237" s="12"/>
+      <c r="Q237" s="12"/>
+      <c r="R237" s="12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A238" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="E238" s="7">
+        <v>2318</v>
+      </c>
+      <c r="F238" s="7">
+        <v>2280.4</v>
+      </c>
+      <c r="G238" s="7">
+        <v>2313.1</v>
+      </c>
+      <c r="H238" s="7">
+        <v>2313.1</v>
+      </c>
+      <c r="I238" s="7">
+        <v>2280.4</v>
+      </c>
+      <c r="J238" s="7">
+        <v>2345.8</v>
+      </c>
+      <c r="K238" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L238" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M238" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="N238" s="7">
+        <v>2345.8</v>
+      </c>
+      <c r="O238" s="6">
+        <v>1</v>
+      </c>
+      <c r="P238" s="8">
+        <v>32.7</v>
+      </c>
+      <c r="Q238" s="9">
+        <v>1.414</v>
+      </c>
+      <c r="R238" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A239" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D239" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="E239" s="13">
+        <v>184.98</v>
+      </c>
+      <c r="F239" s="13">
+        <v>182.15</v>
+      </c>
+      <c r="G239" s="13">
+        <v>184.62</v>
+      </c>
+      <c r="H239" s="13">
+        <v>184.54</v>
+      </c>
+      <c r="I239" s="13">
+        <v>182.15</v>
+      </c>
+      <c r="J239" s="13">
+        <v>186.93</v>
+      </c>
+      <c r="K239" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L239" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M239" s="12"/>
+      <c r="N239" s="12"/>
+      <c r="O239" s="12"/>
+      <c r="P239" s="12"/>
+      <c r="Q239" s="12"/>
+      <c r="R239" s="12" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A240" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="B240" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C240" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D240" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="E240" s="13">
+        <v>1392.8</v>
+      </c>
+      <c r="F240" s="13">
+        <v>1378.1</v>
+      </c>
+      <c r="G240" s="13">
+        <v>1389.7</v>
+      </c>
+      <c r="H240" s="13">
+        <v>1389.5</v>
+      </c>
+      <c r="I240" s="13">
+        <v>1378.1</v>
+      </c>
+      <c r="J240" s="13">
+        <v>1400.9</v>
+      </c>
+      <c r="K240" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L240" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M240" s="12"/>
+      <c r="N240" s="12"/>
+      <c r="O240" s="12"/>
+      <c r="P240" s="12"/>
+      <c r="Q240" s="12"/>
+      <c r="R240" s="12" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E241" s="3">
+        <v>598.25</v>
+      </c>
+      <c r="F241" s="3">
+        <v>593.3</v>
+      </c>
+      <c r="G241" s="3">
+        <v>593.65</v>
+      </c>
+      <c r="H241" s="3">
+        <v>593.8</v>
+      </c>
+      <c r="I241" s="3">
+        <v>593.3</v>
+      </c>
+      <c r="J241" s="3">
+        <v>593.3</v>
+      </c>
+      <c r="K241" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L241" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M241" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="N241" s="3">
+        <v>593.3</v>
+      </c>
+      <c r="O241" s="2">
+        <v>1</v>
+      </c>
+      <c r="P241" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="Q241" s="11">
+        <v>0.084</v>
+      </c>
+      <c r="R241" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A242" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="B242" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D242" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="E242" s="13">
+        <v>379.8</v>
+      </c>
+      <c r="F242" s="13">
+        <v>376.2</v>
+      </c>
+      <c r="G242" s="13">
+        <v>379.6</v>
+      </c>
+      <c r="H242" s="13">
+        <v>379.7</v>
+      </c>
+      <c r="I242" s="13">
+        <v>376.2</v>
+      </c>
+      <c r="J242" s="13">
+        <v>383.2</v>
+      </c>
+      <c r="K242" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L242" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M242" s="12"/>
+      <c r="N242" s="12"/>
+      <c r="O242" s="12"/>
+      <c r="P242" s="12"/>
+      <c r="Q242" s="12"/>
+      <c r="R242" s="12" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="B243" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="B190" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="C190" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="E190" s="13">
-        <v>6880</v>
-      </c>
-      <c r="F190" s="13">
-        <v>6840.5</v>
-      </c>
-      <c r="G190" s="13">
-        <v>6870</v>
-      </c>
-      <c r="H190" s="12"/>
-      <c r="I190" s="13">
-        <v>6840.5</v>
-      </c>
-      <c r="J190" s="12"/>
-      <c r="K190" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L190" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M190" s="12"/>
-      <c r="N190" s="12"/>
-      <c r="O190" s="12"/>
-      <c r="P190" s="12"/>
-      <c r="Q190" s="12"/>
-      <c r="R190" s="12" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A191" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="B191" s="12" t="s">
-        <v>472</v>
-      </c>
-      <c r="C191" s="12" t="s">
+      <c r="C243" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D191" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="E191" s="13">
-        <v>130.72</v>
-      </c>
-      <c r="F191" s="13">
-        <v>130.13</v>
-      </c>
-      <c r="G191" s="13">
-        <v>130.14</v>
-      </c>
-      <c r="H191" s="12"/>
-      <c r="I191" s="13">
-        <v>130.13</v>
-      </c>
-      <c r="J191" s="12"/>
-      <c r="K191" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L191" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M191" s="12"/>
-      <c r="N191" s="12"/>
-      <c r="O191" s="12"/>
-      <c r="P191" s="12"/>
-      <c r="Q191" s="12"/>
-      <c r="R191" s="12" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A192" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="B192" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="C192" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="E192" s="13">
-        <v>3970</v>
-      </c>
-      <c r="F192" s="13">
-        <v>3951.8</v>
-      </c>
-      <c r="G192" s="13">
-        <v>3959.9</v>
-      </c>
-      <c r="H192" s="12"/>
-      <c r="I192" s="13">
-        <v>3951.8</v>
-      </c>
-      <c r="J192" s="12"/>
-      <c r="K192" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L192" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M192" s="12"/>
-      <c r="N192" s="12"/>
-      <c r="O192" s="12"/>
-      <c r="P192" s="12"/>
-      <c r="Q192" s="12"/>
-      <c r="R192" s="12" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A194" s="14" t="s">
-        <v>475</v>
-      </c>
-      <c r="P194" s="15">
-        <v>534.62</v>
-      </c>
-      <c r="R194" s="14" t="s">
-        <v>476</v>
+      <c r="D243" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="E243" s="13">
+        <v>6825</v>
+      </c>
+      <c r="F243" s="13">
+        <v>6764</v>
+      </c>
+      <c r="G243" s="13">
+        <v>6768.5</v>
+      </c>
+      <c r="H243" s="13">
+        <v>6769.5</v>
+      </c>
+      <c r="I243" s="13">
+        <v>6764</v>
+      </c>
+      <c r="J243" s="13">
+        <v>6764</v>
+      </c>
+      <c r="K243" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L243" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="M243" s="12"/>
+      <c r="N243" s="12"/>
+      <c r="O243" s="12"/>
+      <c r="P243" s="12"/>
+      <c r="Q243" s="12"/>
+      <c r="R243" s="12" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A245" s="14" t="s">
+        <v>582</v>
+      </c>
+      <c r="P245" s="15">
+        <v>435.24</v>
+      </c>
+      <c r="R245" s="14" t="s">
+        <v>583</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="633">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1435,12 +1435,138 @@
     <t>NSE:TVSMOTOR-EQ</t>
   </si>
   <si>
+    <t>NSE:APLAPOLLO-EQ_BULL_1772091900_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BEAR_1772082900_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BEAR_1772087400_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ_BEAR_1772085600_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BEAR_1772088300_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:MUTHOOTFIN-EQ_BEAR_1772081100_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:MUTHOOTFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ_BEAR_1772086500_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1772089200_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:VOLTAS-EQ_BULL_1772097300_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:VOLTAS-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 11:15</t>
+  </si>
+  <si>
+    <t>NSE:YESBANK-EQ_BEAR_1772088300_1772163900</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ_BULL_1772079300_1772164800</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:30</t>
+  </si>
+  <si>
+    <t>NSE:RECLTD-EQ_BEAR_1772086500_1772165700</t>
+  </si>
+  <si>
+    <t>NSE:RECLTD-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:15</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BEAR_1772082000_1772166600</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ_BEAR_1772088300_1772166600</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ_BEAR_1772164800_1772169300</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BEAR_1772165700_1772171100</t>
+  </si>
+  <si>
+    <t>2026-02-27 11:45</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ_BEAR_1772077500_1772175600</t>
+  </si>
+  <si>
+    <t>2026-02-27 12:30</t>
+  </si>
+  <si>
+    <t>2026-02-27 13:00</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BEAR_1772165700_1772176500</t>
+  </si>
+  <si>
+    <t>2026-02-27 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-27 13:15</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1772078400_1772180100</t>
+  </si>
+  <si>
+    <t>2026-02-27 13:45</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:15</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BEAR_1772170200_1772181000</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:30</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BEAR_1772095500_1772181900</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:45</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BULL_1772180100_1772183700</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:15</t>
+  </si>
+  <si>
     <t>NSE:ABCAPITAL-EQ_BEAR_1772165700_1772184600</t>
   </si>
   <si>
     <t>2026-02-27 15:00</t>
   </si>
   <si>
+    <t>NSE:DMART-EQ_BEAR_1772085600_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ</t>
+  </si>
+  <si>
     <t>NSE:BIOCON-EQ_BEAR_1772167500_1772184600</t>
   </si>
   <si>
@@ -1450,22 +1576,10 @@
     <t>NSE:EXIDEIND-EQ_BEAR_1772163900_1772184600</t>
   </si>
   <si>
-    <t>NSE:GODREJCP-EQ_BEAR_1772165700_1772176500</t>
-  </si>
-  <si>
-    <t>2026-02-27 12:45</t>
-  </si>
-  <si>
-    <t>2026-02-27 13:15</t>
-  </si>
-  <si>
-    <t>NSE:HDFCAMC-EQ_BEAR_1772164800_1772169300</t>
-  </si>
-  <si>
-    <t>NSE:HDFCAMC-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-27 11:15</t>
+    <t>NSE:HAVELLS-EQ_BEAR_1772091900_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ</t>
   </si>
   <si>
     <t>NSE:HINDUNILVR-EQ_BEAR_1772166600_1772184600</t>
@@ -1480,12 +1594,27 @@
     <t>NSE:ICICIGI-EQ</t>
   </si>
   <si>
+    <t>NSE:KAYNES-EQ_BEAR_1772165700_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BEAR_1772168400_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ_BEAR_1772092800_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BEAR_1772088300_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ_BEAR_1772099100_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1772170200_1772184600</t>
+  </si>
+  <si>
     <t>NSE:IEX-EQ_BEAR_1772172000_1772185500</t>
   </si>
   <si>
-    <t>2026-02-27 15:15</t>
-  </si>
-  <si>
     <t>2026-03-04 09:15</t>
   </si>
   <si>
@@ -1495,31 +1624,22 @@
     <t>2026-03-02 09:30</t>
   </si>
   <si>
-    <t>NSE:KAYNES-EQ_BEAR_1772165700_1772184600</t>
-  </si>
-  <si>
-    <t>NSE:PFC-EQ_BEAR_1772168400_1772184600</t>
-  </si>
-  <si>
     <t>NSE:SONACOMS-EQ_BEAR_1772169300_1772185500</t>
   </si>
   <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 74 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:UNOMINDA-EQ_BEAR_1772170200_1772181000</t>
-  </si>
-  <si>
-    <t>2026-02-27 14:00</t>
-  </si>
-  <si>
-    <t>2026-02-27 14:30</t>
-  </si>
-  <si>
-    <t>NSE:VBL-EQ_BEAR_1772170200_1772184600</t>
+    <t>Checked 99 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:45</t>
   </si>
   <si>
     <t>NSE:AXISBANK-EQ_BEAR_1772164800_1772424000</t>
@@ -1537,15 +1657,6 @@
     <t>2026-03-02 10:30</t>
   </si>
   <si>
-    <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
-  </si>
-  <si>
-    <t>NSE:ICICIPRULI-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-02 09:45</t>
-  </si>
-  <si>
     <t>NSE:NESTLEIND-EQ_BEAR_1772163900_1772425800</t>
   </si>
   <si>
@@ -1564,6 +1675,78 @@
     <t>NSE:M&amp;M-EQ</t>
   </si>
   <si>
+    <t>NSE:DABUR-EQ_BEAR_1772423100_1772433000</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:30</t>
+  </si>
+  <si>
+    <t>NSE:EICHERMOT-EQ_BEAR_1772185500_1772433000</t>
+  </si>
+  <si>
+    <t>NSE:EICHERMOT-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BEAR_1772163900_1772433900</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:45</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ_BEAR_1772184600_1772433900</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BEAR_1772185500_1772434800</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:00</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1772167500_1772434800</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1772185500_1772434800</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BEAR_1772424000_1772436600</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:30</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ_BEAR_1772185500_1772437500</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:15</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:45</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1772423100_1772437500</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BEAR_1772168400_1772439300</t>
+  </si>
+  <si>
+    <t>2026-03-02 14:15</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BEAR_1772423100_1772442900</t>
+  </si>
+  <si>
+    <t>2026-03-02 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-02 15:15</t>
+  </si>
+  <si>
     <t>NSE:AUROPHARMA-EQ_BEAR_1772430300_1772595900</t>
   </si>
   <si>
@@ -1582,6 +1765,15 @@
     <t>NSE:COLPAL-EQ</t>
   </si>
   <si>
+    <t>NSE:CUMMINSIND-EQ_BEAR_1772423100_1772597700</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:15</t>
+  </si>
+  <si>
     <t>NSE:IDFCFIRSTB-EQ_BEAR_1772423100_1772601300</t>
   </si>
   <si>
@@ -1606,163 +1798,118 @@
     <t>NSE:KALYANKJIL-EQ_BEAR_1772423100_1772595900</t>
   </si>
   <si>
-    <t>NSE:MAXHEALTH-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:NCC-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:NTPC-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:DIXON-EQ_BEAR_1772423100_1772604900</t>
-  </si>
-  <si>
-    <t>2026-03-04 11:45</t>
-  </si>
-  <si>
-    <t>2026-03-04 12:15</t>
-  </si>
-  <si>
-    <t>NSE:CUMMINSIND-EQ_BEAR_1772423100_1772605800</t>
-  </si>
-  <si>
-    <t>NSE:CUMMINSIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-04 12:00</t>
-  </si>
-  <si>
-    <t>2026-03-04 12:30</t>
-  </si>
-  <si>
-    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772609400</t>
-  </si>
-  <si>
-    <t>2026-03-04 13:00</t>
-  </si>
-  <si>
-    <t>2026-03-04 14:15</t>
-  </si>
-  <si>
-    <t>NSE:NATIONALUM-EQ_BULL_1772424900_1772615700</t>
-  </si>
-  <si>
-    <t>NSE:NATIONALUM-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-04 14:45</t>
-  </si>
-  <si>
-    <t>2026-03-05 09:15</t>
-  </si>
-  <si>
-    <t>NSE:DIVISLAB-EQ_BEAR_1772424000_1772617500</t>
-  </si>
-  <si>
-    <t>2026-03-04 15:15</t>
-  </si>
-  <si>
-    <t>2026-03-05 09:30</t>
-  </si>
-  <si>
-    <t>NSE:PIDILITIND-EQ_BEAR_1772423100_1772616600</t>
-  </si>
-  <si>
-    <t>2026-03-04 15:00</t>
-  </si>
-  <si>
-    <t>NSE:DABUR-EQ_BEAR_1772423100_1772616600</t>
-  </si>
-  <si>
-    <t>NSE:BHEL-EQ_BEAR_1772427600_1772616600</t>
+    <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ_BEAR_1772427600_1772595900</t>
   </si>
   <si>
     <t>NSE:BHEL-EQ</t>
   </si>
   <si>
-    <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772616600</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ_BEAR_1772423100_1772617500</t>
-  </si>
-  <si>
-    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772617500</t>
-  </si>
-  <si>
-    <t>Checked 24 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ_BULL_1772598600_1772682300</t>
+    <t>NSE:CIPLA-EQ_BEAR_1772595900_1772597700</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-06 15:00</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1772685900_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:45</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BULL_1772683200_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772684100_1772768700</t>
   </si>
   <si>
     <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
-    <t>NSE:LUPIN-EQ_BULL_1772615700_1772682300</t>
-  </si>
-  <si>
-    <t>NSE:LUPIN-EQ</t>
-  </si>
-  <si>
-    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772693100</t>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772768700</t>
   </si>
   <si>
     <t>NSE:MAZDOCK-EQ</t>
   </si>
   <si>
-    <t>2026-03-05 12:15</t>
-  </si>
-  <si>
-    <t>2026-03-05 12:45</t>
-  </si>
-  <si>
-    <t>NSE:BANDHANBNK-EQ_BULL_1772685900_1772701200</t>
-  </si>
-  <si>
-    <t>NSE:BANDHANBNK-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-05 14:30</t>
-  </si>
-  <si>
-    <t>Checked 2 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772701200</t>
-  </si>
-  <si>
-    <t>NSE:HINDZINC-EQ_BEAR_1772595900_1772702100</t>
-  </si>
-  <si>
-    <t>2026-03-05 14:45</t>
-  </si>
-  <si>
-    <t>2026-03-05 15:15</t>
-  </si>
-  <si>
-    <t>NSE:NTPC-EQ_BULL_1772691300_1772702100</t>
-  </si>
-  <si>
-    <t>Checked 1 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:OFSS-EQ_BEAR_1772686800_1772703000</t>
-  </si>
-  <si>
-    <t>2026-03-05 15:00</t>
+    <t>NSE:POLYCAB-EQ_BULL_1772702100_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1772688600_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BEAR_1772701200_1772770500</t>
+  </si>
+  <si>
+    <t>2026-03-06 10:15</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ_BULL_1772698500_1772786700</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:15</t>
+  </si>
+  <si>
+    <t>Checked 3 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ_BEAR_1772701200_1772786700</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:45</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BULL_1772778600_1772786700</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772789400</t>
   </si>
   <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>SUMMARY — 75W / 159L / 8 OPEN  |  Win Rate: 32.1%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 234 of 242</t>
+    <t>NSE:IREDA-EQ_BULL_1772772300_1772789400</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1772771400_1772790300</t>
+  </si>
+  <si>
+    <t>2026-03-06 15:15</t>
+  </si>
+  <si>
+    <t>Entry candle not yet available — trade not entered</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1772772300_1772790300</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1772693100_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:30</t>
+  </si>
+  <si>
+    <t>SUMMARY — 87W / 179L / 11 OPEN  |  Win Rate: 32.7%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 266 of 277</t>
   </si>
 </sst>
 </file>
@@ -2223,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R245"/>
+  <dimension ref="A1:R280"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -10940,7 +11087,7 @@
         <v>510.4</v>
       </c>
       <c r="F156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="G156" s="3">
         <v>509.4</v>
@@ -10949,10 +11096,10 @@
         <v>509.4</v>
       </c>
       <c r="I156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="J156" s="3">
-        <v>512.5</v>
+        <v>512.65</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>22</v>
@@ -10964,16 +11111,16 @@
         <v>399</v>
       </c>
       <c r="N156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="O156" s="2">
         <v>1</v>
       </c>
       <c r="P156" s="4">
-        <v>-3.1</v>
+        <v>-3.25</v>
       </c>
       <c r="Q156" s="5">
-        <v>-0.609</v>
+        <v>-0.638</v>
       </c>
       <c r="R156" s="2" t="s">
         <v>25</v>
@@ -13000,31 +13147,31 @@
         <v>474</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>291</v>
+        <v>163</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>475</v>
+        <v>435</v>
       </c>
       <c r="E193" s="3">
-        <v>347.25</v>
+        <v>2241.8</v>
       </c>
       <c r="F193" s="3">
-        <v>338.2</v>
+        <v>2224.4</v>
       </c>
       <c r="G193" s="3">
-        <v>344.9</v>
+        <v>2238</v>
       </c>
       <c r="H193" s="3">
-        <v>344.9</v>
+        <v>2238</v>
       </c>
       <c r="I193" s="3">
-        <v>338.2</v>
+        <v>2224.4</v>
       </c>
       <c r="J193" s="3">
-        <v>338.2</v>
+        <v>2251.6</v>
       </c>
       <c r="K193" s="2" t="s">
         <v>22</v>
@@ -13033,19 +13180,19 @@
         <v>23</v>
       </c>
       <c r="M193" s="2" t="s">
-        <v>207</v>
+        <v>469</v>
       </c>
       <c r="N193" s="3">
-        <v>338.2</v>
+        <v>2224.4</v>
       </c>
       <c r="O193" s="2">
-        <v>1</v>
-      </c>
-      <c r="P193" s="10">
-        <v>6.7</v>
-      </c>
-      <c r="Q193" s="11">
-        <v>1.943</v>
+        <v>2</v>
+      </c>
+      <c r="P193" s="4">
+        <v>-13.6</v>
+      </c>
+      <c r="Q193" s="5">
+        <v>-0.608</v>
       </c>
       <c r="R193" s="2" t="s">
         <v>25</v>
@@ -13053,34 +13200,34 @@
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>477</v>
+        <v>179</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>475</v>
+        <v>435</v>
       </c>
       <c r="E194" s="3">
-        <v>391.7</v>
+        <v>6142.5</v>
       </c>
       <c r="F194" s="3">
-        <v>388.8</v>
+        <v>6065.5</v>
       </c>
       <c r="G194" s="3">
-        <v>389.8</v>
+        <v>6065.5</v>
       </c>
       <c r="H194" s="3">
-        <v>389.8</v>
+        <v>6067</v>
       </c>
       <c r="I194" s="3">
-        <v>388.8</v>
+        <v>6065.5</v>
       </c>
       <c r="J194" s="3">
-        <v>388.8</v>
+        <v>6065.5</v>
       </c>
       <c r="K194" s="2" t="s">
         <v>22</v>
@@ -13089,110 +13236,110 @@
         <v>23</v>
       </c>
       <c r="M194" s="2" t="s">
-        <v>207</v>
+        <v>426</v>
       </c>
       <c r="N194" s="3">
-        <v>388.8</v>
+        <v>6065.5</v>
       </c>
       <c r="O194" s="2">
         <v>1</v>
       </c>
       <c r="P194" s="10">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q194" s="11">
-        <v>0.257</v>
+        <v>0.025</v>
       </c>
       <c r="R194" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A195" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C195" s="6" t="s">
+      <c r="A195" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D195" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="E195" s="7">
-        <v>337.2</v>
-      </c>
-      <c r="F195" s="7">
-        <v>333.5</v>
-      </c>
-      <c r="G195" s="7">
-        <v>334</v>
-      </c>
-      <c r="H195" s="7">
-        <v>334</v>
-      </c>
-      <c r="I195" s="7">
-        <v>333.5</v>
-      </c>
-      <c r="J195" s="7">
-        <v>333.5</v>
-      </c>
-      <c r="K195" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L195" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M195" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="N195" s="7">
-        <v>333.5</v>
-      </c>
-      <c r="O195" s="6">
-        <v>1</v>
-      </c>
-      <c r="P195" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q195" s="9">
-        <v>0.15</v>
-      </c>
-      <c r="R195" s="6" t="s">
+      <c r="D195" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E195" s="3">
+        <v>504.9</v>
+      </c>
+      <c r="F195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="G195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="H195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="I195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="J195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L195" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M195" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="N195" s="3">
+        <v>497.5</v>
+      </c>
+      <c r="O195" s="2">
+        <v>1</v>
+      </c>
+      <c r="P195" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q195" s="11">
+        <v>0</v>
+      </c>
+      <c r="R195" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="E196" s="3">
-        <v>1228.4</v>
+        <v>297.5</v>
       </c>
       <c r="F196" s="3">
-        <v>1220.3</v>
+        <v>278</v>
       </c>
       <c r="G196" s="3">
-        <v>1220.9</v>
+        <v>289.6</v>
       </c>
       <c r="H196" s="3">
-        <v>1220.9</v>
+        <v>289.6</v>
       </c>
       <c r="I196" s="3">
-        <v>1220.3</v>
+        <v>278</v>
       </c>
       <c r="J196" s="3">
-        <v>1220.3</v>
+        <v>278</v>
       </c>
       <c r="K196" s="2" t="s">
         <v>22</v>
@@ -13201,19 +13348,19 @@
         <v>23</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>481</v>
+        <v>426</v>
       </c>
       <c r="N196" s="3">
-        <v>1220.3</v>
+        <v>278</v>
       </c>
       <c r="O196" s="2">
         <v>1</v>
       </c>
       <c r="P196" s="10">
-        <v>0.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q196" s="11">
-        <v>0.049</v>
+        <v>4.006</v>
       </c>
       <c r="R196" s="2" t="s">
         <v>25</v>
@@ -13221,34 +13368,34 @@
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>483</v>
+        <v>186</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="E197" s="3">
-        <v>2731</v>
+        <v>1854.6</v>
       </c>
       <c r="F197" s="3">
-        <v>2717</v>
+        <v>1840</v>
       </c>
       <c r="G197" s="3">
-        <v>2718.6</v>
+        <v>1841.7</v>
       </c>
       <c r="H197" s="3">
-        <v>2718.6</v>
+        <v>1841.4</v>
       </c>
       <c r="I197" s="3">
-        <v>2717</v>
+        <v>1840</v>
       </c>
       <c r="J197" s="3">
-        <v>2717</v>
+        <v>1840</v>
       </c>
       <c r="K197" s="2" t="s">
         <v>22</v>
@@ -13257,166 +13404,166 @@
         <v>23</v>
       </c>
       <c r="M197" s="2" t="s">
-        <v>484</v>
+        <v>426</v>
       </c>
       <c r="N197" s="3">
-        <v>2717</v>
+        <v>1840</v>
       </c>
       <c r="O197" s="2">
         <v>1</v>
       </c>
       <c r="P197" s="10">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q197" s="11">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="R197" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A198" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C198" s="2" t="s">
+      <c r="A198" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C198" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E198" s="3">
-        <v>2349.3</v>
-      </c>
-      <c r="F198" s="3">
-        <v>2330.6</v>
-      </c>
-      <c r="G198" s="3">
-        <v>2339.5</v>
-      </c>
-      <c r="H198" s="3">
-        <v>2339.4</v>
-      </c>
-      <c r="I198" s="3">
-        <v>2330.6</v>
-      </c>
-      <c r="J198" s="3">
-        <v>2330.6</v>
-      </c>
-      <c r="K198" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L198" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M198" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="N198" s="3">
-        <v>2330.6</v>
-      </c>
-      <c r="O198" s="2">
-        <v>1</v>
-      </c>
-      <c r="P198" s="10">
-        <v>8.8</v>
-      </c>
-      <c r="Q198" s="11">
-        <v>0.376</v>
-      </c>
-      <c r="R198" s="2" t="s">
+      <c r="D198" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E198" s="7">
+        <v>3458</v>
+      </c>
+      <c r="F198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="G198" s="7">
+        <v>3408</v>
+      </c>
+      <c r="H198" s="7">
+        <v>3408</v>
+      </c>
+      <c r="I198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="J198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="K198" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L198" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M198" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="N198" s="7">
+        <v>3396.1</v>
+      </c>
+      <c r="O198" s="6">
+        <v>1</v>
+      </c>
+      <c r="P198" s="8">
+        <v>11.9</v>
+      </c>
+      <c r="Q198" s="9">
+        <v>0.349</v>
+      </c>
+      <c r="R198" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A199" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C199" s="2" t="s">
+      <c r="A199" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C199" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D199" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E199" s="3">
-        <v>1914</v>
-      </c>
-      <c r="F199" s="3">
-        <v>1894.6</v>
-      </c>
-      <c r="G199" s="3">
-        <v>1898</v>
-      </c>
-      <c r="H199" s="3">
-        <v>1898</v>
-      </c>
-      <c r="I199" s="3">
-        <v>1894.6</v>
-      </c>
-      <c r="J199" s="3">
-        <v>1894.6</v>
-      </c>
-      <c r="K199" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L199" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M199" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="N199" s="3">
-        <v>1894.6</v>
-      </c>
-      <c r="O199" s="2">
-        <v>1</v>
-      </c>
-      <c r="P199" s="10">
-        <v>3.4</v>
-      </c>
-      <c r="Q199" s="11">
-        <v>0.179</v>
-      </c>
-      <c r="R199" s="2" t="s">
+      <c r="D199" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E199" s="7">
+        <v>162.4</v>
+      </c>
+      <c r="F199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="G199" s="7">
+        <v>160.78</v>
+      </c>
+      <c r="H199" s="7">
+        <v>160.78</v>
+      </c>
+      <c r="I199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="J199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="K199" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L199" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M199" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="N199" s="7">
+        <v>160.7</v>
+      </c>
+      <c r="O199" s="6">
+        <v>1</v>
+      </c>
+      <c r="P199" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="Q199" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="R199" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="E200" s="7">
-        <v>125.75</v>
+        <v>12897</v>
       </c>
       <c r="F200" s="7">
-        <v>125.07</v>
+        <v>12763</v>
       </c>
       <c r="G200" s="7">
-        <v>125.16</v>
+        <v>12806</v>
       </c>
       <c r="H200" s="7">
-        <v>122.14</v>
+        <v>12808</v>
       </c>
       <c r="I200" s="7">
-        <v>125.07</v>
+        <v>12763</v>
       </c>
       <c r="J200" s="7">
-        <v>119.21</v>
+        <v>12763</v>
       </c>
       <c r="K200" s="6" t="s">
         <v>22</v>
@@ -13425,110 +13572,110 @@
         <v>33</v>
       </c>
       <c r="M200" s="6" t="s">
-        <v>491</v>
+        <v>426</v>
       </c>
       <c r="N200" s="7">
-        <v>119.21</v>
+        <v>12763</v>
       </c>
       <c r="O200" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="P200" s="8">
-        <v>2.93</v>
+        <v>45</v>
       </c>
       <c r="Q200" s="9">
-        <v>2.399</v>
+        <v>0.351</v>
       </c>
       <c r="R200" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A201" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E201" s="3">
-        <v>488.55</v>
-      </c>
-      <c r="F201" s="3">
-        <v>484.35</v>
-      </c>
-      <c r="G201" s="3">
-        <v>485.55</v>
-      </c>
-      <c r="H201" s="3">
-        <v>468</v>
-      </c>
-      <c r="I201" s="3">
-        <v>484.35</v>
-      </c>
-      <c r="J201" s="3">
-        <v>451.65</v>
-      </c>
-      <c r="K201" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L201" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M201" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="N201" s="3">
-        <v>484.35</v>
-      </c>
-      <c r="O201" s="2">
-        <v>1</v>
-      </c>
-      <c r="P201" s="4">
-        <v>-16.35</v>
-      </c>
-      <c r="Q201" s="5">
-        <v>-3.494</v>
-      </c>
-      <c r="R201" s="2" t="s">
+      <c r="A201" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E201" s="7">
+        <v>1555.5</v>
+      </c>
+      <c r="F201" s="7">
+        <v>1534.2</v>
+      </c>
+      <c r="G201" s="7">
+        <v>1553.3</v>
+      </c>
+      <c r="H201" s="7">
+        <v>1553.7</v>
+      </c>
+      <c r="I201" s="7">
+        <v>1534.2</v>
+      </c>
+      <c r="J201" s="7">
+        <v>1573.2</v>
+      </c>
+      <c r="K201" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L201" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M201" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="N201" s="7">
+        <v>1573.2</v>
+      </c>
+      <c r="O201" s="6">
+        <v>7</v>
+      </c>
+      <c r="P201" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="Q201" s="9">
+        <v>1.255</v>
+      </c>
+      <c r="R201" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>475</v>
+        <v>435</v>
       </c>
       <c r="E202" s="7">
-        <v>3904</v>
+        <v>21.01</v>
       </c>
       <c r="F202" s="7">
-        <v>3841</v>
+        <v>20.8</v>
       </c>
       <c r="G202" s="7">
-        <v>3848.6</v>
+        <v>20.81</v>
       </c>
       <c r="H202" s="7">
-        <v>3852</v>
+        <v>20.82</v>
       </c>
       <c r="I202" s="7">
-        <v>3841</v>
+        <v>20.8</v>
       </c>
       <c r="J202" s="7">
-        <v>3841</v>
+        <v>20.8</v>
       </c>
       <c r="K202" s="6" t="s">
         <v>22</v>
@@ -13537,19 +13684,19 @@
         <v>33</v>
       </c>
       <c r="M202" s="6" t="s">
-        <v>207</v>
+        <v>426</v>
       </c>
       <c r="N202" s="7">
-        <v>3841</v>
+        <v>20.8</v>
       </c>
       <c r="O202" s="6">
         <v>1</v>
       </c>
       <c r="P202" s="8">
-        <v>11</v>
+        <v>0.02</v>
       </c>
       <c r="Q202" s="9">
-        <v>0.286</v>
+        <v>0.096</v>
       </c>
       <c r="R202" s="6" t="s">
         <v>25</v>
@@ -13557,34 +13704,34 @@
     </row>
     <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>358</v>
+        <v>301</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="E203" s="7">
-        <v>418.75</v>
+        <v>478.6</v>
       </c>
       <c r="F203" s="7">
-        <v>413.3</v>
+        <v>473.5</v>
       </c>
       <c r="G203" s="7">
-        <v>414.05</v>
+        <v>477.2</v>
       </c>
       <c r="H203" s="7">
-        <v>414.05</v>
+        <v>477.1</v>
       </c>
       <c r="I203" s="7">
-        <v>413.3</v>
+        <v>473.5</v>
       </c>
       <c r="J203" s="7">
-        <v>413.3</v>
+        <v>480.7</v>
       </c>
       <c r="K203" s="6" t="s">
         <v>22</v>
@@ -13593,212 +13740,222 @@
         <v>33</v>
       </c>
       <c r="M203" s="6" t="s">
-        <v>207</v>
+        <v>488</v>
       </c>
       <c r="N203" s="7">
-        <v>413.3</v>
+        <v>480.7</v>
       </c>
       <c r="O203" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P203" s="8">
-        <v>0.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q203" s="9">
-        <v>0.181</v>
+        <v>0.755</v>
       </c>
       <c r="R203" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A204" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="B204" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="C204" s="12" t="s">
+      <c r="A204" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D204" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="E204" s="13">
-        <v>536.2</v>
-      </c>
-      <c r="F204" s="13">
-        <v>532.05</v>
-      </c>
-      <c r="G204" s="13">
-        <v>533.25</v>
-      </c>
-      <c r="H204" s="13">
-        <v>502</v>
-      </c>
-      <c r="I204" s="13">
-        <v>532.05</v>
-      </c>
-      <c r="J204" s="13">
-        <v>471.95</v>
-      </c>
-      <c r="K204" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L204" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M204" s="12"/>
-      <c r="N204" s="12"/>
-      <c r="O204" s="12"/>
-      <c r="P204" s="12"/>
-      <c r="Q204" s="12"/>
-      <c r="R204" s="12" t="s">
-        <v>498</v>
+      <c r="D204" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E204" s="3">
+        <v>352.7</v>
+      </c>
+      <c r="F204" s="3">
+        <v>350.8</v>
+      </c>
+      <c r="G204" s="3">
+        <v>351</v>
+      </c>
+      <c r="H204" s="3">
+        <v>350.7</v>
+      </c>
+      <c r="I204" s="3">
+        <v>350.8</v>
+      </c>
+      <c r="J204" s="3">
+        <v>350.6</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M204" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="N204" s="3">
+        <v>350.8</v>
+      </c>
+      <c r="O204" s="2">
+        <v>1</v>
+      </c>
+      <c r="P204" s="4">
+        <v>-0.1</v>
+      </c>
+      <c r="Q204" s="5">
+        <v>-0.029</v>
+      </c>
+      <c r="R204" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A205" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="C205" s="6" t="s">
+      <c r="A205" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D205" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="E205" s="7">
-        <v>1205.8</v>
-      </c>
-      <c r="F205" s="7">
-        <v>1201.1</v>
-      </c>
-      <c r="G205" s="7">
-        <v>1201.1</v>
-      </c>
-      <c r="H205" s="7">
-        <v>1201.1</v>
-      </c>
-      <c r="I205" s="7">
-        <v>1201.1</v>
-      </c>
-      <c r="J205" s="7">
-        <v>1201.1</v>
-      </c>
-      <c r="K205" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L205" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M205" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="N205" s="7">
-        <v>1201.1</v>
-      </c>
-      <c r="O205" s="6">
-        <v>1</v>
-      </c>
-      <c r="P205" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q205" s="9">
-        <v>0</v>
-      </c>
-      <c r="R205" s="6" t="s">
+      <c r="D205" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E205" s="3">
+        <v>69</v>
+      </c>
+      <c r="F205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="G205" s="3">
+        <v>68.77</v>
+      </c>
+      <c r="H205" s="3">
+        <v>68.77</v>
+      </c>
+      <c r="I205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="J205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="K205" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L205" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M205" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="N205" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="O205" s="2">
+        <v>1</v>
+      </c>
+      <c r="P205" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="Q205" s="11">
+        <v>0.029</v>
+      </c>
+      <c r="R205" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A206" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C206" s="6" t="s">
+      <c r="A206" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D206" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="E206" s="7">
-        <v>455.55</v>
-      </c>
-      <c r="F206" s="7">
-        <v>450</v>
-      </c>
-      <c r="G206" s="7">
-        <v>451</v>
-      </c>
-      <c r="H206" s="7">
-        <v>451</v>
-      </c>
-      <c r="I206" s="7">
-        <v>450</v>
-      </c>
-      <c r="J206" s="7">
-        <v>450</v>
-      </c>
-      <c r="K206" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L206" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M206" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="N206" s="7">
-        <v>450</v>
-      </c>
-      <c r="O206" s="6">
-        <v>1</v>
-      </c>
-      <c r="P206" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q206" s="9">
-        <v>0.222</v>
-      </c>
-      <c r="R206" s="6" t="s">
+      <c r="D206" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E206" s="3">
+        <v>302.8</v>
+      </c>
+      <c r="F206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="G206" s="3">
+        <v>302.05</v>
+      </c>
+      <c r="H206" s="3">
+        <v>302.05</v>
+      </c>
+      <c r="I206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="J206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="K206" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L206" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M206" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="N206" s="3">
+        <v>301.5</v>
+      </c>
+      <c r="O206" s="2">
+        <v>1</v>
+      </c>
+      <c r="P206" s="10">
+        <v>0.55</v>
+      </c>
+      <c r="Q206" s="11">
+        <v>0.182</v>
+      </c>
+      <c r="R206" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>206</v>
+        <v>495</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="E207" s="3">
-        <v>1373.1</v>
+        <v>2731</v>
       </c>
       <c r="F207" s="3">
-        <v>1365.5</v>
+        <v>2717</v>
       </c>
       <c r="G207" s="3">
-        <v>1366.2</v>
+        <v>2718.6</v>
       </c>
       <c r="H207" s="3">
-        <v>1366.1</v>
+        <v>2718.6</v>
       </c>
       <c r="I207" s="3">
-        <v>1365.5</v>
+        <v>2717</v>
       </c>
       <c r="J207" s="3">
-        <v>1365.5</v>
+        <v>2717</v>
       </c>
       <c r="K207" s="2" t="s">
         <v>22</v>
@@ -13807,19 +13964,19 @@
         <v>23</v>
       </c>
       <c r="M207" s="2" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="N207" s="3">
-        <v>1365.5</v>
+        <v>2717</v>
       </c>
       <c r="O207" s="2">
         <v>1</v>
       </c>
       <c r="P207" s="10">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q207" s="11">
-        <v>0.044</v>
+        <v>0.059</v>
       </c>
       <c r="R207" s="2" t="s">
         <v>25</v>
@@ -13827,34 +13984,34 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>506</v>
+        <v>88</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="E208" s="3">
-        <v>1278.8</v>
+        <v>429.7</v>
       </c>
       <c r="F208" s="3">
-        <v>1274</v>
+        <v>426.9</v>
       </c>
       <c r="G208" s="3">
-        <v>1276.6</v>
+        <v>426.9</v>
       </c>
       <c r="H208" s="3">
-        <v>1277.3</v>
+        <v>427.1</v>
       </c>
       <c r="I208" s="3">
-        <v>1274</v>
+        <v>426.9</v>
       </c>
       <c r="J208" s="3">
-        <v>1274</v>
+        <v>426.9</v>
       </c>
       <c r="K208" s="2" t="s">
         <v>22</v>
@@ -13863,19 +14020,19 @@
         <v>23</v>
       </c>
       <c r="M208" s="2" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="N208" s="3">
-        <v>1274</v>
+        <v>426.9</v>
       </c>
       <c r="O208" s="2">
         <v>1</v>
       </c>
       <c r="P208" s="10">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q208" s="11">
-        <v>0.258</v>
+        <v>0.047</v>
       </c>
       <c r="R208" s="2" t="s">
         <v>25</v>
@@ -13883,34 +14040,34 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>509</v>
+        <v>304</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>207</v>
+        <v>499</v>
       </c>
       <c r="E209" s="3">
-        <v>654</v>
+        <v>770</v>
       </c>
       <c r="F209" s="3">
-        <v>646.35</v>
+        <v>768.5</v>
       </c>
       <c r="G209" s="3">
-        <v>647.35</v>
+        <v>768.95</v>
       </c>
       <c r="H209" s="3">
-        <v>646.9</v>
+        <v>768.95</v>
       </c>
       <c r="I209" s="3">
-        <v>646.35</v>
+        <v>768.5</v>
       </c>
       <c r="J209" s="3">
-        <v>646.35</v>
+        <v>768.5</v>
       </c>
       <c r="K209" s="2" t="s">
         <v>22</v>
@@ -13919,19 +14076,19 @@
         <v>23</v>
       </c>
       <c r="M209" s="2" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="N209" s="3">
-        <v>646.35</v>
+        <v>768.5</v>
       </c>
       <c r="O209" s="2">
         <v>1</v>
       </c>
       <c r="P209" s="10">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="Q209" s="11">
-        <v>0.085</v>
+        <v>0.059</v>
       </c>
       <c r="R209" s="2" t="s">
         <v>25</v>
@@ -13939,34 +14096,34 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E210" s="3">
-        <v>1280</v>
+        <v>1228.4</v>
       </c>
       <c r="F210" s="3">
-        <v>1275.1</v>
+        <v>1220.3</v>
       </c>
       <c r="G210" s="3">
-        <v>1276</v>
+        <v>1220.9</v>
       </c>
       <c r="H210" s="3">
-        <v>1276.2</v>
+        <v>1220.9</v>
       </c>
       <c r="I210" s="3">
-        <v>1275.1</v>
+        <v>1220.3</v>
       </c>
       <c r="J210" s="3">
-        <v>1275.1</v>
+        <v>1220.3</v>
       </c>
       <c r="K210" s="2" t="s">
         <v>22</v>
@@ -13975,19 +14132,19 @@
         <v>23</v>
       </c>
       <c r="M210" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="N210" s="3">
-        <v>1275.1</v>
+        <v>1220.3</v>
       </c>
       <c r="O210" s="2">
         <v>1</v>
       </c>
       <c r="P210" s="10">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q210" s="11">
-        <v>0.086</v>
+        <v>0.049</v>
       </c>
       <c r="R210" s="2" t="s">
         <v>25</v>
@@ -13995,34 +14152,34 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>106</v>
+        <v>468</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="E211" s="3">
-        <v>122.43</v>
+        <v>6985</v>
       </c>
       <c r="F211" s="3">
-        <v>121.51</v>
+        <v>6950</v>
       </c>
       <c r="G211" s="3">
-        <v>121.51</v>
+        <v>6976</v>
       </c>
       <c r="H211" s="3">
-        <v>121.56</v>
+        <v>6976</v>
       </c>
       <c r="I211" s="3">
-        <v>121.51</v>
+        <v>6950</v>
       </c>
       <c r="J211" s="3">
-        <v>121.51</v>
+        <v>7002</v>
       </c>
       <c r="K211" s="2" t="s">
         <v>22</v>
@@ -14031,110 +14188,110 @@
         <v>23</v>
       </c>
       <c r="M211" s="2" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="N211" s="3">
-        <v>121.51</v>
+        <v>6950</v>
       </c>
       <c r="O211" s="2">
         <v>1</v>
       </c>
-      <c r="P211" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="Q211" s="11">
-        <v>0.041</v>
+      <c r="P211" s="4">
+        <v>-26</v>
+      </c>
+      <c r="Q211" s="5">
+        <v>-0.373</v>
       </c>
       <c r="R211" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A212" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C212" s="2" t="s">
+      <c r="A212" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C212" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D212" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E212" s="3">
-        <v>3306.1</v>
-      </c>
-      <c r="F212" s="3">
-        <v>3283.4</v>
-      </c>
-      <c r="G212" s="3">
-        <v>3285.9</v>
-      </c>
-      <c r="H212" s="3">
-        <v>3285.2</v>
-      </c>
-      <c r="I212" s="3">
-        <v>3283.4</v>
-      </c>
-      <c r="J212" s="3">
-        <v>3283.4</v>
-      </c>
-      <c r="K212" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L212" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M212" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="N212" s="3">
-        <v>3283.4</v>
-      </c>
-      <c r="O212" s="2">
-        <v>1</v>
-      </c>
-      <c r="P212" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="Q212" s="11">
-        <v>0.055</v>
-      </c>
-      <c r="R212" s="2" t="s">
+      <c r="D212" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E212" s="7">
+        <v>1205.8</v>
+      </c>
+      <c r="F212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="G212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="H212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="I212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="J212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="K212" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L212" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M212" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="N212" s="7">
+        <v>1201.1</v>
+      </c>
+      <c r="O212" s="6">
+        <v>1</v>
+      </c>
+      <c r="P212" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q212" s="9">
+        <v>0</v>
+      </c>
+      <c r="R212" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>253</v>
+        <v>388</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="E213" s="3">
-        <v>1202.9</v>
+        <v>151.28</v>
       </c>
       <c r="F213" s="3">
-        <v>1183.4</v>
+        <v>150.67</v>
       </c>
       <c r="G213" s="3">
-        <v>1188.3</v>
+        <v>150.75</v>
       </c>
       <c r="H213" s="3">
-        <v>1188.4</v>
+        <v>150.81</v>
       </c>
       <c r="I213" s="3">
-        <v>1183.4</v>
+        <v>150.67</v>
       </c>
       <c r="J213" s="3">
-        <v>1183.4</v>
+        <v>150.67</v>
       </c>
       <c r="K213" s="2" t="s">
         <v>22</v>
@@ -14143,19 +14300,19 @@
         <v>23</v>
       </c>
       <c r="M213" s="2" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N213" s="3">
-        <v>1183.4</v>
+        <v>150.67</v>
       </c>
       <c r="O213" s="2">
         <v>1</v>
       </c>
       <c r="P213" s="10">
-        <v>5</v>
+        <v>0.14</v>
       </c>
       <c r="Q213" s="11">
-        <v>0.421</v>
+        <v>0.093</v>
       </c>
       <c r="R213" s="2" t="s">
         <v>25</v>
@@ -14163,34 +14320,34 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>520</v>
+        <v>275</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="E214" s="3">
-        <v>1870</v>
+        <v>3159.3</v>
       </c>
       <c r="F214" s="3">
-        <v>1833</v>
+        <v>3139.3</v>
       </c>
       <c r="G214" s="3">
-        <v>1841.4</v>
+        <v>3159.3</v>
       </c>
       <c r="H214" s="3">
-        <v>1840.4</v>
+        <v>3158.6</v>
       </c>
       <c r="I214" s="3">
-        <v>1833</v>
+        <v>3139.3</v>
       </c>
       <c r="J214" s="3">
-        <v>1833</v>
+        <v>3177.9</v>
       </c>
       <c r="K214" s="2" t="s">
         <v>22</v>
@@ -14199,19 +14356,19 @@
         <v>23</v>
       </c>
       <c r="M214" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N214" s="3">
-        <v>1833</v>
+        <v>3139.3</v>
       </c>
       <c r="O214" s="2">
         <v>1</v>
       </c>
-      <c r="P214" s="10">
-        <v>7.4</v>
-      </c>
-      <c r="Q214" s="11">
-        <v>0.402</v>
+      <c r="P214" s="4">
+        <v>-19.3</v>
+      </c>
+      <c r="Q214" s="5">
+        <v>-0.611</v>
       </c>
       <c r="R214" s="2" t="s">
         <v>25</v>
@@ -14219,34 +14376,34 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>522</v>
+        <v>291</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="E215" s="3">
-        <v>2203.6</v>
+        <v>347.25</v>
       </c>
       <c r="F215" s="3">
-        <v>2185.4</v>
+        <v>338.2</v>
       </c>
       <c r="G215" s="3">
-        <v>2192.8</v>
+        <v>344.9</v>
       </c>
       <c r="H215" s="3">
-        <v>2192.6</v>
+        <v>344.9</v>
       </c>
       <c r="I215" s="3">
-        <v>2185.4</v>
+        <v>338.2</v>
       </c>
       <c r="J215" s="3">
-        <v>2185.4</v>
+        <v>338.2</v>
       </c>
       <c r="K215" s="2" t="s">
         <v>22</v>
@@ -14255,278 +14412,278 @@
         <v>23</v>
       </c>
       <c r="M215" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N215" s="3">
+        <v>338.2</v>
+      </c>
+      <c r="O215" s="2">
+        <v>1</v>
+      </c>
+      <c r="P215" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="Q215" s="11">
+        <v>1.943</v>
+      </c>
+      <c r="R215" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A216" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E216" s="7">
+        <v>3866.5</v>
+      </c>
+      <c r="F216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="G216" s="7">
+        <v>3841.2</v>
+      </c>
+      <c r="H216" s="7">
+        <v>3842.1</v>
+      </c>
+      <c r="I216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="J216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="K216" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L216" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M216" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N216" s="7">
+        <v>3840</v>
+      </c>
+      <c r="O216" s="6">
+        <v>1</v>
+      </c>
+      <c r="P216" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="Q216" s="9">
+        <v>0.055</v>
+      </c>
+      <c r="R216" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="N215" s="3">
-        <v>2185.4</v>
-      </c>
-      <c r="O215" s="2">
-        <v>1</v>
-      </c>
-      <c r="P215" s="10">
-        <v>7.2</v>
-      </c>
-      <c r="Q215" s="11">
-        <v>0.328</v>
-      </c>
-      <c r="R215" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C216" s="2" t="s">
+      <c r="B217" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D216" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E216" s="3">
-        <v>70.31</v>
-      </c>
-      <c r="F216" s="3">
-        <v>70.02</v>
-      </c>
-      <c r="G216" s="3">
-        <v>70.1</v>
-      </c>
-      <c r="H216" s="3">
-        <v>70.08</v>
-      </c>
-      <c r="I216" s="3">
-        <v>70.02</v>
-      </c>
-      <c r="J216" s="3">
-        <v>70.02</v>
-      </c>
-      <c r="K216" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L216" s="2" t="s">
+      <c r="D217" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E217" s="3">
+        <v>391.7</v>
+      </c>
+      <c r="F217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="G217" s="3">
+        <v>389.8</v>
+      </c>
+      <c r="H217" s="3">
+        <v>389.8</v>
+      </c>
+      <c r="I217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="J217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L217" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M216" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="N216" s="3">
-        <v>70.02</v>
-      </c>
-      <c r="O216" s="2">
-        <v>1</v>
-      </c>
-      <c r="P216" s="10">
-        <v>0.06</v>
-      </c>
-      <c r="Q216" s="11">
-        <v>0.086</v>
-      </c>
-      <c r="R216" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A217" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="C217" s="6" t="s">
+      <c r="M217" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N217" s="3">
+        <v>388.8</v>
+      </c>
+      <c r="O217" s="2">
+        <v>1</v>
+      </c>
+      <c r="P217" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q217" s="11">
+        <v>0.257</v>
+      </c>
+      <c r="R217" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A218" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C218" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D217" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="E217" s="7">
-        <v>961.35</v>
-      </c>
-      <c r="F217" s="7">
-        <v>947.1</v>
-      </c>
-      <c r="G217" s="7">
-        <v>949.25</v>
-      </c>
-      <c r="H217" s="7">
-        <v>949.05</v>
-      </c>
-      <c r="I217" s="7">
-        <v>947.1</v>
-      </c>
-      <c r="J217" s="7">
-        <v>947.1</v>
-      </c>
-      <c r="K217" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L217" s="6" t="s">
+      <c r="D218" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E218" s="7">
+        <v>337.2</v>
+      </c>
+      <c r="F218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="G218" s="7">
+        <v>334</v>
+      </c>
+      <c r="H218" s="7">
+        <v>334</v>
+      </c>
+      <c r="I218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="J218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="K218" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L218" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M217" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="N217" s="7">
-        <v>947.1</v>
-      </c>
-      <c r="O217" s="6">
-        <v>1</v>
-      </c>
-      <c r="P217" s="8">
-        <v>1.95</v>
-      </c>
-      <c r="Q217" s="9">
-        <v>0.205</v>
-      </c>
-      <c r="R217" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C218" s="2" t="s">
+      <c r="M218" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N218" s="7">
+        <v>333.5</v>
+      </c>
+      <c r="O218" s="6">
+        <v>1</v>
+      </c>
+      <c r="P218" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q218" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="R218" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A219" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C219" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D218" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E218" s="3">
-        <v>165.26</v>
-      </c>
-      <c r="F218" s="3">
-        <v>162.03</v>
-      </c>
-      <c r="G218" s="3">
-        <v>162.38</v>
-      </c>
-      <c r="H218" s="3">
-        <v>162.4</v>
-      </c>
-      <c r="I218" s="3">
-        <v>162.03</v>
-      </c>
-      <c r="J218" s="3">
-        <v>162.03</v>
-      </c>
-      <c r="K218" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L218" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M218" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="N218" s="3">
-        <v>162.03</v>
-      </c>
-      <c r="O218" s="2">
-        <v>1</v>
-      </c>
-      <c r="P218" s="10">
-        <v>0.37</v>
-      </c>
-      <c r="Q218" s="11">
-        <v>0.228</v>
-      </c>
-      <c r="R218" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A219" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E219" s="3">
-        <v>1253.9</v>
-      </c>
-      <c r="F219" s="3">
-        <v>1215.3</v>
-      </c>
-      <c r="G219" s="3">
-        <v>1217</v>
-      </c>
-      <c r="H219" s="3">
-        <v>1218</v>
-      </c>
-      <c r="I219" s="3">
-        <v>1215.3</v>
-      </c>
-      <c r="J219" s="3">
-        <v>1215.3</v>
-      </c>
-      <c r="K219" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L219" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M219" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="N219" s="3">
-        <v>1215.3</v>
-      </c>
-      <c r="O219" s="2">
-        <v>1</v>
-      </c>
-      <c r="P219" s="10">
-        <v>2.7</v>
-      </c>
-      <c r="Q219" s="11">
-        <v>0.222</v>
-      </c>
-      <c r="R219" s="2" t="s">
+      <c r="D219" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E219" s="7">
+        <v>1415.8</v>
+      </c>
+      <c r="F219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="G219" s="7">
+        <v>1397</v>
+      </c>
+      <c r="H219" s="7">
+        <v>1396.7</v>
+      </c>
+      <c r="I219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="J219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="K219" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L219" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M219" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N219" s="7">
+        <v>1395.4</v>
+      </c>
+      <c r="O219" s="6">
+        <v>1</v>
+      </c>
+      <c r="P219" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="Q219" s="9">
+        <v>0.093</v>
+      </c>
+      <c r="R219" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>202</v>
+        <v>524</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="E220" s="3">
-        <v>396.3</v>
+        <v>2349.3</v>
       </c>
       <c r="F220" s="3">
-        <v>390.05</v>
+        <v>2330.6</v>
       </c>
       <c r="G220" s="3">
-        <v>392.55</v>
+        <v>2339.5</v>
       </c>
       <c r="H220" s="3">
-        <v>392.45</v>
+        <v>2339.4</v>
       </c>
       <c r="I220" s="3">
-        <v>390.05</v>
+        <v>2330.6</v>
       </c>
       <c r="J220" s="3">
-        <v>390.05</v>
+        <v>2330.6</v>
       </c>
       <c r="K220" s="2" t="s">
         <v>22</v>
@@ -14535,19 +14692,19 @@
         <v>23</v>
       </c>
       <c r="M220" s="2" t="s">
-        <v>518</v>
+        <v>207</v>
       </c>
       <c r="N220" s="3">
-        <v>390.05</v>
+        <v>2330.6</v>
       </c>
       <c r="O220" s="2">
         <v>1</v>
       </c>
       <c r="P220" s="10">
-        <v>2.4</v>
+        <v>8.8</v>
       </c>
       <c r="Q220" s="11">
-        <v>0.612</v>
+        <v>0.376</v>
       </c>
       <c r="R220" s="2" t="s">
         <v>25</v>
@@ -14555,34 +14712,34 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>446</v>
+        <v>526</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="E221" s="3">
-        <v>1067.8</v>
+        <v>1914</v>
       </c>
       <c r="F221" s="3">
-        <v>1047</v>
+        <v>1894.6</v>
       </c>
       <c r="G221" s="3">
-        <v>1050.6</v>
+        <v>1898</v>
       </c>
       <c r="H221" s="3">
-        <v>1051.4</v>
+        <v>1898</v>
       </c>
       <c r="I221" s="3">
-        <v>1047</v>
+        <v>1894.6</v>
       </c>
       <c r="J221" s="3">
-        <v>1047</v>
+        <v>1894.6</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>22</v>
@@ -14591,222 +14748,222 @@
         <v>23</v>
       </c>
       <c r="M221" s="2" t="s">
-        <v>518</v>
+        <v>207</v>
       </c>
       <c r="N221" s="3">
-        <v>1047</v>
+        <v>1894.6</v>
       </c>
       <c r="O221" s="2">
         <v>1</v>
       </c>
       <c r="P221" s="10">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q221" s="11">
-        <v>0.418</v>
+        <v>0.179</v>
       </c>
       <c r="R221" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C222" s="2" t="s">
+      <c r="A222" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C222" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E222" s="3">
-        <v>147.09</v>
-      </c>
-      <c r="F222" s="3">
-        <v>145</v>
-      </c>
-      <c r="G222" s="3">
-        <v>145.4</v>
-      </c>
-      <c r="H222" s="3">
-        <v>145.31</v>
-      </c>
-      <c r="I222" s="3">
-        <v>145</v>
-      </c>
-      <c r="J222" s="3">
-        <v>145</v>
-      </c>
-      <c r="K222" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L222" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M222" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="N222" s="3">
-        <v>145</v>
-      </c>
-      <c r="O222" s="2">
-        <v>1</v>
-      </c>
-      <c r="P222" s="10">
-        <v>0.31</v>
-      </c>
-      <c r="Q222" s="11">
-        <v>0.213</v>
-      </c>
-      <c r="R222" s="2" t="s">
+      <c r="D222" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E222" s="7">
+        <v>3904</v>
+      </c>
+      <c r="F222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="G222" s="7">
+        <v>3848.6</v>
+      </c>
+      <c r="H222" s="7">
+        <v>3852</v>
+      </c>
+      <c r="I222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="J222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="K222" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L222" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M222" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N222" s="7">
+        <v>3841</v>
+      </c>
+      <c r="O222" s="6">
+        <v>1</v>
+      </c>
+      <c r="P222" s="8">
+        <v>11</v>
+      </c>
+      <c r="Q222" s="9">
+        <v>0.286</v>
+      </c>
+      <c r="R222" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C223" s="2" t="s">
+      <c r="A223" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C223" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E223" s="3">
-        <v>373.85</v>
-      </c>
-      <c r="F223" s="3">
-        <v>366.6</v>
-      </c>
-      <c r="G223" s="3">
-        <v>366.9</v>
-      </c>
-      <c r="H223" s="3">
-        <v>366.75</v>
-      </c>
-      <c r="I223" s="3">
-        <v>366.6</v>
-      </c>
-      <c r="J223" s="3">
-        <v>366.6</v>
-      </c>
-      <c r="K223" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L223" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M223" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="N223" s="3">
-        <v>366.6</v>
-      </c>
-      <c r="O223" s="2">
-        <v>1</v>
-      </c>
-      <c r="P223" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="Q223" s="11">
-        <v>0.041</v>
-      </c>
-      <c r="R223" s="2" t="s">
+      <c r="D223" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E223" s="7">
+        <v>418.75</v>
+      </c>
+      <c r="F223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="G223" s="7">
+        <v>414.05</v>
+      </c>
+      <c r="H223" s="7">
+        <v>414.05</v>
+      </c>
+      <c r="I223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="J223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="K223" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L223" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M223" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N223" s="7">
+        <v>413.3</v>
+      </c>
+      <c r="O223" s="6">
+        <v>1</v>
+      </c>
+      <c r="P223" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="Q223" s="9">
+        <v>0.181</v>
+      </c>
+      <c r="R223" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C224" s="2" t="s">
+      <c r="A224" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C224" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D224" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E224" s="3">
-        <v>606.95</v>
-      </c>
-      <c r="F224" s="3">
-        <v>590.5</v>
-      </c>
-      <c r="G224" s="3">
-        <v>591.7</v>
-      </c>
-      <c r="H224" s="3">
-        <v>591.55</v>
-      </c>
-      <c r="I224" s="3">
-        <v>590.5</v>
-      </c>
-      <c r="J224" s="3">
-        <v>590.5</v>
-      </c>
-      <c r="K224" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L224" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M224" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="N224" s="3">
-        <v>590.5</v>
-      </c>
-      <c r="O224" s="2">
-        <v>1</v>
-      </c>
-      <c r="P224" s="10">
-        <v>1.05</v>
-      </c>
-      <c r="Q224" s="11">
-        <v>0.177</v>
-      </c>
-      <c r="R224" s="2" t="s">
+      <c r="D224" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E224" s="7">
+        <v>130.45</v>
+      </c>
+      <c r="F224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="G224" s="7">
+        <v>129.4</v>
+      </c>
+      <c r="H224" s="7">
+        <v>129.39</v>
+      </c>
+      <c r="I224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="J224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="K224" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L224" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M224" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="N224" s="7">
+        <v>129.25</v>
+      </c>
+      <c r="O224" s="6">
+        <v>1</v>
+      </c>
+      <c r="P224" s="8">
+        <v>0.14</v>
+      </c>
+      <c r="Q224" s="9">
+        <v>0.108</v>
+      </c>
+      <c r="R224" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="E225" s="3">
-        <v>9827</v>
+        <v>2050.3</v>
       </c>
       <c r="F225" s="3">
-        <v>9792</v>
+        <v>2030.9</v>
       </c>
       <c r="G225" s="3">
-        <v>9797</v>
+        <v>2038</v>
       </c>
       <c r="H225" s="3">
-        <v>9795</v>
+        <v>2037.7</v>
       </c>
       <c r="I225" s="3">
-        <v>9792</v>
+        <v>2030.9</v>
       </c>
       <c r="J225" s="3">
-        <v>9792</v>
+        <v>2030.9</v>
       </c>
       <c r="K225" s="2" t="s">
         <v>22</v>
@@ -14815,19 +14972,19 @@
         <v>23</v>
       </c>
       <c r="M225" s="2" t="s">
-        <v>537</v>
+        <v>207</v>
       </c>
       <c r="N225" s="3">
-        <v>9792</v>
+        <v>2030.9</v>
       </c>
       <c r="O225" s="2">
         <v>1</v>
       </c>
       <c r="P225" s="10">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="Q225" s="11">
-        <v>0.031</v>
+        <v>0.334</v>
       </c>
       <c r="R225" s="2" t="s">
         <v>25</v>
@@ -14835,34 +14992,34 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>539</v>
+        <v>318</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="E226" s="7">
-        <v>4662.9</v>
+        <v>26285</v>
       </c>
       <c r="F226" s="7">
-        <v>4646.6</v>
+        <v>25990</v>
       </c>
       <c r="G226" s="7">
-        <v>4650.6</v>
+        <v>26085</v>
       </c>
       <c r="H226" s="7">
-        <v>4651.3</v>
+        <v>26090</v>
       </c>
       <c r="I226" s="7">
-        <v>4646.6</v>
+        <v>25990</v>
       </c>
       <c r="J226" s="7">
-        <v>4646.6</v>
+        <v>25990</v>
       </c>
       <c r="K226" s="6" t="s">
         <v>22</v>
@@ -14871,19 +15028,19 @@
         <v>33</v>
       </c>
       <c r="M226" s="6" t="s">
-        <v>541</v>
+        <v>207</v>
       </c>
       <c r="N226" s="7">
-        <v>4646.6</v>
+        <v>25990</v>
       </c>
       <c r="O226" s="6">
         <v>1</v>
       </c>
       <c r="P226" s="8">
-        <v>4.7</v>
+        <v>100</v>
       </c>
       <c r="Q226" s="9">
-        <v>0.101</v>
+        <v>0.383</v>
       </c>
       <c r="R226" s="6" t="s">
         <v>25</v>
@@ -14891,34 +15048,34 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
       <c r="E227" s="7">
-        <v>14499</v>
+        <v>455.55</v>
       </c>
       <c r="F227" s="7">
-        <v>14393</v>
+        <v>450</v>
       </c>
       <c r="G227" s="7">
-        <v>14455</v>
+        <v>451</v>
       </c>
       <c r="H227" s="7">
-        <v>14465</v>
+        <v>451</v>
       </c>
       <c r="I227" s="7">
-        <v>14393</v>
+        <v>450</v>
       </c>
       <c r="J227" s="7">
-        <v>14537</v>
+        <v>450</v>
       </c>
       <c r="K227" s="6" t="s">
         <v>22</v>
@@ -14927,19 +15084,19 @@
         <v>33</v>
       </c>
       <c r="M227" s="6" t="s">
-        <v>544</v>
+        <v>207</v>
       </c>
       <c r="N227" s="7">
-        <v>14537</v>
+        <v>450</v>
       </c>
       <c r="O227" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P227" s="8">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="Q227" s="9">
-        <v>0.498</v>
+        <v>0.222</v>
       </c>
       <c r="R227" s="6" t="s">
         <v>25</v>
@@ -14947,34 +15104,34 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>546</v>
+        <v>106</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="E228" s="7">
-        <v>377.3</v>
+        <v>125.75</v>
       </c>
       <c r="F228" s="7">
-        <v>371.4</v>
+        <v>125.07</v>
       </c>
       <c r="G228" s="7">
-        <v>375.95</v>
+        <v>125.16</v>
       </c>
       <c r="H228" s="7">
-        <v>375.8</v>
+        <v>122.14</v>
       </c>
       <c r="I228" s="7">
-        <v>371.4</v>
+        <v>125.07</v>
       </c>
       <c r="J228" s="7">
-        <v>380.2</v>
+        <v>119.21</v>
       </c>
       <c r="K228" s="6" t="s">
         <v>22</v>
@@ -14983,19 +15140,19 @@
         <v>33</v>
       </c>
       <c r="M228" s="6" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="N228" s="7">
-        <v>380.2</v>
+        <v>119.21</v>
       </c>
       <c r="O228" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="P228" s="8">
-        <v>4.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q228" s="9">
-        <v>1.171</v>
+        <v>2.399</v>
       </c>
       <c r="R228" s="6" t="s">
         <v>25</v>
@@ -15003,34 +15160,34 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="E229" s="3">
-        <v>6317.5</v>
+        <v>488.55</v>
       </c>
       <c r="F229" s="3">
-        <v>6281.5</v>
+        <v>484.35</v>
       </c>
       <c r="G229" s="3">
-        <v>6281.5</v>
+        <v>485.55</v>
       </c>
       <c r="H229" s="3">
-        <v>6316.5</v>
+        <v>468</v>
       </c>
       <c r="I229" s="3">
-        <v>6281.5</v>
+        <v>484.35</v>
       </c>
       <c r="J229" s="3">
-        <v>6281.5</v>
+        <v>451.65</v>
       </c>
       <c r="K229" s="2" t="s">
         <v>22</v>
@@ -15039,110 +15196,100 @@
         <v>23</v>
       </c>
       <c r="M229" s="2" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="N229" s="3">
-        <v>6281.5</v>
+        <v>484.35</v>
       </c>
       <c r="O229" s="2">
         <v>1</v>
       </c>
-      <c r="P229" s="10">
-        <v>35</v>
-      </c>
-      <c r="Q229" s="11">
-        <v>0.554</v>
+      <c r="P229" s="4">
+        <v>-16.35</v>
+      </c>
+      <c r="Q229" s="5">
+        <v>-3.494</v>
       </c>
       <c r="R229" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C230" s="2" t="s">
+      <c r="A230" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C230" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E230" s="3">
-        <v>1444</v>
-      </c>
-      <c r="F230" s="3">
-        <v>1436.5</v>
-      </c>
-      <c r="G230" s="3">
-        <v>1436.9</v>
-      </c>
-      <c r="H230" s="3">
-        <v>1437.2</v>
-      </c>
-      <c r="I230" s="3">
-        <v>1436.5</v>
-      </c>
-      <c r="J230" s="3">
-        <v>1436.5</v>
-      </c>
-      <c r="K230" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L230" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M230" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="N230" s="3">
-        <v>1436.5</v>
-      </c>
-      <c r="O230" s="2">
-        <v>1</v>
-      </c>
-      <c r="P230" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="Q230" s="11">
-        <v>0.049</v>
-      </c>
-      <c r="R230" s="2" t="s">
-        <v>25</v>
+      <c r="D230" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="E230" s="13">
+        <v>536.2</v>
+      </c>
+      <c r="F230" s="13">
+        <v>532.05</v>
+      </c>
+      <c r="G230" s="13">
+        <v>533.25</v>
+      </c>
+      <c r="H230" s="13">
+        <v>502</v>
+      </c>
+      <c r="I230" s="13">
+        <v>532.05</v>
+      </c>
+      <c r="J230" s="13">
+        <v>471.95</v>
+      </c>
+      <c r="K230" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L230" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M230" s="12"/>
+      <c r="N230" s="12"/>
+      <c r="O230" s="12"/>
+      <c r="P230" s="12"/>
+      <c r="Q230" s="12"/>
+      <c r="R230" s="12" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>95</v>
+        <v>541</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>553</v>
+        <v>207</v>
       </c>
       <c r="E231" s="3">
-        <v>490.8</v>
+        <v>654</v>
       </c>
       <c r="F231" s="3">
-        <v>486.65</v>
+        <v>646.35</v>
       </c>
       <c r="G231" s="3">
-        <v>487.15</v>
+        <v>647.35</v>
       </c>
       <c r="H231" s="3">
-        <v>487.15</v>
+        <v>646.9</v>
       </c>
       <c r="I231" s="3">
-        <v>486.65</v>
+        <v>646.35</v>
       </c>
       <c r="J231" s="3">
-        <v>486.65</v>
+        <v>646.35</v>
       </c>
       <c r="K231" s="2" t="s">
         <v>22</v>
@@ -15151,19 +15298,19 @@
         <v>23</v>
       </c>
       <c r="M231" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="N231" s="3">
-        <v>486.65</v>
+        <v>646.35</v>
       </c>
       <c r="O231" s="2">
         <v>1</v>
       </c>
       <c r="P231" s="10">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="Q231" s="11">
-        <v>0.103</v>
+        <v>0.085</v>
       </c>
       <c r="R231" s="2" t="s">
         <v>25</v>
@@ -15171,34 +15318,34 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>556</v>
+        <v>206</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="E232" s="3">
-        <v>249.5</v>
+        <v>1373.1</v>
       </c>
       <c r="F232" s="3">
-        <v>247.25</v>
+        <v>1365.5</v>
       </c>
       <c r="G232" s="3">
-        <v>247.45</v>
+        <v>1366.2</v>
       </c>
       <c r="H232" s="3">
-        <v>247.4</v>
+        <v>1366.1</v>
       </c>
       <c r="I232" s="3">
-        <v>247.25</v>
+        <v>1365.5</v>
       </c>
       <c r="J232" s="3">
-        <v>247.25</v>
+        <v>1365.5</v>
       </c>
       <c r="K232" s="2" t="s">
         <v>22</v>
@@ -15207,19 +15354,19 @@
         <v>23</v>
       </c>
       <c r="M232" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="N232" s="3">
-        <v>247.25</v>
+        <v>1365.5</v>
       </c>
       <c r="O232" s="2">
         <v>1</v>
       </c>
       <c r="P232" s="10">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="Q232" s="11">
-        <v>0.061</v>
+        <v>0.044</v>
       </c>
       <c r="R232" s="2" t="s">
         <v>25</v>
@@ -15227,34 +15374,34 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>336</v>
+        <v>546</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E233" s="3">
-        <v>1656.3</v>
+        <v>1278.8</v>
       </c>
       <c r="F233" s="3">
-        <v>1645</v>
+        <v>1274</v>
       </c>
       <c r="G233" s="3">
-        <v>1647.7</v>
+        <v>1276.6</v>
       </c>
       <c r="H233" s="3">
-        <v>1647.7</v>
+        <v>1277.3</v>
       </c>
       <c r="I233" s="3">
-        <v>1645</v>
+        <v>1274</v>
       </c>
       <c r="J233" s="3">
-        <v>1645</v>
+        <v>1274</v>
       </c>
       <c r="K233" s="2" t="s">
         <v>22</v>
@@ -15263,19 +15410,19 @@
         <v>23</v>
       </c>
       <c r="M233" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N233" s="3">
-        <v>1645</v>
+        <v>1274</v>
       </c>
       <c r="O233" s="2">
         <v>1</v>
       </c>
       <c r="P233" s="10">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="Q233" s="11">
-        <v>0.164</v>
+        <v>0.258</v>
       </c>
       <c r="R233" s="2" t="s">
         <v>25</v>
@@ -15283,34 +15430,34 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E234" s="3">
-        <v>157.7</v>
+        <v>1280</v>
       </c>
       <c r="F234" s="3">
-        <v>156.8</v>
+        <v>1275.1</v>
       </c>
       <c r="G234" s="3">
-        <v>157.18</v>
+        <v>1276</v>
       </c>
       <c r="H234" s="3">
-        <v>157.99</v>
+        <v>1276.2</v>
       </c>
       <c r="I234" s="3">
-        <v>156.8</v>
+        <v>1275.1</v>
       </c>
       <c r="J234" s="3">
-        <v>156.8</v>
+        <v>1275.1</v>
       </c>
       <c r="K234" s="2" t="s">
         <v>22</v>
@@ -15319,340 +15466,390 @@
         <v>23</v>
       </c>
       <c r="M234" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="N234" s="3">
+        <v>1275.1</v>
+      </c>
+      <c r="O234" s="2">
+        <v>1</v>
+      </c>
+      <c r="P234" s="10">
+        <v>1.1</v>
+      </c>
+      <c r="Q234" s="11">
+        <v>0.086</v>
+      </c>
+      <c r="R234" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E235" s="3">
+        <v>122.43</v>
+      </c>
+      <c r="F235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="G235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="H235" s="3">
+        <v>121.56</v>
+      </c>
+      <c r="I235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="J235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="K235" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L235" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M235" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="N234" s="3">
-        <v>156.8</v>
-      </c>
-      <c r="O234" s="2">
-        <v>1</v>
-      </c>
-      <c r="P234" s="10">
-        <v>1.19</v>
-      </c>
-      <c r="Q234" s="11">
-        <v>0.753</v>
-      </c>
-      <c r="R234" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A235" s="12" t="s">
+      <c r="N235" s="3">
+        <v>121.51</v>
+      </c>
+      <c r="O235" s="2">
+        <v>1</v>
+      </c>
+      <c r="P235" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q235" s="11">
+        <v>0.041</v>
+      </c>
+      <c r="R235" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E236" s="3">
+        <v>3306.1</v>
+      </c>
+      <c r="F236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="G236" s="3">
+        <v>3285.9</v>
+      </c>
+      <c r="H236" s="3">
+        <v>3285.2</v>
+      </c>
+      <c r="I236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="J236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L236" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M236" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="N236" s="3">
+        <v>3283.4</v>
+      </c>
+      <c r="O236" s="2">
+        <v>1</v>
+      </c>
+      <c r="P236" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="Q236" s="11">
+        <v>0.055</v>
+      </c>
+      <c r="R236" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A237" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="E237" s="7">
+        <v>507.65</v>
+      </c>
+      <c r="F237" s="7">
+        <v>506.3</v>
+      </c>
+      <c r="G237" s="7">
+        <v>506.85</v>
+      </c>
+      <c r="H237" s="7">
+        <v>506.15</v>
+      </c>
+      <c r="I237" s="7">
+        <v>506.3</v>
+      </c>
+      <c r="J237" s="7">
+        <v>506</v>
+      </c>
+      <c r="K237" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L237" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M237" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="N237" s="7">
+        <v>506</v>
+      </c>
+      <c r="O237" s="6">
+        <v>1</v>
+      </c>
+      <c r="P237" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="Q237" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R237" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E238" s="3">
+        <v>7808</v>
+      </c>
+      <c r="F238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="G238" s="3">
+        <v>7780</v>
+      </c>
+      <c r="H238" s="3">
+        <v>7778.5</v>
+      </c>
+      <c r="I238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="J238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="K238" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L238" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M238" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="N238" s="3">
+        <v>7772.5</v>
+      </c>
+      <c r="O238" s="2">
+        <v>1</v>
+      </c>
+      <c r="P238" s="10">
+        <v>6</v>
+      </c>
+      <c r="Q238" s="11">
+        <v>0.077</v>
+      </c>
+      <c r="R238" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A239" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="B235" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C235" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D235" s="12" t="s">
-        <v>550</v>
-      </c>
-      <c r="E235" s="13">
-        <v>14599</v>
-      </c>
-      <c r="F235" s="13">
-        <v>14500</v>
-      </c>
-      <c r="G235" s="13">
-        <v>14598</v>
-      </c>
-      <c r="H235" s="13">
-        <v>14796</v>
-      </c>
-      <c r="I235" s="13">
-        <v>14500</v>
-      </c>
-      <c r="J235" s="13">
-        <v>15092</v>
-      </c>
-      <c r="K235" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L235" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M235" s="12"/>
-      <c r="N235" s="12"/>
-      <c r="O235" s="12"/>
-      <c r="P235" s="12"/>
-      <c r="Q235" s="12"/>
-      <c r="R235" s="12" t="s">
+      <c r="B239" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="E239" s="7">
+        <v>1457.4</v>
+      </c>
+      <c r="F239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="G239" s="7">
+        <v>1450.7</v>
+      </c>
+      <c r="H239" s="7">
+        <v>1450.2</v>
+      </c>
+      <c r="I239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="J239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="K239" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L239" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M239" s="6" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A236" s="12" t="s">
+      <c r="N239" s="7">
+        <v>1450</v>
+      </c>
+      <c r="O239" s="6">
+        <v>1</v>
+      </c>
+      <c r="P239" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="Q239" s="9">
+        <v>0.014</v>
+      </c>
+      <c r="R239" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B236" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C236" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D236" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="E236" s="13">
-        <v>452.4</v>
-      </c>
-      <c r="F236" s="13">
-        <v>440</v>
-      </c>
-      <c r="G236" s="13">
-        <v>451.05</v>
-      </c>
-      <c r="H236" s="13">
-        <v>451.05</v>
-      </c>
-      <c r="I236" s="13">
-        <v>440</v>
-      </c>
-      <c r="J236" s="13">
-        <v>462.1</v>
-      </c>
-      <c r="K236" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L236" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M236" s="12"/>
-      <c r="N236" s="12"/>
-      <c r="O236" s="12"/>
-      <c r="P236" s="12"/>
-      <c r="Q236" s="12"/>
-      <c r="R236" s="12" t="s">
+      <c r="B240" s="2" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A237" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="B237" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="C237" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D237" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="E237" s="13">
-        <v>2352.3</v>
-      </c>
-      <c r="F237" s="13">
-        <v>2310</v>
-      </c>
-      <c r="G237" s="13">
-        <v>2348</v>
-      </c>
-      <c r="H237" s="13">
-        <v>2349.9</v>
-      </c>
-      <c r="I237" s="13">
-        <v>2310</v>
-      </c>
-      <c r="J237" s="13">
-        <v>2389.8</v>
-      </c>
-      <c r="K237" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L237" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M237" s="12"/>
-      <c r="N237" s="12"/>
-      <c r="O237" s="12"/>
-      <c r="P237" s="12"/>
-      <c r="Q237" s="12"/>
-      <c r="R237" s="12" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A238" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="C238" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D238" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="E238" s="7">
-        <v>2318</v>
-      </c>
-      <c r="F238" s="7">
-        <v>2280.4</v>
-      </c>
-      <c r="G238" s="7">
-        <v>2313.1</v>
-      </c>
-      <c r="H238" s="7">
-        <v>2313.1</v>
-      </c>
-      <c r="I238" s="7">
-        <v>2280.4</v>
-      </c>
-      <c r="J238" s="7">
-        <v>2345.8</v>
-      </c>
-      <c r="K238" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L238" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M238" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="N238" s="7">
-        <v>2345.8</v>
-      </c>
-      <c r="O238" s="6">
-        <v>1</v>
-      </c>
-      <c r="P238" s="8">
-        <v>32.7</v>
-      </c>
-      <c r="Q238" s="9">
-        <v>1.414</v>
-      </c>
-      <c r="R238" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A239" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="B239" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="C239" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D239" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="E239" s="13">
-        <v>184.98</v>
-      </c>
-      <c r="F239" s="13">
-        <v>182.15</v>
-      </c>
-      <c r="G239" s="13">
-        <v>184.62</v>
-      </c>
-      <c r="H239" s="13">
-        <v>184.54</v>
-      </c>
-      <c r="I239" s="13">
-        <v>182.15</v>
-      </c>
-      <c r="J239" s="13">
-        <v>186.93</v>
-      </c>
-      <c r="K239" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L239" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M239" s="12"/>
-      <c r="N239" s="12"/>
-      <c r="O239" s="12"/>
-      <c r="P239" s="12"/>
-      <c r="Q239" s="12"/>
-      <c r="R239" s="12" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A240" s="12" t="s">
-        <v>573</v>
-      </c>
-      <c r="B240" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C240" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D240" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="E240" s="13">
-        <v>1392.8</v>
-      </c>
-      <c r="F240" s="13">
-        <v>1378.1</v>
-      </c>
-      <c r="G240" s="13">
-        <v>1389.7</v>
-      </c>
-      <c r="H240" s="13">
-        <v>1389.5</v>
-      </c>
-      <c r="I240" s="13">
-        <v>1378.1</v>
-      </c>
-      <c r="J240" s="13">
-        <v>1400.9</v>
-      </c>
-      <c r="K240" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L240" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M240" s="12"/>
-      <c r="N240" s="12"/>
-      <c r="O240" s="12"/>
-      <c r="P240" s="12"/>
-      <c r="Q240" s="12"/>
-      <c r="R240" s="12" t="s">
-        <v>572</v>
+      <c r="C240" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E240" s="3">
+        <v>96.29</v>
+      </c>
+      <c r="F240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="G240" s="3">
+        <v>95.77</v>
+      </c>
+      <c r="H240" s="3">
+        <v>95.77</v>
+      </c>
+      <c r="I240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="J240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="K240" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L240" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M240" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="N240" s="3">
+        <v>95.65</v>
+      </c>
+      <c r="O240" s="2">
+        <v>1</v>
+      </c>
+      <c r="P240" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="Q240" s="11">
+        <v>0.125</v>
+      </c>
+      <c r="R240" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>370</v>
+        <v>143</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="E241" s="3">
-        <v>598.25</v>
+        <v>963.5</v>
       </c>
       <c r="F241" s="3">
-        <v>593.3</v>
+        <v>957</v>
       </c>
       <c r="G241" s="3">
-        <v>593.65</v>
+        <v>957.4</v>
       </c>
       <c r="H241" s="3">
-        <v>593.8</v>
+        <v>957.4</v>
       </c>
       <c r="I241" s="3">
-        <v>593.3</v>
+        <v>957</v>
       </c>
       <c r="J241" s="3">
-        <v>593.3</v>
+        <v>957</v>
       </c>
       <c r="K241" s="2" t="s">
         <v>22</v>
@@ -15661,125 +15858,1997 @@
         <v>23</v>
       </c>
       <c r="M241" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N241" s="3">
+        <v>957</v>
+      </c>
+      <c r="O241" s="2">
+        <v>1</v>
+      </c>
+      <c r="P241" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="Q241" s="11">
+        <v>0.042</v>
+      </c>
+      <c r="R241" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E242" s="3">
+        <v>2091.2</v>
+      </c>
+      <c r="F242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="G242" s="3">
+        <v>2078.4</v>
+      </c>
+      <c r="H242" s="3">
+        <v>2077.5</v>
+      </c>
+      <c r="I242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="J242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="K242" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L242" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M242" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N242" s="3">
+        <v>2075.2</v>
+      </c>
+      <c r="O242" s="2">
+        <v>1</v>
+      </c>
+      <c r="P242" s="10">
+        <v>2.3</v>
+      </c>
+      <c r="Q242" s="11">
+        <v>0.111</v>
+      </c>
+      <c r="R242" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E243" s="3">
+        <v>9730</v>
+      </c>
+      <c r="F243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="G243" s="3">
+        <v>9668</v>
+      </c>
+      <c r="H243" s="3">
+        <v>9668</v>
+      </c>
+      <c r="I243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="J243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="K243" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L243" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M243" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N243" s="3">
+        <v>9663</v>
+      </c>
+      <c r="O243" s="2">
+        <v>1</v>
+      </c>
+      <c r="P243" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q243" s="11">
+        <v>0.052</v>
+      </c>
+      <c r="R243" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E244" s="3">
+        <v>373.95</v>
+      </c>
+      <c r="F244" s="3">
+        <v>372</v>
+      </c>
+      <c r="G244" s="3">
+        <v>372.2</v>
+      </c>
+      <c r="H244" s="3">
+        <v>372.25</v>
+      </c>
+      <c r="I244" s="3">
+        <v>372</v>
+      </c>
+      <c r="J244" s="3">
+        <v>372</v>
+      </c>
+      <c r="K244" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L244" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M244" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="N244" s="3">
+        <v>372</v>
+      </c>
+      <c r="O244" s="2">
+        <v>1</v>
+      </c>
+      <c r="P244" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="Q244" s="11">
+        <v>0.067</v>
+      </c>
+      <c r="R244" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E245" s="3">
+        <v>526.05</v>
+      </c>
+      <c r="F245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="G245" s="3">
+        <v>523.9</v>
+      </c>
+      <c r="H245" s="3">
+        <v>523.9</v>
+      </c>
+      <c r="I245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="J245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="K245" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L245" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M245" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="N245" s="3">
+        <v>523.85</v>
+      </c>
+      <c r="O245" s="2">
+        <v>1</v>
+      </c>
+      <c r="P245" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q245" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="R245" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E246" s="3">
+        <v>609.05</v>
+      </c>
+      <c r="F246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="G246" s="3">
+        <v>606.8</v>
+      </c>
+      <c r="H246" s="3">
+        <v>606.8</v>
+      </c>
+      <c r="I246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="J246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="K246" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L246" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M246" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="N246" s="3">
+        <v>606.75</v>
+      </c>
+      <c r="O246" s="2">
+        <v>1</v>
+      </c>
+      <c r="P246" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q246" s="11">
+        <v>0.008</v>
+      </c>
+      <c r="R246" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E247" s="3">
+        <v>401.2</v>
+      </c>
+      <c r="F247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="G247" s="3">
+        <v>399.2</v>
+      </c>
+      <c r="H247" s="3">
+        <v>399.25</v>
+      </c>
+      <c r="I247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="J247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="K247" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L247" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M247" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="N247" s="3">
+        <v>398.7</v>
+      </c>
+      <c r="O247" s="2">
+        <v>1</v>
+      </c>
+      <c r="P247" s="10">
+        <v>0.55</v>
+      </c>
+      <c r="Q247" s="11">
+        <v>0.138</v>
+      </c>
+      <c r="R247" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="N241" s="3">
-        <v>593.3</v>
-      </c>
-      <c r="O241" s="2">
-        <v>1</v>
-      </c>
-      <c r="P241" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="Q241" s="11">
-        <v>0.084</v>
-      </c>
-      <c r="R241" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A242" s="12" t="s">
+      <c r="E248" s="3">
+        <v>1242.6</v>
+      </c>
+      <c r="F248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="G248" s="3">
+        <v>1235.6</v>
+      </c>
+      <c r="H248" s="3">
+        <v>1236.3</v>
+      </c>
+      <c r="I248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="J248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="K248" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L248" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M248" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B242" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C242" s="12" t="s">
+      <c r="N248" s="3">
+        <v>1235</v>
+      </c>
+      <c r="O248" s="2">
+        <v>1</v>
+      </c>
+      <c r="P248" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="Q248" s="11">
+        <v>0.105</v>
+      </c>
+      <c r="R248" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E249" s="3">
+        <v>1202.9</v>
+      </c>
+      <c r="F249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="G249" s="3">
+        <v>1188.3</v>
+      </c>
+      <c r="H249" s="3">
+        <v>1188.4</v>
+      </c>
+      <c r="I249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="J249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="K249" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L249" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M249" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N249" s="3">
+        <v>1183.4</v>
+      </c>
+      <c r="O249" s="2">
+        <v>1</v>
+      </c>
+      <c r="P249" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q249" s="11">
+        <v>0.421</v>
+      </c>
+      <c r="R249" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E250" s="3">
+        <v>1870</v>
+      </c>
+      <c r="F250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="G250" s="3">
+        <v>1841.4</v>
+      </c>
+      <c r="H250" s="3">
+        <v>1840.4</v>
+      </c>
+      <c r="I250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="J250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="K250" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L250" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M250" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N250" s="3">
+        <v>1833</v>
+      </c>
+      <c r="O250" s="2">
+        <v>1</v>
+      </c>
+      <c r="P250" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="Q250" s="11">
+        <v>0.402</v>
+      </c>
+      <c r="R250" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E251" s="3">
+        <v>2203.6</v>
+      </c>
+      <c r="F251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="G251" s="3">
+        <v>2192.8</v>
+      </c>
+      <c r="H251" s="3">
+        <v>2192.6</v>
+      </c>
+      <c r="I251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="J251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="K251" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L251" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M251" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N251" s="3">
+        <v>2185.4</v>
+      </c>
+      <c r="O251" s="2">
+        <v>1</v>
+      </c>
+      <c r="P251" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="Q251" s="11">
+        <v>0.328</v>
+      </c>
+      <c r="R251" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E252" s="3">
+        <v>4728.8</v>
+      </c>
+      <c r="F252" s="3">
+        <v>4704.9</v>
+      </c>
+      <c r="G252" s="3">
+        <v>4710.4</v>
+      </c>
+      <c r="H252" s="3">
+        <v>4703.3</v>
+      </c>
+      <c r="I252" s="3">
+        <v>4704.9</v>
+      </c>
+      <c r="J252" s="3">
+        <v>4701.7</v>
+      </c>
+      <c r="K252" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L252" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M252" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="N252" s="3">
+        <v>4704.9</v>
+      </c>
+      <c r="O252" s="2">
+        <v>1</v>
+      </c>
+      <c r="P252" s="4">
+        <v>-1.6</v>
+      </c>
+      <c r="Q252" s="5">
+        <v>-0.034</v>
+      </c>
+      <c r="R252" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E253" s="3">
+        <v>70.31</v>
+      </c>
+      <c r="F253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="G253" s="3">
+        <v>70.1</v>
+      </c>
+      <c r="H253" s="3">
+        <v>70.08</v>
+      </c>
+      <c r="I253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="J253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="K253" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L253" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M253" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="N253" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="O253" s="2">
+        <v>1</v>
+      </c>
+      <c r="P253" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="Q253" s="11">
+        <v>0.086</v>
+      </c>
+      <c r="R253" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A254" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="E254" s="7">
+        <v>961.35</v>
+      </c>
+      <c r="F254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="G254" s="7">
+        <v>949.25</v>
+      </c>
+      <c r="H254" s="7">
+        <v>949.05</v>
+      </c>
+      <c r="I254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="J254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="K254" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L254" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M254" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="N254" s="7">
+        <v>947.1</v>
+      </c>
+      <c r="O254" s="6">
+        <v>1</v>
+      </c>
+      <c r="P254" s="8">
+        <v>1.95</v>
+      </c>
+      <c r="Q254" s="9">
+        <v>0.205</v>
+      </c>
+      <c r="R254" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E255" s="3">
+        <v>165.26</v>
+      </c>
+      <c r="F255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="G255" s="3">
+        <v>162.38</v>
+      </c>
+      <c r="H255" s="3">
+        <v>162.4</v>
+      </c>
+      <c r="I255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="J255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="K255" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L255" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M255" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N255" s="3">
+        <v>162.03</v>
+      </c>
+      <c r="O255" s="2">
+        <v>1</v>
+      </c>
+      <c r="P255" s="10">
+        <v>0.37</v>
+      </c>
+      <c r="Q255" s="11">
+        <v>0.228</v>
+      </c>
+      <c r="R255" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E256" s="3">
+        <v>1253.9</v>
+      </c>
+      <c r="F256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="G256" s="3">
+        <v>1217</v>
+      </c>
+      <c r="H256" s="3">
+        <v>1218</v>
+      </c>
+      <c r="I256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="J256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="K256" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L256" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M256" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N256" s="3">
+        <v>1215.3</v>
+      </c>
+      <c r="O256" s="2">
+        <v>1</v>
+      </c>
+      <c r="P256" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="Q256" s="11">
+        <v>0.222</v>
+      </c>
+      <c r="R256" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E257" s="3">
+        <v>396.3</v>
+      </c>
+      <c r="F257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="G257" s="3">
+        <v>392.55</v>
+      </c>
+      <c r="H257" s="3">
+        <v>392.45</v>
+      </c>
+      <c r="I257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="J257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="K257" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L257" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M257" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N257" s="3">
+        <v>390.05</v>
+      </c>
+      <c r="O257" s="2">
+        <v>1</v>
+      </c>
+      <c r="P257" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="Q257" s="11">
+        <v>0.612</v>
+      </c>
+      <c r="R257" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E258" s="3">
+        <v>1649.4</v>
+      </c>
+      <c r="F258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="G258" s="3">
+        <v>1627.1</v>
+      </c>
+      <c r="H258" s="3">
+        <v>1628</v>
+      </c>
+      <c r="I258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="J258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L258" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M258" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N258" s="3">
+        <v>1624.3</v>
+      </c>
+      <c r="O258" s="2">
+        <v>1</v>
+      </c>
+      <c r="P258" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="Q258" s="11">
+        <v>0.227</v>
+      </c>
+      <c r="R258" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E259" s="3">
+        <v>258.95</v>
+      </c>
+      <c r="F259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="G259" s="3">
+        <v>253.5</v>
+      </c>
+      <c r="H259" s="3">
+        <v>253.45</v>
+      </c>
+      <c r="I259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="J259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="K259" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L259" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M259" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N259" s="3">
+        <v>252.5</v>
+      </c>
+      <c r="O259" s="2">
+        <v>1</v>
+      </c>
+      <c r="P259" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="Q259" s="11">
+        <v>0.375</v>
+      </c>
+      <c r="R259" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E260" s="3">
+        <v>1340.9</v>
+      </c>
+      <c r="F260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="G260" s="3">
+        <v>1329</v>
+      </c>
+      <c r="H260" s="3">
+        <v>1328.9</v>
+      </c>
+      <c r="I260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="J260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="K260" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L260" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M260" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="N260" s="3">
+        <v>1328.8</v>
+      </c>
+      <c r="O260" s="2">
+        <v>1</v>
+      </c>
+      <c r="P260" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="Q260" s="11">
+        <v>0.008</v>
+      </c>
+      <c r="R260" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D242" s="12" t="s">
-        <v>575</v>
-      </c>
-      <c r="E242" s="13">
-        <v>379.8</v>
-      </c>
-      <c r="F242" s="13">
-        <v>376.2</v>
-      </c>
-      <c r="G242" s="13">
-        <v>379.6</v>
-      </c>
-      <c r="H242" s="13">
-        <v>379.7</v>
-      </c>
-      <c r="I242" s="13">
-        <v>376.2</v>
-      </c>
-      <c r="J242" s="13">
-        <v>383.2</v>
-      </c>
-      <c r="K242" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L242" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M242" s="12"/>
-      <c r="N242" s="12"/>
-      <c r="O242" s="12"/>
-      <c r="P242" s="12"/>
-      <c r="Q242" s="12"/>
-      <c r="R242" s="12" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A243" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="B243" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="C243" s="12" t="s">
+      <c r="D261" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E261" s="3">
+        <v>980.15</v>
+      </c>
+      <c r="F261" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="G261" s="3">
+        <v>977.9</v>
+      </c>
+      <c r="H261" s="3">
+        <v>977.9</v>
+      </c>
+      <c r="I261" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="J261" s="3">
+        <v>990.1</v>
+      </c>
+      <c r="K261" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L261" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M261" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="N261" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="O261" s="2">
+        <v>22</v>
+      </c>
+      <c r="P261" s="4">
+        <v>-12.2</v>
+      </c>
+      <c r="Q261" s="5">
+        <v>-1.248</v>
+      </c>
+      <c r="R261" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E262" s="3">
+        <v>1235</v>
+      </c>
+      <c r="F262" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="G262" s="3">
+        <v>1233.1</v>
+      </c>
+      <c r="H262" s="3">
+        <v>1233</v>
+      </c>
+      <c r="I262" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="J262" s="3">
+        <v>1245.7</v>
+      </c>
+      <c r="K262" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L262" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M262" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="N262" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="O262" s="2">
+        <v>1</v>
+      </c>
+      <c r="P262" s="4">
+        <v>-12.7</v>
+      </c>
+      <c r="Q262" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="R262" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A263" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E263" s="7">
+        <v>1327.9</v>
+      </c>
+      <c r="F263" s="7">
+        <v>1276.1</v>
+      </c>
+      <c r="G263" s="7">
+        <v>1324.6</v>
+      </c>
+      <c r="H263" s="7">
+        <v>1323.7</v>
+      </c>
+      <c r="I263" s="7">
+        <v>1276.1</v>
+      </c>
+      <c r="J263" s="7">
+        <v>1371.3</v>
+      </c>
+      <c r="K263" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L263" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M263" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="N263" s="7">
+        <v>1371.3</v>
+      </c>
+      <c r="O263" s="6">
+        <v>2</v>
+      </c>
+      <c r="P263" s="8">
+        <v>47.6</v>
+      </c>
+      <c r="Q263" s="9">
+        <v>3.596</v>
+      </c>
+      <c r="R263" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A264" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B264" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D264" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E264" s="13">
+        <v>469.7</v>
+      </c>
+      <c r="F264" s="13">
+        <v>460.35</v>
+      </c>
+      <c r="G264" s="13">
+        <v>468.65</v>
+      </c>
+      <c r="H264" s="13">
+        <v>468.6</v>
+      </c>
+      <c r="I264" s="13">
+        <v>460.35</v>
+      </c>
+      <c r="J264" s="13">
+        <v>476.85</v>
+      </c>
+      <c r="K264" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L264" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M264" s="12"/>
+      <c r="N264" s="12"/>
+      <c r="O264" s="12"/>
+      <c r="P264" s="12"/>
+      <c r="Q264" s="12"/>
+      <c r="R264" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A265" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="C265" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D265" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E265" s="13">
+        <v>2135.5</v>
+      </c>
+      <c r="F265" s="13">
+        <v>2094.4</v>
+      </c>
+      <c r="G265" s="13">
+        <v>2131.5</v>
+      </c>
+      <c r="H265" s="13">
+        <v>2131</v>
+      </c>
+      <c r="I265" s="13">
+        <v>2094.4</v>
+      </c>
+      <c r="J265" s="13">
+        <v>2167.6</v>
+      </c>
+      <c r="K265" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L265" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M265" s="12"/>
+      <c r="N265" s="12"/>
+      <c r="O265" s="12"/>
+      <c r="P265" s="12"/>
+      <c r="Q265" s="12"/>
+      <c r="R265" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A266" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E266" s="7">
+        <v>2476</v>
+      </c>
+      <c r="F266" s="7">
+        <v>2370.1</v>
+      </c>
+      <c r="G266" s="7">
+        <v>2457.7</v>
+      </c>
+      <c r="H266" s="7">
+        <v>2457.9</v>
+      </c>
+      <c r="I266" s="7">
+        <v>2370.1</v>
+      </c>
+      <c r="J266" s="7">
+        <v>2545.7</v>
+      </c>
+      <c r="K266" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L266" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M266" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="N266" s="7">
+        <v>2545.7</v>
+      </c>
+      <c r="O266" s="6">
+        <v>1</v>
+      </c>
+      <c r="P266" s="8">
+        <v>87.8</v>
+      </c>
+      <c r="Q266" s="9">
+        <v>3.572</v>
+      </c>
+      <c r="R266" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A267" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C267" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D267" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E267" s="13">
+        <v>8628</v>
+      </c>
+      <c r="F267" s="13">
+        <v>8480</v>
+      </c>
+      <c r="G267" s="13">
+        <v>8621</v>
+      </c>
+      <c r="H267" s="13">
+        <v>8621</v>
+      </c>
+      <c r="I267" s="13">
+        <v>8480</v>
+      </c>
+      <c r="J267" s="13">
+        <v>8762</v>
+      </c>
+      <c r="K267" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L267" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M267" s="12"/>
+      <c r="N267" s="12"/>
+      <c r="O267" s="12"/>
+      <c r="P267" s="12"/>
+      <c r="Q267" s="12"/>
+      <c r="R267" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A268" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="B268" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D268" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E268" s="13">
+        <v>1415.7</v>
+      </c>
+      <c r="F268" s="13">
+        <v>1390.3</v>
+      </c>
+      <c r="G268" s="13">
+        <v>1414.6</v>
+      </c>
+      <c r="H268" s="13">
+        <v>1414.7</v>
+      </c>
+      <c r="I268" s="13">
+        <v>1390.3</v>
+      </c>
+      <c r="J268" s="13">
+        <v>1439.1</v>
+      </c>
+      <c r="K268" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L268" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M268" s="12"/>
+      <c r="N268" s="12"/>
+      <c r="O268" s="12"/>
+      <c r="P268" s="12"/>
+      <c r="Q268" s="12"/>
+      <c r="R268" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A269" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D269" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="E269" s="13">
+        <v>382.25</v>
+      </c>
+      <c r="F269" s="13">
+        <v>373.1</v>
+      </c>
+      <c r="G269" s="13">
+        <v>382.1</v>
+      </c>
+      <c r="H269" s="13">
+        <v>382.25</v>
+      </c>
+      <c r="I269" s="13">
+        <v>373.1</v>
+      </c>
+      <c r="J269" s="13">
+        <v>391.4</v>
+      </c>
+      <c r="K269" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L269" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M269" s="12"/>
+      <c r="N269" s="12"/>
+      <c r="O269" s="12"/>
+      <c r="P269" s="12"/>
+      <c r="Q269" s="12"/>
+      <c r="R269" s="12" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A270" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C270" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D243" s="12" t="s">
-        <v>580</v>
-      </c>
-      <c r="E243" s="13">
-        <v>6825</v>
-      </c>
-      <c r="F243" s="13">
-        <v>6764</v>
-      </c>
-      <c r="G243" s="13">
-        <v>6768.5</v>
-      </c>
-      <c r="H243" s="13">
-        <v>6769.5</v>
-      </c>
-      <c r="I243" s="13">
-        <v>6764</v>
-      </c>
-      <c r="J243" s="13">
-        <v>6764</v>
-      </c>
-      <c r="K243" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L243" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M243" s="12"/>
-      <c r="N243" s="12"/>
-      <c r="O243" s="12"/>
-      <c r="P243" s="12"/>
-      <c r="Q243" s="12"/>
-      <c r="R243" s="12" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A245" s="14" t="s">
-        <v>582</v>
-      </c>
-      <c r="P245" s="15">
-        <v>435.24</v>
-      </c>
-      <c r="R245" s="14" t="s">
-        <v>583</v>
+      <c r="D270" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E270" s="7">
+        <v>4344.9</v>
+      </c>
+      <c r="F270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="G270" s="7">
+        <v>4339.9</v>
+      </c>
+      <c r="H270" s="7">
+        <v>4339.9</v>
+      </c>
+      <c r="I270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="J270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="K270" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L270" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M270" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="N270" s="7">
+        <v>4335</v>
+      </c>
+      <c r="O270" s="6">
+        <v>1</v>
+      </c>
+      <c r="P270" s="8">
+        <v>4.9</v>
+      </c>
+      <c r="Q270" s="9">
+        <v>0.113</v>
+      </c>
+      <c r="R270" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A271" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D271" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="E271" s="13">
+        <v>3903.9</v>
+      </c>
+      <c r="F271" s="13">
+        <v>3861.2</v>
+      </c>
+      <c r="G271" s="13">
+        <v>3890</v>
+      </c>
+      <c r="H271" s="13">
+        <v>3890.8</v>
+      </c>
+      <c r="I271" s="13">
+        <v>3861.2</v>
+      </c>
+      <c r="J271" s="13">
+        <v>3920.4</v>
+      </c>
+      <c r="K271" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L271" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M271" s="12"/>
+      <c r="N271" s="12"/>
+      <c r="O271" s="12"/>
+      <c r="P271" s="12"/>
+      <c r="Q271" s="12"/>
+      <c r="R271" s="12" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A272" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="E272" s="7">
+        <v>1885.1</v>
+      </c>
+      <c r="F272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="G272" s="7">
+        <v>1879.1</v>
+      </c>
+      <c r="H272" s="7">
+        <v>1879.1</v>
+      </c>
+      <c r="I272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="J272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="K272" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L272" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M272" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="N272" s="7">
+        <v>1879</v>
+      </c>
+      <c r="O272" s="6">
+        <v>1</v>
+      </c>
+      <c r="P272" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="Q272" s="9">
+        <v>0.005</v>
+      </c>
+      <c r="R272" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E273" s="3">
+        <v>6013</v>
+      </c>
+      <c r="F273" s="3">
+        <v>5990.5</v>
+      </c>
+      <c r="G273" s="3">
+        <v>6002.5</v>
+      </c>
+      <c r="H273" s="3">
+        <v>6005.5</v>
+      </c>
+      <c r="I273" s="3">
+        <v>5990.5</v>
+      </c>
+      <c r="J273" s="3">
+        <v>6020.5</v>
+      </c>
+      <c r="K273" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L273" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M273" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="N273" s="3">
+        <v>5990.5</v>
+      </c>
+      <c r="O273" s="2">
+        <v>1</v>
+      </c>
+      <c r="P273" s="4">
+        <v>-15</v>
+      </c>
+      <c r="Q273" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="R273" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A274" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="C274" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D274" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="E274" s="13">
+        <v>2126.1</v>
+      </c>
+      <c r="F274" s="13">
+        <v>2118.3</v>
+      </c>
+      <c r="G274" s="13">
+        <v>2126.1</v>
+      </c>
+      <c r="H274" s="13">
+        <v>2125.6</v>
+      </c>
+      <c r="I274" s="13">
+        <v>2118.3</v>
+      </c>
+      <c r="J274" s="13">
+        <v>2132.9</v>
+      </c>
+      <c r="K274" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L274" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M274" s="12"/>
+      <c r="N274" s="12"/>
+      <c r="O274" s="12"/>
+      <c r="P274" s="12"/>
+      <c r="Q274" s="12"/>
+      <c r="R274" s="12" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A275" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="B275" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C275" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D275" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="E275" s="13">
+        <v>117.6</v>
+      </c>
+      <c r="F275" s="13">
+        <v>116.64</v>
+      </c>
+      <c r="G275" s="13">
+        <v>117.54</v>
+      </c>
+      <c r="H275" s="13">
+        <v>117.54</v>
+      </c>
+      <c r="I275" s="13">
+        <v>116.64</v>
+      </c>
+      <c r="J275" s="13">
+        <v>118.44</v>
+      </c>
+      <c r="K275" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L275" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M275" s="12"/>
+      <c r="N275" s="12"/>
+      <c r="O275" s="12"/>
+      <c r="P275" s="12"/>
+      <c r="Q275" s="12"/>
+      <c r="R275" s="12" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A276" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D276" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="E276" s="13">
+        <v>2190.3</v>
+      </c>
+      <c r="F276" s="13">
+        <v>2180.9</v>
+      </c>
+      <c r="G276" s="13">
+        <v>2182</v>
+      </c>
+      <c r="H276" s="12"/>
+      <c r="I276" s="13">
+        <v>2180.9</v>
+      </c>
+      <c r="J276" s="12"/>
+      <c r="K276" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L276" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M276" s="12"/>
+      <c r="N276" s="12"/>
+      <c r="O276" s="12"/>
+      <c r="P276" s="12"/>
+      <c r="Q276" s="12"/>
+      <c r="R276" s="12" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A277" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C277" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D277" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="E277" s="13">
+        <v>790.15</v>
+      </c>
+      <c r="F277" s="13">
+        <v>784.05</v>
+      </c>
+      <c r="G277" s="13">
+        <v>789.95</v>
+      </c>
+      <c r="H277" s="12"/>
+      <c r="I277" s="13">
+        <v>784.05</v>
+      </c>
+      <c r="J277" s="12"/>
+      <c r="K277" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L277" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M277" s="12"/>
+      <c r="N277" s="12"/>
+      <c r="O277" s="12"/>
+      <c r="P277" s="12"/>
+      <c r="Q277" s="12"/>
+      <c r="R277" s="12" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E278" s="3">
+        <v>422.45</v>
+      </c>
+      <c r="F278" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="G278" s="3">
+        <v>421.75</v>
+      </c>
+      <c r="H278" s="3">
+        <v>422</v>
+      </c>
+      <c r="I278" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="J278" s="3">
+        <v>431.8</v>
+      </c>
+      <c r="K278" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L278" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M278" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="N278" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="O278" s="2">
+        <v>16</v>
+      </c>
+      <c r="P278" s="4">
+        <v>-9.8</v>
+      </c>
+      <c r="Q278" s="5">
+        <v>-2.322</v>
+      </c>
+      <c r="R278" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A280" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="P280" s="15">
+        <v>529.16</v>
+      </c>
+      <c r="R280" s="14" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="725">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1639,7 +1639,7 @@
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 124 candle(s) — neither SL nor Target hit yet</t>
+    <t>Checked 149 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
     <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
@@ -1918,7 +1918,7 @@
     <t>2026-03-06 15:15</t>
   </si>
   <si>
-    <t>Checked 24 candle(s) — neither SL nor Target hit yet</t>
+    <t>2026-03-10 09:15</t>
   </si>
   <si>
     <t>NSE:MARICO-EQ_BULL_1772772300_1772790300</t>
@@ -1936,79 +1936,256 @@
     <t>NSE:KALYANKJIL-EQ_BEAR_1772775000_1773027900</t>
   </si>
   <si>
+    <t>NSE:NUVAMA-EQ_BEAR_1772784900_1773027900</t>
+  </si>
+  <si>
+    <t>NSE:NUVAMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 14:15</t>
+  </si>
+  <si>
+    <t>NSE:TATATECH-EQ_BEAR_1772788500_1773027900</t>
+  </si>
+  <si>
+    <t>NSE:TATATECH-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1772771400_1773029700</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1773028800_1773037800</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:00</t>
+  </si>
+  <si>
+    <t>Checked 37 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BEAR_1772788500_1773038700</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:45</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BEAR_1773027900_1773041400</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:00</t>
+  </si>
+  <si>
+    <t>NSE:GRASIM-EQ_BEAR_1772789400_1773049500</t>
+  </si>
+  <si>
+    <t>NSE:GRASIM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:30</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BEAR_1773027900_1773049500</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1773036000_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:15</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1773044100_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:00</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1773045900_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:15</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BEAR_1773029700_1773114300</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:00</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1773046800_1773114300</t>
+  </si>
+  <si>
     <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
-    <t>NSE:NUVAMA-EQ_BEAR_1772784900_1773027900</t>
-  </si>
-  <si>
-    <t>NSE:NUVAMA-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-09 14:15</t>
-  </si>
-  <si>
-    <t>NSE:TATATECH-EQ_BEAR_1772788500_1773027900</t>
-  </si>
-  <si>
-    <t>NSE:TATATECH-EQ</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ_BEAR_1772771400_1773029700</t>
-  </si>
-  <si>
-    <t>2026-03-09 09:45</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ_BEAR_1773028800_1773037800</t>
-  </si>
-  <si>
-    <t>2026-03-09 12:00</t>
-  </si>
-  <si>
-    <t>Checked 12 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:HAVELLS-EQ_BEAR_1772788500_1773038700</t>
-  </si>
-  <si>
-    <t>2026-03-09 12:15</t>
-  </si>
-  <si>
-    <t>2026-03-09 12:45</t>
-  </si>
-  <si>
-    <t>NSE:BANDHANBNK-EQ_BEAR_1773027900_1773041400</t>
-  </si>
-  <si>
-    <t>NSE:BANDHANBNK-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-09 13:00</t>
-  </si>
-  <si>
-    <t>Checked 8 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:GRASIM-EQ_BEAR_1772789400_1773049500</t>
-  </si>
-  <si>
-    <t>NSE:GRASIM-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-09 15:15</t>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1773028800_1773115200</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:15</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1773029700_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BEAR_1773027900_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:45</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:30</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1773117000_1773132300</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:45</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1773027900_1773132300</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BULL_1773117000_1773133200</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:30</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773134100</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BULL_1773126000_1773134100</t>
+  </si>
+  <si>
+    <t>Checked 1 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1773121500_1773134100</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1773123300_1773135000</t>
+  </si>
+  <si>
+    <t>No candles after entry yet — trade open</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ_BULL_1773121500_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BULL_1773116100_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1773126000_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773135900</t>
   </si>
   <si>
     <t>Entry candle not yet available — trade not entered</t>
   </si>
   <si>
-    <t>NSE:MARICO-EQ_BEAR_1773027900_1773049500</t>
-  </si>
-  <si>
-    <t>SUMMARY — 140W / 138L / 8 OPEN  |  Win Rate: 50.4%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 278 of 286</t>
+    <t>NSE:CGPOWER-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CGPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ_BULL_1773120600_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BULL_1773131400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ_BULL_1773126900_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ_BULL_1773130500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BULL_1773133200_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ_BULL_1773132300_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>SUMMARY — 147W / 150L / 24 OPEN  |  Win Rate: 49.5%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 297 of 321</t>
   </si>
 </sst>
 </file>
@@ -2051,7 +2228,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF90EE90"/>
+      <color rgb="FFFF6B6B"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
@@ -2469,7 +2646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R289"/>
+  <dimension ref="A1:R324"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -11186,7 +11363,7 @@
         <v>510.4</v>
       </c>
       <c r="F156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="G156" s="3">
         <v>509.4</v>
@@ -11195,10 +11372,10 @@
         <v>509.4</v>
       </c>
       <c r="I156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="J156" s="3">
-        <v>512.5</v>
+        <v>512.65</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>22</v>
@@ -11210,16 +11387,16 @@
         <v>384</v>
       </c>
       <c r="N156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="O156" s="2">
         <v>1</v>
       </c>
       <c r="P156" s="4">
-        <v>-3.1</v>
+        <v>-3.25</v>
       </c>
       <c r="Q156" s="5">
-        <v>-0.609</v>
+        <v>-0.638</v>
       </c>
       <c r="R156" s="2" t="s">
         <v>25</v>
@@ -17880,49 +18057,59 @@
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A276" s="10" t="s">
+      <c r="A276" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="B276" s="10" t="s">
+      <c r="B276" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C276" s="10" t="s">
+      <c r="C276" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D276" s="10" t="s">
+      <c r="D276" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="E276" s="11">
+      <c r="E276" s="3">
         <v>2190.3</v>
       </c>
-      <c r="F276" s="11">
+      <c r="F276" s="3">
         <v>2180.9</v>
       </c>
-      <c r="G276" s="11">
+      <c r="G276" s="3">
         <v>2182</v>
       </c>
-      <c r="H276" s="11">
+      <c r="H276" s="3">
         <v>2131</v>
       </c>
-      <c r="I276" s="11">
+      <c r="I276" s="3">
         <v>2190.3</v>
       </c>
-      <c r="J276" s="11">
+      <c r="J276" s="3">
         <v>2071.7</v>
       </c>
-      <c r="K276" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L276" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M276" s="10"/>
-      <c r="N276" s="10"/>
-      <c r="O276" s="10"/>
-      <c r="P276" s="10"/>
-      <c r="Q276" s="10"/>
-      <c r="R276" s="10" t="s">
+      <c r="K276" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L276" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M276" s="2" t="s">
         <v>635</v>
+      </c>
+      <c r="N276" s="3">
+        <v>2190.3</v>
+      </c>
+      <c r="O276" s="2">
+        <v>25</v>
+      </c>
+      <c r="P276" s="4">
+        <v>-59.3</v>
+      </c>
+      <c r="Q276" s="5">
+        <v>-2.783</v>
+      </c>
+      <c r="R276" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.25">
@@ -18038,57 +18225,67 @@
       </c>
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A279" s="10" t="s">
+      <c r="A279" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B279" s="10" t="s">
+      <c r="B279" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C279" s="10" t="s">
+      <c r="C279" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D279" s="10" t="s">
+      <c r="D279" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="E279" s="11">
+      <c r="E279" s="3">
         <v>391.9</v>
       </c>
-      <c r="F279" s="11">
+      <c r="F279" s="3">
         <v>382.65</v>
       </c>
-      <c r="G279" s="11">
+      <c r="G279" s="3">
         <v>384.1</v>
       </c>
-      <c r="H279" s="11">
+      <c r="H279" s="3">
         <v>384.15</v>
       </c>
-      <c r="I279" s="11">
+      <c r="I279" s="3">
         <v>391.9</v>
       </c>
-      <c r="J279" s="11">
+      <c r="J279" s="3">
         <v>376.4</v>
       </c>
-      <c r="K279" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L279" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M279" s="10"/>
-      <c r="N279" s="10"/>
-      <c r="O279" s="10"/>
-      <c r="P279" s="10"/>
-      <c r="Q279" s="10"/>
-      <c r="R279" s="10" t="s">
-        <v>641</v>
+      <c r="K279" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L279" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M279" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="N279" s="3">
+        <v>391.9</v>
+      </c>
+      <c r="O279" s="2">
+        <v>24</v>
+      </c>
+      <c r="P279" s="4">
+        <v>-7.75</v>
+      </c>
+      <c r="Q279" s="5">
+        <v>-2.017</v>
+      </c>
+      <c r="R279" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>64</v>
@@ -18121,7 +18318,7 @@
         <v>23</v>
       </c>
       <c r="M280" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="N280" s="3">
         <v>1202</v>
@@ -18140,54 +18337,64 @@
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A281" s="10" t="s">
+      <c r="A281" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B281" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="C281" s="10" t="s">
+      <c r="C281" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D281" s="10" t="s">
+      <c r="D281" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="E281" s="11">
+      <c r="E281" s="3">
         <v>570</v>
       </c>
-      <c r="F281" s="11">
+      <c r="F281" s="3">
         <v>558.8</v>
       </c>
-      <c r="G281" s="11">
+      <c r="G281" s="3">
         <v>561.75</v>
       </c>
-      <c r="H281" s="11">
+      <c r="H281" s="3">
         <v>562</v>
       </c>
-      <c r="I281" s="11">
+      <c r="I281" s="3">
         <v>570</v>
       </c>
-      <c r="J281" s="11">
+      <c r="J281" s="3">
         <v>554</v>
       </c>
-      <c r="K281" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L281" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M281" s="10"/>
-      <c r="N281" s="10"/>
-      <c r="O281" s="10"/>
-      <c r="P281" s="10"/>
-      <c r="Q281" s="10"/>
-      <c r="R281" s="10" t="s">
-        <v>641</v>
+      <c r="K281" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L281" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M281" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="N281" s="3">
+        <v>570</v>
+      </c>
+      <c r="O281" s="2">
+        <v>24</v>
+      </c>
+      <c r="P281" s="4">
+        <v>-8</v>
+      </c>
+      <c r="Q281" s="5">
+        <v>-1.423</v>
+      </c>
+      <c r="R281" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>180</v>
@@ -18196,7 +18403,7 @@
         <v>64</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E282" s="7">
         <v>2136</v>
@@ -18243,7 +18450,7 @@
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B283" s="10" t="s">
         <v>156</v>
@@ -18252,7 +18459,7 @@
         <v>64</v>
       </c>
       <c r="D283" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E283" s="11">
         <v>7673</v>
@@ -18284,12 +18491,12 @@
       <c r="P283" s="10"/>
       <c r="Q283" s="10"/>
       <c r="R283" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>525</v>
@@ -18298,7 +18505,7 @@
         <v>64</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E284" s="3">
         <v>1321.5</v>
@@ -18325,7 +18532,7 @@
         <v>23</v>
       </c>
       <c r="M284" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="N284" s="3">
         <v>1321.5</v>
@@ -18344,144 +18551,1862 @@
       </c>
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A285" s="10" t="s">
+      <c r="A285" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="C285" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="C285" s="10" t="s">
+      <c r="E285" s="3">
+        <v>176</v>
+      </c>
+      <c r="F285" s="3">
+        <v>173.76</v>
+      </c>
+      <c r="G285" s="3">
+        <v>173.9</v>
+      </c>
+      <c r="H285" s="3">
+        <v>173.86</v>
+      </c>
+      <c r="I285" s="3">
+        <v>176</v>
+      </c>
+      <c r="J285" s="3">
+        <v>171.72</v>
+      </c>
+      <c r="K285" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L285" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M285" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="N285" s="3">
+        <v>176</v>
+      </c>
+      <c r="O285" s="2">
+        <v>9</v>
+      </c>
+      <c r="P285" s="4">
+        <v>-2.14</v>
+      </c>
+      <c r="Q285" s="5">
+        <v>-1.231</v>
+      </c>
+      <c r="R285" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A286" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C286" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D285" s="10" t="s">
-        <v>657</v>
-      </c>
-      <c r="E285" s="11">
-        <v>176</v>
-      </c>
-      <c r="F285" s="11">
-        <v>173.76</v>
-      </c>
-      <c r="G285" s="11">
-        <v>173.9</v>
-      </c>
-      <c r="H285" s="11">
-        <v>173.86</v>
-      </c>
-      <c r="I285" s="11">
-        <v>176</v>
-      </c>
-      <c r="J285" s="11">
-        <v>171.72</v>
-      </c>
-      <c r="K285" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L285" s="10" t="s">
+      <c r="D286" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E286" s="3">
+        <v>2682.4</v>
+      </c>
+      <c r="F286" s="3">
+        <v>2669.4</v>
+      </c>
+      <c r="G286" s="3">
+        <v>2669.4</v>
+      </c>
+      <c r="H286" s="3">
+        <v>2701</v>
+      </c>
+      <c r="I286" s="3">
+        <v>2682.4</v>
+      </c>
+      <c r="J286" s="3">
+        <v>2682.4</v>
+      </c>
+      <c r="K286" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L286" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M286" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="N286" s="3">
+        <v>2682.4</v>
+      </c>
+      <c r="O286" s="2">
+        <v>1</v>
+      </c>
+      <c r="P286" s="12">
+        <v>18.6</v>
+      </c>
+      <c r="Q286" s="13">
+        <v>0.689</v>
+      </c>
+      <c r="R286" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A287" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E287" s="3">
+        <v>783.9</v>
+      </c>
+      <c r="F287" s="3">
+        <v>772</v>
+      </c>
+      <c r="G287" s="3">
+        <v>774.7</v>
+      </c>
+      <c r="H287" s="3">
+        <v>779.95</v>
+      </c>
+      <c r="I287" s="3">
+        <v>783.9</v>
+      </c>
+      <c r="J287" s="3">
+        <v>776</v>
+      </c>
+      <c r="K287" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L287" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M287" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="N287" s="3">
+        <v>783.9</v>
+      </c>
+      <c r="O287" s="2">
+        <v>2</v>
+      </c>
+      <c r="P287" s="4">
+        <v>-3.95</v>
+      </c>
+      <c r="Q287" s="5">
+        <v>-0.506</v>
+      </c>
+      <c r="R287" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A288" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E288" s="7">
+        <v>1270</v>
+      </c>
+      <c r="F288" s="7">
+        <v>1249</v>
+      </c>
+      <c r="G288" s="7">
+        <v>1269</v>
+      </c>
+      <c r="H288" s="7">
+        <v>1269</v>
+      </c>
+      <c r="I288" s="7">
+        <v>1249</v>
+      </c>
+      <c r="J288" s="7">
+        <v>1289</v>
+      </c>
+      <c r="K288" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L288" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M288" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="N288" s="7">
+        <v>1289</v>
+      </c>
+      <c r="O288" s="6">
+        <v>23</v>
+      </c>
+      <c r="P288" s="8">
+        <v>20</v>
+      </c>
+      <c r="Q288" s="9">
+        <v>1.576</v>
+      </c>
+      <c r="R288" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A289" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E289" s="7">
+        <v>2832</v>
+      </c>
+      <c r="F289" s="7">
+        <v>2805.3</v>
+      </c>
+      <c r="G289" s="7">
+        <v>2828</v>
+      </c>
+      <c r="H289" s="7">
+        <v>2827.8</v>
+      </c>
+      <c r="I289" s="7">
+        <v>2805.3</v>
+      </c>
+      <c r="J289" s="7">
+        <v>2850.3</v>
+      </c>
+      <c r="K289" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L289" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M289" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="N289" s="7">
+        <v>2850.3</v>
+      </c>
+      <c r="O289" s="6">
+        <v>2</v>
+      </c>
+      <c r="P289" s="8">
+        <v>22.5</v>
+      </c>
+      <c r="Q289" s="9">
+        <v>0.796</v>
+      </c>
+      <c r="R289" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A290" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E290" s="7">
+        <v>2177.8</v>
+      </c>
+      <c r="F290" s="7">
+        <v>2130.4</v>
+      </c>
+      <c r="G290" s="7">
+        <v>2173.8</v>
+      </c>
+      <c r="H290" s="7">
+        <v>2173.8</v>
+      </c>
+      <c r="I290" s="7">
+        <v>2130.4</v>
+      </c>
+      <c r="J290" s="7">
+        <v>2217.2</v>
+      </c>
+      <c r="K290" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L290" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M290" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="N290" s="7">
+        <v>2217.2</v>
+      </c>
+      <c r="O290" s="6">
+        <v>11</v>
+      </c>
+      <c r="P290" s="8">
+        <v>43.4</v>
+      </c>
+      <c r="Q290" s="9">
+        <v>1.997</v>
+      </c>
+      <c r="R290" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E291" s="3">
+        <v>957.75</v>
+      </c>
+      <c r="F291" s="3">
+        <v>938.1</v>
+      </c>
+      <c r="G291" s="3">
+        <v>938.4</v>
+      </c>
+      <c r="H291" s="3">
+        <v>938.45</v>
+      </c>
+      <c r="I291" s="3">
+        <v>957.75</v>
+      </c>
+      <c r="J291" s="3">
+        <v>919.15</v>
+      </c>
+      <c r="K291" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L291" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M291" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="N291" s="3">
+        <v>957.75</v>
+      </c>
+      <c r="O291" s="2">
+        <v>22</v>
+      </c>
+      <c r="P291" s="4">
+        <v>-19.3</v>
+      </c>
+      <c r="Q291" s="5">
+        <v>-2.057</v>
+      </c>
+      <c r="R291" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A292" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="B292" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C292" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D292" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="E292" s="11">
+        <v>4432</v>
+      </c>
+      <c r="F292" s="11">
+        <v>4389</v>
+      </c>
+      <c r="G292" s="11">
+        <v>4428.5</v>
+      </c>
+      <c r="H292" s="11">
+        <v>4432.6</v>
+      </c>
+      <c r="I292" s="11">
+        <v>4389</v>
+      </c>
+      <c r="J292" s="11">
+        <v>4476.2</v>
+      </c>
+      <c r="K292" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L292" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="M285" s="10"/>
-      <c r="N285" s="10"/>
-      <c r="O285" s="10"/>
-      <c r="P285" s="10"/>
-      <c r="Q285" s="10"/>
-      <c r="R285" s="10" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A286" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="B286" s="10" t="s">
+      <c r="M292" s="10"/>
+      <c r="N292" s="10"/>
+      <c r="O292" s="10"/>
+      <c r="P292" s="10"/>
+      <c r="Q292" s="10"/>
+      <c r="R292" s="10" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D293" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="C286" s="10" t="s">
+      <c r="E293" s="3">
+        <v>1902</v>
+      </c>
+      <c r="F293" s="3">
+        <v>1882.4</v>
+      </c>
+      <c r="G293" s="3">
+        <v>1891</v>
+      </c>
+      <c r="H293" s="3">
+        <v>1890.9</v>
+      </c>
+      <c r="I293" s="3">
+        <v>1902</v>
+      </c>
+      <c r="J293" s="3">
+        <v>1879.8</v>
+      </c>
+      <c r="K293" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L293" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M293" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="N293" s="3">
+        <v>1902</v>
+      </c>
+      <c r="O293" s="2">
+        <v>1</v>
+      </c>
+      <c r="P293" s="4">
+        <v>-11.1</v>
+      </c>
+      <c r="Q293" s="5">
+        <v>-0.587</v>
+      </c>
+      <c r="R293" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D286" s="10" t="s">
-        <v>661</v>
-      </c>
-      <c r="E286" s="11">
-        <v>2682.4</v>
-      </c>
-      <c r="F286" s="11">
-        <v>2669.4</v>
-      </c>
-      <c r="G286" s="11">
-        <v>2669.4</v>
-      </c>
-      <c r="H286" s="10"/>
-      <c r="I286" s="11">
-        <v>2682.4</v>
-      </c>
-      <c r="J286" s="10"/>
-      <c r="K286" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L286" s="10" t="s">
+      <c r="D294" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E294" s="3">
+        <v>7292</v>
+      </c>
+      <c r="F294" s="3">
+        <v>7221</v>
+      </c>
+      <c r="G294" s="3">
+        <v>7231</v>
+      </c>
+      <c r="H294" s="3">
+        <v>7234.5</v>
+      </c>
+      <c r="I294" s="3">
+        <v>7292</v>
+      </c>
+      <c r="J294" s="3">
+        <v>7177</v>
+      </c>
+      <c r="K294" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L294" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M294" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="N294" s="3">
+        <v>7292</v>
+      </c>
+      <c r="O294" s="2">
+        <v>1</v>
+      </c>
+      <c r="P294" s="4">
+        <v>-57.5</v>
+      </c>
+      <c r="Q294" s="5">
+        <v>-0.795</v>
+      </c>
+      <c r="R294" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A295" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="E295" s="7">
+        <v>1849.7</v>
+      </c>
+      <c r="F295" s="7">
+        <v>1841.2</v>
+      </c>
+      <c r="G295" s="7">
+        <v>1841.7</v>
+      </c>
+      <c r="H295" s="7">
+        <v>1841.7</v>
+      </c>
+      <c r="I295" s="7">
+        <v>1849.7</v>
+      </c>
+      <c r="J295" s="7">
+        <v>1833.7</v>
+      </c>
+      <c r="K295" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L295" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M295" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="N295" s="7">
+        <v>1833.7</v>
+      </c>
+      <c r="O295" s="6">
+        <v>1</v>
+      </c>
+      <c r="P295" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q295" s="9">
+        <v>0.434</v>
+      </c>
+      <c r="R295" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E296" s="3">
+        <v>31255</v>
+      </c>
+      <c r="F296" s="3">
+        <v>30955</v>
+      </c>
+      <c r="G296" s="3">
+        <v>30985</v>
+      </c>
+      <c r="H296" s="3">
+        <v>30985</v>
+      </c>
+      <c r="I296" s="3">
+        <v>31255</v>
+      </c>
+      <c r="J296" s="3">
+        <v>30715</v>
+      </c>
+      <c r="K296" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L296" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M296" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="N296" s="3">
+        <v>31255</v>
+      </c>
+      <c r="O296" s="2">
+        <v>7</v>
+      </c>
+      <c r="P296" s="4">
+        <v>-270</v>
+      </c>
+      <c r="Q296" s="5">
+        <v>-0.871</v>
+      </c>
+      <c r="R296" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A297" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="E297" s="7">
+        <v>8213</v>
+      </c>
+      <c r="F297" s="7">
+        <v>8161.5</v>
+      </c>
+      <c r="G297" s="7">
+        <v>8165.5</v>
+      </c>
+      <c r="H297" s="7">
+        <v>8165.5</v>
+      </c>
+      <c r="I297" s="7">
+        <v>8213</v>
+      </c>
+      <c r="J297" s="7">
+        <v>8118</v>
+      </c>
+      <c r="K297" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L297" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M297" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="N297" s="7">
+        <v>8118</v>
+      </c>
+      <c r="O297" s="6">
+        <v>2</v>
+      </c>
+      <c r="P297" s="8">
+        <v>47.5</v>
+      </c>
+      <c r="Q297" s="9">
+        <v>0.582</v>
+      </c>
+      <c r="R297" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A298" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="E298" s="7">
+        <v>70.26</v>
+      </c>
+      <c r="F298" s="7">
+        <v>69.42</v>
+      </c>
+      <c r="G298" s="7">
+        <v>69.73</v>
+      </c>
+      <c r="H298" s="7">
+        <v>69.72</v>
+      </c>
+      <c r="I298" s="7">
+        <v>69.42</v>
+      </c>
+      <c r="J298" s="7">
+        <v>70.02</v>
+      </c>
+      <c r="K298" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L298" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M298" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="N298" s="7">
+        <v>70.02</v>
+      </c>
+      <c r="O298" s="6">
+        <v>1</v>
+      </c>
+      <c r="P298" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="Q298" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="R298" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E299" s="3">
+        <v>437.1</v>
+      </c>
+      <c r="F299" s="3">
+        <v>435.05</v>
+      </c>
+      <c r="G299" s="3">
+        <v>435.6</v>
+      </c>
+      <c r="H299" s="3">
+        <v>435.6</v>
+      </c>
+      <c r="I299" s="3">
+        <v>437.1</v>
+      </c>
+      <c r="J299" s="3">
+        <v>434.1</v>
+      </c>
+      <c r="K299" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L299" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M299" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="N299" s="3">
+        <v>437.1</v>
+      </c>
+      <c r="O299" s="2">
+        <v>3</v>
+      </c>
+      <c r="P299" s="4">
+        <v>-1.5</v>
+      </c>
+      <c r="Q299" s="5">
+        <v>-0.344</v>
+      </c>
+      <c r="R299" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E300" s="3">
+        <v>5664.5</v>
+      </c>
+      <c r="F300" s="3">
+        <v>5624</v>
+      </c>
+      <c r="G300" s="3">
+        <v>5638.5</v>
+      </c>
+      <c r="H300" s="3">
+        <v>5635</v>
+      </c>
+      <c r="I300" s="3">
+        <v>5624</v>
+      </c>
+      <c r="J300" s="3">
+        <v>5646</v>
+      </c>
+      <c r="K300" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L300" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M300" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="N300" s="3">
+        <v>5624</v>
+      </c>
+      <c r="O300" s="2">
+        <v>1</v>
+      </c>
+      <c r="P300" s="4">
+        <v>-11</v>
+      </c>
+      <c r="Q300" s="5">
+        <v>-0.195</v>
+      </c>
+      <c r="R300" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A301" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="E301" s="7">
+        <v>444.85</v>
+      </c>
+      <c r="F301" s="7">
+        <v>441.6</v>
+      </c>
+      <c r="G301" s="7">
+        <v>443.15</v>
+      </c>
+      <c r="H301" s="7">
+        <v>443</v>
+      </c>
+      <c r="I301" s="7">
+        <v>441.6</v>
+      </c>
+      <c r="J301" s="7">
+        <v>444.4</v>
+      </c>
+      <c r="K301" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L301" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M301" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="N301" s="7">
+        <v>444.4</v>
+      </c>
+      <c r="O301" s="6">
+        <v>1</v>
+      </c>
+      <c r="P301" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="Q301" s="9">
+        <v>0.316</v>
+      </c>
+      <c r="R301" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A302" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="B302" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C302" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D302" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E302" s="11">
+        <v>101.05</v>
+      </c>
+      <c r="F302" s="11">
+        <v>99.93</v>
+      </c>
+      <c r="G302" s="11">
+        <v>101</v>
+      </c>
+      <c r="H302" s="11">
+        <v>101</v>
+      </c>
+      <c r="I302" s="11">
+        <v>99.93</v>
+      </c>
+      <c r="J302" s="11">
+        <v>102.07</v>
+      </c>
+      <c r="K302" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L302" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="M286" s="10"/>
-      <c r="N286" s="10"/>
-      <c r="O286" s="10"/>
-      <c r="P286" s="10"/>
-      <c r="Q286" s="10"/>
-      <c r="R286" s="10" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A287" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="B287" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="C287" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D287" s="10" t="s">
-        <v>661</v>
-      </c>
-      <c r="E287" s="11">
-        <v>783.9</v>
-      </c>
-      <c r="F287" s="11">
-        <v>772</v>
-      </c>
-      <c r="G287" s="11">
-        <v>774.7</v>
-      </c>
-      <c r="H287" s="10"/>
-      <c r="I287" s="11">
-        <v>783.9</v>
-      </c>
-      <c r="J287" s="10"/>
-      <c r="K287" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L287" s="10" t="s">
+      <c r="M302" s="10"/>
+      <c r="N302" s="10"/>
+      <c r="O302" s="10"/>
+      <c r="P302" s="10"/>
+      <c r="Q302" s="10"/>
+      <c r="R302" s="10" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A303" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="B303" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C303" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D303" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E303" s="11">
+        <v>6825.5</v>
+      </c>
+      <c r="F303" s="11">
+        <v>6798.5</v>
+      </c>
+      <c r="G303" s="11">
+        <v>6824.5</v>
+      </c>
+      <c r="H303" s="11">
+        <v>6824</v>
+      </c>
+      <c r="I303" s="11">
+        <v>6798.5</v>
+      </c>
+      <c r="J303" s="11">
+        <v>6849.5</v>
+      </c>
+      <c r="K303" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L303" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="M287" s="10"/>
-      <c r="N287" s="10"/>
-      <c r="O287" s="10"/>
-      <c r="P287" s="10"/>
-      <c r="Q287" s="10"/>
-      <c r="R287" s="10" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A289" s="14" t="s">
+      <c r="M303" s="10"/>
+      <c r="N303" s="10"/>
+      <c r="O303" s="10"/>
+      <c r="P303" s="10"/>
+      <c r="Q303" s="10"/>
+      <c r="R303" s="10" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A304" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="B304" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C304" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D304" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="E304" s="11">
+        <v>145.4</v>
+      </c>
+      <c r="F304" s="11">
+        <v>144.4</v>
+      </c>
+      <c r="G304" s="11">
+        <v>144.83</v>
+      </c>
+      <c r="H304" s="11">
+        <v>144.83</v>
+      </c>
+      <c r="I304" s="11">
+        <v>144.4</v>
+      </c>
+      <c r="J304" s="11">
+        <v>145.26</v>
+      </c>
+      <c r="K304" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L304" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M304" s="10"/>
+      <c r="N304" s="10"/>
+      <c r="O304" s="10"/>
+      <c r="P304" s="10"/>
+      <c r="Q304" s="10"/>
+      <c r="R304" s="10" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A305" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="B305" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C305" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D305" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="E305" s="11">
+        <v>2601.5</v>
+      </c>
+      <c r="F305" s="11">
+        <v>2589</v>
+      </c>
+      <c r="G305" s="11">
+        <v>2596.1</v>
+      </c>
+      <c r="H305" s="11">
+        <v>2596</v>
+      </c>
+      <c r="I305" s="11">
+        <v>2589</v>
+      </c>
+      <c r="J305" s="11">
+        <v>2603</v>
+      </c>
+      <c r="K305" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L305" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M305" s="10"/>
+      <c r="N305" s="10"/>
+      <c r="O305" s="10"/>
+      <c r="P305" s="10"/>
+      <c r="Q305" s="10"/>
+      <c r="R305" s="10" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A306" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="B306" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C306" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D306" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="E306" s="11">
+        <v>1408.4</v>
+      </c>
+      <c r="F306" s="11">
+        <v>1401.8</v>
+      </c>
+      <c r="G306" s="11">
+        <v>1406.2</v>
+      </c>
+      <c r="H306" s="11">
+        <v>1405.9</v>
+      </c>
+      <c r="I306" s="11">
+        <v>1401.8</v>
+      </c>
+      <c r="J306" s="11">
+        <v>1410</v>
+      </c>
+      <c r="K306" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L306" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M306" s="10"/>
+      <c r="N306" s="10"/>
+      <c r="O306" s="10"/>
+      <c r="P306" s="10"/>
+      <c r="Q306" s="10"/>
+      <c r="R306" s="10" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A307" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="B307" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C307" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D307" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="E307" s="11">
+        <v>723.7</v>
+      </c>
+      <c r="F307" s="11">
+        <v>718.15</v>
+      </c>
+      <c r="G307" s="11">
+        <v>722.15</v>
+      </c>
+      <c r="H307" s="11">
+        <v>722.15</v>
+      </c>
+      <c r="I307" s="11">
+        <v>718.15</v>
+      </c>
+      <c r="J307" s="11">
+        <v>726.15</v>
+      </c>
+      <c r="K307" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L307" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M307" s="10"/>
+      <c r="N307" s="10"/>
+      <c r="O307" s="10"/>
+      <c r="P307" s="10"/>
+      <c r="Q307" s="10"/>
+      <c r="R307" s="10" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A308" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="B308" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="C308" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D308" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="P289" s="15">
-        <v>148.6</v>
-      </c>
-      <c r="R289" s="14" t="s">
-        <v>665</v>
+      <c r="E308" s="11">
+        <v>1668</v>
+      </c>
+      <c r="F308" s="11">
+        <v>1658</v>
+      </c>
+      <c r="G308" s="11">
+        <v>1665</v>
+      </c>
+      <c r="H308" s="10"/>
+      <c r="I308" s="11">
+        <v>1658</v>
+      </c>
+      <c r="J308" s="10"/>
+      <c r="K308" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L308" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M308" s="10"/>
+      <c r="N308" s="10"/>
+      <c r="O308" s="10"/>
+      <c r="P308" s="10"/>
+      <c r="Q308" s="10"/>
+      <c r="R308" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A309" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="B309" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="C309" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D309" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E309" s="11">
+        <v>731.95</v>
+      </c>
+      <c r="F309" s="11">
+        <v>725.95</v>
+      </c>
+      <c r="G309" s="11">
+        <v>730</v>
+      </c>
+      <c r="H309" s="10"/>
+      <c r="I309" s="11">
+        <v>725.95</v>
+      </c>
+      <c r="J309" s="10"/>
+      <c r="K309" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L309" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M309" s="10"/>
+      <c r="N309" s="10"/>
+      <c r="O309" s="10"/>
+      <c r="P309" s="10"/>
+      <c r="Q309" s="10"/>
+      <c r="R309" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A310" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="B310" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="C310" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D310" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E310" s="11">
+        <v>1254</v>
+      </c>
+      <c r="F310" s="11">
+        <v>1247.1</v>
+      </c>
+      <c r="G310" s="11">
+        <v>1253.5</v>
+      </c>
+      <c r="H310" s="10"/>
+      <c r="I310" s="11">
+        <v>1247.1</v>
+      </c>
+      <c r="J310" s="10"/>
+      <c r="K310" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L310" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M310" s="10"/>
+      <c r="N310" s="10"/>
+      <c r="O310" s="10"/>
+      <c r="P310" s="10"/>
+      <c r="Q310" s="10"/>
+      <c r="R310" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A311" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="B311" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C311" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D311" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E311" s="11">
+        <v>1631</v>
+      </c>
+      <c r="F311" s="11">
+        <v>1619</v>
+      </c>
+      <c r="G311" s="11">
+        <v>1631</v>
+      </c>
+      <c r="H311" s="10"/>
+      <c r="I311" s="11">
+        <v>1619</v>
+      </c>
+      <c r="J311" s="10"/>
+      <c r="K311" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L311" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M311" s="10"/>
+      <c r="N311" s="10"/>
+      <c r="O311" s="10"/>
+      <c r="P311" s="10"/>
+      <c r="Q311" s="10"/>
+      <c r="R311" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A312" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B312" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="C312" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E312" s="11">
+        <v>2210.7</v>
+      </c>
+      <c r="F312" s="11">
+        <v>2191.4</v>
+      </c>
+      <c r="G312" s="11">
+        <v>2210.4</v>
+      </c>
+      <c r="H312" s="10"/>
+      <c r="I312" s="11">
+        <v>2191.4</v>
+      </c>
+      <c r="J312" s="10"/>
+      <c r="K312" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L312" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M312" s="10"/>
+      <c r="N312" s="10"/>
+      <c r="O312" s="10"/>
+      <c r="P312" s="10"/>
+      <c r="Q312" s="10"/>
+      <c r="R312" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A313" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="B313" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="C313" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D313" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E313" s="11">
+        <v>587</v>
+      </c>
+      <c r="F313" s="11">
+        <v>583.05</v>
+      </c>
+      <c r="G313" s="11">
+        <v>585.3</v>
+      </c>
+      <c r="H313" s="10"/>
+      <c r="I313" s="11">
+        <v>583.05</v>
+      </c>
+      <c r="J313" s="10"/>
+      <c r="K313" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L313" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M313" s="10"/>
+      <c r="N313" s="10"/>
+      <c r="O313" s="10"/>
+      <c r="P313" s="10"/>
+      <c r="Q313" s="10"/>
+      <c r="R313" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A314" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="B314" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C314" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D314" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E314" s="11">
+        <v>427.7</v>
+      </c>
+      <c r="F314" s="11">
+        <v>424.15</v>
+      </c>
+      <c r="G314" s="11">
+        <v>426.5</v>
+      </c>
+      <c r="H314" s="10"/>
+      <c r="I314" s="11">
+        <v>424.15</v>
+      </c>
+      <c r="J314" s="10"/>
+      <c r="K314" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L314" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M314" s="10"/>
+      <c r="N314" s="10"/>
+      <c r="O314" s="10"/>
+      <c r="P314" s="10"/>
+      <c r="Q314" s="10"/>
+      <c r="R314" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A315" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="B315" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="C315" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D315" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E315" s="11">
+        <v>258.4</v>
+      </c>
+      <c r="F315" s="11">
+        <v>256.15</v>
+      </c>
+      <c r="G315" s="11">
+        <v>257.05</v>
+      </c>
+      <c r="H315" s="10"/>
+      <c r="I315" s="11">
+        <v>256.15</v>
+      </c>
+      <c r="J315" s="10"/>
+      <c r="K315" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L315" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M315" s="10"/>
+      <c r="N315" s="10"/>
+      <c r="O315" s="10"/>
+      <c r="P315" s="10"/>
+      <c r="Q315" s="10"/>
+      <c r="R315" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A316" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="B316" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="C316" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D316" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E316" s="11">
+        <v>97</v>
+      </c>
+      <c r="F316" s="11">
+        <v>95.27</v>
+      </c>
+      <c r="G316" s="11">
+        <v>96.35</v>
+      </c>
+      <c r="H316" s="10"/>
+      <c r="I316" s="11">
+        <v>95.27</v>
+      </c>
+      <c r="J316" s="10"/>
+      <c r="K316" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L316" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M316" s="10"/>
+      <c r="N316" s="10"/>
+      <c r="O316" s="10"/>
+      <c r="P316" s="10"/>
+      <c r="Q316" s="10"/>
+      <c r="R316" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="B317" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C317" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D317" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E317" s="11">
+        <v>117.5</v>
+      </c>
+      <c r="F317" s="11">
+        <v>116.55</v>
+      </c>
+      <c r="G317" s="11">
+        <v>117.31</v>
+      </c>
+      <c r="H317" s="10"/>
+      <c r="I317" s="11">
+        <v>116.55</v>
+      </c>
+      <c r="J317" s="10"/>
+      <c r="K317" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L317" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M317" s="10"/>
+      <c r="N317" s="10"/>
+      <c r="O317" s="10"/>
+      <c r="P317" s="10"/>
+      <c r="Q317" s="10"/>
+      <c r="R317" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A318" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="B318" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C318" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D318" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E318" s="11">
+        <v>1041.9</v>
+      </c>
+      <c r="F318" s="11">
+        <v>1036.1</v>
+      </c>
+      <c r="G318" s="11">
+        <v>1041.9</v>
+      </c>
+      <c r="H318" s="10"/>
+      <c r="I318" s="11">
+        <v>1036.1</v>
+      </c>
+      <c r="J318" s="10"/>
+      <c r="K318" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L318" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M318" s="10"/>
+      <c r="N318" s="10"/>
+      <c r="O318" s="10"/>
+      <c r="P318" s="10"/>
+      <c r="Q318" s="10"/>
+      <c r="R318" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A319" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="B319" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="C319" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D319" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E319" s="11">
+        <v>2346.3</v>
+      </c>
+      <c r="F319" s="11">
+        <v>2332.8</v>
+      </c>
+      <c r="G319" s="11">
+        <v>2345</v>
+      </c>
+      <c r="H319" s="10"/>
+      <c r="I319" s="11">
+        <v>2332.8</v>
+      </c>
+      <c r="J319" s="10"/>
+      <c r="K319" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L319" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M319" s="10"/>
+      <c r="N319" s="10"/>
+      <c r="O319" s="10"/>
+      <c r="P319" s="10"/>
+      <c r="Q319" s="10"/>
+      <c r="R319" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A320" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="B320" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="C320" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D320" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E320" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="F320" s="11">
+        <v>86.77</v>
+      </c>
+      <c r="G320" s="11">
+        <v>87.2</v>
+      </c>
+      <c r="H320" s="10"/>
+      <c r="I320" s="11">
+        <v>86.77</v>
+      </c>
+      <c r="J320" s="10"/>
+      <c r="K320" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L320" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M320" s="10"/>
+      <c r="N320" s="10"/>
+      <c r="O320" s="10"/>
+      <c r="P320" s="10"/>
+      <c r="Q320" s="10"/>
+      <c r="R320" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A321" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="B321" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="C321" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D321" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E321" s="11">
+        <v>1506</v>
+      </c>
+      <c r="F321" s="11">
+        <v>1489</v>
+      </c>
+      <c r="G321" s="11">
+        <v>1506</v>
+      </c>
+      <c r="H321" s="10"/>
+      <c r="I321" s="11">
+        <v>1489</v>
+      </c>
+      <c r="J321" s="10"/>
+      <c r="K321" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L321" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M321" s="10"/>
+      <c r="N321" s="10"/>
+      <c r="O321" s="10"/>
+      <c r="P321" s="10"/>
+      <c r="Q321" s="10"/>
+      <c r="R321" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A322" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="B322" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C322" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D322" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E322" s="11">
+        <v>797</v>
+      </c>
+      <c r="F322" s="11">
+        <v>788.95</v>
+      </c>
+      <c r="G322" s="11">
+        <v>797</v>
+      </c>
+      <c r="H322" s="10"/>
+      <c r="I322" s="11">
+        <v>788.95</v>
+      </c>
+      <c r="J322" s="10"/>
+      <c r="K322" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L322" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M322" s="10"/>
+      <c r="N322" s="10"/>
+      <c r="O322" s="10"/>
+      <c r="P322" s="10"/>
+      <c r="Q322" s="10"/>
+      <c r="R322" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A324" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="P324" s="15">
+        <v>-141.39</v>
+      </c>
+      <c r="R324" s="14" t="s">
+        <v>724</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="791">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1636,334 +1636,334 @@
     <t>NSE:SONACOMS-EQ_BEAR_1772169300_1772185500</t>
   </si>
   <si>
+    <t>2026-03-11 09:30</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ_BEAR_1772164800_1772424000</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:30</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:45</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ_BEAR_1772167500_1772425800</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:00</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:30</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BEAR_1772163900_1772425800</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:45</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1772172000_1772432100</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:45</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ_BEAR_1772164800_1772432100</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:15</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BEAR_1772423100_1772433000</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:30</t>
+  </si>
+  <si>
+    <t>NSE:EICHERMOT-EQ_BEAR_1772185500_1772433000</t>
+  </si>
+  <si>
+    <t>NSE:EICHERMOT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:00</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BEAR_1772163900_1772433900</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:45</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ_BEAR_1772184600_1772433900</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BEAR_1772185500_1772434800</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1772167500_1772434800</t>
+  </si>
+  <si>
+    <t>2026-03-02 14:00</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1772185500_1772434800</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BEAR_1772424000_1772436600</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ_BEAR_1772185500_1772437500</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1772423100_1772437500</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BEAR_1772168400_1772439300</t>
+  </si>
+  <si>
+    <t>2026-03-02 14:15</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BEAR_1772423100_1772442900</t>
+  </si>
+  <si>
+    <t>2026-03-02 14:45</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1772430300_1772595900</t>
+  </si>
+  <si>
+    <t>2026-03-05 09:15</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1772431200_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:00</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:15</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ_BEAR_1772423100_1772597700</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 09:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:30</t>
+  </si>
+  <si>
+    <t>NSE:IDFCFIRSTB-EQ_BEAR_1772423100_1772601300</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 11:30</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ_BEAR_1772426700_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>2026-03-09 10:15</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>2026-03-04 11:45</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ_BEAR_1772427600_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 12:15</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BEAR_1772595900_1772597700</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:00</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 15:00</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1772685900_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:45</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BULL_1772683200_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772684100_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:15</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1772702100_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1772688600_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BEAR_1772701200_1772770500</t>
+  </si>
+  <si>
+    <t>2026-03-06 10:15</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ_BULL_1772698500_1772786700</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:15</t>
+  </si>
+  <si>
+    <t>NSE:BHARTIARTL-EQ_BEAR_1772701200_1772786700</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:45</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BULL_1772778600_1772786700</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772789400</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BULL_1772772300_1772789400</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1772771400_1772790300</t>
+  </si>
+  <si>
+    <t>2026-03-06 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:15</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1772772300_1772790300</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:30</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1772693100_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:30</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1772775000_1773027900</t>
+  </si>
+  <si>
+    <t>NSE:NUVAMA-EQ_BEAR_1772784900_1773027900</t>
+  </si>
+  <si>
+    <t>NSE:NUVAMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 14:15</t>
+  </si>
+  <si>
+    <t>NSE:TATATECH-EQ_BEAR_1772788500_1773027900</t>
+  </si>
+  <si>
+    <t>NSE:TATATECH-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1772771400_1773029700</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1773028800_1773037800</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:00</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 149 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
-  </si>
-  <si>
-    <t>NSE:ICICIPRULI-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-02 09:45</t>
-  </si>
-  <si>
-    <t>NSE:AXISBANK-EQ_BEAR_1772164800_1772424000</t>
-  </si>
-  <si>
-    <t>2026-03-02 09:30</t>
-  </si>
-  <si>
-    <t>2026-03-02 13:45</t>
-  </si>
-  <si>
-    <t>NSE:DRREDDY-EQ_BEAR_1772167500_1772425800</t>
-  </si>
-  <si>
-    <t>NSE:DRREDDY-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-02 10:00</t>
-  </si>
-  <si>
-    <t>2026-03-02 10:30</t>
-  </si>
-  <si>
-    <t>NSE:NESTLEIND-EQ_BEAR_1772163900_1772425800</t>
-  </si>
-  <si>
-    <t>2026-03-02 10:45</t>
-  </si>
-  <si>
-    <t>NSE:IEX-EQ_BEAR_1772172000_1772432100</t>
-  </si>
-  <si>
-    <t>2026-03-02 11:45</t>
-  </si>
-  <si>
-    <t>NSE:M&amp;M-EQ_BEAR_1772164800_1772432100</t>
-  </si>
-  <si>
-    <t>NSE:M&amp;M-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-02 13:15</t>
-  </si>
-  <si>
-    <t>NSE:DABUR-EQ_BEAR_1772423100_1772433000</t>
-  </si>
-  <si>
-    <t>2026-03-02 12:00</t>
-  </si>
-  <si>
-    <t>2026-03-02 12:30</t>
-  </si>
-  <si>
-    <t>NSE:EICHERMOT-EQ_BEAR_1772185500_1772433000</t>
-  </si>
-  <si>
-    <t>NSE:EICHERMOT-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-02 13:00</t>
-  </si>
-  <si>
-    <t>NSE:ADANIPORTS-EQ_BEAR_1772163900_1772433900</t>
-  </si>
-  <si>
-    <t>2026-03-02 12:15</t>
-  </si>
-  <si>
-    <t>2026-03-02 12:45</t>
-  </si>
-  <si>
-    <t>NSE:GMRAIRPORT-EQ_BEAR_1772184600_1772433900</t>
-  </si>
-  <si>
-    <t>NSE:GMRAIRPORT-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENSOL-EQ_BEAR_1772185500_1772434800</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENT-EQ_BEAR_1772167500_1772434800</t>
-  </si>
-  <si>
-    <t>2026-03-02 14:00</t>
-  </si>
-  <si>
-    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1772185500_1772434800</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ_BEAR_1772424000_1772436600</t>
-  </si>
-  <si>
-    <t>NSE:LICHSGFIN-EQ_BEAR_1772185500_1772437500</t>
-  </si>
-  <si>
-    <t>NSE:PGEL-EQ_BEAR_1772423100_1772437500</t>
-  </si>
-  <si>
-    <t>NSE:PFC-EQ_BEAR_1772168400_1772439300</t>
-  </si>
-  <si>
-    <t>2026-03-02 14:15</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BEAR_1772423100_1772442900</t>
-  </si>
-  <si>
-    <t>2026-03-02 14:45</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ_BEAR_1772430300_1772595900</t>
-  </si>
-  <si>
-    <t>2026-03-05 09:15</t>
-  </si>
-  <si>
-    <t>NSE:BHARATFORG-EQ_BEAR_1772431200_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:BHARATFORG-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-04 10:00</t>
-  </si>
-  <si>
-    <t>NSE:COLPAL-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:COLPAL-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-04 10:15</t>
-  </si>
-  <si>
-    <t>NSE:CUMMINSIND-EQ_BEAR_1772423100_1772597700</t>
-  </si>
-  <si>
-    <t>NSE:CUMMINSIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-04 09:45</t>
-  </si>
-  <si>
-    <t>2026-03-04 10:30</t>
-  </si>
-  <si>
-    <t>NSE:IDFCFIRSTB-EQ_BEAR_1772423100_1772601300</t>
-  </si>
-  <si>
-    <t>2026-03-04 10:45</t>
-  </si>
-  <si>
-    <t>2026-03-04 11:30</t>
-  </si>
-  <si>
-    <t>NSE:INDIANB-EQ_BEAR_1772426700_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:INDIANB-EQ</t>
-  </si>
-  <si>
-    <t>NSE:IGL-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:JSWSTEEL-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>2026-03-09 10:15</t>
-  </si>
-  <si>
-    <t>NSE:KALYANKJIL-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772595900</t>
-  </si>
-  <si>
-    <t>2026-03-04 11:45</t>
-  </si>
-  <si>
-    <t>NSE:BHEL-EQ_BEAR_1772427600_1772595900</t>
-  </si>
-  <si>
-    <t>NSE:BHEL-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-04 12:15</t>
-  </si>
-  <si>
-    <t>NSE:CIPLA-EQ_BEAR_1772595900_1772597700</t>
-  </si>
-  <si>
-    <t>2026-03-04 15:00</t>
-  </si>
-  <si>
-    <t>NSE:AUBANK-EQ_BULL_1772689500_1772768700</t>
-  </si>
-  <si>
-    <t>2026-03-06 15:00</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ_BULL_1772685900_1772768700</t>
-  </si>
-  <si>
-    <t>2026-03-06 09:45</t>
-  </si>
-  <si>
-    <t>NSE:BDL-EQ_BULL_1772683200_1772768700</t>
-  </si>
-  <si>
-    <t>2026-03-06 10:00</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ_BULL_1772684100_1772768700</t>
-  </si>
-  <si>
-    <t>2026-03-09 09:15</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772768700</t>
-  </si>
-  <si>
-    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772768700</t>
-  </si>
-  <si>
-    <t>NSE:MAZDOCK-EQ</t>
-  </si>
-  <si>
-    <t>NSE:POLYCAB-EQ_BULL_1772702100_1772768700</t>
-  </si>
-  <si>
-    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772768700</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ_BULL_1772688600_1772768700</t>
-  </si>
-  <si>
-    <t>NSE:TORNTPHARM-EQ_BEAR_1772701200_1772770500</t>
-  </si>
-  <si>
-    <t>2026-03-06 10:15</t>
-  </si>
-  <si>
-    <t>NSE:DMART-EQ_BULL_1772698500_1772786700</t>
-  </si>
-  <si>
-    <t>2026-03-06 14:15</t>
-  </si>
-  <si>
-    <t>NSE:BHARTIARTL-EQ_BEAR_1772701200_1772786700</t>
-  </si>
-  <si>
-    <t>2026-03-06 14:45</t>
-  </si>
-  <si>
-    <t>NSE:BRITANNIA-EQ_BULL_1772778600_1772786700</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772789400</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ_BULL_1772772300_1772789400</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ_BEAR_1772771400_1772790300</t>
-  </si>
-  <si>
-    <t>2026-03-06 15:15</t>
-  </si>
-  <si>
-    <t>2026-03-10 09:15</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ_BULL_1772772300_1772790300</t>
-  </si>
-  <si>
-    <t>2026-03-09 09:30</t>
-  </si>
-  <si>
-    <t>NSE:PFC-EQ_BULL_1772693100_1772768700</t>
-  </si>
-  <si>
-    <t>2026-03-06 13:30</t>
-  </si>
-  <si>
-    <t>NSE:KALYANKJIL-EQ_BEAR_1772775000_1773027900</t>
-  </si>
-  <si>
-    <t>NSE:NUVAMA-EQ_BEAR_1772784900_1773027900</t>
-  </si>
-  <si>
-    <t>NSE:NUVAMA-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-09 14:15</t>
-  </si>
-  <si>
-    <t>NSE:TATATECH-EQ_BEAR_1772788500_1773027900</t>
-  </si>
-  <si>
-    <t>NSE:TATATECH-EQ</t>
-  </si>
-  <si>
-    <t>NSE:MANKIND-EQ_BEAR_1772771400_1773029700</t>
-  </si>
-  <si>
-    <t>2026-03-09 09:45</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ_BEAR_1773028800_1773037800</t>
-  </si>
-  <si>
-    <t>2026-03-09 12:00</t>
-  </si>
-  <si>
-    <t>Checked 37 candle(s) — neither SL nor Target hit yet</t>
+    <t>Checked 62 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
     <t>NSE:HAVELLS-EQ_BEAR_1772788500_1773038700</t>
@@ -2032,160 +2032,358 @@
     <t>NSE:TORNTPHARM-EQ_BULL_1773046800_1773114300</t>
   </si>
   <si>
+    <t>Checked 48 candle(s) — neither SL nor Target hit yet</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1773028800_1773115200</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:15</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1773029700_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BEAR_1773027900_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:45</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:30</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1773117000_1773132300</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:45</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1773027900_1773132300</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BULL_1773117000_1773133200</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:30</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773134100</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BULL_1773126000_1773134100</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:30</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1773121500_1773134100</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:15</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1773123300_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ_BULL_1773121500_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BULL_1773116100_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1773126000_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CGPOWER-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CGPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ_BULL_1773120600_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BULL_1773131400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ_BULL_1773126900_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:15</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ_BULL_1773130500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BULL_1773133200_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:00</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ_BULL_1773132300_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:45</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BULL_1773118800_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:45</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ_BULL_1773128700_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:30</t>
+  </si>
+  <si>
+    <t>NSE:CAMS-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CAMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ_BULL_1773126900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:30</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BULL_1773118800_1773200700</t>
+  </si>
+  <si>
     <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
-    <t>NSE:BLUESTARCO-EQ_BEAR_1773028800_1773115200</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ_BEAR_1773028800_1773116100</t>
-  </si>
-  <si>
-    <t>2026-03-10 10:15</t>
-  </si>
-  <si>
-    <t>NSE:BHARATFORG-EQ_BEAR_1773029700_1773116100</t>
-  </si>
-  <si>
-    <t>NSE:PAGEIND-EQ_BEAR_1773027900_1773116100</t>
-  </si>
-  <si>
-    <t>NSE:PAGEIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-10 11:45</t>
-  </si>
-  <si>
-    <t>NSE:POLYCAB-EQ_BEAR_1773028800_1773116100</t>
-  </si>
-  <si>
-    <t>2026-03-10 10:30</t>
-  </si>
-  <si>
-    <t>NSE:HFCL-EQ_BULL_1773117000_1773132300</t>
-  </si>
-  <si>
-    <t>2026-03-10 14:15</t>
-  </si>
-  <si>
-    <t>2026-03-10 14:45</t>
-  </si>
-  <si>
-    <t>NSE:VBL-EQ_BEAR_1773027900_1773132300</t>
-  </si>
-  <si>
-    <t>NSE:ALKEM-EQ_BULL_1773117000_1773133200</t>
-  </si>
-  <si>
-    <t>NSE:ALKEM-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-10 14:30</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773134100</t>
-  </si>
-  <si>
-    <t>NSE:IRFC-EQ_BULL_1773126000_1773134100</t>
-  </si>
-  <si>
-    <t>Checked 1 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:OFSS-EQ_BULL_1773121500_1773134100</t>
-  </si>
-  <si>
-    <t>NSE:NCC-EQ_BULL_1773123300_1773135000</t>
+    <t>NSE:HEROMOTOCO-EQ_BULL_1773117900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BULL_1773131400_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:00</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BULL_1773125100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BULL_1773126000_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INDIGO-EQ_BULL_1773130500_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INDIGO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1773123300_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:15</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1773117900_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:45</t>
+  </si>
+  <si>
+    <t>NSE:MUTHOOTFIN-EQ_BEAR_1773129600_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ_BULL_1773119700_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BULL_1773134100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BULL_1773132300_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SIEMENS-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SIEMENS-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:15</t>
+  </si>
+  <si>
+    <t>NSE:SUZLON-EQ_BULL_1773120600_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SUZLON-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:15</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ_BEAR_1773115200_1773201600</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:45</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1773119700_1773201600</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BEAR_1773126900_1773202500</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1773117000_1773207000</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:00</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BEAR_1773130500_1773210600</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:00</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BEAR_1773200700_1773214200</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BEAR_1773126000_1773215100</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:45</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BULL_1773130500_1773216900</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BULL_1773117000_1773218700</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773218700</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:15</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BULL_1773126900_1773218700</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ_BEAR_1773214200_1773219600</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1773207900_1773220500</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BEAR_1773203400_1773221400</t>
   </si>
   <si>
     <t>No candles after entry yet — trade open</t>
   </si>
   <si>
-    <t>NSE:SRF-EQ_BULL_1773121500_1773135000</t>
-  </si>
-  <si>
-    <t>NSE:SRF-EQ</t>
-  </si>
-  <si>
-    <t>NSE:UNITDSPR-EQ_BULL_1773116100_1773135000</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ_BULL_1773126000_1773135000</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773135900</t>
+    <t>NSE:PATANJALI-EQ_BEAR_1773207900_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:RBLBANK-EQ_BEAR_1773209700_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:RBLBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BEAR_1773210600_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:INDHOTEL-EQ_BEAR_1773207900_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:INDHOTEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BULL_1773201600_1773222300</t>
   </si>
   <si>
     <t>Entry candle not yet available — trade not entered</t>
   </si>
   <si>
-    <t>NSE:CGPOWER-EQ_BULL_1773117000_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:CGPOWER-EQ</t>
-  </si>
-  <si>
-    <t>NSE:CDSL-EQ_BULL_1773120600_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:CDSL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:CHOLAFIN-EQ_BULL_1773127800_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:COLPAL-EQ_BULL_1773131400_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:DLF-EQ_BULL_1773122400_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:DLF-EQ</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ_BULL_1773121500_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:NYKAA-EQ_BULL_1773126900_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:NYKAA-EQ</t>
-  </si>
-  <si>
-    <t>NSE:GMRAIRPORT-EQ_BULL_1773130500_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ_BULL_1773133200_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ_BULL_1773121500_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:LUPIN-EQ_BULL_1773117000_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:LUPIN-EQ</t>
-  </si>
-  <si>
-    <t>NSE:NBCC-EQ_BULL_1773132300_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:NBCC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:OBEROIRLTY-EQ_BULL_1773122400_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:OBEROIRLTY-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PNBHOUSING-EQ_BULL_1773127800_1773135900</t>
-  </si>
-  <si>
-    <t>SUMMARY — 147W / 150L / 24 OPEN  |  Win Rate: 49.5%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 297 of 321</t>
+    <t>SUMMARY — 172W / 176L / 12 OPEN  |  Win Rate: 49.4%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 348 of 360</t>
   </si>
 </sst>
 </file>
@@ -2301,10 +2499,10 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -2646,7 +2844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R324"/>
+  <dimension ref="A1:R363"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -11363,7 +11561,7 @@
         <v>510.4</v>
       </c>
       <c r="F156" s="3">
-        <v>506.15</v>
+        <v>506.3</v>
       </c>
       <c r="G156" s="3">
         <v>509.4</v>
@@ -11372,10 +11570,10 @@
         <v>509.4</v>
       </c>
       <c r="I156" s="3">
-        <v>506.15</v>
+        <v>506.3</v>
       </c>
       <c r="J156" s="3">
-        <v>512.65</v>
+        <v>512.5</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>22</v>
@@ -11387,16 +11585,16 @@
         <v>384</v>
       </c>
       <c r="N156" s="3">
-        <v>506.15</v>
+        <v>506.3</v>
       </c>
       <c r="O156" s="2">
         <v>1</v>
       </c>
       <c r="P156" s="4">
-        <v>-3.25</v>
+        <v>-3.1</v>
       </c>
       <c r="Q156" s="5">
-        <v>-0.638</v>
+        <v>-0.609</v>
       </c>
       <c r="R156" s="2" t="s">
         <v>25</v>
@@ -15491,57 +15689,67 @@
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A230" s="10" t="s">
+      <c r="A230" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B230" s="10" t="s">
+      <c r="B230" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C230" s="10" t="s">
+      <c r="C230" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D230" s="10" t="s">
+      <c r="D230" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E230" s="11">
+      <c r="E230" s="3">
         <v>536.2</v>
       </c>
-      <c r="F230" s="11">
+      <c r="F230" s="3">
         <v>532.05</v>
       </c>
-      <c r="G230" s="11">
+      <c r="G230" s="3">
         <v>533.25</v>
       </c>
-      <c r="H230" s="11">
+      <c r="H230" s="3">
         <v>502</v>
       </c>
-      <c r="I230" s="11">
+      <c r="I230" s="3">
         <v>536.2</v>
       </c>
-      <c r="J230" s="11">
+      <c r="J230" s="3">
         <v>467.8</v>
       </c>
-      <c r="K230" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L230" s="10" t="s">
+      <c r="K230" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L230" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M230" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="M230" s="10"/>
-      <c r="N230" s="10"/>
-      <c r="O230" s="10"/>
-      <c r="P230" s="10"/>
-      <c r="Q230" s="10"/>
-      <c r="R230" s="10" t="s">
-        <v>542</v>
+      <c r="N230" s="3">
+        <v>536.2</v>
+      </c>
+      <c r="O230" s="2">
+        <v>151</v>
+      </c>
+      <c r="P230" s="4">
+        <v>-34.2</v>
+      </c>
+      <c r="Q230" s="5">
+        <v>-6.813</v>
+      </c>
+      <c r="R230" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>64</v>
@@ -15574,7 +15782,7 @@
         <v>23</v>
       </c>
       <c r="M231" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N231" s="3">
         <v>654</v>
@@ -15594,7 +15802,7 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>209</v>
@@ -15603,7 +15811,7 @@
         <v>64</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E232" s="7">
         <v>1373.1</v>
@@ -15630,7 +15838,7 @@
         <v>33</v>
       </c>
       <c r="M232" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N232" s="7">
         <v>1359.1</v>
@@ -15650,16 +15858,16 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B233" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E233" s="3">
         <v>1278.8</v>
@@ -15686,7 +15894,7 @@
         <v>23</v>
       </c>
       <c r="M233" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N233" s="3">
         <v>1278.8</v>
@@ -15706,7 +15914,7 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>228</v>
@@ -15715,7 +15923,7 @@
         <v>64</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E234" s="7">
         <v>1280</v>
@@ -15742,7 +15950,7 @@
         <v>33</v>
       </c>
       <c r="M234" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N234" s="7">
         <v>1272.4</v>
@@ -15762,7 +15970,7 @@
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>110</v>
@@ -15771,7 +15979,7 @@
         <v>64</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E235" s="7">
         <v>122.43</v>
@@ -15798,7 +16006,7 @@
         <v>33</v>
       </c>
       <c r="M235" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N235" s="7">
         <v>120.69</v>
@@ -15818,16 +16026,16 @@
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E236" s="3">
         <v>3306.1</v>
@@ -15854,7 +16062,7 @@
         <v>23</v>
       </c>
       <c r="M236" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="N236" s="3">
         <v>3306.1</v>
@@ -15874,7 +16082,7 @@
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>98</v>
@@ -15883,7 +16091,7 @@
         <v>64</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E237" s="7">
         <v>507.65</v>
@@ -15910,7 +16118,7 @@
         <v>33</v>
       </c>
       <c r="M237" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N237" s="7">
         <v>504.65</v>
@@ -15930,16 +16138,16 @@
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B238" s="6" t="s">
         <v>563</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>564</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E238" s="7">
         <v>7808</v>
@@ -15966,7 +16174,7 @@
         <v>33</v>
       </c>
       <c r="M238" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N238" s="7">
         <v>7749</v>
@@ -15986,7 +16194,7 @@
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>81</v>
@@ -15995,7 +16203,7 @@
         <v>64</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E239" s="7">
         <v>1457.4</v>
@@ -16022,7 +16230,7 @@
         <v>33</v>
       </c>
       <c r="M239" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="N239" s="7">
         <v>1443</v>
@@ -16042,16 +16250,16 @@
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B240" s="6" t="s">
         <v>569</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>570</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E240" s="7">
         <v>96.29</v>
@@ -16078,7 +16286,7 @@
         <v>33</v>
       </c>
       <c r="M240" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="N240" s="7">
         <v>95.25</v>
@@ -16098,7 +16306,7 @@
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>149</v>
@@ -16107,7 +16315,7 @@
         <v>64</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E241" s="7">
         <v>963.5</v>
@@ -16134,7 +16342,7 @@
         <v>33</v>
       </c>
       <c r="M241" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N241" s="7">
         <v>951.3</v>
@@ -16154,7 +16362,7 @@
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>152</v>
@@ -16163,7 +16371,7 @@
         <v>64</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E242" s="3">
         <v>2091.2</v>
@@ -16190,7 +16398,7 @@
         <v>23</v>
       </c>
       <c r="M242" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N242" s="3">
         <v>2091.2</v>
@@ -16210,7 +16418,7 @@
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>19</v>
@@ -16219,7 +16427,7 @@
         <v>64</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E243" s="7">
         <v>9730</v>
@@ -16246,7 +16454,7 @@
         <v>33</v>
       </c>
       <c r="M243" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N243" s="7">
         <v>9606</v>
@@ -16266,7 +16474,7 @@
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>291</v>
@@ -16275,7 +16483,7 @@
         <v>64</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E244" s="7">
         <v>373.95</v>
@@ -16302,7 +16510,7 @@
         <v>33</v>
       </c>
       <c r="M244" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N244" s="7">
         <v>370.55</v>
@@ -16322,7 +16530,7 @@
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>347</v>
@@ -16331,7 +16539,7 @@
         <v>64</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E245" s="3">
         <v>526.05</v>
@@ -16358,7 +16566,7 @@
         <v>23</v>
       </c>
       <c r="M245" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N245" s="3">
         <v>526.05</v>
@@ -16378,7 +16586,7 @@
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>129</v>
@@ -16387,7 +16595,7 @@
         <v>64</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E246" s="7">
         <v>609.05</v>
@@ -16414,7 +16622,7 @@
         <v>33</v>
       </c>
       <c r="M246" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N246" s="7">
         <v>604.55</v>
@@ -16434,7 +16642,7 @@
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>363</v>
@@ -16443,7 +16651,7 @@
         <v>64</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E247" s="3">
         <v>401.2</v>
@@ -16470,7 +16678,7 @@
         <v>23</v>
       </c>
       <c r="M247" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N247" s="3">
         <v>401.2</v>
@@ -16490,7 +16698,7 @@
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>221</v>
@@ -16499,7 +16707,7 @@
         <v>64</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E248" s="7">
         <v>1242.6</v>
@@ -16546,7 +16754,7 @@
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>256</v>
@@ -16582,7 +16790,7 @@
         <v>23</v>
       </c>
       <c r="M249" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="N249" s="3">
         <v>1202.9</v>
@@ -16602,10 +16810,10 @@
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B250" s="6" t="s">
         <v>584</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>585</v>
       </c>
       <c r="C250" s="6" t="s">
         <v>64</v>
@@ -16638,7 +16846,7 @@
         <v>33</v>
       </c>
       <c r="M250" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N250" s="7">
         <v>1810.8</v>
@@ -16658,10 +16866,10 @@
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>64</v>
@@ -16694,7 +16902,7 @@
         <v>23</v>
       </c>
       <c r="M251" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N251" s="3">
         <v>2203.6</v>
@@ -16714,16 +16922,16 @@
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B252" s="6" t="s">
         <v>590</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>591</v>
       </c>
       <c r="C252" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E252" s="7">
         <v>4728.8</v>
@@ -16750,7 +16958,7 @@
         <v>33</v>
       </c>
       <c r="M252" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="N252" s="7">
         <v>4677.8</v>
@@ -16770,7 +16978,7 @@
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>36</v>
@@ -16779,7 +16987,7 @@
         <v>64</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E253" s="7">
         <v>70.31</v>
@@ -16806,7 +17014,7 @@
         <v>33</v>
       </c>
       <c r="M253" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N253" s="7">
         <v>69.85</v>
@@ -16826,10 +17034,10 @@
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B254" s="6" t="s">
         <v>597</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>598</v>
       </c>
       <c r="C254" s="6" t="s">
         <v>64</v>
@@ -16862,7 +17070,7 @@
         <v>33</v>
       </c>
       <c r="M254" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N254" s="7">
         <v>936.75</v>
@@ -16882,7 +17090,7 @@
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>117</v>
@@ -16918,7 +17126,7 @@
         <v>33</v>
       </c>
       <c r="M255" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N255" s="7">
         <v>159.54</v>
@@ -16938,7 +17146,7 @@
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>345</v>
@@ -16974,7 +17182,7 @@
         <v>33</v>
       </c>
       <c r="M256" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="N256" s="7">
         <v>1182.1</v>
@@ -16994,7 +17202,7 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>205</v>
@@ -17030,7 +17238,7 @@
         <v>33</v>
       </c>
       <c r="M257" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N257" s="7">
         <v>388.6</v>
@@ -17050,7 +17258,7 @@
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>341</v>
@@ -17086,7 +17294,7 @@
         <v>23</v>
       </c>
       <c r="M258" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="N258" s="3">
         <v>1649.4</v>
@@ -17106,10 +17314,10 @@
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="B259" s="6" t="s">
         <v>605</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>606</v>
       </c>
       <c r="C259" s="6" t="s">
         <v>64</v>
@@ -17142,7 +17350,7 @@
         <v>33</v>
       </c>
       <c r="M259" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="N259" s="7">
         <v>247.95</v>
@@ -17162,7 +17370,7 @@
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>87</v>
@@ -17171,7 +17379,7 @@
         <v>64</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E260" s="7">
         <v>1340.9</v>
@@ -17198,7 +17406,7 @@
         <v>33</v>
       </c>
       <c r="M260" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N260" s="7">
         <v>1316.9</v>
@@ -17218,7 +17426,7 @@
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>416</v>
@@ -17254,7 +17462,7 @@
         <v>23</v>
       </c>
       <c r="M261" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="N261" s="3">
         <v>965.7</v>
@@ -17274,7 +17482,7 @@
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>256</v>
@@ -17310,7 +17518,7 @@
         <v>23</v>
       </c>
       <c r="M262" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N262" s="3">
         <v>1220.3</v>
@@ -17330,7 +17538,7 @@
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>297</v>
@@ -17366,7 +17574,7 @@
         <v>33</v>
       </c>
       <c r="M263" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="N263" s="7">
         <v>1371.3</v>
@@ -17386,7 +17594,7 @@
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>246</v>
@@ -17422,7 +17630,7 @@
         <v>23</v>
       </c>
       <c r="M264" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N264" s="3">
         <v>460.35</v>
@@ -17442,7 +17650,7 @@
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>333</v>
@@ -17478,7 +17686,7 @@
         <v>23</v>
       </c>
       <c r="M265" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N265" s="3">
         <v>2094.4</v>
@@ -17498,10 +17706,10 @@
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="B266" s="6" t="s">
         <v>619</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>620</v>
       </c>
       <c r="C266" s="6" t="s">
         <v>20</v>
@@ -17534,7 +17742,7 @@
         <v>33</v>
       </c>
       <c r="M266" s="6" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N266" s="7">
         <v>2545.7</v>
@@ -17554,7 +17762,7 @@
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>259</v>
@@ -17590,7 +17798,7 @@
         <v>23</v>
       </c>
       <c r="M267" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N267" s="3">
         <v>8480</v>
@@ -17610,7 +17818,7 @@
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>134</v>
@@ -17646,7 +17854,7 @@
         <v>23</v>
       </c>
       <c r="M268" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N268" s="3">
         <v>1390.3</v>
@@ -17666,7 +17874,7 @@
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>237</v>
@@ -17702,7 +17910,7 @@
         <v>23</v>
       </c>
       <c r="M269" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N269" s="3">
         <v>373.1</v>
@@ -17722,7 +17930,7 @@
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>193</v>
@@ -17731,7 +17939,7 @@
         <v>64</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E270" s="7">
         <v>4344.9</v>
@@ -17758,7 +17966,7 @@
         <v>33</v>
       </c>
       <c r="M270" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="N270" s="7">
         <v>4334.9</v>
@@ -17778,7 +17986,7 @@
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>520</v>
@@ -17787,7 +17995,7 @@
         <v>20</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E271" s="3">
         <v>3903.9</v>
@@ -17814,7 +18022,7 @@
         <v>23</v>
       </c>
       <c r="M271" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N271" s="3">
         <v>3861.2</v>
@@ -17834,7 +18042,7 @@
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>84</v>
@@ -17843,7 +18051,7 @@
         <v>64</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E272" s="7">
         <v>1885.1</v>
@@ -17870,7 +18078,7 @@
         <v>33</v>
       </c>
       <c r="M272" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="N272" s="7">
         <v>1873.1</v>
@@ -17890,7 +18098,7 @@
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>183</v>
@@ -17899,7 +18107,7 @@
         <v>20</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E273" s="3">
         <v>6013</v>
@@ -17926,7 +18134,7 @@
         <v>23</v>
       </c>
       <c r="M273" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="N273" s="3">
         <v>5990.5</v>
@@ -17946,7 +18154,7 @@
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>333</v>
@@ -17955,7 +18163,7 @@
         <v>20</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E274" s="3">
         <v>2126.1</v>
@@ -17982,7 +18190,7 @@
         <v>23</v>
       </c>
       <c r="M274" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N274" s="3">
         <v>2118.3</v>
@@ -18002,7 +18210,7 @@
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>115</v>
@@ -18011,7 +18219,7 @@
         <v>20</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E275" s="3">
         <v>117.6</v>
@@ -18038,7 +18246,7 @@
         <v>23</v>
       </c>
       <c r="M275" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N275" s="3">
         <v>116.64</v>
@@ -18058,7 +18266,7 @@
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>180</v>
@@ -18067,7 +18275,7 @@
         <v>64</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E276" s="3">
         <v>2190.3</v>
@@ -18094,7 +18302,7 @@
         <v>23</v>
       </c>
       <c r="M276" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N276" s="3">
         <v>2190.3</v>
@@ -18114,7 +18322,7 @@
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>282</v>
@@ -18123,7 +18331,7 @@
         <v>20</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E277" s="3">
         <v>790.15</v>
@@ -18150,7 +18358,7 @@
         <v>23</v>
       </c>
       <c r="M277" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="N277" s="3">
         <v>784.05</v>
@@ -18158,10 +18366,10 @@
       <c r="O277" s="2">
         <v>1</v>
       </c>
-      <c r="P277" s="12">
+      <c r="P277" s="10">
         <v>1</v>
       </c>
-      <c r="Q277" s="13">
+      <c r="Q277" s="11">
         <v>0.128</v>
       </c>
       <c r="R277" s="2" t="s">
@@ -18170,7 +18378,7 @@
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>363</v>
@@ -18206,7 +18414,7 @@
         <v>23</v>
       </c>
       <c r="M278" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="N278" s="3">
         <v>412.2</v>
@@ -18226,7 +18434,7 @@
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>205</v>
@@ -18235,7 +18443,7 @@
         <v>64</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E279" s="3">
         <v>391.9</v>
@@ -18262,7 +18470,7 @@
         <v>23</v>
       </c>
       <c r="M279" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N279" s="3">
         <v>391.9</v>
@@ -18282,16 +18490,16 @@
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E280" s="3">
         <v>1202</v>
@@ -18318,7 +18526,7 @@
         <v>23</v>
       </c>
       <c r="M280" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="N280" s="3">
         <v>1202</v>
@@ -18338,16 +18546,16 @@
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E281" s="3">
         <v>570</v>
@@ -18374,7 +18582,7 @@
         <v>23</v>
       </c>
       <c r="M281" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N281" s="3">
         <v>570</v>
@@ -18394,7 +18602,7 @@
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>180</v>
@@ -18403,7 +18611,7 @@
         <v>64</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E282" s="7">
         <v>2136</v>
@@ -18430,7 +18638,7 @@
         <v>33</v>
       </c>
       <c r="M282" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="N282" s="7">
         <v>2112</v>
@@ -18449,48 +18657,48 @@
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A283" s="10" t="s">
+      <c r="A283" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C283" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D283" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="B283" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C283" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D283" s="10" t="s">
+      <c r="E283" s="13">
+        <v>7673</v>
+      </c>
+      <c r="F283" s="13">
+        <v>7305.5</v>
+      </c>
+      <c r="G283" s="13">
+        <v>7312.5</v>
+      </c>
+      <c r="H283" s="13">
+        <v>7312.5</v>
+      </c>
+      <c r="I283" s="13">
+        <v>7673</v>
+      </c>
+      <c r="J283" s="13">
+        <v>6952</v>
+      </c>
+      <c r="K283" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L283" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="E283" s="11">
-        <v>7673</v>
-      </c>
-      <c r="F283" s="11">
-        <v>7305.5</v>
-      </c>
-      <c r="G283" s="11">
-        <v>7312.5</v>
-      </c>
-      <c r="H283" s="11">
-        <v>7312.5</v>
-      </c>
-      <c r="I283" s="11">
-        <v>7673</v>
-      </c>
-      <c r="J283" s="11">
-        <v>6952</v>
-      </c>
-      <c r="K283" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L283" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M283" s="10"/>
-      <c r="N283" s="10"/>
-      <c r="O283" s="10"/>
-      <c r="P283" s="10"/>
-      <c r="Q283" s="10"/>
-      <c r="R283" s="10" t="s">
+      <c r="M283" s="12"/>
+      <c r="N283" s="12"/>
+      <c r="O283" s="12"/>
+      <c r="P283" s="12"/>
+      <c r="Q283" s="12"/>
+      <c r="R283" s="12" t="s">
         <v>650</v>
       </c>
     </row>
@@ -18588,7 +18796,7 @@
         <v>23</v>
       </c>
       <c r="M285" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N285" s="3">
         <v>176</v>
@@ -18652,10 +18860,10 @@
       <c r="O286" s="2">
         <v>1</v>
       </c>
-      <c r="P286" s="12">
+      <c r="P286" s="10">
         <v>18.6</v>
       </c>
-      <c r="Q286" s="13">
+      <c r="Q286" s="11">
         <v>0.689</v>
       </c>
       <c r="R286" s="2" t="s">
@@ -18729,7 +18937,7 @@
         <v>20</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E288" s="7">
         <v>1270</v>
@@ -18785,7 +18993,7 @@
         <v>20</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E289" s="7">
         <v>2832</v>
@@ -18841,7 +19049,7 @@
         <v>20</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E290" s="7">
         <v>2177.8</v>
@@ -18897,7 +19105,7 @@
         <v>64</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E291" s="3">
         <v>957.75</v>
@@ -18943,48 +19151,48 @@
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A292" s="10" t="s">
+      <c r="A292" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="B292" s="10" t="s">
+      <c r="B292" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C292" s="10" t="s">
+      <c r="C292" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D292" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="E292" s="11">
+      <c r="D292" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="E292" s="13">
         <v>4432</v>
       </c>
-      <c r="F292" s="11">
+      <c r="F292" s="13">
         <v>4389</v>
       </c>
-      <c r="G292" s="11">
+      <c r="G292" s="13">
         <v>4428.5</v>
       </c>
-      <c r="H292" s="11">
+      <c r="H292" s="13">
         <v>4432.6</v>
       </c>
-      <c r="I292" s="11">
+      <c r="I292" s="13">
         <v>4389</v>
       </c>
-      <c r="J292" s="11">
+      <c r="J292" s="13">
         <v>4476.2</v>
       </c>
-      <c r="K292" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L292" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M292" s="10"/>
-      <c r="N292" s="10"/>
-      <c r="O292" s="10"/>
-      <c r="P292" s="10"/>
-      <c r="Q292" s="10"/>
-      <c r="R292" s="10" t="s">
+      <c r="K292" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L292" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M292" s="12"/>
+      <c r="N292" s="12"/>
+      <c r="O292" s="12"/>
+      <c r="P292" s="12"/>
+      <c r="Q292" s="12"/>
+      <c r="R292" s="12" t="s">
         <v>673</v>
       </c>
     </row>
@@ -19105,7 +19313,7 @@
         <v>677</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C295" s="6" t="s">
         <v>64</v>
@@ -19493,920 +19701,3270 @@
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A302" s="10" t="s">
+      <c r="A302" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B302" s="10" t="s">
+      <c r="B302" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C302" s="10" t="s">
+      <c r="C302" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D302" s="10" t="s">
+      <c r="D302" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="E302" s="11">
+      <c r="E302" s="3">
         <v>101.05</v>
       </c>
-      <c r="F302" s="11">
+      <c r="F302" s="3">
         <v>99.93</v>
       </c>
-      <c r="G302" s="11">
+      <c r="G302" s="3">
         <v>101</v>
       </c>
-      <c r="H302" s="11">
+      <c r="H302" s="3">
         <v>101</v>
       </c>
-      <c r="I302" s="11">
+      <c r="I302" s="3">
         <v>99.93</v>
       </c>
-      <c r="J302" s="11">
+      <c r="J302" s="3">
         <v>102.07</v>
       </c>
-      <c r="K302" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L302" s="10" t="s">
+      <c r="K302" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L302" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M302" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="N302" s="3">
+        <v>99.93</v>
+      </c>
+      <c r="O302" s="2">
+        <v>11</v>
+      </c>
+      <c r="P302" s="4">
+        <v>-1.07</v>
+      </c>
+      <c r="Q302" s="5">
+        <v>-1.059</v>
+      </c>
+      <c r="R302" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A303" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="E303" s="7">
+        <v>6825.5</v>
+      </c>
+      <c r="F303" s="7">
+        <v>6798.5</v>
+      </c>
+      <c r="G303" s="7">
+        <v>6824.5</v>
+      </c>
+      <c r="H303" s="7">
+        <v>6824</v>
+      </c>
+      <c r="I303" s="7">
+        <v>6798.5</v>
+      </c>
+      <c r="J303" s="7">
+        <v>6849.5</v>
+      </c>
+      <c r="K303" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L303" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M303" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="N303" s="7">
+        <v>6849.5</v>
+      </c>
+      <c r="O303" s="6">
+        <v>2</v>
+      </c>
+      <c r="P303" s="8">
+        <v>25.5</v>
+      </c>
+      <c r="Q303" s="9">
+        <v>0.374</v>
+      </c>
+      <c r="R303" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A304" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="E304" s="7">
+        <v>145.4</v>
+      </c>
+      <c r="F304" s="7">
+        <v>144.4</v>
+      </c>
+      <c r="G304" s="7">
+        <v>144.83</v>
+      </c>
+      <c r="H304" s="7">
+        <v>144.83</v>
+      </c>
+      <c r="I304" s="7">
+        <v>144.4</v>
+      </c>
+      <c r="J304" s="7">
+        <v>145.26</v>
+      </c>
+      <c r="K304" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L304" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M304" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="N304" s="7">
+        <v>145.26</v>
+      </c>
+      <c r="O304" s="6">
+        <v>1</v>
+      </c>
+      <c r="P304" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="Q304" s="9">
+        <v>0.297</v>
+      </c>
+      <c r="R304" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E305" s="3">
+        <v>2601.5</v>
+      </c>
+      <c r="F305" s="3">
+        <v>2589</v>
+      </c>
+      <c r="G305" s="3">
+        <v>2596.1</v>
+      </c>
+      <c r="H305" s="3">
+        <v>2596</v>
+      </c>
+      <c r="I305" s="3">
+        <v>2589</v>
+      </c>
+      <c r="J305" s="3">
+        <v>2603</v>
+      </c>
+      <c r="K305" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L305" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M305" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="N305" s="3">
+        <v>2589</v>
+      </c>
+      <c r="O305" s="2">
+        <v>1</v>
+      </c>
+      <c r="P305" s="4">
+        <v>-7</v>
+      </c>
+      <c r="Q305" s="5">
+        <v>-0.27</v>
+      </c>
+      <c r="R305" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E306" s="3">
+        <v>1408.4</v>
+      </c>
+      <c r="F306" s="3">
+        <v>1401.8</v>
+      </c>
+      <c r="G306" s="3">
+        <v>1406.2</v>
+      </c>
+      <c r="H306" s="3">
+        <v>1405.9</v>
+      </c>
+      <c r="I306" s="3">
+        <v>1401.8</v>
+      </c>
+      <c r="J306" s="3">
+        <v>1410</v>
+      </c>
+      <c r="K306" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L306" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M306" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="N306" s="3">
+        <v>1401.8</v>
+      </c>
+      <c r="O306" s="2">
+        <v>1</v>
+      </c>
+      <c r="P306" s="4">
+        <v>-4.1</v>
+      </c>
+      <c r="Q306" s="5">
+        <v>-0.292</v>
+      </c>
+      <c r="R306" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A307" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="E307" s="7">
+        <v>723.7</v>
+      </c>
+      <c r="F307" s="7">
+        <v>718.15</v>
+      </c>
+      <c r="G307" s="7">
+        <v>722.15</v>
+      </c>
+      <c r="H307" s="7">
+        <v>722.15</v>
+      </c>
+      <c r="I307" s="7">
+        <v>718.15</v>
+      </c>
+      <c r="J307" s="7">
+        <v>726.15</v>
+      </c>
+      <c r="K307" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L307" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M307" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="N307" s="7">
+        <v>726.15</v>
+      </c>
+      <c r="O307" s="6">
+        <v>1</v>
+      </c>
+      <c r="P307" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q307" s="9">
+        <v>0.554</v>
+      </c>
+      <c r="R307" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A308" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E308" s="7">
+        <v>1668</v>
+      </c>
+      <c r="F308" s="7">
+        <v>1658</v>
+      </c>
+      <c r="G308" s="7">
+        <v>1665</v>
+      </c>
+      <c r="H308" s="7">
+        <v>1681.8</v>
+      </c>
+      <c r="I308" s="7">
+        <v>1658</v>
+      </c>
+      <c r="J308" s="7">
+        <v>1705.6</v>
+      </c>
+      <c r="K308" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L308" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M308" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="N308" s="7">
+        <v>1705.6</v>
+      </c>
+      <c r="O308" s="6">
+        <v>9</v>
+      </c>
+      <c r="P308" s="8">
+        <v>23.8</v>
+      </c>
+      <c r="Q308" s="9">
+        <v>1.415</v>
+      </c>
+      <c r="R308" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A309" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E309" s="7">
+        <v>731.95</v>
+      </c>
+      <c r="F309" s="7">
+        <v>725.95</v>
+      </c>
+      <c r="G309" s="7">
+        <v>730</v>
+      </c>
+      <c r="H309" s="7">
+        <v>730.4</v>
+      </c>
+      <c r="I309" s="7">
+        <v>725.95</v>
+      </c>
+      <c r="J309" s="7">
+        <v>734.85</v>
+      </c>
+      <c r="K309" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L309" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M309" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="M302" s="10"/>
-      <c r="N302" s="10"/>
-      <c r="O302" s="10"/>
-      <c r="P302" s="10"/>
-      <c r="Q302" s="10"/>
-      <c r="R302" s="10" t="s">
+      <c r="N309" s="7">
+        <v>734.85</v>
+      </c>
+      <c r="O309" s="6">
+        <v>1</v>
+      </c>
+      <c r="P309" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="Q309" s="9">
+        <v>0.609</v>
+      </c>
+      <c r="R309" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A310" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E310" s="7">
+        <v>1254</v>
+      </c>
+      <c r="F310" s="7">
+        <v>1247.1</v>
+      </c>
+      <c r="G310" s="7">
+        <v>1253.5</v>
+      </c>
+      <c r="H310" s="7">
+        <v>1249</v>
+      </c>
+      <c r="I310" s="7">
+        <v>1247.1</v>
+      </c>
+      <c r="J310" s="7">
+        <v>1250.9</v>
+      </c>
+      <c r="K310" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L310" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M310" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N310" s="7">
+        <v>1250.9</v>
+      </c>
+      <c r="O310" s="6">
+        <v>1</v>
+      </c>
+      <c r="P310" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="Q310" s="9">
+        <v>0.152</v>
+      </c>
+      <c r="R310" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A311" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E311" s="3">
+        <v>1631</v>
+      </c>
+      <c r="F311" s="3">
+        <v>1619</v>
+      </c>
+      <c r="G311" s="3">
+        <v>1631</v>
+      </c>
+      <c r="H311" s="3">
+        <v>1620.1</v>
+      </c>
+      <c r="I311" s="3">
+        <v>1619</v>
+      </c>
+      <c r="J311" s="3">
+        <v>1621.2</v>
+      </c>
+      <c r="K311" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L311" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M311" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="N311" s="3">
+        <v>1619</v>
+      </c>
+      <c r="O311" s="2">
+        <v>1</v>
+      </c>
+      <c r="P311" s="4">
+        <v>-1.1</v>
+      </c>
+      <c r="Q311" s="5">
+        <v>-0.068</v>
+      </c>
+      <c r="R311" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E312" s="3">
+        <v>2210.7</v>
+      </c>
+      <c r="F312" s="3">
+        <v>2191.4</v>
+      </c>
+      <c r="G312" s="3">
+        <v>2210.4</v>
+      </c>
+      <c r="H312" s="3">
+        <v>2198.3</v>
+      </c>
+      <c r="I312" s="3">
+        <v>2191.4</v>
+      </c>
+      <c r="J312" s="3">
+        <v>2205.2</v>
+      </c>
+      <c r="K312" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L312" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M312" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="N312" s="3">
+        <v>2191.4</v>
+      </c>
+      <c r="O312" s="2">
+        <v>1</v>
+      </c>
+      <c r="P312" s="4">
+        <v>-6.9</v>
+      </c>
+      <c r="Q312" s="5">
+        <v>-0.314</v>
+      </c>
+      <c r="R312" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A313" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E313" s="7">
+        <v>587</v>
+      </c>
+      <c r="F313" s="7">
+        <v>583.05</v>
+      </c>
+      <c r="G313" s="7">
+        <v>585.3</v>
+      </c>
+      <c r="H313" s="7">
+        <v>585.3</v>
+      </c>
+      <c r="I313" s="7">
+        <v>583.05</v>
+      </c>
+      <c r="J313" s="7">
+        <v>587.55</v>
+      </c>
+      <c r="K313" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L313" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M313" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N313" s="7">
+        <v>587.55</v>
+      </c>
+      <c r="O313" s="6">
+        <v>1</v>
+      </c>
+      <c r="P313" s="8">
+        <v>2.25</v>
+      </c>
+      <c r="Q313" s="9">
+        <v>0.384</v>
+      </c>
+      <c r="R313" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A314" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E314" s="7">
+        <v>427.7</v>
+      </c>
+      <c r="F314" s="7">
+        <v>424.15</v>
+      </c>
+      <c r="G314" s="7">
+        <v>426.5</v>
+      </c>
+      <c r="H314" s="7">
+        <v>424.85</v>
+      </c>
+      <c r="I314" s="7">
+        <v>424.15</v>
+      </c>
+      <c r="J314" s="7">
+        <v>425.55</v>
+      </c>
+      <c r="K314" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L314" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M314" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N314" s="7">
+        <v>425.55</v>
+      </c>
+      <c r="O314" s="6">
+        <v>1</v>
+      </c>
+      <c r="P314" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="Q314" s="9">
+        <v>0.165</v>
+      </c>
+      <c r="R314" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E315" s="3">
+        <v>258.4</v>
+      </c>
+      <c r="F315" s="3">
+        <v>256.15</v>
+      </c>
+      <c r="G315" s="3">
+        <v>257.05</v>
+      </c>
+      <c r="H315" s="3">
+        <v>257.9</v>
+      </c>
+      <c r="I315" s="3">
+        <v>256.15</v>
+      </c>
+      <c r="J315" s="3">
+        <v>259.65</v>
+      </c>
+      <c r="K315" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L315" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M315" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="N315" s="3">
+        <v>256.15</v>
+      </c>
+      <c r="O315" s="2">
+        <v>8</v>
+      </c>
+      <c r="P315" s="4">
+        <v>-1.75</v>
+      </c>
+      <c r="Q315" s="5">
+        <v>-0.679</v>
+      </c>
+      <c r="R315" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A316" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E316" s="7">
+        <v>97</v>
+      </c>
+      <c r="F316" s="7">
+        <v>95.27</v>
+      </c>
+      <c r="G316" s="7">
+        <v>96.35</v>
+      </c>
+      <c r="H316" s="7">
+        <v>95.53</v>
+      </c>
+      <c r="I316" s="7">
+        <v>95.27</v>
+      </c>
+      <c r="J316" s="7">
+        <v>95.79</v>
+      </c>
+      <c r="K316" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L316" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M316" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N316" s="7">
+        <v>95.79</v>
+      </c>
+      <c r="O316" s="6">
+        <v>1</v>
+      </c>
+      <c r="P316" s="8">
+        <v>0.26</v>
+      </c>
+      <c r="Q316" s="9">
+        <v>0.272</v>
+      </c>
+      <c r="R316" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E317" s="7">
+        <v>117.5</v>
+      </c>
+      <c r="F317" s="7">
+        <v>116.55</v>
+      </c>
+      <c r="G317" s="7">
+        <v>117.31</v>
+      </c>
+      <c r="H317" s="7">
+        <v>117.31</v>
+      </c>
+      <c r="I317" s="7">
+        <v>116.55</v>
+      </c>
+      <c r="J317" s="7">
+        <v>118.07</v>
+      </c>
+      <c r="K317" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L317" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M317" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N317" s="7">
+        <v>118.07</v>
+      </c>
+      <c r="O317" s="6">
+        <v>1</v>
+      </c>
+      <c r="P317" s="8">
+        <v>0.76</v>
+      </c>
+      <c r="Q317" s="9">
+        <v>0.648</v>
+      </c>
+      <c r="R317" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A318" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E318" s="7">
+        <v>1041.9</v>
+      </c>
+      <c r="F318" s="7">
+        <v>1036.1</v>
+      </c>
+      <c r="G318" s="7">
+        <v>1041.9</v>
+      </c>
+      <c r="H318" s="7">
+        <v>1043.7</v>
+      </c>
+      <c r="I318" s="7">
+        <v>1036.1</v>
+      </c>
+      <c r="J318" s="7">
+        <v>1051.3</v>
+      </c>
+      <c r="K318" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L318" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M318" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="N318" s="7">
+        <v>1051.3</v>
+      </c>
+      <c r="O318" s="6">
+        <v>3</v>
+      </c>
+      <c r="P318" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="Q318" s="9">
+        <v>0.728</v>
+      </c>
+      <c r="R318" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A319" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E319" s="7">
+        <v>2346.3</v>
+      </c>
+      <c r="F319" s="7">
+        <v>2332.8</v>
+      </c>
+      <c r="G319" s="7">
+        <v>2345</v>
+      </c>
+      <c r="H319" s="7">
+        <v>2350</v>
+      </c>
+      <c r="I319" s="7">
+        <v>2332.8</v>
+      </c>
+      <c r="J319" s="7">
+        <v>2367.2</v>
+      </c>
+      <c r="K319" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L319" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M319" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="N319" s="7">
+        <v>2367.2</v>
+      </c>
+      <c r="O319" s="6">
+        <v>3</v>
+      </c>
+      <c r="P319" s="8">
+        <v>17.2</v>
+      </c>
+      <c r="Q319" s="9">
+        <v>0.732</v>
+      </c>
+      <c r="R319" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A320" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E320" s="7">
+        <v>87.5</v>
+      </c>
+      <c r="F320" s="7">
+        <v>86.77</v>
+      </c>
+      <c r="G320" s="7">
+        <v>87.2</v>
+      </c>
+      <c r="H320" s="7">
+        <v>87</v>
+      </c>
+      <c r="I320" s="7">
+        <v>86.77</v>
+      </c>
+      <c r="J320" s="7">
+        <v>87.23</v>
+      </c>
+      <c r="K320" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L320" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M320" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N320" s="7">
+        <v>87.23</v>
+      </c>
+      <c r="O320" s="6">
+        <v>1</v>
+      </c>
+      <c r="P320" s="8">
+        <v>0.23</v>
+      </c>
+      <c r="Q320" s="9">
+        <v>0.264</v>
+      </c>
+      <c r="R320" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A321" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E321" s="7">
+        <v>1506</v>
+      </c>
+      <c r="F321" s="7">
+        <v>1489</v>
+      </c>
+      <c r="G321" s="7">
+        <v>1506</v>
+      </c>
+      <c r="H321" s="7">
+        <v>1501</v>
+      </c>
+      <c r="I321" s="7">
+        <v>1489</v>
+      </c>
+      <c r="J321" s="7">
+        <v>1513</v>
+      </c>
+      <c r="K321" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L321" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M321" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="N321" s="7">
+        <v>1513</v>
+      </c>
+      <c r="O321" s="6">
+        <v>2</v>
+      </c>
+      <c r="P321" s="8">
+        <v>12</v>
+      </c>
+      <c r="Q321" s="9">
+        <v>0.799</v>
+      </c>
+      <c r="R321" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A322" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E322" s="7">
+        <v>797</v>
+      </c>
+      <c r="F322" s="7">
+        <v>788.95</v>
+      </c>
+      <c r="G322" s="7">
+        <v>797</v>
+      </c>
+      <c r="H322" s="7">
+        <v>790</v>
+      </c>
+      <c r="I322" s="7">
+        <v>788.95</v>
+      </c>
+      <c r="J322" s="7">
+        <v>791.05</v>
+      </c>
+      <c r="K322" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L322" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M322" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N322" s="7">
+        <v>791.05</v>
+      </c>
+      <c r="O322" s="6">
+        <v>1</v>
+      </c>
+      <c r="P322" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="Q322" s="9">
+        <v>0.133</v>
+      </c>
+      <c r="R322" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E323" s="3">
+        <v>1031.6</v>
+      </c>
+      <c r="F323" s="3">
+        <v>1010</v>
+      </c>
+      <c r="G323" s="3">
+        <v>1027.8</v>
+      </c>
+      <c r="H323" s="3">
+        <v>1028</v>
+      </c>
+      <c r="I323" s="3">
+        <v>1010</v>
+      </c>
+      <c r="J323" s="3">
+        <v>1046</v>
+      </c>
+      <c r="K323" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L323" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M323" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="N323" s="3">
+        <v>1010</v>
+      </c>
+      <c r="O323" s="2">
+        <v>5</v>
+      </c>
+      <c r="P323" s="4">
+        <v>-18</v>
+      </c>
+      <c r="Q323" s="5">
+        <v>-1.751</v>
+      </c>
+      <c r="R323" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A324" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E324" s="3">
+        <v>227.7</v>
+      </c>
+      <c r="F324" s="3">
+        <v>224.61</v>
+      </c>
+      <c r="G324" s="3">
+        <v>226.09</v>
+      </c>
+      <c r="H324" s="3">
+        <v>226.22</v>
+      </c>
+      <c r="I324" s="3">
+        <v>224.61</v>
+      </c>
+      <c r="J324" s="3">
+        <v>227.83</v>
+      </c>
+      <c r="K324" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L324" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M324" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="N324" s="3">
+        <v>224.61</v>
+      </c>
+      <c r="O324" s="2">
+        <v>2</v>
+      </c>
+      <c r="P324" s="4">
+        <v>-1.61</v>
+      </c>
+      <c r="Q324" s="5">
+        <v>-0.712</v>
+      </c>
+      <c r="R324" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A325" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="E325" s="7">
+        <v>451.8</v>
+      </c>
+      <c r="F325" s="7">
+        <v>445.15</v>
+      </c>
+      <c r="G325" s="7">
+        <v>447.1</v>
+      </c>
+      <c r="H325" s="7">
+        <v>447.05</v>
+      </c>
+      <c r="I325" s="7">
+        <v>445.15</v>
+      </c>
+      <c r="J325" s="7">
+        <v>448.95</v>
+      </c>
+      <c r="K325" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L325" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M325" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="N325" s="7">
+        <v>448.95</v>
+      </c>
+      <c r="O325" s="6">
+        <v>4</v>
+      </c>
+      <c r="P325" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="Q325" s="9">
+        <v>0.425</v>
+      </c>
+      <c r="R325" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A326" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D326" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="E326" s="7">
+        <v>680.5</v>
+      </c>
+      <c r="F326" s="7">
+        <v>671.9</v>
+      </c>
+      <c r="G326" s="7">
+        <v>674.1</v>
+      </c>
+      <c r="H326" s="7">
+        <v>674.45</v>
+      </c>
+      <c r="I326" s="7">
+        <v>671.9</v>
+      </c>
+      <c r="J326" s="7">
+        <v>677</v>
+      </c>
+      <c r="K326" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L326" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M326" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="N326" s="7">
+        <v>677</v>
+      </c>
+      <c r="O326" s="6">
+        <v>1</v>
+      </c>
+      <c r="P326" s="8">
+        <v>2.55</v>
+      </c>
+      <c r="Q326" s="9">
+        <v>0.378</v>
+      </c>
+      <c r="R326" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A327" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="E327" s="7">
+        <v>928</v>
+      </c>
+      <c r="F327" s="7">
+        <v>900</v>
+      </c>
+      <c r="G327" s="7">
+        <v>924.65</v>
+      </c>
+      <c r="H327" s="7">
+        <v>924.75</v>
+      </c>
+      <c r="I327" s="7">
+        <v>900</v>
+      </c>
+      <c r="J327" s="7">
+        <v>949.5</v>
+      </c>
+      <c r="K327" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L327" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M327" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="N327" s="7">
+        <v>949.5</v>
+      </c>
+      <c r="O327" s="6">
+        <v>20</v>
+      </c>
+      <c r="P327" s="8">
+        <v>24.75</v>
+      </c>
+      <c r="Q327" s="9">
+        <v>2.676</v>
+      </c>
+      <c r="R327" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A328" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="B328" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="C328" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D328" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="E328" s="13">
+        <v>1404.6</v>
+      </c>
+      <c r="F328" s="13">
+        <v>1359.8</v>
+      </c>
+      <c r="G328" s="13">
+        <v>1397.4</v>
+      </c>
+      <c r="H328" s="13">
+        <v>1397.4</v>
+      </c>
+      <c r="I328" s="13">
+        <v>1359.8</v>
+      </c>
+      <c r="J328" s="13">
+        <v>1435</v>
+      </c>
+      <c r="K328" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L328" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M328" s="12"/>
+      <c r="N328" s="12"/>
+      <c r="O328" s="12"/>
+      <c r="P328" s="12"/>
+      <c r="Q328" s="12"/>
+      <c r="R328" s="12" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A329" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E329" s="3">
+        <v>5766</v>
+      </c>
+      <c r="F329" s="3">
+        <v>5700.5</v>
+      </c>
+      <c r="G329" s="3">
+        <v>5750</v>
+      </c>
+      <c r="H329" s="3">
+        <v>5745</v>
+      </c>
+      <c r="I329" s="3">
+        <v>5700.5</v>
+      </c>
+      <c r="J329" s="3">
+        <v>5789.5</v>
+      </c>
+      <c r="K329" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L329" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M329" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="N329" s="3">
+        <v>5700.5</v>
+      </c>
+      <c r="O329" s="2">
+        <v>1</v>
+      </c>
+      <c r="P329" s="4">
+        <v>-44.5</v>
+      </c>
+      <c r="Q329" s="5">
+        <v>-0.775</v>
+      </c>
+      <c r="R329" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A330" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E330" s="3">
+        <v>972.9</v>
+      </c>
+      <c r="F330" s="3">
+        <v>957</v>
+      </c>
+      <c r="G330" s="3">
+        <v>972.8</v>
+      </c>
+      <c r="H330" s="3">
+        <v>972.8</v>
+      </c>
+      <c r="I330" s="3">
+        <v>957</v>
+      </c>
+      <c r="J330" s="3">
+        <v>988.6</v>
+      </c>
+      <c r="K330" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L330" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M330" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="N330" s="3">
+        <v>957</v>
+      </c>
+      <c r="O330" s="2">
+        <v>14</v>
+      </c>
+      <c r="P330" s="4">
+        <v>-15.8</v>
+      </c>
+      <c r="Q330" s="5">
+        <v>-1.624</v>
+      </c>
+      <c r="R330" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A331" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E331" s="3">
+        <v>182.1</v>
+      </c>
+      <c r="F331" s="3">
+        <v>179.09</v>
+      </c>
+      <c r="G331" s="3">
+        <v>181.31</v>
+      </c>
+      <c r="H331" s="3">
+        <v>181.31</v>
+      </c>
+      <c r="I331" s="3">
+        <v>179.09</v>
+      </c>
+      <c r="J331" s="3">
+        <v>183.53</v>
+      </c>
+      <c r="K331" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L331" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M331" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="N331" s="3">
+        <v>179.09</v>
+      </c>
+      <c r="O331" s="2">
+        <v>4</v>
+      </c>
+      <c r="P331" s="4">
+        <v>-2.22</v>
+      </c>
+      <c r="Q331" s="5">
+        <v>-1.224</v>
+      </c>
+      <c r="R331" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A332" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E332" s="3">
+        <v>101.79</v>
+      </c>
+      <c r="F332" s="3">
+        <v>100.44</v>
+      </c>
+      <c r="G332" s="3">
+        <v>101.21</v>
+      </c>
+      <c r="H332" s="3">
+        <v>101.21</v>
+      </c>
+      <c r="I332" s="3">
+        <v>100.44</v>
+      </c>
+      <c r="J332" s="3">
+        <v>101.98</v>
+      </c>
+      <c r="K332" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L332" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M332" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="N332" s="3">
+        <v>100.44</v>
+      </c>
+      <c r="O332" s="2">
+        <v>2</v>
+      </c>
+      <c r="P332" s="4">
+        <v>-0.77</v>
+      </c>
+      <c r="Q332" s="5">
+        <v>-0.761</v>
+      </c>
+      <c r="R332" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A333" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E333" s="3">
+        <v>4502.9</v>
+      </c>
+      <c r="F333" s="3">
+        <v>4366</v>
+      </c>
+      <c r="G333" s="3">
+        <v>4498.7</v>
+      </c>
+      <c r="H333" s="3">
+        <v>4498.7</v>
+      </c>
+      <c r="I333" s="3">
+        <v>4366</v>
+      </c>
+      <c r="J333" s="3">
+        <v>4631.4</v>
+      </c>
+      <c r="K333" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L333" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M333" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="N333" s="3">
+        <v>4366</v>
+      </c>
+      <c r="O333" s="2">
+        <v>14</v>
+      </c>
+      <c r="P333" s="4">
+        <v>-132.7</v>
+      </c>
+      <c r="Q333" s="5">
+        <v>-2.95</v>
+      </c>
+      <c r="R333" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A334" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E334" s="3">
+        <v>1201.5</v>
+      </c>
+      <c r="F334" s="3">
+        <v>1186.1</v>
+      </c>
+      <c r="G334" s="3">
+        <v>1199</v>
+      </c>
+      <c r="H334" s="3">
+        <v>1198.8</v>
+      </c>
+      <c r="I334" s="3">
+        <v>1186.1</v>
+      </c>
+      <c r="J334" s="3">
+        <v>1211.5</v>
+      </c>
+      <c r="K334" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L334" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M334" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="N334" s="3">
+        <v>1186.1</v>
+      </c>
+      <c r="O334" s="2">
+        <v>19</v>
+      </c>
+      <c r="P334" s="4">
+        <v>-12.7</v>
+      </c>
+      <c r="Q334" s="5">
+        <v>-1.059</v>
+      </c>
+      <c r="R334" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A335" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E335" s="3">
+        <v>498.5</v>
+      </c>
+      <c r="F335" s="3">
+        <v>488.8</v>
+      </c>
+      <c r="G335" s="3">
+        <v>497.6</v>
+      </c>
+      <c r="H335" s="3">
+        <v>497.8</v>
+      </c>
+      <c r="I335" s="3">
+        <v>488.8</v>
+      </c>
+      <c r="J335" s="3">
+        <v>506.8</v>
+      </c>
+      <c r="K335" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L335" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M335" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="N335" s="3">
+        <v>488.8</v>
+      </c>
+      <c r="O335" s="2">
+        <v>21</v>
+      </c>
+      <c r="P335" s="4">
+        <v>-9</v>
+      </c>
+      <c r="Q335" s="5">
+        <v>-1.808</v>
+      </c>
+      <c r="R335" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A336" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="E336" s="7">
+        <v>3302.4</v>
+      </c>
+      <c r="F336" s="7">
+        <v>3260.6</v>
+      </c>
+      <c r="G336" s="7">
+        <v>3265</v>
+      </c>
+      <c r="H336" s="7">
+        <v>3264.9</v>
+      </c>
+      <c r="I336" s="7">
+        <v>3302.4</v>
+      </c>
+      <c r="J336" s="7">
+        <v>3227.4</v>
+      </c>
+      <c r="K336" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L336" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M336" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="N336" s="7">
+        <v>3227.4</v>
+      </c>
+      <c r="O336" s="6">
+        <v>4</v>
+      </c>
+      <c r="P336" s="8">
+        <v>37.5</v>
+      </c>
+      <c r="Q336" s="9">
+        <v>1.149</v>
+      </c>
+      <c r="R336" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A337" s="12" t="s">
+        <v>750</v>
+      </c>
+      <c r="B337" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="C337" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D337" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="E337" s="13">
+        <v>1488.6</v>
+      </c>
+      <c r="F337" s="13">
+        <v>1449.1</v>
+      </c>
+      <c r="G337" s="13">
+        <v>1480.4</v>
+      </c>
+      <c r="H337" s="13">
+        <v>1481</v>
+      </c>
+      <c r="I337" s="13">
+        <v>1449.1</v>
+      </c>
+      <c r="J337" s="13">
+        <v>1512.9</v>
+      </c>
+      <c r="K337" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L337" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M337" s="12"/>
+      <c r="N337" s="12"/>
+      <c r="O337" s="12"/>
+      <c r="P337" s="12"/>
+      <c r="Q337" s="12"/>
+      <c r="R337" s="12" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A338" s="12" t="s">
+        <v>751</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="C338" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D338" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="E338" s="13">
+        <v>149.2</v>
+      </c>
+      <c r="F338" s="13">
+        <v>144.85</v>
+      </c>
+      <c r="G338" s="13">
+        <v>148.35</v>
+      </c>
+      <c r="H338" s="13">
+        <v>148.37</v>
+      </c>
+      <c r="I338" s="13">
+        <v>144.85</v>
+      </c>
+      <c r="J338" s="13">
+        <v>151.89</v>
+      </c>
+      <c r="K338" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L338" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M338" s="12"/>
+      <c r="N338" s="12"/>
+      <c r="O338" s="12"/>
+      <c r="P338" s="12"/>
+      <c r="Q338" s="12"/>
+      <c r="R338" s="12" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A339" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E339" s="3">
+        <v>125.98</v>
+      </c>
+      <c r="F339" s="3">
+        <v>122.85</v>
+      </c>
+      <c r="G339" s="3">
+        <v>125.66</v>
+      </c>
+      <c r="H339" s="3">
+        <v>125.66</v>
+      </c>
+      <c r="I339" s="3">
+        <v>122.85</v>
+      </c>
+      <c r="J339" s="3">
+        <v>128.47</v>
+      </c>
+      <c r="K339" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L339" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M339" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="N339" s="3">
+        <v>122.85</v>
+      </c>
+      <c r="O339" s="2">
+        <v>4</v>
+      </c>
+      <c r="P339" s="4">
+        <v>-2.81</v>
+      </c>
+      <c r="Q339" s="5">
+        <v>-2.236</v>
+      </c>
+      <c r="R339" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A340" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E340" s="3">
+        <v>3344.6</v>
+      </c>
+      <c r="F340" s="3">
+        <v>3284</v>
+      </c>
+      <c r="G340" s="3">
+        <v>3334.1</v>
+      </c>
+      <c r="H340" s="3">
+        <v>3337.1</v>
+      </c>
+      <c r="I340" s="3">
+        <v>3284</v>
+      </c>
+      <c r="J340" s="3">
+        <v>3390.2</v>
+      </c>
+      <c r="K340" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L340" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M340" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="N340" s="3">
+        <v>3284</v>
+      </c>
+      <c r="O340" s="2">
+        <v>15</v>
+      </c>
+      <c r="P340" s="4">
+        <v>-53.1</v>
+      </c>
+      <c r="Q340" s="5">
+        <v>-1.591</v>
+      </c>
+      <c r="R340" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A341" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E341" s="3">
+        <v>42.06</v>
+      </c>
+      <c r="F341" s="3">
+        <v>41.49</v>
+      </c>
+      <c r="G341" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="H341" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="I341" s="3">
+        <v>41.49</v>
+      </c>
+      <c r="J341" s="3">
+        <v>42.01</v>
+      </c>
+      <c r="K341" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L341" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M341" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="N341" s="3">
+        <v>41.49</v>
+      </c>
+      <c r="O341" s="2">
+        <v>3</v>
+      </c>
+      <c r="P341" s="4">
+        <v>-0.26</v>
+      </c>
+      <c r="Q341" s="5">
+        <v>-0.623</v>
+      </c>
+      <c r="R341" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A342" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C342" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D342" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="E342" s="13">
+        <v>390.35</v>
+      </c>
+      <c r="F342" s="13">
+        <v>382.35</v>
+      </c>
+      <c r="G342" s="13">
+        <v>389</v>
+      </c>
+      <c r="H342" s="13">
+        <v>389</v>
+      </c>
+      <c r="I342" s="13">
+        <v>382.35</v>
+      </c>
+      <c r="J342" s="13">
+        <v>395.65</v>
+      </c>
+      <c r="K342" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L342" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M342" s="12"/>
+      <c r="N342" s="12"/>
+      <c r="O342" s="12"/>
+      <c r="P342" s="12"/>
+      <c r="Q342" s="12"/>
+      <c r="R342" s="12" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A343" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="E343" s="7">
+        <v>1293.8</v>
+      </c>
+      <c r="F343" s="7">
+        <v>1286.1</v>
+      </c>
+      <c r="G343" s="7">
+        <v>1287.2</v>
+      </c>
+      <c r="H343" s="7">
+        <v>1287.4</v>
+      </c>
+      <c r="I343" s="7">
+        <v>1293.8</v>
+      </c>
+      <c r="J343" s="7">
+        <v>1281</v>
+      </c>
+      <c r="K343" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L343" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M343" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="N343" s="7">
+        <v>1281</v>
+      </c>
+      <c r="O343" s="6">
+        <v>12</v>
+      </c>
+      <c r="P343" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="Q343" s="9">
+        <v>0.497</v>
+      </c>
+      <c r="R343" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A344" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E344" s="3">
+        <v>3866</v>
+      </c>
+      <c r="F344" s="3">
+        <v>3789</v>
+      </c>
+      <c r="G344" s="3">
+        <v>3861.9</v>
+      </c>
+      <c r="H344" s="3">
+        <v>3862</v>
+      </c>
+      <c r="I344" s="3">
+        <v>3789</v>
+      </c>
+      <c r="J344" s="3">
+        <v>3935</v>
+      </c>
+      <c r="K344" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L344" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M344" s="2" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A303" s="10" t="s">
-        <v>693</v>
-      </c>
-      <c r="B303" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="C303" s="10" t="s">
+      <c r="N344" s="3">
+        <v>3789</v>
+      </c>
+      <c r="O344" s="2">
+        <v>7</v>
+      </c>
+      <c r="P344" s="4">
+        <v>-73</v>
+      </c>
+      <c r="Q344" s="5">
+        <v>-1.89</v>
+      </c>
+      <c r="R344" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A345" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="E345" s="3">
+        <v>1114.4</v>
+      </c>
+      <c r="F345" s="3">
+        <v>1103</v>
+      </c>
+      <c r="G345" s="3">
+        <v>1103.7</v>
+      </c>
+      <c r="H345" s="3">
+        <v>1103</v>
+      </c>
+      <c r="I345" s="3">
+        <v>1114.4</v>
+      </c>
+      <c r="J345" s="3">
+        <v>1091.6</v>
+      </c>
+      <c r="K345" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L345" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M345" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="N345" s="3">
+        <v>1114.4</v>
+      </c>
+      <c r="O345" s="2">
+        <v>1</v>
+      </c>
+      <c r="P345" s="4">
+        <v>-11.4</v>
+      </c>
+      <c r="Q345" s="5">
+        <v>-1.034</v>
+      </c>
+      <c r="R345" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A346" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C346" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D303" s="10" t="s">
-        <v>685</v>
-      </c>
-      <c r="E303" s="11">
-        <v>6825.5</v>
-      </c>
-      <c r="F303" s="11">
-        <v>6798.5</v>
-      </c>
-      <c r="G303" s="11">
-        <v>6824.5</v>
-      </c>
-      <c r="H303" s="11">
-        <v>6824</v>
-      </c>
-      <c r="I303" s="11">
-        <v>6798.5</v>
-      </c>
-      <c r="J303" s="11">
-        <v>6849.5</v>
-      </c>
-      <c r="K303" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L303" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M303" s="10"/>
-      <c r="N303" s="10"/>
-      <c r="O303" s="10"/>
-      <c r="P303" s="10"/>
-      <c r="Q303" s="10"/>
-      <c r="R303" s="10" t="s">
+      <c r="D346" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="E346" s="7">
+        <v>71.65</v>
+      </c>
+      <c r="F346" s="7">
+        <v>70.62</v>
+      </c>
+      <c r="G346" s="7">
+        <v>71.13</v>
+      </c>
+      <c r="H346" s="7">
+        <v>71.12</v>
+      </c>
+      <c r="I346" s="7">
+        <v>70.62</v>
+      </c>
+      <c r="J346" s="7">
+        <v>71.62</v>
+      </c>
+      <c r="K346" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L346" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M346" s="6" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A304" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="B304" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="C304" s="10" t="s">
+      <c r="N346" s="7">
+        <v>71.62</v>
+      </c>
+      <c r="O346" s="6">
+        <v>1</v>
+      </c>
+      <c r="P346" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q346" s="9">
+        <v>0.703</v>
+      </c>
+      <c r="R346" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A347" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="E347" s="3">
+        <v>25165</v>
+      </c>
+      <c r="F347" s="3">
+        <v>24935</v>
+      </c>
+      <c r="G347" s="3">
+        <v>24940</v>
+      </c>
+      <c r="H347" s="3">
+        <v>24950</v>
+      </c>
+      <c r="I347" s="3">
+        <v>25165</v>
+      </c>
+      <c r="J347" s="3">
+        <v>24735</v>
+      </c>
+      <c r="K347" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L347" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M347" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="N347" s="3">
+        <v>25165</v>
+      </c>
+      <c r="O347" s="2">
+        <v>11</v>
+      </c>
+      <c r="P347" s="4">
+        <v>-215</v>
+      </c>
+      <c r="Q347" s="5">
+        <v>-0.862</v>
+      </c>
+      <c r="R347" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A348" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D348" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="E348" s="7">
+        <v>2078.5</v>
+      </c>
+      <c r="F348" s="7">
+        <v>2066</v>
+      </c>
+      <c r="G348" s="7">
+        <v>2069</v>
+      </c>
+      <c r="H348" s="7">
+        <v>2068.6</v>
+      </c>
+      <c r="I348" s="7">
+        <v>2078.5</v>
+      </c>
+      <c r="J348" s="7">
+        <v>2058.7</v>
+      </c>
+      <c r="K348" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L348" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M348" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="N348" s="7">
+        <v>2058.7</v>
+      </c>
+      <c r="O348" s="6">
+        <v>7</v>
+      </c>
+      <c r="P348" s="8">
+        <v>9.9</v>
+      </c>
+      <c r="Q348" s="9">
+        <v>0.479</v>
+      </c>
+      <c r="R348" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A349" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="E349" s="7">
+        <v>2100.6</v>
+      </c>
+      <c r="F349" s="7">
+        <v>2064</v>
+      </c>
+      <c r="G349" s="7">
+        <v>2067</v>
+      </c>
+      <c r="H349" s="7">
+        <v>2068.6</v>
+      </c>
+      <c r="I349" s="7">
+        <v>2100.6</v>
+      </c>
+      <c r="J349" s="7">
+        <v>2036.6</v>
+      </c>
+      <c r="K349" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L349" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M349" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="N349" s="7">
+        <v>2036.6</v>
+      </c>
+      <c r="O349" s="6">
+        <v>1</v>
+      </c>
+      <c r="P349" s="8">
+        <v>32</v>
+      </c>
+      <c r="Q349" s="9">
+        <v>1.547</v>
+      </c>
+      <c r="R349" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A350" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C350" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D304" s="10" t="s">
-        <v>671</v>
-      </c>
-      <c r="E304" s="11">
-        <v>145.4</v>
-      </c>
-      <c r="F304" s="11">
-        <v>144.4</v>
-      </c>
-      <c r="G304" s="11">
-        <v>144.83</v>
-      </c>
-      <c r="H304" s="11">
-        <v>144.83</v>
-      </c>
-      <c r="I304" s="11">
-        <v>144.4</v>
-      </c>
-      <c r="J304" s="11">
-        <v>145.26</v>
-      </c>
-      <c r="K304" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L304" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M304" s="10"/>
-      <c r="N304" s="10"/>
-      <c r="O304" s="10"/>
-      <c r="P304" s="10"/>
-      <c r="Q304" s="10"/>
-      <c r="R304" s="10" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A305" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="B305" s="10" t="s">
-        <v>697</v>
-      </c>
-      <c r="C305" s="10" t="s">
+      <c r="D350" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="E350" s="3">
+        <v>1741.4</v>
+      </c>
+      <c r="F350" s="3">
+        <v>1723.9</v>
+      </c>
+      <c r="G350" s="3">
+        <v>1739.4</v>
+      </c>
+      <c r="H350" s="3">
+        <v>1739.4</v>
+      </c>
+      <c r="I350" s="3">
+        <v>1723.9</v>
+      </c>
+      <c r="J350" s="3">
+        <v>1754.9</v>
+      </c>
+      <c r="K350" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L350" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M350" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="N350" s="3">
+        <v>1723.9</v>
+      </c>
+      <c r="O350" s="2">
+        <v>4</v>
+      </c>
+      <c r="P350" s="4">
+        <v>-15.5</v>
+      </c>
+      <c r="Q350" s="5">
+        <v>-0.891</v>
+      </c>
+      <c r="R350" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A351" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C351" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D305" s="10" t="s">
-        <v>671</v>
-      </c>
-      <c r="E305" s="11">
-        <v>2601.5</v>
-      </c>
-      <c r="F305" s="11">
-        <v>2589</v>
-      </c>
-      <c r="G305" s="11">
-        <v>2596.1</v>
-      </c>
-      <c r="H305" s="11">
-        <v>2596</v>
-      </c>
-      <c r="I305" s="11">
-        <v>2589</v>
-      </c>
-      <c r="J305" s="11">
-        <v>2603</v>
-      </c>
-      <c r="K305" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L305" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M305" s="10"/>
-      <c r="N305" s="10"/>
-      <c r="O305" s="10"/>
-      <c r="P305" s="10"/>
-      <c r="Q305" s="10"/>
-      <c r="R305" s="10" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A306" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="B306" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C306" s="10" t="s">
+      <c r="D351" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="E351" s="3">
+        <v>5645.5</v>
+      </c>
+      <c r="F351" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G351" s="3">
+        <v>5644.5</v>
+      </c>
+      <c r="H351" s="3">
+        <v>5644</v>
+      </c>
+      <c r="I351" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J351" s="3">
+        <v>5688</v>
+      </c>
+      <c r="K351" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L351" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M351" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="N351" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O351" s="2">
+        <v>1</v>
+      </c>
+      <c r="P351" s="4">
+        <v>-44</v>
+      </c>
+      <c r="Q351" s="5">
+        <v>-0.78</v>
+      </c>
+      <c r="R351" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A352" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C352" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D306" s="10" t="s">
-        <v>671</v>
-      </c>
-      <c r="E306" s="11">
-        <v>1408.4</v>
-      </c>
-      <c r="F306" s="11">
-        <v>1401.8</v>
-      </c>
-      <c r="G306" s="11">
-        <v>1406.2</v>
-      </c>
-      <c r="H306" s="11">
-        <v>1405.9</v>
-      </c>
-      <c r="I306" s="11">
-        <v>1401.8</v>
-      </c>
-      <c r="J306" s="11">
-        <v>1410</v>
-      </c>
-      <c r="K306" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L306" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M306" s="10"/>
-      <c r="N306" s="10"/>
-      <c r="O306" s="10"/>
-      <c r="P306" s="10"/>
-      <c r="Q306" s="10"/>
-      <c r="R306" s="10" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A307" s="10" t="s">
-        <v>699</v>
-      </c>
-      <c r="B307" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="C307" s="10" t="s">
+      <c r="D352" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="E352" s="7">
+        <v>1740.6</v>
+      </c>
+      <c r="F352" s="7">
+        <v>1720</v>
+      </c>
+      <c r="G352" s="7">
+        <v>1739.5</v>
+      </c>
+      <c r="H352" s="7">
+        <v>1739.4</v>
+      </c>
+      <c r="I352" s="7">
+        <v>1720</v>
+      </c>
+      <c r="J352" s="7">
+        <v>1758.8</v>
+      </c>
+      <c r="K352" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L352" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M352" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="N352" s="7">
+        <v>1758.8</v>
+      </c>
+      <c r="O352" s="6">
+        <v>3</v>
+      </c>
+      <c r="P352" s="8">
+        <v>19.4</v>
+      </c>
+      <c r="Q352" s="9">
+        <v>1.115</v>
+      </c>
+      <c r="R352" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A353" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="C353" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D307" s="10" t="s">
-        <v>671</v>
-      </c>
-      <c r="E307" s="11">
-        <v>723.7</v>
-      </c>
-      <c r="F307" s="11">
-        <v>718.15</v>
-      </c>
-      <c r="G307" s="11">
-        <v>722.15</v>
-      </c>
-      <c r="H307" s="11">
-        <v>722.15</v>
-      </c>
-      <c r="I307" s="11">
-        <v>718.15</v>
-      </c>
-      <c r="J307" s="11">
-        <v>726.15</v>
-      </c>
-      <c r="K307" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L307" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M307" s="10"/>
-      <c r="N307" s="10"/>
-      <c r="O307" s="10"/>
-      <c r="P307" s="10"/>
-      <c r="Q307" s="10"/>
-      <c r="R307" s="10" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A308" s="10" t="s">
-        <v>700</v>
-      </c>
-      <c r="B308" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="C308" s="10" t="s">
+      <c r="D353" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="E353" s="3">
+        <v>184.31</v>
+      </c>
+      <c r="F353" s="3">
+        <v>183.1</v>
+      </c>
+      <c r="G353" s="3">
+        <v>184.27</v>
+      </c>
+      <c r="H353" s="3">
+        <v>184.28</v>
+      </c>
+      <c r="I353" s="3">
+        <v>183.1</v>
+      </c>
+      <c r="J353" s="3">
+        <v>185.46</v>
+      </c>
+      <c r="K353" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L353" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M353" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="N353" s="3">
+        <v>183.1</v>
+      </c>
+      <c r="O353" s="2">
+        <v>1</v>
+      </c>
+      <c r="P353" s="4">
+        <v>-1.18</v>
+      </c>
+      <c r="Q353" s="5">
+        <v>-0.64</v>
+      </c>
+      <c r="R353" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A354" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="E354" s="3">
+        <v>254</v>
+      </c>
+      <c r="F354" s="3">
+        <v>252.6</v>
+      </c>
+      <c r="G354" s="3">
+        <v>252.95</v>
+      </c>
+      <c r="H354" s="3">
+        <v>252.9</v>
+      </c>
+      <c r="I354" s="3">
+        <v>254</v>
+      </c>
+      <c r="J354" s="3">
+        <v>251.8</v>
+      </c>
+      <c r="K354" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L354" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M354" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="N354" s="3">
+        <v>254</v>
+      </c>
+      <c r="O354" s="2">
+        <v>1</v>
+      </c>
+      <c r="P354" s="4">
+        <v>-1.1</v>
+      </c>
+      <c r="Q354" s="5">
+        <v>-0.435</v>
+      </c>
+      <c r="R354" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A355" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="E355" s="7">
+        <v>312.95</v>
+      </c>
+      <c r="F355" s="7">
+        <v>311.6</v>
+      </c>
+      <c r="G355" s="7">
+        <v>311.75</v>
+      </c>
+      <c r="H355" s="7">
+        <v>312.25</v>
+      </c>
+      <c r="I355" s="7">
+        <v>312.95</v>
+      </c>
+      <c r="J355" s="7">
+        <v>311.55</v>
+      </c>
+      <c r="K355" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L355" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M355" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="N355" s="7">
+        <v>311.55</v>
+      </c>
+      <c r="O355" s="6">
+        <v>1</v>
+      </c>
+      <c r="P355" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="Q355" s="9">
+        <v>0.224</v>
+      </c>
+      <c r="R355" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A356" s="12" t="s">
+        <v>779</v>
+      </c>
+      <c r="B356" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C356" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D356" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="E356" s="13">
+        <v>766.05</v>
+      </c>
+      <c r="F356" s="13">
+        <v>760.2</v>
+      </c>
+      <c r="G356" s="13">
+        <v>760.4</v>
+      </c>
+      <c r="H356" s="13">
+        <v>760.45</v>
+      </c>
+      <c r="I356" s="13">
+        <v>766.05</v>
+      </c>
+      <c r="J356" s="13">
+        <v>754.85</v>
+      </c>
+      <c r="K356" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L356" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M356" s="12"/>
+      <c r="N356" s="12"/>
+      <c r="O356" s="12"/>
+      <c r="P356" s="12"/>
+      <c r="Q356" s="12"/>
+      <c r="R356" s="12" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A357" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="B357" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C357" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D357" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="E357" s="13">
+        <v>499.4</v>
+      </c>
+      <c r="F357" s="13">
+        <v>494.2</v>
+      </c>
+      <c r="G357" s="13">
+        <v>494.75</v>
+      </c>
+      <c r="H357" s="13">
+        <v>494.7</v>
+      </c>
+      <c r="I357" s="13">
+        <v>499.4</v>
+      </c>
+      <c r="J357" s="13">
+        <v>490</v>
+      </c>
+      <c r="K357" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L357" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M357" s="12"/>
+      <c r="N357" s="12"/>
+      <c r="O357" s="12"/>
+      <c r="P357" s="12"/>
+      <c r="Q357" s="12"/>
+      <c r="R357" s="12" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A358" s="12" t="s">
+        <v>782</v>
+      </c>
+      <c r="B358" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="C358" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D358" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="E358" s="13">
+        <v>299.95</v>
+      </c>
+      <c r="F358" s="13">
+        <v>297.15</v>
+      </c>
+      <c r="G358" s="13">
+        <v>297.45</v>
+      </c>
+      <c r="H358" s="13">
+        <v>297.3</v>
+      </c>
+      <c r="I358" s="13">
+        <v>299.95</v>
+      </c>
+      <c r="J358" s="13">
+        <v>294.65</v>
+      </c>
+      <c r="K358" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L358" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M358" s="12"/>
+      <c r="N358" s="12"/>
+      <c r="O358" s="12"/>
+      <c r="P358" s="12"/>
+      <c r="Q358" s="12"/>
+      <c r="R358" s="12" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A359" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="B359" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="C359" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D359" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="E359" s="13">
+        <v>121.74</v>
+      </c>
+      <c r="F359" s="13">
+        <v>121.01</v>
+      </c>
+      <c r="G359" s="13">
+        <v>121.01</v>
+      </c>
+      <c r="H359" s="13">
+        <v>121.02</v>
+      </c>
+      <c r="I359" s="13">
+        <v>121.74</v>
+      </c>
+      <c r="J359" s="13">
+        <v>120.3</v>
+      </c>
+      <c r="K359" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L359" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M359" s="12"/>
+      <c r="N359" s="12"/>
+      <c r="O359" s="12"/>
+      <c r="P359" s="12"/>
+      <c r="Q359" s="12"/>
+      <c r="R359" s="12" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A360" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="B360" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="C360" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D360" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="E360" s="13">
+        <v>626.75</v>
+      </c>
+      <c r="F360" s="13">
+        <v>623.05</v>
+      </c>
+      <c r="G360" s="13">
+        <v>624.1</v>
+      </c>
+      <c r="H360" s="13">
+        <v>623.8</v>
+      </c>
+      <c r="I360" s="13">
+        <v>626.75</v>
+      </c>
+      <c r="J360" s="13">
+        <v>620.85</v>
+      </c>
+      <c r="K360" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L360" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M360" s="12"/>
+      <c r="N360" s="12"/>
+      <c r="O360" s="12"/>
+      <c r="P360" s="12"/>
+      <c r="Q360" s="12"/>
+      <c r="R360" s="12" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A361" s="12" t="s">
+        <v>787</v>
+      </c>
+      <c r="B361" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="C361" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D308" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E308" s="11">
-        <v>1668</v>
-      </c>
-      <c r="F308" s="11">
-        <v>1658</v>
-      </c>
-      <c r="G308" s="11">
-        <v>1665</v>
-      </c>
-      <c r="H308" s="10"/>
-      <c r="I308" s="11">
-        <v>1658</v>
-      </c>
-      <c r="J308" s="10"/>
-      <c r="K308" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L308" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M308" s="10"/>
-      <c r="N308" s="10"/>
-      <c r="O308" s="10"/>
-      <c r="P308" s="10"/>
-      <c r="Q308" s="10"/>
-      <c r="R308" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A309" s="10" t="s">
-        <v>702</v>
-      </c>
-      <c r="B309" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="C309" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D309" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E309" s="11">
-        <v>731.95</v>
-      </c>
-      <c r="F309" s="11">
-        <v>725.95</v>
-      </c>
-      <c r="G309" s="11">
-        <v>730</v>
-      </c>
-      <c r="H309" s="10"/>
-      <c r="I309" s="11">
-        <v>725.95</v>
-      </c>
-      <c r="J309" s="10"/>
-      <c r="K309" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L309" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M309" s="10"/>
-      <c r="N309" s="10"/>
-      <c r="O309" s="10"/>
-      <c r="P309" s="10"/>
-      <c r="Q309" s="10"/>
-      <c r="R309" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A310" s="10" t="s">
-        <v>704</v>
-      </c>
-      <c r="B310" s="10" t="s">
-        <v>705</v>
-      </c>
-      <c r="C310" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D310" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E310" s="11">
-        <v>1254</v>
-      </c>
-      <c r="F310" s="11">
-        <v>1247.1</v>
-      </c>
-      <c r="G310" s="11">
-        <v>1253.5</v>
-      </c>
-      <c r="H310" s="10"/>
-      <c r="I310" s="11">
-        <v>1247.1</v>
-      </c>
-      <c r="J310" s="10"/>
-      <c r="K310" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L310" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M310" s="10"/>
-      <c r="N310" s="10"/>
-      <c r="O310" s="10"/>
-      <c r="P310" s="10"/>
-      <c r="Q310" s="10"/>
-      <c r="R310" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A311" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="B311" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C311" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D311" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E311" s="11">
-        <v>1631</v>
-      </c>
-      <c r="F311" s="11">
-        <v>1619</v>
-      </c>
-      <c r="G311" s="11">
-        <v>1631</v>
-      </c>
-      <c r="H311" s="10"/>
-      <c r="I311" s="11">
-        <v>1619</v>
-      </c>
-      <c r="J311" s="10"/>
-      <c r="K311" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L311" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M311" s="10"/>
-      <c r="N311" s="10"/>
-      <c r="O311" s="10"/>
-      <c r="P311" s="10"/>
-      <c r="Q311" s="10"/>
-      <c r="R311" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A312" s="10" t="s">
-        <v>707</v>
-      </c>
-      <c r="B312" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="C312" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D312" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E312" s="11">
-        <v>2210.7</v>
-      </c>
-      <c r="F312" s="11">
-        <v>2191.4</v>
-      </c>
-      <c r="G312" s="11">
-        <v>2210.4</v>
-      </c>
-      <c r="H312" s="10"/>
-      <c r="I312" s="11">
-        <v>2191.4</v>
-      </c>
-      <c r="J312" s="10"/>
-      <c r="K312" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L312" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M312" s="10"/>
-      <c r="N312" s="10"/>
-      <c r="O312" s="10"/>
-      <c r="P312" s="10"/>
-      <c r="Q312" s="10"/>
-      <c r="R312" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A313" s="10" t="s">
-        <v>708</v>
-      </c>
-      <c r="B313" s="10" t="s">
-        <v>709</v>
-      </c>
-      <c r="C313" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D313" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E313" s="11">
-        <v>587</v>
-      </c>
-      <c r="F313" s="11">
-        <v>583.05</v>
-      </c>
-      <c r="G313" s="11">
-        <v>585.3</v>
-      </c>
-      <c r="H313" s="10"/>
-      <c r="I313" s="11">
-        <v>583.05</v>
-      </c>
-      <c r="J313" s="10"/>
-      <c r="K313" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L313" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M313" s="10"/>
-      <c r="N313" s="10"/>
-      <c r="O313" s="10"/>
-      <c r="P313" s="10"/>
-      <c r="Q313" s="10"/>
-      <c r="R313" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A314" s="10" t="s">
-        <v>710</v>
-      </c>
-      <c r="B314" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="C314" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D314" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E314" s="11">
-        <v>427.7</v>
-      </c>
-      <c r="F314" s="11">
-        <v>424.15</v>
-      </c>
-      <c r="G314" s="11">
-        <v>426.5</v>
-      </c>
-      <c r="H314" s="10"/>
-      <c r="I314" s="11">
-        <v>424.15</v>
-      </c>
-      <c r="J314" s="10"/>
-      <c r="K314" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L314" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M314" s="10"/>
-      <c r="N314" s="10"/>
-      <c r="O314" s="10"/>
-      <c r="P314" s="10"/>
-      <c r="Q314" s="10"/>
-      <c r="R314" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A315" s="10" t="s">
-        <v>711</v>
-      </c>
-      <c r="B315" s="10" t="s">
-        <v>712</v>
-      </c>
-      <c r="C315" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D315" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E315" s="11">
-        <v>258.4</v>
-      </c>
-      <c r="F315" s="11">
-        <v>256.15</v>
-      </c>
-      <c r="G315" s="11">
-        <v>257.05</v>
-      </c>
-      <c r="H315" s="10"/>
-      <c r="I315" s="11">
-        <v>256.15</v>
-      </c>
-      <c r="J315" s="10"/>
-      <c r="K315" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L315" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M315" s="10"/>
-      <c r="N315" s="10"/>
-      <c r="O315" s="10"/>
-      <c r="P315" s="10"/>
-      <c r="Q315" s="10"/>
-      <c r="R315" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A316" s="10" t="s">
-        <v>713</v>
-      </c>
-      <c r="B316" s="10" t="s">
-        <v>570</v>
-      </c>
-      <c r="C316" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D316" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E316" s="11">
-        <v>97</v>
-      </c>
-      <c r="F316" s="11">
-        <v>95.27</v>
-      </c>
-      <c r="G316" s="11">
-        <v>96.35</v>
-      </c>
-      <c r="H316" s="10"/>
-      <c r="I316" s="11">
-        <v>95.27</v>
-      </c>
-      <c r="J316" s="10"/>
-      <c r="K316" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L316" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M316" s="10"/>
-      <c r="N316" s="10"/>
-      <c r="O316" s="10"/>
-      <c r="P316" s="10"/>
-      <c r="Q316" s="10"/>
-      <c r="R316" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A317" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="B317" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C317" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D317" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E317" s="11">
-        <v>117.5</v>
-      </c>
-      <c r="F317" s="11">
-        <v>116.55</v>
-      </c>
-      <c r="G317" s="11">
-        <v>117.31</v>
-      </c>
-      <c r="H317" s="10"/>
-      <c r="I317" s="11">
-        <v>116.55</v>
-      </c>
-      <c r="J317" s="10"/>
-      <c r="K317" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L317" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M317" s="10"/>
-      <c r="N317" s="10"/>
-      <c r="O317" s="10"/>
-      <c r="P317" s="10"/>
-      <c r="Q317" s="10"/>
-      <c r="R317" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A318" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="B318" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C318" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D318" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E318" s="11">
-        <v>1041.9</v>
-      </c>
-      <c r="F318" s="11">
-        <v>1036.1</v>
-      </c>
-      <c r="G318" s="11">
-        <v>1041.9</v>
-      </c>
-      <c r="H318" s="10"/>
-      <c r="I318" s="11">
-        <v>1036.1</v>
-      </c>
-      <c r="J318" s="10"/>
-      <c r="K318" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L318" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M318" s="10"/>
-      <c r="N318" s="10"/>
-      <c r="O318" s="10"/>
-      <c r="P318" s="10"/>
-      <c r="Q318" s="10"/>
-      <c r="R318" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A319" s="10" t="s">
-        <v>716</v>
-      </c>
-      <c r="B319" s="10" t="s">
-        <v>717</v>
-      </c>
-      <c r="C319" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D319" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E319" s="11">
-        <v>2346.3</v>
-      </c>
-      <c r="F319" s="11">
-        <v>2332.8</v>
-      </c>
-      <c r="G319" s="11">
-        <v>2345</v>
-      </c>
-      <c r="H319" s="10"/>
-      <c r="I319" s="11">
-        <v>2332.8</v>
-      </c>
-      <c r="J319" s="10"/>
-      <c r="K319" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L319" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M319" s="10"/>
-      <c r="N319" s="10"/>
-      <c r="O319" s="10"/>
-      <c r="P319" s="10"/>
-      <c r="Q319" s="10"/>
-      <c r="R319" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A320" s="10" t="s">
-        <v>718</v>
-      </c>
-      <c r="B320" s="10" t="s">
-        <v>719</v>
-      </c>
-      <c r="C320" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D320" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E320" s="11">
-        <v>87.5</v>
-      </c>
-      <c r="F320" s="11">
-        <v>86.77</v>
-      </c>
-      <c r="G320" s="11">
-        <v>87.2</v>
-      </c>
-      <c r="H320" s="10"/>
-      <c r="I320" s="11">
-        <v>86.77</v>
-      </c>
-      <c r="J320" s="10"/>
-      <c r="K320" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L320" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M320" s="10"/>
-      <c r="N320" s="10"/>
-      <c r="O320" s="10"/>
-      <c r="P320" s="10"/>
-      <c r="Q320" s="10"/>
-      <c r="R320" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A321" s="10" t="s">
-        <v>720</v>
-      </c>
-      <c r="B321" s="10" t="s">
-        <v>721</v>
-      </c>
-      <c r="C321" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D321" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E321" s="11">
-        <v>1506</v>
-      </c>
-      <c r="F321" s="11">
-        <v>1489</v>
-      </c>
-      <c r="G321" s="11">
-        <v>1506</v>
-      </c>
-      <c r="H321" s="10"/>
-      <c r="I321" s="11">
-        <v>1489</v>
-      </c>
-      <c r="J321" s="10"/>
-      <c r="K321" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L321" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M321" s="10"/>
-      <c r="N321" s="10"/>
-      <c r="O321" s="10"/>
-      <c r="P321" s="10"/>
-      <c r="Q321" s="10"/>
-      <c r="R321" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A322" s="10" t="s">
-        <v>722</v>
-      </c>
-      <c r="B322" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="C322" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D322" s="10" t="s">
-        <v>664</v>
-      </c>
-      <c r="E322" s="11">
-        <v>797</v>
-      </c>
-      <c r="F322" s="11">
-        <v>788.95</v>
-      </c>
-      <c r="G322" s="11">
-        <v>797</v>
-      </c>
-      <c r="H322" s="10"/>
-      <c r="I322" s="11">
-        <v>788.95</v>
-      </c>
-      <c r="J322" s="10"/>
-      <c r="K322" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L322" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="M322" s="10"/>
-      <c r="N322" s="10"/>
-      <c r="O322" s="10"/>
-      <c r="P322" s="10"/>
-      <c r="Q322" s="10"/>
-      <c r="R322" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A324" s="14" t="s">
-        <v>723</v>
-      </c>
-      <c r="P324" s="15">
-        <v>-141.39</v>
-      </c>
-      <c r="R324" s="14" t="s">
-        <v>724</v>
+      <c r="D361" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="E361" s="13">
+        <v>31745</v>
+      </c>
+      <c r="F361" s="13">
+        <v>31480</v>
+      </c>
+      <c r="G361" s="13">
+        <v>31745</v>
+      </c>
+      <c r="H361" s="12"/>
+      <c r="I361" s="13">
+        <v>31480</v>
+      </c>
+      <c r="J361" s="12"/>
+      <c r="K361" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L361" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="M361" s="12"/>
+      <c r="N361" s="12"/>
+      <c r="O361" s="12"/>
+      <c r="P361" s="12"/>
+      <c r="Q361" s="12"/>
+      <c r="R361" s="12" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A363" s="14" t="s">
+        <v>789</v>
+      </c>
+      <c r="P363" s="15">
+        <v>-614.28</v>
+      </c>
+      <c r="R363" s="14" t="s">
+        <v>790</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="855">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1960,430 +1960,622 @@
     <t>2026-03-09 12:00</t>
   </si>
   <si>
+    <t>2026-03-12 09:30</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BEAR_1772788500_1773038700</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:45</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BEAR_1773027900_1773041400</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:00</t>
+  </si>
+  <si>
+    <t>NSE:GRASIM-EQ_BEAR_1772789400_1773049500</t>
+  </si>
+  <si>
+    <t>NSE:GRASIM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:30</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BEAR_1773027900_1773049500</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1773036000_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:15</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1773044100_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:00</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1773045900_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:15</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BEAR_1773029700_1773114300</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:00</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1773046800_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:30</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1773028800_1773115200</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:15</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1773029700_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BEAR_1773027900_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:45</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:30</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1773117000_1773132300</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:45</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1773027900_1773132300</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BULL_1773117000_1773133200</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:30</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773134100</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BULL_1773126000_1773134100</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:30</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1773121500_1773134100</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:15</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1773123300_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ_BULL_1773121500_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BULL_1773116100_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1773126000_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CGPOWER-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CGPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ_BULL_1773120600_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BULL_1773131400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ_BULL_1773126900_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:15</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ_BULL_1773130500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BULL_1773133200_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:00</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ_BULL_1773132300_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:45</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BULL_1773118800_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:45</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ_BULL_1773128700_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:30</t>
+  </si>
+  <si>
+    <t>NSE:CAMS-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CAMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ_BULL_1773126900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:30</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BULL_1773118800_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-12 09:15</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ_BULL_1773117900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BULL_1773131400_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:00</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BULL_1773125100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BULL_1773126000_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INDIGO-EQ_BULL_1773130500_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INDIGO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1773123300_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:15</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1773117900_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:45</t>
+  </si>
+  <si>
+    <t>NSE:MUTHOOTFIN-EQ_BEAR_1773129600_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ_BULL_1773119700_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BULL_1773134100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BULL_1773132300_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SIEMENS-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SIEMENS-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:15</t>
+  </si>
+  <si>
+    <t>NSE:SUZLON-EQ_BULL_1773120600_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SUZLON-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:15</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-12 10:15</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ_BEAR_1773115200_1773201600</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:45</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1773119700_1773201600</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BEAR_1773126900_1773202500</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1773117000_1773207000</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:00</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BEAR_1773130500_1773210600</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:00</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BEAR_1773200700_1773214200</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BEAR_1773126000_1773215100</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:45</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BULL_1773130500_1773216900</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BULL_1773117000_1773218700</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773218700</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:15</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BULL_1773126900_1773218700</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ_BEAR_1773214200_1773219600</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1773207900_1773220500</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BEAR_1773203400_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ_BEAR_1773207900_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:RBLBANK-EQ_BEAR_1773209700_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:RBLBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BEAR_1773210600_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:INDHOTEL-EQ_BEAR_1773207900_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:INDHOTEL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BULL_1773201600_1773222300</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ_BEAR_1773202500_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-12 09:45</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ_BEAR_1773208800_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-12 10:30</t>
+  </si>
+  <si>
+    <t>NSE:MCX-EQ_BEAR_1773216000_1773287100</t>
+  </si>
+  <si>
+    <t>NSE:MCX-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-12 13:15</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BEAR_1773202500_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:15</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BEAR_1773204300_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-12 12:15</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BEAR_1773221400_1773287100</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ_BULL_1773214200_1773288000</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BULL_1773201600_1773291600</t>
+  </si>
+  <si>
+    <t>2026-03-12 13:45</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ_BEAR_1773206100_1773294300</t>
+  </si>
+  <si>
+    <t>2026-03-12 11:15</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ_BULL_1773200700_1773302400</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-12 13:30</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ_BEAR_1773221400_1773304200</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:00</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:30</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BEAR_1773288900_1773305100</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:45</t>
+  </si>
+  <si>
+    <t>NSE:NUVAMA-EQ_BEAR_1773217800_1773306900</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:15</t>
+  </si>
+  <si>
+    <t>NSE:VOLTAS-EQ_BEAR_1773287100_1773306900</t>
+  </si>
+  <si>
+    <t>NSE:DALBHARAT-EQ_BULL_1773301500_1773307800</t>
+  </si>
+  <si>
+    <t>NSE:DALBHARAT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:00</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1773218700_1773307800</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ_BEAR_1773206100_1773307800</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BULL_1773295200_1773308700</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ_BEAR_1773208800_1773308700</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BEAR_1773287100_1773308700</t>
+  </si>
+  <si>
+    <t>NSE:ADANIGREEN-EQ_BULL_1773299700_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:ADANIGREEN-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:45</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ_BULL_1773296100_1773373500</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:00</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BEAR_1773288900_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BEAR_1773288000_1773373500</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>Checked 62 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:HAVELLS-EQ_BEAR_1772788500_1773038700</t>
-  </si>
-  <si>
-    <t>2026-03-09 12:15</t>
-  </si>
-  <si>
-    <t>2026-03-09 12:45</t>
-  </si>
-  <si>
-    <t>NSE:BANDHANBNK-EQ_BEAR_1773027900_1773041400</t>
-  </si>
-  <si>
-    <t>NSE:BANDHANBNK-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-09 13:00</t>
-  </si>
-  <si>
-    <t>NSE:GRASIM-EQ_BEAR_1772789400_1773049500</t>
-  </si>
-  <si>
-    <t>NSE:GRASIM-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-09 15:15</t>
-  </si>
-  <si>
-    <t>2026-03-10 09:30</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ_BEAR_1773027900_1773049500</t>
-  </si>
-  <si>
-    <t>2026-03-10 09:45</t>
-  </si>
-  <si>
-    <t>NSE:AUROPHARMA-EQ_BULL_1773036000_1773114300</t>
-  </si>
-  <si>
-    <t>2026-03-10 15:15</t>
-  </si>
-  <si>
-    <t>NSE:BSE-EQ_BULL_1773044100_1773114300</t>
-  </si>
-  <si>
-    <t>2026-03-10 10:00</t>
-  </si>
-  <si>
-    <t>NSE:GLENMARK-EQ_BULL_1773045900_1773114300</t>
-  </si>
-  <si>
-    <t>2026-03-10 12:15</t>
-  </si>
-  <si>
-    <t>NSE:HINDALCO-EQ_BEAR_1773029700_1773114300</t>
-  </si>
-  <si>
-    <t>NSE:HINDALCO-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-10 15:00</t>
-  </si>
-  <si>
-    <t>NSE:TORNTPHARM-EQ_BULL_1773046800_1773114300</t>
-  </si>
-  <si>
-    <t>Checked 48 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
-    <t>NSE:BLUESTARCO-EQ_BEAR_1773028800_1773115200</t>
-  </si>
-  <si>
-    <t>NSE:AMBER-EQ_BEAR_1773028800_1773116100</t>
-  </si>
-  <si>
-    <t>2026-03-10 10:15</t>
-  </si>
-  <si>
-    <t>NSE:BHARATFORG-EQ_BEAR_1773029700_1773116100</t>
-  </si>
-  <si>
-    <t>NSE:PAGEIND-EQ_BEAR_1773027900_1773116100</t>
-  </si>
-  <si>
-    <t>NSE:PAGEIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-10 11:45</t>
-  </si>
-  <si>
-    <t>NSE:POLYCAB-EQ_BEAR_1773028800_1773116100</t>
-  </si>
-  <si>
-    <t>2026-03-10 10:30</t>
-  </si>
-  <si>
-    <t>NSE:HFCL-EQ_BULL_1773117000_1773132300</t>
-  </si>
-  <si>
-    <t>2026-03-10 14:15</t>
-  </si>
-  <si>
-    <t>2026-03-10 14:45</t>
-  </si>
-  <si>
-    <t>NSE:VBL-EQ_BEAR_1773027900_1773132300</t>
-  </si>
-  <si>
-    <t>NSE:ALKEM-EQ_BULL_1773117000_1773133200</t>
-  </si>
-  <si>
-    <t>NSE:ALKEM-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-10 14:30</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773134100</t>
-  </si>
-  <si>
-    <t>NSE:IRFC-EQ_BULL_1773126000_1773134100</t>
-  </si>
-  <si>
-    <t>2026-03-11 11:30</t>
-  </si>
-  <si>
-    <t>NSE:OFSS-EQ_BULL_1773121500_1773134100</t>
-  </si>
-  <si>
-    <t>2026-03-11 09:15</t>
-  </si>
-  <si>
-    <t>NSE:NCC-EQ_BULL_1773123300_1773135000</t>
-  </si>
-  <si>
-    <t>NSE:SRF-EQ_BULL_1773121500_1773135000</t>
-  </si>
-  <si>
-    <t>NSE:SRF-EQ</t>
-  </si>
-  <si>
-    <t>NSE:UNITDSPR-EQ_BULL_1773116100_1773135000</t>
-  </si>
-  <si>
-    <t>NSE:VEDL-EQ_BULL_1773126000_1773135000</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:CGPOWER-EQ_BULL_1773117000_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:CGPOWER-EQ</t>
-  </si>
-  <si>
-    <t>NSE:CDSL-EQ_BULL_1773120600_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:CDSL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:CHOLAFIN-EQ_BULL_1773127800_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:COLPAL-EQ_BULL_1773131400_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:DLF-EQ_BULL_1773122400_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:DLF-EQ</t>
-  </si>
-  <si>
-    <t>NSE:DELHIVERY-EQ_BULL_1773121500_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:NYKAA-EQ_BULL_1773126900_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:NYKAA-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-11 11:15</t>
-  </si>
-  <si>
-    <t>NSE:GMRAIRPORT-EQ_BULL_1773130500_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:IREDA-EQ_BULL_1773133200_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ_BULL_1773121500_1773135900</t>
-  </si>
-  <si>
-    <t>2026-03-11 10:00</t>
-  </si>
-  <si>
-    <t>NSE:LUPIN-EQ_BULL_1773117000_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:LUPIN-EQ</t>
-  </si>
-  <si>
-    <t>NSE:NBCC-EQ_BULL_1773132300_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:NBCC-EQ</t>
-  </si>
-  <si>
-    <t>NSE:OBEROIRLTY-EQ_BULL_1773122400_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:OBEROIRLTY-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-11 09:45</t>
-  </si>
-  <si>
-    <t>NSE:PNBHOUSING-EQ_BULL_1773127800_1773135900</t>
-  </si>
-  <si>
-    <t>NSE:ADANIENSOL-EQ_BULL_1773118800_1773200700</t>
-  </si>
-  <si>
-    <t>2026-03-11 10:45</t>
-  </si>
-  <si>
-    <t>NSE:ANGELONE-EQ_BULL_1773128700_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:ANGELONE-EQ</t>
-  </si>
-  <si>
-    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773200700</t>
-  </si>
-  <si>
-    <t>2026-03-11 10:30</t>
-  </si>
-  <si>
-    <t>NSE:CAMS-EQ_BULL_1773116100_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:CAMS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:CYIENT-EQ_BULL_1773126900_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:CYIENT-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-11 14:30</t>
-  </si>
-  <si>
-    <t>NSE:HAVELLS-EQ_BULL_1773118800_1773200700</t>
-  </si>
-  <si>
     <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
   </si>
   <si>
-    <t>NSE:HEROMOTOCO-EQ_BULL_1773117900_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:HINDALCO-EQ_BULL_1773131400_1773200700</t>
-  </si>
-  <si>
-    <t>2026-03-11 13:00</t>
-  </si>
-  <si>
-    <t>NSE:HUDCO-EQ_BULL_1773125100_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:IRFC-EQ_BULL_1773126000_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:INDIGO-EQ_BULL_1773130500_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:INDIGO-EQ</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1773123300_1773200700</t>
-  </si>
-  <si>
-    <t>2026-03-11 14:15</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BULL_1773117900_1773200700</t>
-  </si>
-  <si>
-    <t>2026-03-11 14:45</t>
-  </si>
-  <si>
-    <t>NSE:MUTHOOTFIN-EQ_BEAR_1773129600_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:POLICYBZR-EQ_BULL_1773119700_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:SAMMAANCAP-EQ_BULL_1773134100_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:MOTHERSON-EQ_BULL_1773132300_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:SIEMENS-EQ_BULL_1773116100_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:SIEMENS-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-11 13:15</t>
-  </si>
-  <si>
-    <t>NSE:SUZLON-EQ_BULL_1773120600_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:SUZLON-EQ</t>
-  </si>
-  <si>
-    <t>2026-03-11 10:15</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ_BULL_1773116100_1773200700</t>
-  </si>
-  <si>
-    <t>NSE:INFY-EQ_BEAR_1773115200_1773201600</t>
-  </si>
-  <si>
-    <t>2026-03-11 12:45</t>
-  </si>
-  <si>
-    <t>NSE:KAYNES-EQ_BULL_1773119700_1773201600</t>
-  </si>
-  <si>
-    <t>NSE:UNOMINDA-EQ_BEAR_1773126900_1773202500</t>
-  </si>
-  <si>
-    <t>NSE:HFCL-EQ_BULL_1773117000_1773207000</t>
-  </si>
-  <si>
-    <t>2026-03-11 11:00</t>
-  </si>
-  <si>
-    <t>NSE:POWERINDIA-EQ_BEAR_1773130500_1773210600</t>
-  </si>
-  <si>
-    <t>2026-03-11 12:00</t>
-  </si>
-  <si>
-    <t>2026-03-11 15:00</t>
-  </si>
-  <si>
-    <t>NSE:COLPAL-EQ_BEAR_1773200700_1773214200</t>
-  </si>
-  <si>
-    <t>NSE:APLAPOLLO-EQ_BEAR_1773126000_1773215100</t>
-  </si>
-  <si>
-    <t>2026-03-11 13:45</t>
-  </si>
-  <si>
-    <t>NSE:MFSL-EQ_BULL_1773130500_1773216900</t>
-  </si>
-  <si>
-    <t>NSE:ALKEM-EQ_BULL_1773117000_1773218700</t>
-  </si>
-  <si>
-    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773218700</t>
-  </si>
-  <si>
-    <t>2026-03-11 15:15</t>
-  </si>
-  <si>
-    <t>NSE:BANDHANBNK-EQ_BULL_1773126900_1773218700</t>
-  </si>
-  <si>
-    <t>NSE:NYKAA-EQ_BEAR_1773214200_1773219600</t>
-  </si>
-  <si>
-    <t>NSE:EXIDEIND-EQ_BEAR_1773207900_1773220500</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ_BEAR_1773203400_1773221400</t>
-  </si>
-  <si>
-    <t>No candles after entry yet — trade open</t>
-  </si>
-  <si>
-    <t>NSE:PATANJALI-EQ_BEAR_1773207900_1773221400</t>
-  </si>
-  <si>
-    <t>NSE:RBLBANK-EQ_BEAR_1773209700_1773221400</t>
-  </si>
-  <si>
-    <t>NSE:RBLBANK-EQ</t>
-  </si>
-  <si>
-    <t>NSE:MOTHERSON-EQ_BEAR_1773210600_1773221400</t>
-  </si>
-  <si>
-    <t>NSE:INDHOTEL-EQ_BEAR_1773207900_1773221400</t>
-  </si>
-  <si>
-    <t>NSE:INDHOTEL-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PAGEIND-EQ_BULL_1773201600_1773222300</t>
-  </si>
-  <si>
-    <t>Entry candle not yet available — trade not entered</t>
-  </si>
-  <si>
-    <t>SUMMARY — 172W / 176L / 12 OPEN  |  Win Rate: 49.4%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 348 of 360</t>
+    <t>NSE:IREDA-EQ_BULL_1773299700_1773373500</t>
+  </si>
+  <si>
+    <t>2026-03-13 10:00</t>
+  </si>
+  <si>
+    <t>NSE:NHPC-EQ_BULL_1773293400_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:NHPC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BEAR_1773287100_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BEAR_1773287100_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BEAR_1773306900_1773374400</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1773306000_1773375300</t>
+  </si>
+  <si>
+    <t>2026-03-13 11:30</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ_BEAR_1773288000_1773375300</t>
+  </si>
+  <si>
+    <t>2026-03-13 10:15</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BEAR_1773287100_1773382500</t>
+  </si>
+  <si>
+    <t>2026-03-13 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-13 13:15</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1773374400_1773384300</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-13 14:45</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BEAR_1773374400_1773384300</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:45</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BEAR_1773287100_1773386100</t>
+  </si>
+  <si>
+    <t>SUMMARY — 197W / 197L / 1 OPEN  |  Win Rate: 50.0%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 394 of 395</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +3036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R363"/>
+  <dimension ref="A1:R398"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -11561,7 +11753,7 @@
         <v>510.4</v>
       </c>
       <c r="F156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="G156" s="3">
         <v>509.4</v>
@@ -11570,10 +11762,10 @@
         <v>509.4</v>
       </c>
       <c r="I156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="J156" s="3">
-        <v>512.5</v>
+        <v>512.65</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>22</v>
@@ -11585,16 +11777,16 @@
         <v>384</v>
       </c>
       <c r="N156" s="3">
-        <v>506.3</v>
+        <v>506.15</v>
       </c>
       <c r="O156" s="2">
         <v>1</v>
       </c>
       <c r="P156" s="4">
-        <v>-3.1</v>
+        <v>-3.25</v>
       </c>
       <c r="Q156" s="5">
-        <v>-0.609</v>
+        <v>-0.638</v>
       </c>
       <c r="R156" s="2" t="s">
         <v>25</v>
@@ -18657,54 +18849,64 @@
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A283" s="12" t="s">
+      <c r="A283" s="6" t="s">
         <v>647</v>
       </c>
-      <c r="B283" s="12" t="s">
+      <c r="B283" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C283" s="12" t="s">
+      <c r="C283" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D283" s="12" t="s">
+      <c r="D283" s="6" t="s">
         <v>648</v>
       </c>
-      <c r="E283" s="13">
+      <c r="E283" s="7">
         <v>7673</v>
       </c>
-      <c r="F283" s="13">
+      <c r="F283" s="7">
         <v>7305.5</v>
       </c>
-      <c r="G283" s="13">
+      <c r="G283" s="7">
         <v>7312.5</v>
       </c>
-      <c r="H283" s="13">
+      <c r="H283" s="7">
         <v>7312.5</v>
       </c>
-      <c r="I283" s="13">
+      <c r="I283" s="7">
         <v>7673</v>
       </c>
-      <c r="J283" s="13">
+      <c r="J283" s="7">
         <v>6952</v>
       </c>
-      <c r="K283" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L283" s="12" t="s">
+      <c r="K283" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L283" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M283" s="6" t="s">
         <v>649</v>
       </c>
-      <c r="M283" s="12"/>
-      <c r="N283" s="12"/>
-      <c r="O283" s="12"/>
-      <c r="P283" s="12"/>
-      <c r="Q283" s="12"/>
-      <c r="R283" s="12" t="s">
-        <v>650</v>
+      <c r="N283" s="7">
+        <v>6952</v>
+      </c>
+      <c r="O283" s="6">
+        <v>64</v>
+      </c>
+      <c r="P283" s="8">
+        <v>360.5</v>
+      </c>
+      <c r="Q283" s="9">
+        <v>4.93</v>
+      </c>
+      <c r="R283" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>525</v>
@@ -18713,7 +18915,7 @@
         <v>64</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E284" s="3">
         <v>1321.5</v>
@@ -18740,7 +18942,7 @@
         <v>23</v>
       </c>
       <c r="M284" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N284" s="3">
         <v>1321.5</v>
@@ -18760,16 +18962,16 @@
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E285" s="3">
         <v>176</v>
@@ -18816,16 +19018,16 @@
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E286" s="3">
         <v>2682.4</v>
@@ -18852,7 +19054,7 @@
         <v>23</v>
       </c>
       <c r="M286" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="N286" s="3">
         <v>2682.4</v>
@@ -18872,7 +19074,7 @@
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>282</v>
@@ -18881,7 +19083,7 @@
         <v>64</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E287" s="3">
         <v>783.9</v>
@@ -18908,7 +19110,7 @@
         <v>23</v>
       </c>
       <c r="M287" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="N287" s="3">
         <v>783.9</v>
@@ -18928,7 +19130,7 @@
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>256</v>
@@ -18964,7 +19166,7 @@
         <v>33</v>
       </c>
       <c r="M288" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N288" s="7">
         <v>1289</v>
@@ -18984,7 +19186,7 @@
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>436</v>
@@ -19020,7 +19222,7 @@
         <v>33</v>
       </c>
       <c r="M289" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N289" s="7">
         <v>2850.3</v>
@@ -19040,7 +19242,7 @@
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>333</v>
@@ -19076,7 +19278,7 @@
         <v>33</v>
       </c>
       <c r="M290" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N290" s="7">
         <v>2217.2</v>
@@ -19096,10 +19298,10 @@
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>64</v>
@@ -19132,7 +19334,7 @@
         <v>23</v>
       </c>
       <c r="M291" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N291" s="3">
         <v>957.75</v>
@@ -19151,54 +19353,64 @@
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A292" s="12" t="s">
+      <c r="A292" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="E292" s="7">
+        <v>4432</v>
+      </c>
+      <c r="F292" s="7">
+        <v>4389</v>
+      </c>
+      <c r="G292" s="7">
+        <v>4428.5</v>
+      </c>
+      <c r="H292" s="7">
+        <v>4432.6</v>
+      </c>
+      <c r="I292" s="7">
+        <v>4389</v>
+      </c>
+      <c r="J292" s="7">
+        <v>4476.2</v>
+      </c>
+      <c r="K292" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L292" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M292" s="6" t="s">
         <v>672</v>
       </c>
-      <c r="B292" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="C292" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D292" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="E292" s="13">
-        <v>4432</v>
-      </c>
-      <c r="F292" s="13">
-        <v>4389</v>
-      </c>
-      <c r="G292" s="13">
-        <v>4428.5</v>
-      </c>
-      <c r="H292" s="13">
-        <v>4432.6</v>
-      </c>
-      <c r="I292" s="13">
-        <v>4389</v>
-      </c>
-      <c r="J292" s="13">
+      <c r="N292" s="7">
         <v>4476.2</v>
       </c>
-      <c r="K292" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L292" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M292" s="12"/>
-      <c r="N292" s="12"/>
-      <c r="O292" s="12"/>
-      <c r="P292" s="12"/>
-      <c r="Q292" s="12"/>
-      <c r="R292" s="12" t="s">
-        <v>673</v>
+      <c r="O292" s="6">
+        <v>75</v>
+      </c>
+      <c r="P292" s="8">
+        <v>43.6</v>
+      </c>
+      <c r="Q292" s="9">
+        <v>0.984</v>
+      </c>
+      <c r="R292" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>27</v>
@@ -19207,7 +19419,7 @@
         <v>64</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E293" s="3">
         <v>1902</v>
@@ -19234,7 +19446,7 @@
         <v>23</v>
       </c>
       <c r="M293" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N293" s="3">
         <v>1902</v>
@@ -19254,7 +19466,7 @@
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>156</v>
@@ -19263,7 +19475,7 @@
         <v>64</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E294" s="3">
         <v>7292</v>
@@ -19290,7 +19502,7 @@
         <v>23</v>
       </c>
       <c r="M294" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N294" s="3">
         <v>7292</v>
@@ -19310,7 +19522,7 @@
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>584</v>
@@ -19319,7 +19531,7 @@
         <v>64</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E295" s="7">
         <v>1849.7</v>
@@ -19346,7 +19558,7 @@
         <v>33</v>
       </c>
       <c r="M295" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N295" s="7">
         <v>1833.7</v>
@@ -19366,16 +19578,16 @@
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E296" s="3">
         <v>31255</v>
@@ -19402,7 +19614,7 @@
         <v>23</v>
       </c>
       <c r="M296" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N296" s="3">
         <v>31255</v>
@@ -19422,7 +19634,7 @@
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>259</v>
@@ -19431,7 +19643,7 @@
         <v>64</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E297" s="7">
         <v>8213</v>
@@ -19458,7 +19670,7 @@
         <v>33</v>
       </c>
       <c r="M297" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="N297" s="7">
         <v>8118</v>
@@ -19478,7 +19690,7 @@
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B298" s="6" t="s">
         <v>31</v>
@@ -19487,7 +19699,7 @@
         <v>20</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E298" s="7">
         <v>70.26</v>
@@ -19514,7 +19726,7 @@
         <v>33</v>
       </c>
       <c r="M298" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="N298" s="7">
         <v>70.02</v>
@@ -19534,7 +19746,7 @@
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>145</v>
@@ -19543,7 +19755,7 @@
         <v>64</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E299" s="3">
         <v>437.1</v>
@@ -19570,7 +19782,7 @@
         <v>23</v>
       </c>
       <c r="M299" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N299" s="3">
         <v>437.1</v>
@@ -19590,16 +19802,16 @@
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E300" s="3">
         <v>5664.5</v>
@@ -19626,7 +19838,7 @@
         <v>23</v>
       </c>
       <c r="M300" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N300" s="3">
         <v>5624</v>
@@ -19646,7 +19858,7 @@
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>90</v>
@@ -19655,7 +19867,7 @@
         <v>20</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E301" s="7">
         <v>444.85</v>
@@ -19682,7 +19894,7 @@
         <v>33</v>
       </c>
       <c r="M301" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N301" s="7">
         <v>444.4</v>
@@ -19702,7 +19914,7 @@
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>113</v>
@@ -19711,7 +19923,7 @@
         <v>20</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E302" s="3">
         <v>101.05</v>
@@ -19738,7 +19950,7 @@
         <v>23</v>
       </c>
       <c r="M302" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N302" s="3">
         <v>99.93</v>
@@ -19758,7 +19970,7 @@
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303" s="6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B303" s="6" t="s">
         <v>472</v>
@@ -19767,7 +19979,7 @@
         <v>20</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E303" s="7">
         <v>6825.5</v>
@@ -19794,7 +20006,7 @@
         <v>33</v>
       </c>
       <c r="M303" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N303" s="7">
         <v>6849.5</v>
@@ -19814,7 +20026,7 @@
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B304" s="6" t="s">
         <v>428</v>
@@ -19823,7 +20035,7 @@
         <v>20</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E304" s="7">
         <v>145.4</v>
@@ -19850,7 +20062,7 @@
         <v>33</v>
       </c>
       <c r="M304" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N304" s="7">
         <v>145.26</v>
@@ -19870,16 +20082,16 @@
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>697</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E305" s="3">
         <v>2601.5</v>
@@ -19906,7 +20118,7 @@
         <v>23</v>
       </c>
       <c r="M305" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N305" s="3">
         <v>2589</v>
@@ -19926,7 +20138,7 @@
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>165</v>
@@ -19935,7 +20147,7 @@
         <v>20</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E306" s="3">
         <v>1408.4</v>
@@ -19962,7 +20174,7 @@
         <v>23</v>
       </c>
       <c r="M306" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N306" s="3">
         <v>1401.8</v>
@@ -19982,7 +20194,7 @@
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B307" s="6" t="s">
         <v>349</v>
@@ -19991,7 +20203,7 @@
         <v>20</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E307" s="7">
         <v>723.7</v>
@@ -20018,7 +20230,7 @@
         <v>33</v>
       </c>
       <c r="M307" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N307" s="7">
         <v>726.15</v>
@@ -20038,7 +20250,7 @@
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B308" s="6" t="s">
         <v>341</v>
@@ -20047,7 +20259,7 @@
         <v>20</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E308" s="7">
         <v>1668</v>
@@ -20074,7 +20286,7 @@
         <v>33</v>
       </c>
       <c r="M308" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N308" s="7">
         <v>1705.6</v>
@@ -20094,16 +20306,16 @@
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="B309" s="6" t="s">
         <v>701</v>
-      </c>
-      <c r="B309" s="6" t="s">
-        <v>702</v>
       </c>
       <c r="C309" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D309" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E309" s="7">
         <v>731.95</v>
@@ -20150,16 +20362,16 @@
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="B310" s="6" t="s">
         <v>703</v>
-      </c>
-      <c r="B310" s="6" t="s">
-        <v>704</v>
       </c>
       <c r="C310" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E310" s="7">
         <v>1254</v>
@@ -20206,7 +20418,7 @@
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>63</v>
@@ -20215,7 +20427,7 @@
         <v>20</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E311" s="3">
         <v>1631</v>
@@ -20262,7 +20474,7 @@
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>587</v>
@@ -20271,7 +20483,7 @@
         <v>20</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E312" s="3">
         <v>2210.7</v>
@@ -20318,16 +20530,16 @@
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="B313" s="6" t="s">
         <v>707</v>
-      </c>
-      <c r="B313" s="6" t="s">
-        <v>708</v>
       </c>
       <c r="C313" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D313" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E313" s="7">
         <v>587</v>
@@ -20374,7 +20586,7 @@
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B314" s="6" t="s">
         <v>276</v>
@@ -20383,7 +20595,7 @@
         <v>20</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E314" s="7">
         <v>427.7</v>
@@ -20430,16 +20642,16 @@
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E315" s="3">
         <v>258.4</v>
@@ -20466,7 +20678,7 @@
         <v>23</v>
       </c>
       <c r="M315" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N315" s="3">
         <v>256.15</v>
@@ -20486,7 +20698,7 @@
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B316" s="6" t="s">
         <v>569</v>
@@ -20495,7 +20707,7 @@
         <v>20</v>
       </c>
       <c r="D316" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E316" s="7">
         <v>97</v>
@@ -20542,7 +20754,7 @@
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B317" s="6" t="s">
         <v>115</v>
@@ -20551,7 +20763,7 @@
         <v>20</v>
       </c>
       <c r="D317" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E317" s="7">
         <v>117.5</v>
@@ -20598,7 +20810,7 @@
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B318" s="6" t="s">
         <v>252</v>
@@ -20607,7 +20819,7 @@
         <v>20</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E318" s="7">
         <v>1041.9</v>
@@ -20634,7 +20846,7 @@
         <v>33</v>
       </c>
       <c r="M318" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N318" s="7">
         <v>1051.3</v>
@@ -20654,16 +20866,16 @@
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B319" s="6" t="s">
         <v>717</v>
-      </c>
-      <c r="B319" s="6" t="s">
-        <v>718</v>
       </c>
       <c r="C319" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D319" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E319" s="7">
         <v>2346.3</v>
@@ -20690,7 +20902,7 @@
         <v>33</v>
       </c>
       <c r="M319" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N319" s="7">
         <v>2367.2</v>
@@ -20710,16 +20922,16 @@
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B320" s="6" t="s">
         <v>719</v>
-      </c>
-      <c r="B320" s="6" t="s">
-        <v>720</v>
       </c>
       <c r="C320" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E320" s="7">
         <v>87.5</v>
@@ -20766,16 +20978,16 @@
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="B321" s="6" t="s">
         <v>721</v>
-      </c>
-      <c r="B321" s="6" t="s">
-        <v>722</v>
       </c>
       <c r="C321" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D321" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E321" s="7">
         <v>1506</v>
@@ -20802,7 +21014,7 @@
         <v>33</v>
       </c>
       <c r="M321" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N321" s="7">
         <v>1513</v>
@@ -20822,7 +21034,7 @@
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B322" s="6" t="s">
         <v>431</v>
@@ -20831,7 +21043,7 @@
         <v>20</v>
       </c>
       <c r="D322" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E322" s="7">
         <v>797</v>
@@ -20878,7 +21090,7 @@
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>149</v>
@@ -20887,7 +21099,7 @@
         <v>20</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E323" s="3">
         <v>1031.6</v>
@@ -20914,7 +21126,7 @@
         <v>23</v>
       </c>
       <c r="M323" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="N323" s="3">
         <v>1010</v>
@@ -20934,16 +21146,16 @@
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B324" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E324" s="3">
         <v>227.7</v>
@@ -20970,7 +21182,7 @@
         <v>23</v>
       </c>
       <c r="M324" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N324" s="3">
         <v>224.61</v>
@@ -20990,7 +21202,7 @@
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A325" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B325" s="6" t="s">
         <v>90</v>
@@ -20999,7 +21211,7 @@
         <v>20</v>
       </c>
       <c r="D325" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E325" s="7">
         <v>451.8</v>
@@ -21026,7 +21238,7 @@
         <v>33</v>
       </c>
       <c r="M325" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N325" s="7">
         <v>448.95</v>
@@ -21046,16 +21258,16 @@
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A326" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="B326" s="6" t="s">
         <v>731</v>
-      </c>
-      <c r="B326" s="6" t="s">
-        <v>732</v>
       </c>
       <c r="C326" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D326" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E326" s="7">
         <v>680.5</v>
@@ -21082,7 +21294,7 @@
         <v>33</v>
       </c>
       <c r="M326" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N326" s="7">
         <v>677</v>
@@ -21102,16 +21314,16 @@
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A327" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="B327" s="6" t="s">
         <v>733</v>
-      </c>
-      <c r="B327" s="6" t="s">
-        <v>734</v>
       </c>
       <c r="C327" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D327" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E327" s="7">
         <v>928</v>
@@ -21138,7 +21350,7 @@
         <v>33</v>
       </c>
       <c r="M327" s="6" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="N327" s="7">
         <v>949.5</v>
@@ -21157,54 +21369,64 @@
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A328" s="12" t="s">
+      <c r="A328" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="E328" s="3">
+        <v>1404.6</v>
+      </c>
+      <c r="F328" s="3">
+        <v>1359.8</v>
+      </c>
+      <c r="G328" s="3">
+        <v>1397.4</v>
+      </c>
+      <c r="H328" s="3">
+        <v>1397.4</v>
+      </c>
+      <c r="I328" s="3">
+        <v>1359.8</v>
+      </c>
+      <c r="J328" s="3">
+        <v>1435</v>
+      </c>
+      <c r="K328" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L328" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M328" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="B328" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="C328" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D328" s="12" t="s">
-        <v>694</v>
-      </c>
-      <c r="E328" s="13">
-        <v>1404.6</v>
-      </c>
-      <c r="F328" s="13">
+      <c r="N328" s="3">
         <v>1359.8</v>
       </c>
-      <c r="G328" s="13">
-        <v>1397.4</v>
-      </c>
-      <c r="H328" s="13">
-        <v>1397.4</v>
-      </c>
-      <c r="I328" s="13">
-        <v>1359.8</v>
-      </c>
-      <c r="J328" s="13">
-        <v>1435</v>
-      </c>
-      <c r="K328" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L328" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M328" s="12"/>
-      <c r="N328" s="12"/>
-      <c r="O328" s="12"/>
-      <c r="P328" s="12"/>
-      <c r="Q328" s="12"/>
-      <c r="R328" s="12" t="s">
-        <v>737</v>
+      <c r="O328" s="2">
+        <v>24</v>
+      </c>
+      <c r="P328" s="4">
+        <v>-37.6</v>
+      </c>
+      <c r="Q328" s="5">
+        <v>-2.691</v>
+      </c>
+      <c r="R328" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>371</v>
@@ -21213,7 +21435,7 @@
         <v>20</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E329" s="3">
         <v>5766</v>
@@ -21240,7 +21462,7 @@
         <v>23</v>
       </c>
       <c r="M329" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N329" s="3">
         <v>5700.5</v>
@@ -21260,16 +21482,16 @@
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E330" s="3">
         <v>972.9</v>
@@ -21296,7 +21518,7 @@
         <v>23</v>
       </c>
       <c r="M330" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N330" s="3">
         <v>957</v>
@@ -21316,7 +21538,7 @@
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>250</v>
@@ -21325,7 +21547,7 @@
         <v>20</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E331" s="3">
         <v>182.1</v>
@@ -21352,7 +21574,7 @@
         <v>23</v>
       </c>
       <c r="M331" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N331" s="3">
         <v>179.09</v>
@@ -21372,7 +21594,7 @@
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>113</v>
@@ -21381,7 +21603,7 @@
         <v>20</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E332" s="3">
         <v>101.79</v>
@@ -21408,7 +21630,7 @@
         <v>23</v>
       </c>
       <c r="M332" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N332" s="3">
         <v>100.44</v>
@@ -21428,16 +21650,16 @@
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B333" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E333" s="3">
         <v>4502.9</v>
@@ -21464,7 +21686,7 @@
         <v>23</v>
       </c>
       <c r="M333" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N333" s="3">
         <v>4366</v>
@@ -21484,7 +21706,7 @@
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>221</v>
@@ -21493,7 +21715,7 @@
         <v>20</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E334" s="3">
         <v>1201.5</v>
@@ -21505,13 +21727,13 @@
         <v>1199</v>
       </c>
       <c r="H334" s="3">
-        <v>1198.8</v>
+        <v>1199</v>
       </c>
       <c r="I334" s="3">
         <v>1186.1</v>
       </c>
       <c r="J334" s="3">
-        <v>1211.5</v>
+        <v>1211.9</v>
       </c>
       <c r="K334" s="2" t="s">
         <v>22</v>
@@ -21520,7 +21742,7 @@
         <v>23</v>
       </c>
       <c r="M334" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="N334" s="3">
         <v>1186.1</v>
@@ -21529,10 +21751,10 @@
         <v>19</v>
       </c>
       <c r="P334" s="4">
-        <v>-12.7</v>
+        <v>-12.9</v>
       </c>
       <c r="Q334" s="5">
-        <v>-1.059</v>
+        <v>-1.076</v>
       </c>
       <c r="R334" s="2" t="s">
         <v>25</v>
@@ -21540,7 +21762,7 @@
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>121</v>
@@ -21549,7 +21771,7 @@
         <v>20</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E335" s="3">
         <v>498.5</v>
@@ -21576,7 +21798,7 @@
         <v>23</v>
       </c>
       <c r="M335" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="N335" s="3">
         <v>488.8</v>
@@ -21596,7 +21818,7 @@
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A336" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>486</v>
@@ -21605,7 +21827,7 @@
         <v>64</v>
       </c>
       <c r="D336" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E336" s="7">
         <v>3302.4</v>
@@ -21632,7 +21854,7 @@
         <v>33</v>
       </c>
       <c r="M336" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N336" s="7">
         <v>3227.4</v>
@@ -21651,100 +21873,120 @@
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A337" s="12" t="s">
+      <c r="A337" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="E337" s="3">
+        <v>1488.6</v>
+      </c>
+      <c r="F337" s="3">
+        <v>1449.1</v>
+      </c>
+      <c r="G337" s="3">
+        <v>1480.4</v>
+      </c>
+      <c r="H337" s="3">
+        <v>1481</v>
+      </c>
+      <c r="I337" s="3">
+        <v>1449.1</v>
+      </c>
+      <c r="J337" s="3">
+        <v>1512.9</v>
+      </c>
+      <c r="K337" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L337" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M337" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="N337" s="3">
+        <v>1449.1</v>
+      </c>
+      <c r="O337" s="2">
+        <v>24</v>
+      </c>
+      <c r="P337" s="4">
+        <v>-31.9</v>
+      </c>
+      <c r="Q337" s="5">
+        <v>-2.154</v>
+      </c>
+      <c r="R337" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A338" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="B337" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="C337" s="12" t="s">
+      <c r="B338" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C338" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D337" s="12" t="s">
-        <v>694</v>
-      </c>
-      <c r="E337" s="13">
-        <v>1488.6</v>
-      </c>
-      <c r="F337" s="13">
-        <v>1449.1</v>
-      </c>
-      <c r="G337" s="13">
-        <v>1480.4</v>
-      </c>
-      <c r="H337" s="13">
-        <v>1481</v>
-      </c>
-      <c r="I337" s="13">
-        <v>1449.1</v>
-      </c>
-      <c r="J337" s="13">
-        <v>1512.9</v>
-      </c>
-      <c r="K337" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L337" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M337" s="12"/>
-      <c r="N337" s="12"/>
-      <c r="O337" s="12"/>
-      <c r="P337" s="12"/>
-      <c r="Q337" s="12"/>
-      <c r="R337" s="12" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A338" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="B338" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="C338" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D338" s="12" t="s">
-        <v>694</v>
-      </c>
-      <c r="E338" s="13">
+      <c r="D338" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="E338" s="3">
         <v>149.2</v>
       </c>
-      <c r="F338" s="13">
+      <c r="F338" s="3">
         <v>144.85</v>
       </c>
-      <c r="G338" s="13">
+      <c r="G338" s="3">
         <v>148.35</v>
       </c>
-      <c r="H338" s="13">
+      <c r="H338" s="3">
         <v>148.37</v>
       </c>
-      <c r="I338" s="13">
+      <c r="I338" s="3">
         <v>144.85</v>
       </c>
-      <c r="J338" s="13">
+      <c r="J338" s="3">
         <v>151.89</v>
       </c>
-      <c r="K338" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L338" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M338" s="12"/>
-      <c r="N338" s="12"/>
-      <c r="O338" s="12"/>
-      <c r="P338" s="12"/>
-      <c r="Q338" s="12"/>
-      <c r="R338" s="12" t="s">
-        <v>737</v>
+      <c r="K338" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L338" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M338" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="N338" s="3">
+        <v>144.85</v>
+      </c>
+      <c r="O338" s="2">
+        <v>24</v>
+      </c>
+      <c r="P338" s="4">
+        <v>-3.52</v>
+      </c>
+      <c r="Q338" s="5">
+        <v>-2.372</v>
+      </c>
+      <c r="R338" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>467</v>
@@ -21753,7 +21995,7 @@
         <v>20</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E339" s="3">
         <v>125.98</v>
@@ -21780,7 +22022,7 @@
         <v>23</v>
       </c>
       <c r="M339" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N339" s="3">
         <v>122.85</v>
@@ -21800,16 +22042,16 @@
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E340" s="3">
         <v>3344.6</v>
@@ -21836,7 +22078,7 @@
         <v>23</v>
       </c>
       <c r="M340" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="N340" s="3">
         <v>3284</v>
@@ -21856,16 +22098,16 @@
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B341" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E341" s="3">
         <v>42.06</v>
@@ -21892,7 +22134,7 @@
         <v>23</v>
       </c>
       <c r="M341" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="N341" s="3">
         <v>41.49</v>
@@ -21911,49 +22153,59 @@
       </c>
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A342" s="12" t="s">
+      <c r="A342" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="E342" s="7">
+        <v>390.35</v>
+      </c>
+      <c r="F342" s="7">
+        <v>382.35</v>
+      </c>
+      <c r="G342" s="7">
+        <v>389</v>
+      </c>
+      <c r="H342" s="7">
+        <v>389</v>
+      </c>
+      <c r="I342" s="7">
+        <v>382.35</v>
+      </c>
+      <c r="J342" s="7">
+        <v>395.65</v>
+      </c>
+      <c r="K342" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L342" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M342" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="B342" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="C342" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D342" s="12" t="s">
-        <v>694</v>
-      </c>
-      <c r="E342" s="13">
-        <v>390.35</v>
-      </c>
-      <c r="F342" s="13">
-        <v>382.35</v>
-      </c>
-      <c r="G342" s="13">
-        <v>389</v>
-      </c>
-      <c r="H342" s="13">
-        <v>389</v>
-      </c>
-      <c r="I342" s="13">
-        <v>382.35</v>
-      </c>
-      <c r="J342" s="13">
+      <c r="N342" s="7">
         <v>395.65</v>
       </c>
-      <c r="K342" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L342" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M342" s="12"/>
-      <c r="N342" s="12"/>
-      <c r="O342" s="12"/>
-      <c r="P342" s="12"/>
-      <c r="Q342" s="12"/>
-      <c r="R342" s="12" t="s">
-        <v>737</v>
+      <c r="O342" s="6">
+        <v>28</v>
+      </c>
+      <c r="P342" s="8">
+        <v>6.65</v>
+      </c>
+      <c r="Q342" s="9">
+        <v>1.71</v>
+      </c>
+      <c r="R342" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.25">
@@ -22050,7 +22302,7 @@
         <v>23</v>
       </c>
       <c r="M344" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N344" s="3">
         <v>3789</v>
@@ -22079,7 +22331,7 @@
         <v>64</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E345" s="3">
         <v>1114.4</v>
@@ -22106,7 +22358,7 @@
         <v>23</v>
       </c>
       <c r="M345" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="N345" s="3">
         <v>1114.4</v>
@@ -22162,7 +22414,7 @@
         <v>33</v>
       </c>
       <c r="M346" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N346" s="7">
         <v>71.62</v>
@@ -22203,13 +22455,13 @@
         <v>24940</v>
       </c>
       <c r="H347" s="3">
-        <v>24950</v>
+        <v>24940</v>
       </c>
       <c r="I347" s="3">
         <v>25165</v>
       </c>
       <c r="J347" s="3">
-        <v>24735</v>
+        <v>24715</v>
       </c>
       <c r="K347" s="2" t="s">
         <v>22</v>
@@ -22227,10 +22479,10 @@
         <v>11</v>
       </c>
       <c r="P347" s="4">
-        <v>-215</v>
+        <v>-225</v>
       </c>
       <c r="Q347" s="5">
-        <v>-0.862</v>
+        <v>-0.902</v>
       </c>
       <c r="R347" s="2" t="s">
         <v>25</v>
@@ -22247,7 +22499,7 @@
         <v>64</v>
       </c>
       <c r="D348" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E348" s="7">
         <v>2078.5</v>
@@ -22303,7 +22555,7 @@
         <v>64</v>
       </c>
       <c r="D349" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E349" s="7">
         <v>2100.6</v>
@@ -22409,13 +22661,13 @@
         <v>773</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E351" s="3">
         <v>5645.5</v>
@@ -22442,7 +22694,7 @@
         <v>23</v>
       </c>
       <c r="M351" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="N351" s="3">
         <v>5600</v>
@@ -22471,7 +22723,7 @@
         <v>20</v>
       </c>
       <c r="D352" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E352" s="7">
         <v>1740.6</v>
@@ -22521,13 +22773,13 @@
         <v>776</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E353" s="3">
         <v>184.31</v>
@@ -22554,7 +22806,7 @@
         <v>23</v>
       </c>
       <c r="M353" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="N353" s="3">
         <v>183.1</v>
@@ -22577,13 +22829,13 @@
         <v>777</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E354" s="3">
         <v>254</v>
@@ -22595,13 +22847,13 @@
         <v>252.95</v>
       </c>
       <c r="H354" s="3">
-        <v>252.9</v>
+        <v>252.95</v>
       </c>
       <c r="I354" s="3">
         <v>254</v>
       </c>
       <c r="J354" s="3">
-        <v>251.8</v>
+        <v>251.9</v>
       </c>
       <c r="K354" s="2" t="s">
         <v>22</v>
@@ -22619,10 +22871,10 @@
         <v>1</v>
       </c>
       <c r="P354" s="4">
-        <v>-1.1</v>
+        <v>-1.05</v>
       </c>
       <c r="Q354" s="5">
-        <v>-0.435</v>
+        <v>-0.415</v>
       </c>
       <c r="R354" s="2" t="s">
         <v>25</v>
@@ -22639,7 +22891,7 @@
         <v>64</v>
       </c>
       <c r="D355" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E355" s="7">
         <v>312.95</v>
@@ -22685,286 +22937,2300 @@
       </c>
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A356" s="12" t="s">
+      <c r="A356" s="6" t="s">
         <v>779</v>
       </c>
-      <c r="B356" s="12" t="s">
+      <c r="B356" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C356" s="12" t="s">
+      <c r="C356" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D356" s="12" t="s">
+      <c r="D356" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="E356" s="13">
+      <c r="E356" s="7">
         <v>766.05</v>
       </c>
-      <c r="F356" s="13">
+      <c r="F356" s="7">
         <v>760.2</v>
       </c>
-      <c r="G356" s="13">
+      <c r="G356" s="7">
         <v>760.4</v>
       </c>
-      <c r="H356" s="13">
+      <c r="H356" s="7">
         <v>760.45</v>
       </c>
-      <c r="I356" s="13">
+      <c r="I356" s="7">
         <v>766.05</v>
       </c>
-      <c r="J356" s="13">
+      <c r="J356" s="7">
         <v>754.85</v>
       </c>
-      <c r="K356" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L356" s="12" t="s">
+      <c r="K356" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L356" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M356" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="N356" s="7">
+        <v>754.85</v>
+      </c>
+      <c r="O356" s="6">
+        <v>1</v>
+      </c>
+      <c r="P356" s="8">
+        <v>5.6</v>
+      </c>
+      <c r="Q356" s="9">
+        <v>0.736</v>
+      </c>
+      <c r="R356" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A357" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="E357" s="7">
+        <v>499.4</v>
+      </c>
+      <c r="F357" s="7">
+        <v>494.2</v>
+      </c>
+      <c r="G357" s="7">
+        <v>494.75</v>
+      </c>
+      <c r="H357" s="7">
+        <v>494.7</v>
+      </c>
+      <c r="I357" s="7">
+        <v>499.4</v>
+      </c>
+      <c r="J357" s="7">
+        <v>490</v>
+      </c>
+      <c r="K357" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L357" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M357" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="N357" s="7">
+        <v>490</v>
+      </c>
+      <c r="O357" s="6">
+        <v>1</v>
+      </c>
+      <c r="P357" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="Q357" s="9">
+        <v>0.95</v>
+      </c>
+      <c r="R357" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A358" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="E358" s="7">
+        <v>299.95</v>
+      </c>
+      <c r="F358" s="7">
+        <v>297.15</v>
+      </c>
+      <c r="G358" s="7">
+        <v>297.45</v>
+      </c>
+      <c r="H358" s="7">
+        <v>297.3</v>
+      </c>
+      <c r="I358" s="7">
+        <v>299.95</v>
+      </c>
+      <c r="J358" s="7">
+        <v>294.65</v>
+      </c>
+      <c r="K358" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L358" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M358" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="N358" s="7">
+        <v>294.65</v>
+      </c>
+      <c r="O358" s="6">
+        <v>1</v>
+      </c>
+      <c r="P358" s="8">
+        <v>2.65</v>
+      </c>
+      <c r="Q358" s="9">
+        <v>0.891</v>
+      </c>
+      <c r="R358" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A359" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="E359" s="7">
+        <v>121.74</v>
+      </c>
+      <c r="F359" s="7">
+        <v>121.01</v>
+      </c>
+      <c r="G359" s="7">
+        <v>121.01</v>
+      </c>
+      <c r="H359" s="7">
+        <v>121.02</v>
+      </c>
+      <c r="I359" s="7">
+        <v>121.74</v>
+      </c>
+      <c r="J359" s="7">
+        <v>120.3</v>
+      </c>
+      <c r="K359" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L359" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M359" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="N359" s="7">
+        <v>120.3</v>
+      </c>
+      <c r="O359" s="6">
+        <v>1</v>
+      </c>
+      <c r="P359" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="Q359" s="9">
+        <v>0.595</v>
+      </c>
+      <c r="R359" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A360" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="E360" s="7">
+        <v>626.75</v>
+      </c>
+      <c r="F360" s="7">
+        <v>623.05</v>
+      </c>
+      <c r="G360" s="7">
+        <v>624.1</v>
+      </c>
+      <c r="H360" s="7">
+        <v>623.8</v>
+      </c>
+      <c r="I360" s="7">
+        <v>626.75</v>
+      </c>
+      <c r="J360" s="7">
+        <v>620.85</v>
+      </c>
+      <c r="K360" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L360" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M360" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="N360" s="7">
+        <v>620.85</v>
+      </c>
+      <c r="O360" s="6">
+        <v>1</v>
+      </c>
+      <c r="P360" s="8">
+        <v>2.95</v>
+      </c>
+      <c r="Q360" s="9">
+        <v>0.473</v>
+      </c>
+      <c r="R360" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A361" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E361" s="3">
+        <v>31745</v>
+      </c>
+      <c r="F361" s="3">
+        <v>31480</v>
+      </c>
+      <c r="G361" s="3">
+        <v>31745</v>
+      </c>
+      <c r="H361" s="3">
+        <v>31550</v>
+      </c>
+      <c r="I361" s="3">
+        <v>31480</v>
+      </c>
+      <c r="J361" s="3">
+        <v>31620</v>
+      </c>
+      <c r="K361" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L361" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M361" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="M356" s="12"/>
-      <c r="N356" s="12"/>
-      <c r="O356" s="12"/>
-      <c r="P356" s="12"/>
-      <c r="Q356" s="12"/>
-      <c r="R356" s="12" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A357" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="B357" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="C357" s="12" t="s">
+      <c r="N361" s="3">
+        <v>31480</v>
+      </c>
+      <c r="O361" s="2">
+        <v>1</v>
+      </c>
+      <c r="P361" s="4">
+        <v>-70</v>
+      </c>
+      <c r="Q361" s="5">
+        <v>-0.222</v>
+      </c>
+      <c r="R361" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A362" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C362" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D357" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="E357" s="13">
-        <v>499.4</v>
-      </c>
-      <c r="F357" s="13">
-        <v>494.2</v>
-      </c>
-      <c r="G357" s="13">
-        <v>494.75</v>
-      </c>
-      <c r="H357" s="13">
-        <v>494.7</v>
-      </c>
-      <c r="I357" s="13">
-        <v>499.4</v>
-      </c>
-      <c r="J357" s="13">
+      <c r="D362" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E362" s="3">
+        <v>2440</v>
+      </c>
+      <c r="F362" s="3">
+        <v>2408.4</v>
+      </c>
+      <c r="G362" s="3">
+        <v>2423.5</v>
+      </c>
+      <c r="H362" s="3">
+        <v>2423.4</v>
+      </c>
+      <c r="I362" s="3">
+        <v>2440</v>
+      </c>
+      <c r="J362" s="3">
+        <v>2406.8</v>
+      </c>
+      <c r="K362" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L362" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M362" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="N362" s="3">
+        <v>2440</v>
+      </c>
+      <c r="O362" s="2">
+        <v>1</v>
+      </c>
+      <c r="P362" s="4">
+        <v>-16.6</v>
+      </c>
+      <c r="Q362" s="5">
+        <v>-0.685</v>
+      </c>
+      <c r="R362" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A363" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E363" s="3">
+        <v>910</v>
+      </c>
+      <c r="F363" s="3">
+        <v>890</v>
+      </c>
+      <c r="G363" s="3">
+        <v>898.4</v>
+      </c>
+      <c r="H363" s="3">
+        <v>897.6</v>
+      </c>
+      <c r="I363" s="3">
+        <v>910</v>
+      </c>
+      <c r="J363" s="3">
+        <v>885.2</v>
+      </c>
+      <c r="K363" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L363" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M363" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="N363" s="3">
+        <v>910</v>
+      </c>
+      <c r="O363" s="2">
+        <v>4</v>
+      </c>
+      <c r="P363" s="4">
+        <v>-12.4</v>
+      </c>
+      <c r="Q363" s="5">
+        <v>-1.381</v>
+      </c>
+      <c r="R363" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="364" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A364" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E364" s="3">
+        <v>2529.7</v>
+      </c>
+      <c r="F364" s="3">
+        <v>2481</v>
+      </c>
+      <c r="G364" s="3">
+        <v>2496</v>
+      </c>
+      <c r="H364" s="3">
+        <v>2496.7</v>
+      </c>
+      <c r="I364" s="3">
+        <v>2529.7</v>
+      </c>
+      <c r="J364" s="3">
+        <v>2463.7</v>
+      </c>
+      <c r="K364" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L364" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M364" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="N364" s="3">
+        <v>2529.7</v>
+      </c>
+      <c r="O364" s="2">
+        <v>15</v>
+      </c>
+      <c r="P364" s="4">
+        <v>-33</v>
+      </c>
+      <c r="Q364" s="5">
+        <v>-1.322</v>
+      </c>
+      <c r="R364" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="365" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A365" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D365" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="E365" s="7">
+        <v>2997.2</v>
+      </c>
+      <c r="F365" s="7">
+        <v>2962.7</v>
+      </c>
+      <c r="G365" s="7">
+        <v>2967.9</v>
+      </c>
+      <c r="H365" s="7">
+        <v>2965.8</v>
+      </c>
+      <c r="I365" s="7">
+        <v>2997.2</v>
+      </c>
+      <c r="J365" s="7">
+        <v>2934.4</v>
+      </c>
+      <c r="K365" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L365" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M365" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="N365" s="7">
+        <v>2934.4</v>
+      </c>
+      <c r="O365" s="6">
+        <v>24</v>
+      </c>
+      <c r="P365" s="8">
+        <v>31.4</v>
+      </c>
+      <c r="Q365" s="9">
+        <v>1.059</v>
+      </c>
+      <c r="R365" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="366" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A366" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E366" s="3">
+        <v>1929</v>
+      </c>
+      <c r="F366" s="3">
+        <v>1910</v>
+      </c>
+      <c r="G366" s="3">
+        <v>1913.2</v>
+      </c>
+      <c r="H366" s="3">
+        <v>1912.1</v>
+      </c>
+      <c r="I366" s="3">
+        <v>1929</v>
+      </c>
+      <c r="J366" s="3">
+        <v>1895.2</v>
+      </c>
+      <c r="K366" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L366" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M366" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="N366" s="3">
+        <v>1929</v>
+      </c>
+      <c r="O366" s="2">
+        <v>11</v>
+      </c>
+      <c r="P366" s="4">
+        <v>-16.9</v>
+      </c>
+      <c r="Q366" s="5">
+        <v>-0.884</v>
+      </c>
+      <c r="R366" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="367" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A367" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E367" s="3">
+        <v>1023</v>
+      </c>
+      <c r="F367" s="3">
+        <v>1008.1</v>
+      </c>
+      <c r="G367" s="3">
+        <v>1014.7</v>
+      </c>
+      <c r="H367" s="3">
+        <v>1014.7</v>
+      </c>
+      <c r="I367" s="3">
+        <v>1023</v>
+      </c>
+      <c r="J367" s="3">
+        <v>1006.4</v>
+      </c>
+      <c r="K367" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L367" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M367" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="N367" s="3">
+        <v>1023</v>
+      </c>
+      <c r="O367" s="2">
+        <v>4</v>
+      </c>
+      <c r="P367" s="4">
+        <v>-8.3</v>
+      </c>
+      <c r="Q367" s="5">
+        <v>-0.818</v>
+      </c>
+      <c r="R367" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="368" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A368" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E368" s="3">
+        <v>486</v>
+      </c>
+      <c r="F368" s="3">
+        <v>480.75</v>
+      </c>
+      <c r="G368" s="3">
+        <v>485.9</v>
+      </c>
+      <c r="H368" s="3">
+        <v>485.75</v>
+      </c>
+      <c r="I368" s="3">
+        <v>480.75</v>
+      </c>
+      <c r="J368" s="3">
+        <v>490.75</v>
+      </c>
+      <c r="K368" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L368" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M368" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="N368" s="3">
+        <v>480.75</v>
+      </c>
+      <c r="O368" s="2">
+        <v>10</v>
+      </c>
+      <c r="P368" s="4">
+        <v>-5</v>
+      </c>
+      <c r="Q368" s="5">
+        <v>-1.029</v>
+      </c>
+      <c r="R368" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="369" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A369" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="B369" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D369" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="E369" s="7">
+        <v>387.5</v>
+      </c>
+      <c r="F369" s="7">
+        <v>383.4</v>
+      </c>
+      <c r="G369" s="7">
+        <v>387.45</v>
+      </c>
+      <c r="H369" s="7">
+        <v>387.35</v>
+      </c>
+      <c r="I369" s="7">
+        <v>383.4</v>
+      </c>
+      <c r="J369" s="7">
+        <v>391.3</v>
+      </c>
+      <c r="K369" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L369" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M369" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="N369" s="7">
+        <v>391.3</v>
+      </c>
+      <c r="O369" s="6">
+        <v>12</v>
+      </c>
+      <c r="P369" s="8">
+        <v>3.95</v>
+      </c>
+      <c r="Q369" s="9">
+        <v>1.02</v>
+      </c>
+      <c r="R369" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="370" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A370" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E370" s="3">
+        <v>7609</v>
+      </c>
+      <c r="F370" s="3">
+        <v>7549.5</v>
+      </c>
+      <c r="G370" s="3">
+        <v>7557</v>
+      </c>
+      <c r="H370" s="3">
+        <v>7553.5</v>
+      </c>
+      <c r="I370" s="3">
+        <v>7609</v>
+      </c>
+      <c r="J370" s="3">
+        <v>7498</v>
+      </c>
+      <c r="K370" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L370" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M370" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="N370" s="3">
+        <v>7609</v>
+      </c>
+      <c r="O370" s="2">
+        <v>7</v>
+      </c>
+      <c r="P370" s="4">
+        <v>-55.5</v>
+      </c>
+      <c r="Q370" s="5">
+        <v>-0.735</v>
+      </c>
+      <c r="R370" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="371" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A371" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="E371" s="3">
+        <v>408.95</v>
+      </c>
+      <c r="F371" s="3">
+        <v>401.65</v>
+      </c>
+      <c r="G371" s="3">
+        <v>407</v>
+      </c>
+      <c r="H371" s="3">
+        <v>407.15</v>
+      </c>
+      <c r="I371" s="3">
+        <v>401.65</v>
+      </c>
+      <c r="J371" s="3">
+        <v>412.65</v>
+      </c>
+      <c r="K371" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L371" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M371" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="N371" s="3">
+        <v>401.65</v>
+      </c>
+      <c r="O371" s="2">
+        <v>7</v>
+      </c>
+      <c r="P371" s="4">
+        <v>-5.5</v>
+      </c>
+      <c r="Q371" s="5">
+        <v>-1.351</v>
+      </c>
+      <c r="R371" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="372" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A372" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="B372" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D372" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="E372" s="7">
+        <v>918.75</v>
+      </c>
+      <c r="F372" s="7">
+        <v>911.5</v>
+      </c>
+      <c r="G372" s="7">
+        <v>915</v>
+      </c>
+      <c r="H372" s="7">
+        <v>915</v>
+      </c>
+      <c r="I372" s="7">
+        <v>918.75</v>
+      </c>
+      <c r="J372" s="7">
+        <v>911.25</v>
+      </c>
+      <c r="K372" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L372" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M372" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="N372" s="7">
+        <v>911.25</v>
+      </c>
+      <c r="O372" s="6">
+        <v>1</v>
+      </c>
+      <c r="P372" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="Q372" s="9">
+        <v>0.41</v>
+      </c>
+      <c r="R372" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="373" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A373" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="E373" s="3">
+        <v>1344</v>
+      </c>
+      <c r="F373" s="3">
+        <v>1339.2</v>
+      </c>
+      <c r="G373" s="3">
+        <v>1340.6</v>
+      </c>
+      <c r="H373" s="3">
+        <v>1340.8</v>
+      </c>
+      <c r="I373" s="3">
+        <v>1344</v>
+      </c>
+      <c r="J373" s="3">
+        <v>1337.6</v>
+      </c>
+      <c r="K373" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L373" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M373" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="N373" s="3">
+        <v>1344</v>
+      </c>
+      <c r="O373" s="2">
+        <v>1</v>
+      </c>
+      <c r="P373" s="4">
+        <v>-3.2</v>
+      </c>
+      <c r="Q373" s="5">
+        <v>-0.239</v>
+      </c>
+      <c r="R373" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="374" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A374" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D374" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="E374" s="7">
+        <v>1191.2</v>
+      </c>
+      <c r="F374" s="7">
+        <v>1184</v>
+      </c>
+      <c r="G374" s="7">
+        <v>1188.7</v>
+      </c>
+      <c r="H374" s="7">
+        <v>1189</v>
+      </c>
+      <c r="I374" s="7">
+        <v>1191.2</v>
+      </c>
+      <c r="J374" s="7">
+        <v>1186.8</v>
+      </c>
+      <c r="K374" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L374" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M374" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="N374" s="7">
+        <v>1186.8</v>
+      </c>
+      <c r="O374" s="6">
+        <v>1</v>
+      </c>
+      <c r="P374" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="Q374" s="9">
+        <v>0.185</v>
+      </c>
+      <c r="R374" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="375" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A375" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="B375" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="K357" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L357" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M357" s="12"/>
-      <c r="N357" s="12"/>
-      <c r="O357" s="12"/>
-      <c r="P357" s="12"/>
-      <c r="Q357" s="12"/>
-      <c r="R357" s="12" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A358" s="12" t="s">
-        <v>782</v>
-      </c>
-      <c r="B358" s="12" t="s">
-        <v>783</v>
-      </c>
-      <c r="C358" s="12" t="s">
+      <c r="C375" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D358" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="E358" s="13">
-        <v>299.95</v>
-      </c>
-      <c r="F358" s="13">
-        <v>297.15</v>
-      </c>
-      <c r="G358" s="13">
-        <v>297.45</v>
-      </c>
-      <c r="H358" s="13">
-        <v>297.3</v>
-      </c>
-      <c r="I358" s="13">
-        <v>299.95</v>
-      </c>
-      <c r="J358" s="13">
-        <v>294.65</v>
-      </c>
-      <c r="K358" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L358" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M358" s="12"/>
-      <c r="N358" s="12"/>
-      <c r="O358" s="12"/>
-      <c r="P358" s="12"/>
-      <c r="Q358" s="12"/>
-      <c r="R358" s="12" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A359" s="12" t="s">
-        <v>784</v>
-      </c>
-      <c r="B359" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="C359" s="12" t="s">
+      <c r="D375" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="E375" s="7">
+        <v>1458.5</v>
+      </c>
+      <c r="F375" s="7">
+        <v>1450.2</v>
+      </c>
+      <c r="G375" s="7">
+        <v>1455.8</v>
+      </c>
+      <c r="H375" s="7">
+        <v>1456.6</v>
+      </c>
+      <c r="I375" s="7">
+        <v>1458.5</v>
+      </c>
+      <c r="J375" s="7">
+        <v>1454.7</v>
+      </c>
+      <c r="K375" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L375" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M375" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="N375" s="7">
+        <v>1454.7</v>
+      </c>
+      <c r="O375" s="6">
+        <v>1</v>
+      </c>
+      <c r="P375" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="Q375" s="9">
+        <v>0.13</v>
+      </c>
+      <c r="R375" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="376" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A376" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="E376" s="3">
+        <v>1897.5</v>
+      </c>
+      <c r="F376" s="3">
+        <v>1883.9</v>
+      </c>
+      <c r="G376" s="3">
+        <v>1896.7</v>
+      </c>
+      <c r="H376" s="3">
+        <v>1896.7</v>
+      </c>
+      <c r="I376" s="3">
+        <v>1883.9</v>
+      </c>
+      <c r="J376" s="3">
+        <v>1909.5</v>
+      </c>
+      <c r="K376" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L376" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M376" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="N376" s="3">
+        <v>1883.9</v>
+      </c>
+      <c r="O376" s="2">
+        <v>1</v>
+      </c>
+      <c r="P376" s="4">
+        <v>-12.8</v>
+      </c>
+      <c r="Q376" s="5">
+        <v>-0.675</v>
+      </c>
+      <c r="R376" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="377" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A377" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C377" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D359" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="E359" s="13">
-        <v>121.74</v>
-      </c>
-      <c r="F359" s="13">
-        <v>121.01</v>
-      </c>
-      <c r="G359" s="13">
-        <v>121.01</v>
-      </c>
-      <c r="H359" s="13">
-        <v>121.02</v>
-      </c>
-      <c r="I359" s="13">
-        <v>121.74</v>
-      </c>
-      <c r="J359" s="13">
-        <v>120.3</v>
-      </c>
-      <c r="K359" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L359" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M359" s="12"/>
-      <c r="N359" s="12"/>
-      <c r="O359" s="12"/>
-      <c r="P359" s="12"/>
-      <c r="Q359" s="12"/>
-      <c r="R359" s="12" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A360" s="12" t="s">
-        <v>785</v>
-      </c>
-      <c r="B360" s="12" t="s">
-        <v>786</v>
-      </c>
-      <c r="C360" s="12" t="s">
+      <c r="D377" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="E377" s="7">
+        <v>3713.7</v>
+      </c>
+      <c r="F377" s="7">
+        <v>3694.6</v>
+      </c>
+      <c r="G377" s="7">
+        <v>3700.8</v>
+      </c>
+      <c r="H377" s="7">
+        <v>3702.5</v>
+      </c>
+      <c r="I377" s="7">
+        <v>3713.7</v>
+      </c>
+      <c r="J377" s="7">
+        <v>3691.3</v>
+      </c>
+      <c r="K377" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L377" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M377" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="N377" s="7">
+        <v>3691.3</v>
+      </c>
+      <c r="O377" s="6">
+        <v>1</v>
+      </c>
+      <c r="P377" s="8">
+        <v>11.2</v>
+      </c>
+      <c r="Q377" s="9">
+        <v>0.302</v>
+      </c>
+      <c r="R377" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="378" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A378" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C378" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D360" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="E360" s="13">
-        <v>626.75</v>
-      </c>
-      <c r="F360" s="13">
-        <v>623.05</v>
-      </c>
-      <c r="G360" s="13">
-        <v>624.1</v>
-      </c>
-      <c r="H360" s="13">
-        <v>623.8</v>
-      </c>
-      <c r="I360" s="13">
-        <v>626.75</v>
-      </c>
-      <c r="J360" s="13">
-        <v>620.85</v>
-      </c>
-      <c r="K360" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L360" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M360" s="12"/>
-      <c r="N360" s="12"/>
-      <c r="O360" s="12"/>
-      <c r="P360" s="12"/>
-      <c r="Q360" s="12"/>
-      <c r="R360" s="12" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A361" s="12" t="s">
-        <v>787</v>
-      </c>
-      <c r="B361" s="12" t="s">
-        <v>679</v>
-      </c>
-      <c r="C361" s="12" t="s">
+      <c r="D378" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="E378" s="7">
+        <v>3433.9</v>
+      </c>
+      <c r="F378" s="7">
+        <v>3419</v>
+      </c>
+      <c r="G378" s="7">
+        <v>3426.1</v>
+      </c>
+      <c r="H378" s="7">
+        <v>3426.5</v>
+      </c>
+      <c r="I378" s="7">
+        <v>3433.9</v>
+      </c>
+      <c r="J378" s="7">
+        <v>3419.1</v>
+      </c>
+      <c r="K378" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L378" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M378" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="N378" s="7">
+        <v>3419.1</v>
+      </c>
+      <c r="O378" s="6">
+        <v>1</v>
+      </c>
+      <c r="P378" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="Q378" s="9">
+        <v>0.216</v>
+      </c>
+      <c r="R378" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="379" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A379" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C379" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D361" s="12" t="s">
-        <v>775</v>
-      </c>
-      <c r="E361" s="13">
-        <v>31745</v>
-      </c>
-      <c r="F361" s="13">
-        <v>31480</v>
-      </c>
-      <c r="G361" s="13">
-        <v>31745</v>
-      </c>
-      <c r="H361" s="12"/>
-      <c r="I361" s="13">
-        <v>31480</v>
-      </c>
-      <c r="J361" s="12"/>
-      <c r="K361" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L361" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="M361" s="12"/>
-      <c r="N361" s="12"/>
-      <c r="O361" s="12"/>
-      <c r="P361" s="12"/>
-      <c r="Q361" s="12"/>
-      <c r="R361" s="12" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A363" s="14" t="s">
-        <v>789</v>
-      </c>
-      <c r="P363" s="15">
-        <v>-614.28</v>
-      </c>
-      <c r="R363" s="14" t="s">
-        <v>790</v>
+      <c r="D379" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="E379" s="7">
+        <v>1019</v>
+      </c>
+      <c r="F379" s="7">
+        <v>1002.7</v>
+      </c>
+      <c r="G379" s="7">
+        <v>1011.9</v>
+      </c>
+      <c r="H379" s="7">
+        <v>1008.1</v>
+      </c>
+      <c r="I379" s="7">
+        <v>1002.7</v>
+      </c>
+      <c r="J379" s="7">
+        <v>1013.5</v>
+      </c>
+      <c r="K379" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L379" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M379" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="N379" s="7">
+        <v>1013.5</v>
+      </c>
+      <c r="O379" s="6">
+        <v>1</v>
+      </c>
+      <c r="P379" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="Q379" s="9">
+        <v>0.536</v>
+      </c>
+      <c r="R379" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="380" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A380" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D380" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="E380" s="7">
+        <v>213.77</v>
+      </c>
+      <c r="F380" s="7">
+        <v>212.36</v>
+      </c>
+      <c r="G380" s="7">
+        <v>212.8</v>
+      </c>
+      <c r="H380" s="7">
+        <v>212.82</v>
+      </c>
+      <c r="I380" s="7">
+        <v>213.77</v>
+      </c>
+      <c r="J380" s="7">
+        <v>211.87</v>
+      </c>
+      <c r="K380" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L380" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M380" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="N380" s="7">
+        <v>211.87</v>
+      </c>
+      <c r="O380" s="6">
+        <v>1</v>
+      </c>
+      <c r="P380" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="Q380" s="9">
+        <v>0.446</v>
+      </c>
+      <c r="R380" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="381" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A381" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="E381" s="3">
+        <v>1366</v>
+      </c>
+      <c r="F381" s="3">
+        <v>1356.1</v>
+      </c>
+      <c r="G381" s="3">
+        <v>1356.7</v>
+      </c>
+      <c r="H381" s="3">
+        <v>1350</v>
+      </c>
+      <c r="I381" s="3">
+        <v>1366</v>
+      </c>
+      <c r="J381" s="3">
+        <v>1334</v>
+      </c>
+      <c r="K381" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L381" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M381" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="N381" s="3">
+        <v>1366</v>
+      </c>
+      <c r="O381" s="2">
+        <v>1</v>
+      </c>
+      <c r="P381" s="4">
+        <v>-16</v>
+      </c>
+      <c r="Q381" s="5">
+        <v>-1.185</v>
+      </c>
+      <c r="R381" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="382" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E382" s="3">
+        <v>878.75</v>
+      </c>
+      <c r="F382" s="3">
+        <v>865.25</v>
+      </c>
+      <c r="G382" s="3">
+        <v>872.9</v>
+      </c>
+      <c r="H382" s="3">
+        <v>873.65</v>
+      </c>
+      <c r="I382" s="3">
+        <v>865.25</v>
+      </c>
+      <c r="J382" s="3">
+        <v>882.05</v>
+      </c>
+      <c r="K382" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L382" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M382" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="N382" s="3">
+        <v>865.25</v>
+      </c>
+      <c r="O382" s="2">
+        <v>1</v>
+      </c>
+      <c r="P382" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="Q382" s="5">
+        <v>-0.961</v>
+      </c>
+      <c r="R382" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="383" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A383" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E383" s="3">
+        <v>4025</v>
+      </c>
+      <c r="F383" s="3">
+        <v>3945</v>
+      </c>
+      <c r="G383" s="3">
+        <v>4023</v>
+      </c>
+      <c r="H383" s="3">
+        <v>4023.1</v>
+      </c>
+      <c r="I383" s="3">
+        <v>3945</v>
+      </c>
+      <c r="J383" s="3">
+        <v>4101.2</v>
+      </c>
+      <c r="K383" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L383" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M383" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="N383" s="3">
+        <v>3945</v>
+      </c>
+      <c r="O383" s="2">
+        <v>10</v>
+      </c>
+      <c r="P383" s="4">
+        <v>-78.1</v>
+      </c>
+      <c r="Q383" s="5">
+        <v>-1.941</v>
+      </c>
+      <c r="R383" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="384" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A384" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="B384" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E384" s="7">
+        <v>1350.9</v>
+      </c>
+      <c r="F384" s="7">
+        <v>1325</v>
+      </c>
+      <c r="G384" s="7">
+        <v>1330.5</v>
+      </c>
+      <c r="H384" s="7">
+        <v>1330.5</v>
+      </c>
+      <c r="I384" s="7">
+        <v>1350.9</v>
+      </c>
+      <c r="J384" s="7">
+        <v>1310.1</v>
+      </c>
+      <c r="K384" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L384" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M384" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="N384" s="7">
+        <v>1310.1</v>
+      </c>
+      <c r="O384" s="6">
+        <v>1</v>
+      </c>
+      <c r="P384" s="8">
+        <v>20.4</v>
+      </c>
+      <c r="Q384" s="9">
+        <v>1.533</v>
+      </c>
+      <c r="R384" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="385" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A385" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="B385" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="C385" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D385" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="E385" s="13">
+        <v>1353.2</v>
+      </c>
+      <c r="F385" s="13">
+        <v>1320.2</v>
+      </c>
+      <c r="G385" s="13">
+        <v>1323.9</v>
+      </c>
+      <c r="H385" s="13">
+        <v>1323.9</v>
+      </c>
+      <c r="I385" s="13">
+        <v>1353.2</v>
+      </c>
+      <c r="J385" s="13">
+        <v>1294.6</v>
+      </c>
+      <c r="K385" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L385" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="M385" s="12"/>
+      <c r="N385" s="12"/>
+      <c r="O385" s="12"/>
+      <c r="P385" s="12"/>
+      <c r="Q385" s="12"/>
+      <c r="R385" s="12" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="386" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A386" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E386" s="3">
+        <v>118.85</v>
+      </c>
+      <c r="F386" s="3">
+        <v>116.42</v>
+      </c>
+      <c r="G386" s="3">
+        <v>118.4</v>
+      </c>
+      <c r="H386" s="3">
+        <v>118.37</v>
+      </c>
+      <c r="I386" s="3">
+        <v>116.42</v>
+      </c>
+      <c r="J386" s="3">
+        <v>120.32</v>
+      </c>
+      <c r="K386" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L386" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M386" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="N386" s="3">
+        <v>116.42</v>
+      </c>
+      <c r="O386" s="2">
+        <v>2</v>
+      </c>
+      <c r="P386" s="4">
+        <v>-1.95</v>
+      </c>
+      <c r="Q386" s="5">
+        <v>-1.647</v>
+      </c>
+      <c r="R386" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="387" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A387" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E387" s="3">
+        <v>76.48</v>
+      </c>
+      <c r="F387" s="3">
+        <v>75.2</v>
+      </c>
+      <c r="G387" s="3">
+        <v>75.94</v>
+      </c>
+      <c r="H387" s="3">
+        <v>75.96</v>
+      </c>
+      <c r="I387" s="3">
+        <v>75.2</v>
+      </c>
+      <c r="J387" s="3">
+        <v>76.72</v>
+      </c>
+      <c r="K387" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L387" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M387" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="N387" s="3">
+        <v>75.2</v>
+      </c>
+      <c r="O387" s="2">
+        <v>1</v>
+      </c>
+      <c r="P387" s="4">
+        <v>-0.76</v>
+      </c>
+      <c r="Q387" s="5">
+        <v>-1.001</v>
+      </c>
+      <c r="R387" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="388" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A388" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E388" s="7">
+        <v>30845</v>
+      </c>
+      <c r="F388" s="7">
+        <v>30270</v>
+      </c>
+      <c r="G388" s="7">
+        <v>30675</v>
+      </c>
+      <c r="H388" s="7">
+        <v>30630</v>
+      </c>
+      <c r="I388" s="7">
+        <v>30845</v>
+      </c>
+      <c r="J388" s="7">
+        <v>30415</v>
+      </c>
+      <c r="K388" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L388" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M388" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="N388" s="7">
+        <v>30415</v>
+      </c>
+      <c r="O388" s="6">
+        <v>1</v>
+      </c>
+      <c r="P388" s="8">
+        <v>215</v>
+      </c>
+      <c r="Q388" s="9">
+        <v>0.702</v>
+      </c>
+      <c r="R388" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="389" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A389" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="B389" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E389" s="7">
+        <v>715.5</v>
+      </c>
+      <c r="F389" s="7">
+        <v>702.1</v>
+      </c>
+      <c r="G389" s="7">
+        <v>705.65</v>
+      </c>
+      <c r="H389" s="7">
+        <v>705.75</v>
+      </c>
+      <c r="I389" s="7">
+        <v>715.5</v>
+      </c>
+      <c r="J389" s="7">
+        <v>696</v>
+      </c>
+      <c r="K389" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L389" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M389" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="N389" s="7">
+        <v>696</v>
+      </c>
+      <c r="O389" s="6">
+        <v>2</v>
+      </c>
+      <c r="P389" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="Q389" s="9">
+        <v>1.382</v>
+      </c>
+      <c r="R389" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="390" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A390" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C390" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D390" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="E390" s="7">
+        <v>176.16</v>
+      </c>
+      <c r="F390" s="7">
+        <v>174.75</v>
+      </c>
+      <c r="G390" s="7">
+        <v>174.78</v>
+      </c>
+      <c r="H390" s="7">
+        <v>174.72</v>
+      </c>
+      <c r="I390" s="7">
+        <v>176.16</v>
+      </c>
+      <c r="J390" s="7">
+        <v>173.28</v>
+      </c>
+      <c r="K390" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L390" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M390" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="N390" s="7">
+        <v>173.28</v>
+      </c>
+      <c r="O390" s="6">
+        <v>1</v>
+      </c>
+      <c r="P390" s="8">
+        <v>1.44</v>
+      </c>
+      <c r="Q390" s="9">
+        <v>0.824</v>
+      </c>
+      <c r="R390" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="391" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A391" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E391" s="3">
+        <v>1988.5</v>
+      </c>
+      <c r="F391" s="3">
+        <v>1970.2</v>
+      </c>
+      <c r="G391" s="3">
+        <v>1970.2</v>
+      </c>
+      <c r="H391" s="3">
+        <v>1970.6</v>
+      </c>
+      <c r="I391" s="3">
+        <v>1988.5</v>
+      </c>
+      <c r="J391" s="3">
+        <v>1952.7</v>
+      </c>
+      <c r="K391" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L391" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M391" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="N391" s="3">
+        <v>1988.5</v>
+      </c>
+      <c r="O391" s="2">
+        <v>6</v>
+      </c>
+      <c r="P391" s="4">
+        <v>-17.9</v>
+      </c>
+      <c r="Q391" s="5">
+        <v>-0.908</v>
+      </c>
+      <c r="R391" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="392" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A392" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C392" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D392" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="E392" s="7">
+        <v>143.42</v>
+      </c>
+      <c r="F392" s="7">
+        <v>142</v>
+      </c>
+      <c r="G392" s="7">
+        <v>142</v>
+      </c>
+      <c r="H392" s="7">
+        <v>142.13</v>
+      </c>
+      <c r="I392" s="7">
+        <v>143.42</v>
+      </c>
+      <c r="J392" s="7">
+        <v>140.84</v>
+      </c>
+      <c r="K392" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L392" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M392" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="N392" s="7">
+        <v>140.84</v>
+      </c>
+      <c r="O392" s="6">
+        <v>1</v>
+      </c>
+      <c r="P392" s="8">
+        <v>1.29</v>
+      </c>
+      <c r="Q392" s="9">
+        <v>0.908</v>
+      </c>
+      <c r="R392" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="393" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A393" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="E393" s="7">
+        <v>1360.6</v>
+      </c>
+      <c r="F393" s="7">
+        <v>1341.7</v>
+      </c>
+      <c r="G393" s="7">
+        <v>1341.8</v>
+      </c>
+      <c r="H393" s="7">
+        <v>1341.7</v>
+      </c>
+      <c r="I393" s="7">
+        <v>1360.6</v>
+      </c>
+      <c r="J393" s="7">
+        <v>1322.8</v>
+      </c>
+      <c r="K393" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L393" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M393" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="N393" s="7">
+        <v>1322.8</v>
+      </c>
+      <c r="O393" s="6">
+        <v>5</v>
+      </c>
+      <c r="P393" s="8">
+        <v>18.9</v>
+      </c>
+      <c r="Q393" s="9">
+        <v>1.409</v>
+      </c>
+      <c r="R393" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="394" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A394" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D394" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="E394" s="7">
+        <v>1869.2</v>
+      </c>
+      <c r="F394" s="7">
+        <v>1846.6</v>
+      </c>
+      <c r="G394" s="7">
+        <v>1848.8</v>
+      </c>
+      <c r="H394" s="7">
+        <v>1848.3</v>
+      </c>
+      <c r="I394" s="7">
+        <v>1869.2</v>
+      </c>
+      <c r="J394" s="7">
+        <v>1827.4</v>
+      </c>
+      <c r="K394" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L394" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M394" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="N394" s="7">
+        <v>1827.4</v>
+      </c>
+      <c r="O394" s="6">
+        <v>9</v>
+      </c>
+      <c r="P394" s="8">
+        <v>20.9</v>
+      </c>
+      <c r="Q394" s="9">
+        <v>1.131</v>
+      </c>
+      <c r="R394" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="395" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A395" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E395" s="3">
+        <v>917.5</v>
+      </c>
+      <c r="F395" s="3">
+        <v>911.25</v>
+      </c>
+      <c r="G395" s="3">
+        <v>912.55</v>
+      </c>
+      <c r="H395" s="3">
+        <v>912.5</v>
+      </c>
+      <c r="I395" s="3">
+        <v>917.5</v>
+      </c>
+      <c r="J395" s="3">
+        <v>907.5</v>
+      </c>
+      <c r="K395" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L395" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M395" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="N395" s="3">
+        <v>917.5</v>
+      </c>
+      <c r="O395" s="2">
+        <v>1</v>
+      </c>
+      <c r="P395" s="4">
+        <v>-5</v>
+      </c>
+      <c r="Q395" s="5">
+        <v>-0.548</v>
+      </c>
+      <c r="R395" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="396" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A396" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="B396" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="C396" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D396" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E396" s="7">
+        <v>5406</v>
+      </c>
+      <c r="F396" s="7">
+        <v>5381.5</v>
+      </c>
+      <c r="G396" s="7">
+        <v>5390</v>
+      </c>
+      <c r="H396" s="7">
+        <v>5390.5</v>
+      </c>
+      <c r="I396" s="7">
+        <v>5406</v>
+      </c>
+      <c r="J396" s="7">
+        <v>5375</v>
+      </c>
+      <c r="K396" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L396" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M396" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="N396" s="7">
+        <v>5375</v>
+      </c>
+      <c r="O396" s="6">
+        <v>1</v>
+      </c>
+      <c r="P396" s="8">
+        <v>15.5</v>
+      </c>
+      <c r="Q396" s="9">
+        <v>0.288</v>
+      </c>
+      <c r="R396" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="398" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A398" s="14" t="s">
+        <v>853</v>
+      </c>
+      <c r="P398" s="15">
+        <v>-266.21</v>
+      </c>
+      <c r="R398" s="14" t="s">
+        <v>854</v>
       </c>
     </row>
   </sheetData>

--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="613">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1504,10 +1504,7 @@
     <t>NSE:SONACOMS-EQ_BEAR_1772169300_1772185500</t>
   </si>
   <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>Checked 74 candle(s) — neither SL nor Target hit yet</t>
+    <t>2026-03-11 09:15</t>
   </si>
   <si>
     <t>NSE:UNOMINDA-EQ_BEAR_1772170200_1772181000</t>
@@ -1693,13 +1690,13 @@
     <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772617500</t>
   </si>
   <si>
-    <t>Checked 24 candle(s) — neither SL nor Target hit yet</t>
+    <t>2026-03-06 09:15</t>
   </si>
   <si>
     <t>NSE:COALINDIA-EQ_BULL_1772598600_1772682300</t>
   </si>
   <si>
-    <t>Checked 23 candle(s) — neither SL nor Target hit yet</t>
+    <t>2026-03-06 14:45</t>
   </si>
   <si>
     <t>NSE:LUPIN-EQ_BULL_1772615700_1772682300</t>
@@ -1708,6 +1705,9 @@
     <t>NSE:LUPIN-EQ</t>
   </si>
   <si>
+    <t>2026-03-09 09:15</t>
+  </si>
+  <si>
     <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772693100</t>
   </si>
   <si>
@@ -1729,7 +1729,7 @@
     <t>2026-03-05 14:30</t>
   </si>
   <si>
-    <t>Checked 2 candle(s) — neither SL nor Target hit yet</t>
+    <t>2026-03-06 15:15</t>
   </si>
   <si>
     <t>NSE:RELIANCE-EQ_BULL_1772689500_1772701200</t>
@@ -1747,22 +1747,109 @@
     <t>NSE:NTPC-EQ_BULL_1772691300_1772702100</t>
   </si>
   <si>
-    <t>Checked 1 candle(s) — neither SL nor Target hit yet</t>
-  </si>
-  <si>
     <t>NSE:OFSS-EQ_BEAR_1772686800_1772703000</t>
   </si>
   <si>
     <t>2026-03-05 15:00</t>
   </si>
   <si>
-    <t>No candles after entry yet — trade open</t>
-  </si>
-  <si>
-    <t>SUMMARY — 75W / 159L / 8 OPEN  |  Win Rate: 32.1%</t>
-  </si>
-  <si>
-    <t>Total closed trades: 234 of 242</t>
+    <t>NSE:AUBANK-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 15:00</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1772685900_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:45</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1772686800_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BULL_1772683200_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772684100_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BULL_1772688600_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:15</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1772702100_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1772693100_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:30</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1772688600_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:45</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1772683200_1773041400</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:30</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1773046800_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:30</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1773045900_1773120600</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:00</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:45</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ_BULL_1773126900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:30</t>
+  </si>
+  <si>
+    <t>SUMMARY — 83W / 176L / 0 OPEN  |  Win Rate: 32.0%</t>
+  </si>
+  <si>
+    <t>Total closed trades: 259 of 259</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1897,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1830,11 +1917,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1865,7 +1947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1880,8 +1962,6 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -2223,7 +2303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R245"/>
+  <dimension ref="A1:R262"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -13612,54 +13692,64 @@
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A204" s="12" t="s">
+      <c r="A204" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B204" s="12" t="s">
+      <c r="B204" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C204" s="12" t="s">
+      <c r="C204" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D204" s="12" t="s">
+      <c r="D204" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="E204" s="13">
+      <c r="E204" s="3">
         <v>536.2</v>
       </c>
-      <c r="F204" s="13">
+      <c r="F204" s="3">
         <v>532.05</v>
       </c>
-      <c r="G204" s="13">
+      <c r="G204" s="3">
         <v>533.25</v>
       </c>
-      <c r="H204" s="13">
+      <c r="H204" s="3">
         <v>502</v>
       </c>
-      <c r="I204" s="13">
+      <c r="I204" s="3">
         <v>532.05</v>
       </c>
-      <c r="J204" s="13">
+      <c r="J204" s="3">
         <v>471.95</v>
       </c>
-      <c r="K204" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L204" s="12" t="s">
+      <c r="K204" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M204" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="M204" s="12"/>
-      <c r="N204" s="12"/>
-      <c r="O204" s="12"/>
-      <c r="P204" s="12"/>
-      <c r="Q204" s="12"/>
-      <c r="R204" s="12" t="s">
-        <v>498</v>
+      <c r="N204" s="3">
+        <v>532.05</v>
+      </c>
+      <c r="O204" s="2">
+        <v>150</v>
+      </c>
+      <c r="P204" s="4">
+        <v>-30.05</v>
+      </c>
+      <c r="Q204" s="5">
+        <v>-5.986</v>
+      </c>
+      <c r="R204" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>395</v>
@@ -13668,7 +13758,7 @@
         <v>64</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E205" s="7">
         <v>1205.8</v>
@@ -13695,7 +13785,7 @@
         <v>33</v>
       </c>
       <c r="M205" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N205" s="7">
         <v>1201.1</v>
@@ -13715,7 +13805,7 @@
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>139</v>
@@ -13771,7 +13861,7 @@
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>206</v>
@@ -13807,7 +13897,7 @@
         <v>23</v>
       </c>
       <c r="M207" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N207" s="3">
         <v>1365.5</v>
@@ -13827,16 +13917,16 @@
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B208" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E208" s="3">
         <v>1278.8</v>
@@ -13863,7 +13953,7 @@
         <v>23</v>
       </c>
       <c r="M208" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N208" s="3">
         <v>1274</v>
@@ -13883,10 +13973,10 @@
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B209" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>64</v>
@@ -13919,7 +14009,7 @@
         <v>23</v>
       </c>
       <c r="M209" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N209" s="3">
         <v>646.35</v>
@@ -13939,7 +14029,7 @@
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>225</v>
@@ -13948,7 +14038,7 @@
         <v>64</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E210" s="3">
         <v>1280</v>
@@ -13975,7 +14065,7 @@
         <v>23</v>
       </c>
       <c r="M210" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N210" s="3">
         <v>1275.1</v>
@@ -13995,7 +14085,7 @@
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>106</v>
@@ -14004,7 +14094,7 @@
         <v>64</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E211" s="3">
         <v>122.43</v>
@@ -14031,7 +14121,7 @@
         <v>23</v>
       </c>
       <c r="M211" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="N211" s="3">
         <v>121.51</v>
@@ -14051,16 +14141,16 @@
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B212" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E212" s="3">
         <v>3306.1</v>
@@ -14087,7 +14177,7 @@
         <v>23</v>
       </c>
       <c r="M212" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="N212" s="3">
         <v>3283.4</v>
@@ -14107,7 +14197,7 @@
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>253</v>
@@ -14143,7 +14233,7 @@
         <v>23</v>
       </c>
       <c r="M213" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N213" s="3">
         <v>1183.4</v>
@@ -14163,10 +14253,10 @@
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>64</v>
@@ -14199,7 +14289,7 @@
         <v>23</v>
       </c>
       <c r="M214" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N214" s="3">
         <v>1833</v>
@@ -14219,10 +14309,10 @@
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>64</v>
@@ -14255,7 +14345,7 @@
         <v>23</v>
       </c>
       <c r="M215" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N215" s="3">
         <v>2185.4</v>
@@ -14275,7 +14365,7 @@
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>36</v>
@@ -14284,7 +14374,7 @@
         <v>64</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E216" s="3">
         <v>70.31</v>
@@ -14311,7 +14401,7 @@
         <v>23</v>
       </c>
       <c r="M216" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="N216" s="3">
         <v>70.02</v>
@@ -14331,10 +14421,10 @@
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="B217" s="6" t="s">
         <v>526</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>527</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>64</v>
@@ -14367,7 +14457,7 @@
         <v>33</v>
       </c>
       <c r="M217" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N217" s="7">
         <v>947.1</v>
@@ -14387,7 +14477,7 @@
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>112</v>
@@ -14423,7 +14513,7 @@
         <v>23</v>
       </c>
       <c r="M218" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N218" s="3">
         <v>162.03</v>
@@ -14443,7 +14533,7 @@
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>340</v>
@@ -14479,7 +14569,7 @@
         <v>23</v>
       </c>
       <c r="M219" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N219" s="3">
         <v>1215.3</v>
@@ -14499,7 +14589,7 @@
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>202</v>
@@ -14535,7 +14625,7 @@
         <v>23</v>
       </c>
       <c r="M220" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N220" s="3">
         <v>390.05</v>
@@ -14555,7 +14645,7 @@
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>446</v>
@@ -14591,7 +14681,7 @@
         <v>23</v>
       </c>
       <c r="M221" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N221" s="3">
         <v>1047</v>
@@ -14611,7 +14701,7 @@
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>422</v>
@@ -14647,7 +14737,7 @@
         <v>23</v>
       </c>
       <c r="M222" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N222" s="3">
         <v>145</v>
@@ -14667,7 +14757,7 @@
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>121</v>
@@ -14703,7 +14793,7 @@
         <v>23</v>
       </c>
       <c r="M223" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N223" s="3">
         <v>366.6</v>
@@ -14723,7 +14813,7 @@
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>123</v>
@@ -14759,7 +14849,7 @@
         <v>23</v>
       </c>
       <c r="M224" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N224" s="3">
         <v>590.5</v>
@@ -14779,7 +14869,7 @@
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>192</v>
@@ -14788,7 +14878,7 @@
         <v>64</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E225" s="3">
         <v>9827</v>
@@ -14815,7 +14905,7 @@
         <v>23</v>
       </c>
       <c r="M225" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N225" s="3">
         <v>9792</v>
@@ -14835,16 +14925,16 @@
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="B226" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>539</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E226" s="7">
         <v>4662.9</v>
@@ -14871,7 +14961,7 @@
         <v>33</v>
       </c>
       <c r="M226" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N226" s="7">
         <v>4646.6</v>
@@ -14891,7 +14981,7 @@
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>44</v>
@@ -14900,7 +14990,7 @@
         <v>20</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E227" s="7">
         <v>14499</v>
@@ -14927,7 +15017,7 @@
         <v>33</v>
       </c>
       <c r="M227" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N227" s="7">
         <v>14537</v>
@@ -14947,16 +15037,16 @@
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B228" s="6" t="s">
         <v>545</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>546</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E228" s="7">
         <v>377.3</v>
@@ -14983,7 +15073,7 @@
         <v>33</v>
       </c>
       <c r="M228" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N228" s="7">
         <v>380.2</v>
@@ -15003,7 +15093,7 @@
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>67</v>
@@ -15012,7 +15102,7 @@
         <v>64</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E229" s="3">
         <v>6317.5</v>
@@ -15039,7 +15129,7 @@
         <v>23</v>
       </c>
       <c r="M229" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N229" s="3">
         <v>6281.5</v>
@@ -15059,7 +15149,7 @@
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>74</v>
@@ -15068,7 +15158,7 @@
         <v>64</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E230" s="3">
         <v>1444</v>
@@ -15095,7 +15185,7 @@
         <v>23</v>
       </c>
       <c r="M230" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N230" s="3">
         <v>1436.5</v>
@@ -15115,7 +15205,7 @@
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>95</v>
@@ -15124,7 +15214,7 @@
         <v>64</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E231" s="3">
         <v>490.8</v>
@@ -15151,7 +15241,7 @@
         <v>23</v>
       </c>
       <c r="M231" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N231" s="3">
         <v>486.65</v>
@@ -15171,16 +15261,16 @@
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E232" s="3">
         <v>249.5</v>
@@ -15207,7 +15297,7 @@
         <v>23</v>
       </c>
       <c r="M232" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N232" s="3">
         <v>247.25</v>
@@ -15227,7 +15317,7 @@
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>336</v>
@@ -15236,7 +15326,7 @@
         <v>64</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E233" s="3">
         <v>1656.3</v>
@@ -15263,7 +15353,7 @@
         <v>23</v>
       </c>
       <c r="M233" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N233" s="3">
         <v>1645</v>
@@ -15283,7 +15373,7 @@
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>112</v>
@@ -15292,7 +15382,7 @@
         <v>64</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E234" s="3">
         <v>157.7</v>
@@ -15319,7 +15409,7 @@
         <v>23</v>
       </c>
       <c r="M234" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N234" s="3">
         <v>156.8</v>
@@ -15338,141 +15428,171 @@
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A235" s="12" t="s">
+      <c r="A235" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="E235" s="7">
+        <v>14599</v>
+      </c>
+      <c r="F235" s="7">
+        <v>14500</v>
+      </c>
+      <c r="G235" s="7">
+        <v>14598</v>
+      </c>
+      <c r="H235" s="7">
+        <v>14796</v>
+      </c>
+      <c r="I235" s="7">
+        <v>14500</v>
+      </c>
+      <c r="J235" s="7">
+        <v>15092</v>
+      </c>
+      <c r="K235" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L235" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M235" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="B235" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C235" s="12" t="s">
+      <c r="N235" s="7">
+        <v>15092</v>
+      </c>
+      <c r="O235" s="6">
+        <v>25</v>
+      </c>
+      <c r="P235" s="8">
+        <v>296</v>
+      </c>
+      <c r="Q235" s="9">
+        <v>2.001</v>
+      </c>
+      <c r="R235" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D235" s="12" t="s">
-        <v>550</v>
-      </c>
-      <c r="E235" s="13">
-        <v>14599</v>
-      </c>
-      <c r="F235" s="13">
-        <v>14500</v>
-      </c>
-      <c r="G235" s="13">
-        <v>14598</v>
-      </c>
-      <c r="H235" s="13">
-        <v>14796</v>
-      </c>
-      <c r="I235" s="13">
-        <v>14500</v>
-      </c>
-      <c r="J235" s="13">
-        <v>15092</v>
-      </c>
-      <c r="K235" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L235" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M235" s="12"/>
-      <c r="N235" s="12"/>
-      <c r="O235" s="12"/>
-      <c r="P235" s="12"/>
-      <c r="Q235" s="12"/>
-      <c r="R235" s="12" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A236" s="12" t="s">
+      <c r="D236" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E236" s="3">
+        <v>452.4</v>
+      </c>
+      <c r="F236" s="3">
+        <v>440</v>
+      </c>
+      <c r="G236" s="3">
+        <v>451.05</v>
+      </c>
+      <c r="H236" s="3">
+        <v>451.05</v>
+      </c>
+      <c r="I236" s="3">
+        <v>440</v>
+      </c>
+      <c r="J236" s="3">
+        <v>462.1</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L236" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M236" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B236" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C236" s="12" t="s">
+      <c r="N236" s="3">
+        <v>440</v>
+      </c>
+      <c r="O236" s="2">
+        <v>46</v>
+      </c>
+      <c r="P236" s="4">
+        <v>-11.05</v>
+      </c>
+      <c r="Q236" s="5">
+        <v>-2.45</v>
+      </c>
+      <c r="R236" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D236" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="E236" s="13">
-        <v>452.4</v>
-      </c>
-      <c r="F236" s="13">
-        <v>440</v>
-      </c>
-      <c r="G236" s="13">
-        <v>451.05</v>
-      </c>
-      <c r="H236" s="13">
-        <v>451.05</v>
-      </c>
-      <c r="I236" s="13">
-        <v>440</v>
-      </c>
-      <c r="J236" s="13">
-        <v>462.1</v>
-      </c>
-      <c r="K236" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L236" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M236" s="12"/>
-      <c r="N236" s="12"/>
-      <c r="O236" s="12"/>
-      <c r="P236" s="12"/>
-      <c r="Q236" s="12"/>
-      <c r="R236" s="12" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A237" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="B237" s="12" t="s">
+      <c r="D237" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E237" s="3">
+        <v>2352.3</v>
+      </c>
+      <c r="F237" s="3">
+        <v>2310</v>
+      </c>
+      <c r="G237" s="3">
+        <v>2348</v>
+      </c>
+      <c r="H237" s="3">
+        <v>2349.9</v>
+      </c>
+      <c r="I237" s="3">
+        <v>2310</v>
+      </c>
+      <c r="J237" s="3">
+        <v>2389.8</v>
+      </c>
+      <c r="K237" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L237" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M237" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C237" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D237" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="E237" s="13">
-        <v>2352.3</v>
-      </c>
-      <c r="F237" s="13">
+      <c r="N237" s="3">
         <v>2310</v>
       </c>
-      <c r="G237" s="13">
-        <v>2348</v>
-      </c>
-      <c r="H237" s="13">
-        <v>2349.9</v>
-      </c>
-      <c r="I237" s="13">
-        <v>2310</v>
-      </c>
-      <c r="J237" s="13">
-        <v>2389.8</v>
-      </c>
-      <c r="K237" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L237" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M237" s="12"/>
-      <c r="N237" s="12"/>
-      <c r="O237" s="12"/>
-      <c r="P237" s="12"/>
-      <c r="Q237" s="12"/>
-      <c r="R237" s="12" t="s">
-        <v>562</v>
+      <c r="O237" s="2">
+        <v>49</v>
+      </c>
+      <c r="P237" s="4">
+        <v>-39.9</v>
+      </c>
+      <c r="Q237" s="5">
+        <v>-1.698</v>
+      </c>
+      <c r="R237" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.25">
@@ -15532,95 +15652,115 @@
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A239" s="12" t="s">
+      <c r="A239" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B239" s="12" t="s">
+      <c r="B239" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C239" s="12" t="s">
+      <c r="C239" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D239" s="12" t="s">
+      <c r="D239" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E239" s="13">
+      <c r="E239" s="3">
         <v>184.98</v>
       </c>
-      <c r="F239" s="13">
+      <c r="F239" s="3">
         <v>182.15</v>
       </c>
-      <c r="G239" s="13">
+      <c r="G239" s="3">
         <v>184.62</v>
       </c>
-      <c r="H239" s="13">
+      <c r="H239" s="3">
         <v>184.54</v>
       </c>
-      <c r="I239" s="13">
+      <c r="I239" s="3">
         <v>182.15</v>
       </c>
-      <c r="J239" s="13">
+      <c r="J239" s="3">
         <v>186.93</v>
       </c>
-      <c r="K239" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L239" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M239" s="12"/>
-      <c r="N239" s="12"/>
-      <c r="O239" s="12"/>
-      <c r="P239" s="12"/>
-      <c r="Q239" s="12"/>
-      <c r="R239" s="12" t="s">
+      <c r="K239" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L239" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M239" s="2" t="s">
         <v>572</v>
       </c>
+      <c r="N239" s="3">
+        <v>182.15</v>
+      </c>
+      <c r="O239" s="2">
+        <v>27</v>
+      </c>
+      <c r="P239" s="4">
+        <v>-2.39</v>
+      </c>
+      <c r="Q239" s="5">
+        <v>-1.295</v>
+      </c>
+      <c r="R239" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A240" s="12" t="s">
+      <c r="A240" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="B240" s="12" t="s">
+      <c r="B240" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C240" s="12" t="s">
+      <c r="C240" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D240" s="12" t="s">
+      <c r="D240" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="E240" s="13">
+      <c r="E240" s="7">
         <v>1392.8</v>
       </c>
-      <c r="F240" s="13">
+      <c r="F240" s="7">
         <v>1378.1</v>
       </c>
-      <c r="G240" s="13">
+      <c r="G240" s="7">
         <v>1389.7</v>
       </c>
-      <c r="H240" s="13">
+      <c r="H240" s="7">
         <v>1389.5</v>
       </c>
-      <c r="I240" s="13">
+      <c r="I240" s="7">
         <v>1378.1</v>
       </c>
-      <c r="J240" s="13">
+      <c r="J240" s="7">
         <v>1400.9</v>
       </c>
-      <c r="K240" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L240" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M240" s="12"/>
-      <c r="N240" s="12"/>
-      <c r="O240" s="12"/>
-      <c r="P240" s="12"/>
-      <c r="Q240" s="12"/>
-      <c r="R240" s="12" t="s">
-        <v>572</v>
+      <c r="K240" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L240" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M240" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="N240" s="7">
+        <v>1400.9</v>
+      </c>
+      <c r="O240" s="6">
+        <v>3</v>
+      </c>
+      <c r="P240" s="8">
+        <v>11.4</v>
+      </c>
+      <c r="Q240" s="9">
+        <v>0.82</v>
+      </c>
+      <c r="R240" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
@@ -15680,106 +15820,1078 @@
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A242" s="12" t="s">
+      <c r="A242" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B242" s="12" t="s">
+      <c r="B242" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C242" s="12" t="s">
+      <c r="C242" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D242" s="12" t="s">
+      <c r="D242" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="E242" s="13">
+      <c r="E242" s="3">
         <v>379.8</v>
       </c>
-      <c r="F242" s="13">
+      <c r="F242" s="3">
         <v>376.2</v>
       </c>
-      <c r="G242" s="13">
+      <c r="G242" s="3">
         <v>379.6</v>
       </c>
-      <c r="H242" s="13">
+      <c r="H242" s="3">
         <v>379.7</v>
       </c>
-      <c r="I242" s="13">
+      <c r="I242" s="3">
         <v>376.2</v>
       </c>
-      <c r="J242" s="13">
+      <c r="J242" s="3">
         <v>383.2</v>
       </c>
-      <c r="K242" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L242" s="12" t="s">
+      <c r="K242" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L242" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M242" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="N242" s="3">
+        <v>376.2</v>
+      </c>
+      <c r="O242" s="2">
+        <v>2</v>
+      </c>
+      <c r="P242" s="4">
+        <v>-3.5</v>
+      </c>
+      <c r="Q242" s="5">
+        <v>-0.922</v>
+      </c>
+      <c r="R242" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E243" s="3">
+        <v>6825</v>
+      </c>
+      <c r="F243" s="3">
+        <v>6764</v>
+      </c>
+      <c r="G243" s="3">
+        <v>6768.5</v>
+      </c>
+      <c r="H243" s="3">
+        <v>6769.5</v>
+      </c>
+      <c r="I243" s="3">
+        <v>6764</v>
+      </c>
+      <c r="J243" s="3">
+        <v>6764</v>
+      </c>
+      <c r="K243" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L243" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M243" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="N243" s="3">
+        <v>6764</v>
+      </c>
+      <c r="O243" s="2">
+        <v>1</v>
+      </c>
+      <c r="P243" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="Q243" s="11">
+        <v>0.081</v>
+      </c>
+      <c r="R243" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E244" s="3">
+        <v>980.15</v>
+      </c>
+      <c r="F244" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="G244" s="3">
+        <v>977.9</v>
+      </c>
+      <c r="H244" s="3">
+        <v>977.9</v>
+      </c>
+      <c r="I244" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="J244" s="3">
+        <v>990.1</v>
+      </c>
+      <c r="K244" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L244" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M244" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="N244" s="3">
+        <v>965.7</v>
+      </c>
+      <c r="O244" s="2">
+        <v>22</v>
+      </c>
+      <c r="P244" s="4">
+        <v>-12.2</v>
+      </c>
+      <c r="Q244" s="5">
+        <v>-1.248</v>
+      </c>
+      <c r="R244" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E245" s="3">
+        <v>1235</v>
+      </c>
+      <c r="F245" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="G245" s="3">
+        <v>1233.1</v>
+      </c>
+      <c r="H245" s="3">
+        <v>1233</v>
+      </c>
+      <c r="I245" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="J245" s="3">
+        <v>1245.7</v>
+      </c>
+      <c r="K245" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L245" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M245" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="N245" s="3">
+        <v>1220.3</v>
+      </c>
+      <c r="O245" s="2">
+        <v>1</v>
+      </c>
+      <c r="P245" s="4">
+        <v>-12.7</v>
+      </c>
+      <c r="Q245" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="R245" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E246" s="3">
+        <v>2789</v>
+      </c>
+      <c r="F246" s="3">
+        <v>2736.4</v>
+      </c>
+      <c r="G246" s="3">
+        <v>2781.8</v>
+      </c>
+      <c r="H246" s="3">
+        <v>2780.9</v>
+      </c>
+      <c r="I246" s="3">
+        <v>2736.4</v>
+      </c>
+      <c r="J246" s="3">
+        <v>2825.4</v>
+      </c>
+      <c r="K246" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L246" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M246" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N246" s="3">
+        <v>2736.4</v>
+      </c>
+      <c r="O246" s="2">
+        <v>24</v>
+      </c>
+      <c r="P246" s="4">
+        <v>-44.5</v>
+      </c>
+      <c r="Q246" s="5">
+        <v>-1.6</v>
+      </c>
+      <c r="R246" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A247" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E247" s="7">
+        <v>1327.9</v>
+      </c>
+      <c r="F247" s="7">
+        <v>1276.1</v>
+      </c>
+      <c r="G247" s="7">
+        <v>1324.6</v>
+      </c>
+      <c r="H247" s="7">
+        <v>1323.7</v>
+      </c>
+      <c r="I247" s="7">
+        <v>1276.1</v>
+      </c>
+      <c r="J247" s="7">
+        <v>1371.3</v>
+      </c>
+      <c r="K247" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L247" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M247" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="N247" s="7">
+        <v>1371.3</v>
+      </c>
+      <c r="O247" s="6">
+        <v>2</v>
+      </c>
+      <c r="P247" s="8">
+        <v>47.6</v>
+      </c>
+      <c r="Q247" s="9">
+        <v>3.596</v>
+      </c>
+      <c r="R247" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E248" s="3">
+        <v>469.7</v>
+      </c>
+      <c r="F248" s="3">
+        <v>460.35</v>
+      </c>
+      <c r="G248" s="3">
+        <v>468.65</v>
+      </c>
+      <c r="H248" s="3">
+        <v>468.6</v>
+      </c>
+      <c r="I248" s="3">
+        <v>460.35</v>
+      </c>
+      <c r="J248" s="3">
+        <v>476.85</v>
+      </c>
+      <c r="K248" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L248" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M248" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N248" s="3">
+        <v>460.35</v>
+      </c>
+      <c r="O248" s="2">
+        <v>24</v>
+      </c>
+      <c r="P248" s="4">
+        <v>-8.25</v>
+      </c>
+      <c r="Q248" s="5">
+        <v>-1.761</v>
+      </c>
+      <c r="R248" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E249" s="3">
+        <v>2135.5</v>
+      </c>
+      <c r="F249" s="3">
+        <v>2094.4</v>
+      </c>
+      <c r="G249" s="3">
+        <v>2131.5</v>
+      </c>
+      <c r="H249" s="3">
+        <v>2131</v>
+      </c>
+      <c r="I249" s="3">
+        <v>2094.4</v>
+      </c>
+      <c r="J249" s="3">
+        <v>2167.6</v>
+      </c>
+      <c r="K249" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L249" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M249" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N249" s="3">
+        <v>2094.4</v>
+      </c>
+      <c r="O249" s="2">
+        <v>24</v>
+      </c>
+      <c r="P249" s="4">
+        <v>-36.6</v>
+      </c>
+      <c r="Q249" s="5">
+        <v>-1.718</v>
+      </c>
+      <c r="R249" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A250" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E250" s="7">
+        <v>25720</v>
+      </c>
+      <c r="F250" s="7">
+        <v>25320</v>
+      </c>
+      <c r="G250" s="7">
+        <v>25650</v>
+      </c>
+      <c r="H250" s="7">
+        <v>25685</v>
+      </c>
+      <c r="I250" s="7">
+        <v>25320</v>
+      </c>
+      <c r="J250" s="7">
+        <v>26050</v>
+      </c>
+      <c r="K250" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L250" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M250" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="N250" s="7">
+        <v>26050</v>
+      </c>
+      <c r="O250" s="6">
+        <v>19</v>
+      </c>
+      <c r="P250" s="8">
+        <v>365</v>
+      </c>
+      <c r="Q250" s="9">
+        <v>1.421</v>
+      </c>
+      <c r="R250" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A251" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E251" s="7">
+        <v>2476</v>
+      </c>
+      <c r="F251" s="7">
+        <v>2370.1</v>
+      </c>
+      <c r="G251" s="7">
+        <v>2457.7</v>
+      </c>
+      <c r="H251" s="7">
+        <v>2457.9</v>
+      </c>
+      <c r="I251" s="7">
+        <v>2370.1</v>
+      </c>
+      <c r="J251" s="7">
+        <v>2545.7</v>
+      </c>
+      <c r="K251" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L251" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M251" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="N251" s="7">
+        <v>2545.7</v>
+      </c>
+      <c r="O251" s="6">
+        <v>1</v>
+      </c>
+      <c r="P251" s="8">
+        <v>87.8</v>
+      </c>
+      <c r="Q251" s="9">
+        <v>3.572</v>
+      </c>
+      <c r="R251" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E252" s="3">
+        <v>8628</v>
+      </c>
+      <c r="F252" s="3">
+        <v>8480</v>
+      </c>
+      <c r="G252" s="3">
+        <v>8621</v>
+      </c>
+      <c r="H252" s="3">
+        <v>8621</v>
+      </c>
+      <c r="I252" s="3">
+        <v>8480</v>
+      </c>
+      <c r="J252" s="3">
+        <v>8762</v>
+      </c>
+      <c r="K252" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L252" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M252" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N252" s="3">
+        <v>8480</v>
+      </c>
+      <c r="O252" s="2">
+        <v>24</v>
+      </c>
+      <c r="P252" s="4">
+        <v>-141</v>
+      </c>
+      <c r="Q252" s="5">
+        <v>-1.636</v>
+      </c>
+      <c r="R252" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E253" s="3">
+        <v>422.45</v>
+      </c>
+      <c r="F253" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="G253" s="3">
+        <v>421.75</v>
+      </c>
+      <c r="H253" s="3">
+        <v>422</v>
+      </c>
+      <c r="I253" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="J253" s="3">
+        <v>431.8</v>
+      </c>
+      <c r="K253" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L253" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M253" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="N253" s="3">
+        <v>412.2</v>
+      </c>
+      <c r="O253" s="2">
+        <v>16</v>
+      </c>
+      <c r="P253" s="4">
+        <v>-9.8</v>
+      </c>
+      <c r="Q253" s="5">
+        <v>-2.322</v>
+      </c>
+      <c r="R253" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E254" s="3">
+        <v>1415.7</v>
+      </c>
+      <c r="F254" s="3">
+        <v>1390.3</v>
+      </c>
+      <c r="G254" s="3">
+        <v>1414.6</v>
+      </c>
+      <c r="H254" s="3">
+        <v>1414.7</v>
+      </c>
+      <c r="I254" s="3">
+        <v>1390.3</v>
+      </c>
+      <c r="J254" s="3">
+        <v>1439.1</v>
+      </c>
+      <c r="K254" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L254" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M254" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N254" s="3">
+        <v>1390.3</v>
+      </c>
+      <c r="O254" s="2">
+        <v>24</v>
+      </c>
+      <c r="P254" s="4">
+        <v>-24.4</v>
+      </c>
+      <c r="Q254" s="5">
+        <v>-1.725</v>
+      </c>
+      <c r="R254" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E255" s="3">
+        <v>382.25</v>
+      </c>
+      <c r="F255" s="3">
+        <v>373.1</v>
+      </c>
+      <c r="G255" s="3">
+        <v>382.1</v>
+      </c>
+      <c r="H255" s="3">
+        <v>382.25</v>
+      </c>
+      <c r="I255" s="3">
+        <v>373.1</v>
+      </c>
+      <c r="J255" s="3">
+        <v>391.4</v>
+      </c>
+      <c r="K255" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L255" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M255" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="N255" s="3">
+        <v>373.1</v>
+      </c>
+      <c r="O255" s="2">
+        <v>24</v>
+      </c>
+      <c r="P255" s="4">
+        <v>-9.15</v>
+      </c>
+      <c r="Q255" s="5">
+        <v>-2.394</v>
+      </c>
+      <c r="R255" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E256" s="3">
+        <v>15153</v>
+      </c>
+      <c r="F256" s="3">
+        <v>14671</v>
+      </c>
+      <c r="G256" s="3">
+        <v>15142</v>
+      </c>
+      <c r="H256" s="3">
+        <v>15146</v>
+      </c>
+      <c r="I256" s="3">
+        <v>14671</v>
+      </c>
+      <c r="J256" s="3">
+        <v>15621</v>
+      </c>
+      <c r="K256" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L256" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M256" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="N256" s="3">
+        <v>14671</v>
+      </c>
+      <c r="O256" s="2">
+        <v>71</v>
+      </c>
+      <c r="P256" s="4">
+        <v>-475</v>
+      </c>
+      <c r="Q256" s="5">
+        <v>-3.136</v>
+      </c>
+      <c r="R256" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A257" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E257" s="7">
+        <v>1805.8</v>
+      </c>
+      <c r="F257" s="7">
+        <v>1796.4</v>
+      </c>
+      <c r="G257" s="7">
+        <v>1804.1</v>
+      </c>
+      <c r="H257" s="7">
+        <v>1804.1</v>
+      </c>
+      <c r="I257" s="7">
+        <v>1796.4</v>
+      </c>
+      <c r="J257" s="7">
+        <v>1811.8</v>
+      </c>
+      <c r="K257" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L257" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M257" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="N257" s="7">
+        <v>1811.8</v>
+      </c>
+      <c r="O257" s="6">
+        <v>1</v>
+      </c>
+      <c r="P257" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="Q257" s="9">
+        <v>0.427</v>
+      </c>
+      <c r="R257" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A258" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E258" s="7">
+        <v>4432</v>
+      </c>
+      <c r="F258" s="7">
+        <v>4389</v>
+      </c>
+      <c r="G258" s="7">
+        <v>4428.5</v>
+      </c>
+      <c r="H258" s="7">
+        <v>4432.6</v>
+      </c>
+      <c r="I258" s="7">
+        <v>4389</v>
+      </c>
+      <c r="J258" s="7">
+        <v>4476.2</v>
+      </c>
+      <c r="K258" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L258" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M258" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="N258" s="7">
+        <v>4476.2</v>
+      </c>
+      <c r="O258" s="6">
+        <v>75</v>
+      </c>
+      <c r="P258" s="8">
+        <v>43.6</v>
+      </c>
+      <c r="Q258" s="9">
+        <v>0.984</v>
+      </c>
+      <c r="R258" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E259" s="3">
+        <v>2198.6</v>
+      </c>
+      <c r="F259" s="3">
+        <v>2175.3</v>
+      </c>
+      <c r="G259" s="3">
+        <v>2191.6</v>
+      </c>
+      <c r="H259" s="3">
+        <v>2192</v>
+      </c>
+      <c r="I259" s="3">
+        <v>2175.3</v>
+      </c>
+      <c r="J259" s="3">
+        <v>2208.7</v>
+      </c>
+      <c r="K259" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L259" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M259" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="N259" s="3">
+        <v>2175.3</v>
+      </c>
+      <c r="O259" s="2">
+        <v>2</v>
+      </c>
+      <c r="P259" s="4">
+        <v>-16.7</v>
+      </c>
+      <c r="Q259" s="5">
+        <v>-0.762</v>
+      </c>
+      <c r="R259" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A260" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D260" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="M242" s="12"/>
-      <c r="N242" s="12"/>
-      <c r="O242" s="12"/>
-      <c r="P242" s="12"/>
-      <c r="Q242" s="12"/>
-      <c r="R242" s="12" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A243" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="B243" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="C243" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D243" s="12" t="s">
-        <v>580</v>
-      </c>
-      <c r="E243" s="13">
-        <v>6825</v>
-      </c>
-      <c r="F243" s="13">
-        <v>6764</v>
-      </c>
-      <c r="G243" s="13">
-        <v>6768.5</v>
-      </c>
-      <c r="H243" s="13">
-        <v>6769.5</v>
-      </c>
-      <c r="I243" s="13">
-        <v>6764</v>
-      </c>
-      <c r="J243" s="13">
-        <v>6764</v>
-      </c>
-      <c r="K243" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L243" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="M243" s="12"/>
-      <c r="N243" s="12"/>
-      <c r="O243" s="12"/>
-      <c r="P243" s="12"/>
-      <c r="Q243" s="12"/>
-      <c r="R243" s="12" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A245" s="14" t="s">
-        <v>582</v>
-      </c>
-      <c r="P245" s="15">
-        <v>435.24</v>
-      </c>
-      <c r="R245" s="14" t="s">
-        <v>583</v>
+      <c r="E260" s="7">
+        <v>928</v>
+      </c>
+      <c r="F260" s="7">
+        <v>900</v>
+      </c>
+      <c r="G260" s="7">
+        <v>924.65</v>
+      </c>
+      <c r="H260" s="7">
+        <v>924.75</v>
+      </c>
+      <c r="I260" s="7">
+        <v>900</v>
+      </c>
+      <c r="J260" s="7">
+        <v>949.5</v>
+      </c>
+      <c r="K260" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L260" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M260" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="N260" s="7">
+        <v>949.5</v>
+      </c>
+      <c r="O260" s="6">
+        <v>20</v>
+      </c>
+      <c r="P260" s="8">
+        <v>24.75</v>
+      </c>
+      <c r="Q260" s="9">
+        <v>2.676</v>
+      </c>
+      <c r="R260" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A262" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="P262" s="13">
+        <v>447.4</v>
+      </c>
+      <c r="R262" s="12" t="s">
+        <v>612</v>
       </c>
     </row>
   </sheetData>
